--- a/library.xlsx
+++ b/library.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xxc/Desktop/xxc/拓殖大学/研究室/評価実験/video-recommend-system/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{032F81A7-8D4B-914F-887C-241B08CE8E27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F0163BA-716F-EF4F-88BE-4EAD1C61A6A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{F40E9203-8E2D-9949-9A4C-F506F7C93633}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="308">
   <si>
     <t>No.</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -1160,6 +1160,307 @@
   </si>
   <si>
     <t>sOnqjkJTMaA</t>
+  </si>
+  <si>
+    <t>kagami mochi style very cute attention seeking loveliness standing on two legs sophie sofa shiba inu kitten close relationship healing gentle bipedal standing posture sleeping window outside climbing on top precious tolerance owner relationship growth kindness collaboration dog cat fatigue heart purification society ideal acceptance clingy love physics smart happiness duo kagami mochi time space species different species peace world relationship affection weight existence combination cohabitation healing video</t>
+  </si>
+  <si>
+    <t>keywords</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>kamikochi shinshu karuizawa kamikochi nature mountain river scenery landscape breathtaking view air fresh greenery stream water sound bird sounds natural sound sound video audio quality atmosphere immersion clarity quietness peace healing relaxation sense of safety purification afterglow memories hometown nostalgia memory experience travel tourist spot trekking bridge place environment natural environment asset gratitude protection value appeal quality balance space time daily life extraordinary mood mind spirit body fatigue stress anxiety release recovery concentration study exam sleep paperwork work habit audio source video nature video healing video satisfaction happiness emotion beauty freshness coolness summer rainy season blue sky rain climate temperature perceived temperature overseas kyushu tateyama kurobe shinshu beef curry</t>
+  </si>
+  <si>
+    <t>ghibli hayao miyazaki director hayao miyazaki food meal scene breakfast bacon bacon and eggs thick cut bacon thin bacon fried egg egg eggshell frying pan fork seasoned salt calcifer howl markl kimutaku ryunosuke kamiki voice actor voice acting script character grandmother fire fire expression eating chewing sound sound audio design sense of life daily life distance warmth life preciousness worldview ghibli food food temptation animation drawing depiction realism detail direction movement gesture hand motion scene iconic scene representative scene quality appeal deliciousness appetite hunger happiness satisfaction emotion tension sensuality handsome cute rationality culture language umashikate umashi kate</t>
+  </si>
+  <si>
+    <t>japan tokyo capital city world earth urban gdp landmark tokyo station tokyo tower odaiba night view illumination scenery cityscape architecture historical architecture skyscraper tradition kyoto edo development predecessors urban development coexistence diversity people life light lighting scale dynamic range video visual beauty video work bgm music quality completion angle work city video appeal pride gratitude love for japan return home overseas thailand region comparison disparity life student days work memory memories nostalgia farewell hope future growth maturity potential energy sense of safety security cleanliness order happiness excitement stimulation ecstasy healing relaxation meditation positivity motivation effort daily life travel tourism visit plan experience presence sense of scale urban power influence brand evaluation country japanese society</t>
+  </si>
+  <si>
+    <t>video bonsai root work plants plant chili plants trees leaves twigs feathers wind nature gardening indoor garden grow light soil mix time lapse process progress result growth transformation movement rhythm breathing life art tree sculpture slow art meditation therapy content editing camera lighting setup behind the scenes idea inspiration dedication patience perseverance consistency lesson visual lesson appreciation respect resilience struggle survival moment time change beauty peace calm relaxation satisfaction connection expression health</t>
+  </si>
+  <si>
+    <t>showa postwar end of war surrender reconstruction japan tokyo edo period high economic growth period high economic growth infrastructure city development neon neon district night view tokyo tower tokyo monorail tamachi streetscape buildings cars retro kimono clothing women people children generation grandparents parents mother high school student life living vitality energy air photochemical smog world era past present future time passage of time record history historical materials cultural heritage roots resilience effort predecessors respect gratitude existence realism immersion familiarity nostalgia memory dream time machine time slip video video technology video processing upscale image quality resolution detail color tone audio sound youtube materials comparison sense of distance change growth momentum urban rural overseas beatles 1965 1963 1990s 2000s</t>
+  </si>
+  <si>
+    <t>voice conversation noise chatter ambient sound bgm white noise cafe food court school nature sound dishware sound sound balance volume sound distance still image commercial study test study qualification study work work use work environment work efficiency routine concentration focus sleep drowsiness sense of safety loneliness distance human presence human presence crowd daily sound living sound japanese intonation kansai dialect baby child daughter outing home outside space</t>
+  </si>
+  <si>
+    <t>grandparents grandchild athlete support cheering applause stadium team fans interview hero interview game postgame tears emotion personality kindness sincerity humanity family family love devotion gratitude feelings love bond support presence heaven watching over pride performance effort growth boy expression words emotion natural reaction atmosphere scene video theme appeal</t>
+  </si>
+  <si>
+    <t>body stretching video body weight constipation improvement flexibility blood flow lower back pain beginner continuity habit breathing full body warmth condition change health motivation refreshed feeling explanation theory effect short time forward bend waist back exercise routine tempo relaxation strength training range of motion refreshing feeling life health maintenance theory sensation mood stability habit formation</t>
+  </si>
+  <si>
+    <t>bolt pet cat speed velocity speed of light light darkness stay at home club metaphor video fast forward streetscape north star dragonfly kyoto scenery viewpoint simulated experience science museum attraction science class animal human comparison bicycle cheetah traffic light deceleration road tourism science humor theme tempo structure stages knowledge sensation movement existence perception limit video children adults laughter study interest curiosity sense of speed vision understanding entertainment quality memory scene idea experience explanation question discovery concept entertainment order afterglow</t>
+  </si>
+  <si>
+    <t>wisdom life hack video practicality practical knowledge ingenuity life daily life information tips method storage method bag sealing banana snacks drain hot water caution suction cup problem solution television program internet summary value trial effect family generation grandmother knowledge base experience life skills stress satisfaction rediscovery trust reality practice sharing organization problem solving quality integration convenience benefit memory usefulness</t>
+  </si>
+  <si>
+    <t>mrbeast content direction drone slider scream horror ronaldo religion body hair chest hair side quest life camera thumbnail ai fan shorts physical challenge water obsession video momentum reaction entertainment experience meme youtube audience energy quality service spirit balance joke speed direction entertainment value algorithm extreme character appearance visual impact evolution fear laughter structure style impression influencer</t>
+  </si>
+  <si>
+    <t>person next to you banknote money magic behavior abnormal behavior impression impact gaze attention focus main character audience video content information density confusion question presence memory theme highlight surroundings situation attention distribution structure gaze guidance noise</t>
+  </si>
+  <si>
+    <t>japanese culture sense of safety chaos information density confusion suit binbocchama style ingenuity reaction mrbeast sushi riku fusion atmosphere collaboration youtuber punchline scale overseas audience confusion editing tempo sound effects global expansion character interaction structure coherence satisfaction representative reaction atmosphere planning ability individuality worldview development joke japanese style global character traits direction quality satisfaction voice translation brand culmination gap structure compatibility discovery comments storytelling audio direction surprise final form initiative editing rhythm impression understanding bridging tension audience service density retention balance evaluation representative work consideration success example symbol adaptability technical skill</t>
+  </si>
+  <si>
+    <t>flame direction cleanup tip whiskey beer magic incantation special move fantasy gesture beauty sword rpg stage art bartender craftsmanship ice sound anime cutscene movement technique japanese culture alcohol artisan skill healing worldview fire ritual pride expression experience work form professionalism artwork performance japan show artist contrast value concentration meaning balance calculation otherworldly feeling love bar counter stage aesthetics work video refinement cultural experience extraordinary meticulousness awareness fusion evaluation pinnacle concept memory weight aesthetic sense respect top class final form technique accumulation art experience strength ideal form soul quality full effort technical ability respect</t>
+  </si>
+  <si>
+    <t>dilatant slime slime rpg higher tier physical immunity late game curiosity experiment independent research content emotion mixture new material liquid solid properties chemistry curiosity video fusion dilatancy bulletproof material appearance color cabbage playfulness drill impact absorbing material dough potential naming game phenomenon speed hardness material development contents subject scientist origin impact understanding idea mindset moment texture commercialization substance excitement process viscosity change appeal defense impression interest monster science video creativity tactile feeling teaching material visual research materials research gap discovery class result science idea familiar reaction expression romance application softness hardening quality tactile science experiment intuition entertainment balance expectation fun depth metaphor application example existence</t>
+  </si>
+  <si>
+    <t>red bull missed calls speed fans butt twerking gta jiggle physics cars booty bakery moment line stupidity bravery life women men start gta 6 adrenaline charts warm up laugh dad lore jump breed cop channel booty shake death content jiggle level jumps darwin award timing reflection sport olympic sport risk respawn rush danger sponsorship gta character replay man crowd reaction movement physics mode heart entertainment hesitation superhero energy result</t>
+  </si>
+  <si>
+    <t>academy awards 2022 will smith chris rock jada pinkett smith slap yelling joke reaction laughter mood silence tension awkwardness moment scene incident controversy argument outburst expression eyes shift shock audience crowd stage ceremony award oscar show broadcast live tv clip video internet meme history culture pop culture legacy memory discussion debate professionalism composure restraint humiliation respect attention focus impact</t>
+  </si>
+  <si>
+    <t>father mother parent child father daughter family divorce single assignment sunday tears emotion video work screenplay short film story words japanese thank you congratulations email number photo affection love bond connection distance reality memory meaning relationship emotion sense of safety happiness sadness sentiment empathy life worldview music subtitles overseas time summer genes feelings afterglow kindness warmth strength satisfaction heart chest</t>
+  </si>
+  <si>
+    <t>nyango star drummer drumming drums sticks suit power suit costume mascot manager youtube youtube rewind youtube recommendations song song choice metal spirit passion job living wedding funeral thanos power mortal form rhythm timing transition cossack dance kazotsky kick russian spy culture cultures japan japanese performances asian drummer interviewer appearance soul emotional state futon season depression internet genre crowd ellen whiplash comments olympics opening anime scream performance character power limiter handicap heat inside week day forehead drum demigod god final form phenomenon creation potential reaction energy intensity control chaos</t>
+  </si>
+  <si>
+    <t>cows cow audience human audiences target audience video cows brass disney princess animals cowbell youtube recommendation americas got talent band world grass music rain company cattle interest live jazz phones future tech predictions oh when the saints go marching in music standing ovation respect moo mind videos college test jazz musicians audiences tuba era concert dislikers watching performers masterpiece tuba player jazz band cowbell experience youtube algorithm gems genre ranch feed content musicians credit pixar opening humans legend france butter band experience magic recommendation grandpa trumpet sound field crowd sunday vibes aliens clarinet call jazz humor monkeys instruments memories ranches comment mystery soul</t>
+  </si>
+  <si>
+    <t>bike parachute rb red bull redbull bike stunts jump man safety fact cold drink clips adrenaline garage mode game shorts thrill shouts joy wings level movie chute sanity mission impossible hr interview vibes friend motorcycle parachute disclaimer life insurance boy school place high speed love anxiety hero company drinks things lad heaven take cameraman descenders drone pilot plus top joke move courage relief drone operator raise genre plot twist drone hats bikes mountains logo gravity meme</t>
+  </si>
+  <si>
+    <t>medieval witch visual ability instrument crow voice clothing beauty black swan manipulation university research woman signal allies conversation academic conference special skill acquisition bird human voice acting industry talent emergency caw red haired woman red haired girl shibuya genius usage cat throat crow language natural enemy group identity bgm anthropomorphism park report count meaning enemy attack outside crow tribe complaint tarzan natsume yuujinchou man ear technique special skill south southeast height theory eye humanization child memories witch trial playful intelligence magic power gap scam miscalculation talent partial resemblance person vocal imitation sailor mars appeal food virtue dog resonance weapon user</t>
+  </si>
+  <si>
+    <t>left knee gen hoshino recommendation left leg gen san composite clothing yui aragaki marriage gum expert inconsistency 2020 theory mouth guitar drums years description bath chair trivia arm moment triplet rhythm mental lyrics third hand rhythm skill hi hat burden 2024 father mirror dance at home music recital reference timestamp hand world anpanman drum corona trend ai video gakki misunderstanding left elbow child drum future foreshadowing clip gratitude real karepanman meme material wall wallpaper battle self derivative electronic drums skin color tuning existence sheet music playing method place door shape reiwa 7 mystery friends together blood song background rapid sequence editing original search mahjong version scale memories adult last technology off screen imagination distortion hand movement link meme</t>
+  </si>
+  <si>
+    <t>money dine and dash man take your time quickly eat three minutes police illegal act etiquette streamer role model one day 720 bowls overseas audience greeting restaurant customer beef bowl serving speed water power phrase entering store order crime smell spoon kitchen bill ten years meal momentum quote change within three minutes parent famous quote moment detective legendary video thank you for the meal human staff laughter consideration egg shell eve of battle two minutes eating checkout leaving store 470 yen register practice swing nervous staff chase mission raw egg two reason analysis cup noodles strong player comments surgery family calmness rta cooperation time chart time slot confusion hostage setting turnover rate tracking ahead standby cleanliness tension noriyuki ishikawa mask timeline speed process uncut sound commercial sad man one coin era staff critical condition family ideal sukiya tablet order egg godlike skill within one minute curry streamer staff video politeness order good impression rice grains mentality merit child fastest staff 470 yen thanks preparation water forty seconds mental rehearsal after fasting tailing detective bill damage voice sukiya speed register strategy excitement second run era spoon serving speed middle aged man toilet president dinner customer water volley uploader combination world beef bowl rta concept</t>
+  </si>
+  <si>
+    <t>anniversary views folks plane september 11 2001 day history footage camcorders quality years heart microsoft flight simulator part price life window office world trade center 747 seconds people videos frame impact sim graphics sensation holiday filming accident peace youtube 11 sep terror video description recreation clip simulation person time world camera fire life channel angle 3d video editing pain hearts tears eyes news shock today america tragedy moment screen recommendation september 11 hiroshima nagasaki usa government comment section activities timeline airplane tower ai bs flight attendants phone news cousin horrors</t>
+  </si>
+  <si>
+    <t>video views lamb hills snowdonia camera heaven childrens storybook life taxes species babies depiction vinland guy human friend reality afterlife scene flashback thing jesus shepherd sun birds lambs puppy plot twist steps disney princess place man grass footage day animals attention lamb vinland saga reference dad music peace happiness boss work love animals snow white life death youtube masterpiece dude lighting affection childhood dream legends legs line signal pets marys little lamb sunlight city noise nature turn kittens field hugs serotonin earth photographer videos moments purpose animal humans years</t>
+  </si>
+  <si>
+    <t>bear bicycle cgi plot twist man japan bear recommendation heart rate bike shadow video tree path branch road wallet climate change horror movie soul career circle stick footage lance armstrong log fear time car warranty choices results reels contrast saturation brain heart adrenaline smell miles effects sense screaming bunny hop movie anxiety tree branch ambush road cyclists bunny hop gopro temple run game circus actor scene cameraman love camera underwear sand gunshots life workout year forest fires jogging plot device home talk soundtrack motivation jesus skin care porridge hug strategy cardio</t>
+  </si>
+  <si>
+    <t>felix felix baumgartner red bull stratos documentary apr 24 friend tuesday paragliding accident july rip man life red bull human fall space moment tv 2025 nov 25 jump work comments entry middle school news wings joseph kittinger advisor ham sandwich nap years peace legend record survival companies fact sound barrier respect level ruhe in frieden 2018 blood eyeballs disbelief pc 1969 2025 comment legacy salute astronaut sound chills joe kittinger 5th grade space skydiving ground landing achievement capability science home steel katy perry friends family elementary school stunts people earth brands marketing video tears achievement emotions anxiety innovation person heights cgi accident</t>
+  </si>
+  <si>
+    <t>gopro room temperature hong kong firefighters tai po hong kong hero pov video firefighter gopro content firefighters office fire content light fires night video work chile volunteer clip visibility heart camera 4k overheating hong kong tai po victims house fire dad internet people interior visibility minutes combat footage respect years prayers salary job world bodycam game training heroes bomberos de chile movies advertisements service ad food prep pov videos house pov youtube video game gopro videos fire wild god cameraman first person pov footage seconds mundo gopros bravery courage first responders be a hero hong kong firefighters pov footage kids mankind enemy adrenaline</t>
+  </si>
+  <si>
+    <t>happiness time ucchan honochan crawling papa mercy race growth unichan meaning example family healing moment crawling toy discipline rival okarachan year end thumbnail smile video laughter year timestamp unikun crawling motivation three siblings youtube healing angel enjoyment family voice new year holidays building blocks safety practice pace first place papa mama growth video affection oasis household dog parenting encounter uni brother okara sister close relationship appearance one year work body purification reaction laughter watching over sitter dog new member new year cold health accident nose two shot petting posture three siblings face new year cute kindness</t>
+  </si>
+  <si>
+    <t>chinchilla temperature humidity temperature control humidity control air conditioner free roaming cage sand dust bath droppings poop fur allergy hospital insurance stress noise construction food snacks exercise wheel travel home mating call sound vocalization bed reference book tissue pokemon wink rent rental high temperature humidity japan highland region money price fur color pet shop exotic animal cat territory fighting injury multi pet keeping individual personality individual differences learning ability rainbow bridge angel fairy management climate control time name hammock wallpaper defense escape family stuffed toy video degu advanced owner cat manga terrorist violet spring affection longevity cooling workplace</t>
+  </si>
+  <si>
+    <t>cherry blossom cherry blossom avenue cherry blossom flowers kawazu cherry blossoms full bloom spring spring scenery season flowers flower viewing cherry blossom petals canola flowers young leaves nature landscape scenery video footage music bgm piano tone bird sounds small birds chirping bush warbler river stream forest sky blue light snowy scenery mount fuji shrine temple japan varieties contrast healing happiness feelings heart bliss dream peace life eyes soul energy health back pain tears vitality courage gratitude comments people world library study coffee morning space time sound appeal beauty paradise</t>
+  </si>
+  <si>
+    <t>music video footage healing heart feelings kindness words message time self fatigue work bed night every night protagonist vibration world place pet dog cancer treatment peace tears people happiness health love essence nature meditation quietness rest soul rhythm starry sky stars galaxy milky way universe technology evolution camera sensor filming video technology landscape scenery earth sea mountains mount fuji aurora sky future study exam concentration relaxation photo comments channel video upload melody sound emotion mood spirit energy blessing life existence value understanding warmth</t>
+  </si>
+  <si>
+    <t>japanese food taste kyoto ritsumeikan university study abroad life comments chikuwa cheese cooking video reference efficiency holiday viewing healing bird piano budgerigar lady itadakimasu family happiness breakfast dining table daily life cleaning shopping interaction fried egg fan dried daikon radish seasoning laughter meal menu affection small bird time lessons housewife familiarity apron update recipe handmade eggplant tofu pork cooking utensils attention to detail nutrition safety subscriber mom chef kitchen utensils peace warmth home love kitchen goods recipe book tools maintenance culture song hydroponics lettuce harvest garden dry climate challenge narration sound imitation new book book ambience colors clothing cleanliness calories salt tamagoyaki wakame pork roll country people places morning vegetables body ingredients side dish main dish microwave frozen meal youtube sheet music bookstore rakuten cabbage tuna electric pot celery garlic ginger husband vacuum cleaner roomba broom daughter scenery outing tableware yachimun chikuwa beijing miso stew dinner kitchen knife flower dance stress pot</t>
+  </si>
+  <si>
+    <t>stew ingredients recipe cream stew white sauce mushrooms potatoes cooking video sound visuals thumbnail appeal channel manner kindness feelings tears healing happiness atmosphere hunger late night after meal stomach camping solo camping winter hot toddy whiskey whiskey lemonade coke highball cinnamon drink cold youtube recommendation algorithm office worker friends friendship partner bear appearance safety life tableware wooden tableware cutlery lamp fireplace kitchen forest woodcutter holiday camerawork video production atmosphere creation presentation cleaning work steam vapor taste texture satisfaction poetry su shi huan xi sha china song dynasty visual beauty audio quality sensitivity healing</t>
+  </si>
+  <si>
+    <t>shanghai bund china taiwan compatriots city beautiful scenery memories business trip country people landscape night view skyline drone video photography camera aerial footage color grading filter urban modernization development technology future society architecture skyscraper river nature tourism business financial city multicultural study abroad overseas hometown residents life people gardens trees parks history culture cafe bistro quietness vitality energy night light lighting red flag communism nation prosperity independence economy success comparison america new york los angeles dubai doha mumbai hollywood science fiction cyberpunk shenzhen futuristic city tech city drone mavic 3 pro low light noise reduction plugin wallpaper vr video production video channel recommendation algorithm comments housing residence overseas life return memories scenery waterside cityscape breathtaking appeal</t>
+  </si>
+  <si>
+    <t>hong kong hong kong people city beautiful scenery memories travel overseas culture night view skyline harbour island building architecture skyscraper urban futuristic city modern ancient power grid lights scenery video drone drone video footage photography channel presentation tourism landmarks boat rides mountain hike observation deck buddhist statue bank of china building container ports port central lan kwai fong wan chai nightlife housing food taxis asia international city multicultural life people memories home pride dreams ambitions discouragement development history british territory 1995 airport change growth comparison new york bangkok jakarta delhi china pakistan malaysia france saudi arabia fiji islands vietnam cambodia future 21st century cyberpunk game gta drone model</t>
+  </si>
+  <si>
+    <t>garden garden garden cost rumah video sound forest air summer rain flowers butterflies view fairy garden life garden channel subscription kanto male flowers place hoa scenery music garden area vlog place house mountains backdrop charm property video calm nature encouragement home scenery flowers peace summer fragrance shortgarden place taman roses flowers canal brasil home garden japan yokohama shop gardening decor november autumn harvest season private gardens nature plants flowers sounds peace support full bloom flowers florist tour heaven scenes meditation monk flower scenery video emotion kansai</t>
+  </si>
+  <si>
+    <t>potting soil cutting propagation soil effort repotting parent plant pot surroundings volume plastic bag pot stand legginess viola idea seed sowing reliability growth speed seedling tohoku region frost cold ingenuity challenge explanation reference beginner body bouquet gardening method success video backup child mentor skill stand simple greenhouse watering clothespin horticulture stretching work conversation cameraman posture legs moisture retention dining table meal reason seedling roots check digging up splits leaves spray bottle plastic dinner moment plant cultivation challenge rooting coleus euphorbia parent plant month viola cuttings timing pansy bouquet daughter sense appearance fukuchan warmth flower posture busy season no days off idea cold concern potting soil akadama cutting soil moisture retention plastic pot daily splits posture spring flowers reference root rot watering overcare temperature propagation method plant flower color flower pot plant pot overspending method one pot management friend flowers viola pansy planter cost flower soil method spring stretching work style flower seedlings plant discovery neighborhood konan opening temperature difference health management</t>
+  </si>
+  <si>
+    <t>tokyo 1970s 1973 1960s 1920s 2020 video image quality film fps video smartphone recording footage materials daily life era modern past time travel time machine streetscape scenery landscape color tone font signboard city infrastructure ww2 war society development country japan culture atmosphere sensation realism illusion cars vintage cars car models design hire car debonair gloria trains highway structures buildings town ginza shinjuku ueno showa dori keisei department store mitsukoshi mcdonalds 7 eleven kfc streetcar war veteran accordion performance drama taiyo ni hoero scene series kochikame postwar 28 years order cleanliness maintenance air summer black and white film color texture interpolation video recording performance camera children girl age 50 51 47 father grandmother family students youth rural countryside tokyo work redevelopment bubble land acquisition smartphone vitality corona nostalgia atmosphere city products made in japan vhs enter the dragon way of the dragon</t>
+  </si>
+  <si>
+    <t>nyc new york london miami los angeles manhattan harlem brooklyn flatbush bronx queens nj new jersey upper east side kings county hospital jfk airport port authority usa india russia morocco 1970s 1960s 1980s 1990s 1970 1971 1972 1973 1975 1950s 80s 90s 70s late 70s early 70s mid 1960s ww2 internet social media phones cellphones chatgpt youtube recommendations video footage music soundtrack bass line boombox kool and the gang street corner symphony led zeppelin msg saturday night fever starsky and hutch serpico the 7 ups dog day afternoon enter the dragon scorsese biggie smalls city metropolis skyline towers buildings skyscrapers apartment airport subway bus street neighborhood suburb country world decade era time past future nostalgia memories dream time machine time capsule vibe atmosphere character spirit culture rhythm tempo life youth childhood teenager family parents mom dad grandmother uncle siblings wife veteran us navy individuals millionaires billionaires health planet kids people girl sarah friends community society outlook connection human technology progress modern development history war optimism depression wealth obesity pizza chinese food fashion clothes hairstyles cars vintage cars auto industry vhs gem content experience</t>
+  </si>
+  <si>
+    <t>exam student 2027 academic year certification study repeat year student studying study start end of term test score multiple choice correct answer button like video motivation pros and cons effort passing entrance exam memorization ability magic button entrance exam real test regular test english reading comments luck review mistakes concentration efficiency general entrance exam final read university fortune dream ranking time version good pace corona health calorie mate weekly spring break mock exam winter first choice report assignment end of term exam time break recommendation success rate tsukuba second semester period desk national exam pressure empathy regret national exam</t>
+  </si>
+  <si>
+    <t>playlist ad interruptions career change different industry song life stress alcohol computer work time memories tears certification exam study 50s sakamoto ryuichi sakamoto music inspiration highball mixed nuts chillpop art life rip love questions words chest reading bgm book world video off day morning day heat family feelings amber melody genre play turning point meditation interpretation expression essence arrangement performance work music tasks feelings piano aqua atmosphere repeat unemployment job recommendation series peace sound emotion time balance soul feelings jazz christmas merry christmas mr lawrence playlist snow ny sofa hometown night reading working fire rain old house guesthouse history excitement self relax love piano sound ticketing bts success ending sigh efficiency artist life podcast quantum physics manifestation book luna rivers patterns self doubt mindset frequency method scene memory melody summer winter years work video endurance video arrangement performance energy flow jazz original calm silk endroll ost youtube channel song selection tatsuro yamashita noriyuki makihara piano version request</t>
+  </si>
+  <si>
+    <t>evidence based commentary news politics channel member perks patreon crossroadsirl politicians video years journalist professionalism speech trait era goalposts perspectives reporter questions answers respect countries behavior taxes billionaires clip interviewer slogan america country decision circles words substance casino hairstyle common sense people poverty hunger progress democrat timeline interview curiosity voice vision history rome starmer hour mountains coins president scotland los angeles california podcast mind future foresight mayor governor kids woman money family love strength peace robot development narcissist score technology china ideas capacities leadership planet street gangs desire fear</t>
+  </si>
+  <si>
+    <t>gamma gtp hba1c body temperature ldl cholesterol menopause middle aged woman doctor primary physician health check abnormal snacking calories values countermeasures risk level alt upper limit screening ultrasound monitoring blood test fluctuation diet exercise husband leukemia treatment test creatinine medication normal range fasting triglycerides ranking cholesterol statin side effects thigh severe pain ezetimibe diarrhea distrust medication adherence smoking cessation fatty liver internal medicine triglycerides juice sweets snacks stress water warm water event teacher book vegetables protein items tasks kidney diabetes ingredients calories blood glucose blood pressure homeostasis disease constitution alcohol dependence continuous drinking abstinence specific health check fecal occult blood endoscopy polyp lecture elderly questions iron deficiency body weight d rating subscription hospital visit lower back pain orthopedics lifestyle hydration diet liver values sixtieth birthday egfr celecoxib tramadol salt ldl donation transfusion blood awareness habits effects mushrooms eggs tofu fish explanation got gpt ast gamma gtp albumin potassium heart rhythm atherosclerosis diabetes test values company results sheet test items psychosomatic medicine prescription damage dietary therapy exercise therapy review notes action plan waking elevator stairs order lifestyle electrocardiogram initial consultation fee policy workers companies screening orthopedics doctor b rating reference range hdl blood test sheet potassium level liver drug induced timing blood draw medical university youtube ldh visceral fat covid infection lymphocytes virus white blood cells</t>
+  </si>
+  <si>
+    <t>hss type hsp tendency habits sympathetic nervous system strength training hiit cold shower sunlight warm water stretching meals relaxation work meditation walking meditation eating meditation effects plating sense nutrients creativity culture nutrition information butter coffee ingredients habits carbohydrates fats eating disorder recovery microorganisms health enthusiast knowledge beauty values health whole foods brown rice barley staple natto kimchi yogurt pickled vegetables mozuku gut health muji fermented bran bed supermarket recipe individual diet lifestyle metabolic capacity gut microbiota research evidence breakfast ingredients shopping basket feelings video diet content rye bread lifestyle richness fermented foods coffee beans preferences red meat health pfc balance mct oil coffee food cost ingredients manual labor calories holiday grass fed butter athlete cutting phase carbohydrates ideal local food principle land grains culture soy products tofu miso soup shiitake onion fish protein fat sea bream mushrooms eggs seasonal vegetables avocado salt moderation body size balance relationships unhappiness fat metabolism dizziness morning scrambled eggs hypoglycemia switching bread solid food foods subscription concept small eating energy pfc calories breakfast supplements nutrients raw materials vegetable oil safflower oil intake vegetables fiber gas gut environment natural toxins oxalate intake monitoring hand blender chopsticks video depression high school soccer boys bulking rice wholesale supermarket imported foods frozen foods rye bread oatmeal chicken breast natural salt olive oil evaluation store blood sugar diet confusion lunch boiled eggs office worker time cooking toast banana women men body temperature immunity fatigue carbohydrate spikes animal fat chicken thigh strength training sleep calories salmon avocado ghee fats diet oils cost performance balance fasting low carb diet glucose tolerance ketones diet fasting doctor nutritionist ambiguity answer canned mackerel skin glow concentration waking testosterone diet national strength caffeine blood sugar hsp stimulation fatigue morning routine quality of life mindful living level mental convenience store food gut health self information shoulder cooking life luxury necessity appearance taste nutrition freedom health awareness sense of balance health hsp traits lifestyle habits life</t>
+  </si>
+  <si>
+    <t>newton apple anecdote biography people expression calculus differentiation integration moon orbit attraction gravity nature humanity world principle starting point recent talk head ear university professor science video voice discovery channel post solo drinking phenomenon research inquiry environment questions person surroundings child question adult knowledge universe mass example complexity theory mystery dark matter dark energy name elevator analogy confidence next swing by museum science museum art museum collaboration audio guide conclusion high school physics grades spacetime curvature force interest graduation research detection genius birth properties scientist matter planet spacetime object underwater water pressure repulsion star center direction difference energy outer space discovery universal gravitation kaluza klein theory heliocentrism geocentrism expectation control background playback meme interstellar re release influence explanation brain locations sleepiness relativity class student jupiter saturn position physicist physics basics solar eclipse light micro particle japanese door four great scientists albert einstein space origin soul earth causality observer system field high school physics time velocity murph explanation graviton existence general relativity acceleration distinction big bang explosion standard model proof inquiry law</t>
+  </si>
+  <si>
+    <t>newton apple anecdote biography people expression calculus differentiation integration moon orbit attraction gravity nature humanity world principle starting point recent talk head ear university professor science video voice discovery channel post solo drinking phenomenon research inquiry environment questions surroundings child question adult knowledge universe mass example complexity theory mystery dark matter dark energy m theory name elevator analogy confidence next swing by museum science museum art museum collaboration audio guide conclusion high school physics grades spacetime curvature force interest graduation research detection genius birth properties scientist planet spacetime object underwater water pressure repulsion star center direction difference energy outer space universal gravitation kaluza klein theory heliocentrism geocentrism expectation control background playback meme interstellar re release influence explanation brain locations sleepiness relativity class student jupiter saturn position physics basics solar eclipse light micro particle japanese door four great scientists albert einstein space origin soul earth causality observer system field high school physics time velocity murph explanation graviton existence general relativity acceleration distinction big bang explosion standard model proof inquiry law water silicon dioxide</t>
+  </si>
+  <si>
+    <t>room view curtains apartment complex drama atmosphere clear sky wind result amateur quality life morning routine ring height apartment neighbor sound people moving reference video recommendation floor ground view feeling surroundings personality cleanliness streaming sequel norah jones man osaka sunset rain scenery japanese film atmosphere chainsaw man aki window coffee air conditioner cleaning living together factory smoke life pajamas one day cutting board place future subscription housework timing home top floor sky kitchen washing machine refrigerator table chair bed items minimal avocado dip english learning strength training interior home cafe moment video nature daily apartment home breakfast music thumbnail house unemployed lifestyle english study resignation situation empathy two person living renovation water area snoopy loungewear haruki murakami novel coffee beans nami living room things support laundry furniture western music books paper rent japan light time flow space richness daily life image meaning lifestyle</t>
+  </si>
+  <si>
+    <t>closed captions language life timeline marriage dedication consistency expression patience discipline time video photo respect staring contest hair storyline glow up kid adult seconds speedrun minutes years guy friends ending smile wife achievement moment idea concept effort day people key peak legend recognition youtube classic algorithm recommendation content storage gallery photos treasure memories frame story frames timeline growth art storytelling pictures change differences start</t>
+  </si>
+  <si>
+    <t>golden buzzer magic vibes aesthetic trick routine cards music choreography magician planet talent showman performance sound facial expressions execution judges shock story short deck human taxes vegas act second card manipulation level speed precision hours work south korean final diamond buzzer look manga smirk confidence breath wizard skill winner ant magic performance korean man exhibition greatness cards video flair audition show villain smile attitude grace dexterity times magic show bgt spades clubs joker stage audiences presentation views film effects south korea world beauty goat magic tricks charisma live performance illusion art explanation talking sleeves talent stage presence guy mars recognition shin lim contender sorcery eden</t>
+  </si>
+  <si>
+    <t>magic performances hair live guy years time shin lim professional magician master elite golden buzzer rule judges performance audition simon wink agt trophy agt celebrity shows background song un nouveau soleil m83 agt 2018 finals words gods memories tyra table surprise card tricks legend las vegas act person magic fool us appearance minutes tricks master presence show mirage colin cloud season ace sleeve start attitudes card magic setup explanation action anyone eyes distraction theatrics magician entertainment purpose sleight of hand skills practice techniques dedication worldclass background magicians talking audience background music success card packet place people goat goats cards beat bruce lee 21st century clip venetia south africa video confidence penn and teller fool us stages family possibility finish vegas wife music everything presentation france got talent swag magic show expression movement performances movements showmanship stage queen of spades tattoo trick set sleight of hand internet years art japan editing boston penn and teller card hand</t>
+  </si>
+  <si>
+    <t>background streetscape alcohol iron man thanos spider man peter tom holland cocktail tolmach video background music chatter glasses smoothness bartender guy bart danger entertaining pov barman flash game motion italy mixology academy russian bartenders credit art drink quality taste chef video restaurant shifts cocktail bar inspiration face oaxaca mexico mezcal sounds movements sir upload website drink recipes cancun waitress hotel bar classic recipes liqueurs elegance france videos garnish character dude school morning youtube channel family bombay bottle shaker recommendations smile workplace video thanks day recommendation canales youtube channel year vids subd youtube recommendation raise bartending school life children us americans russia world leaders drinks brasil work camera pov channel asmr drinks party alcohol videos machine tricks bottles recommended technique cocktails female bartender camera concoctions eyes bartender professional night drink water ice owner hotel restaurant employees dedication legend years brother archive</t>
+  </si>
+  <si>
+    <t>england aa meeting life scottish accent guy barmen whiskey ringtone phone algorithm sir cowboy glass rocks scotch house parents bed bachelor party moustache scent times phd alcoholism restaurant peg luck local dog freedom wife shag pile gentleman lads hello value london year friend freemason bar video channel subscribers alcoholic level happy hour shirt taste finger experience scotsman alcohol shape words poet sound ice bucket maid neck richard paterson master blender dalmore jura whyte and mackay wolfcraig legend industry noses style begbie trainspotting ml milk asylum bottle nose whisky burns bartender floor ice cubes pro art reality hat chap step pour room spirit animal time whisky review search results methods water soul nightmares faces gentleman track countries salute lexicon forever world tazed golden god minute legendary man business face nose podcast hours window day classic today</t>
+  </si>
+  <si>
+    <t>10 years program production meeting explosion experiment denjiro teacher chukyo tv information density coulomb explosion during the early stages of the reaction of alkali metals with water nature chemistry hazardous materials exam knowledge chemistry video phenomenon textbook science channel physical attack filming studio explosion hydrogen fixed ideas creativity respect sodium water reaction science argon atom electron multivalent ion carbon nanotube coulomb force principle explanation coulomb explosion coanda effect lift adiabatic compression air test tube oil research general theory verification common sense oxygen sodium metal fast breeder reactor high school experiment oil na peanuts teacher content electromagnetic repulsive force tension official name title legendary episode posture happiene history mechanism white smoke paper tape electromagnetic force idea smoke tip mass material perspective life kyoto animation hyouka kudryavka sequence tv anime final manuscript phantom thief jumonji direction gian flame arrow romance object interaction acceleration fragments liquid courtyard explanation coulomb force term electricity mol power image quality components surprise question importance chemistry club trial membership emotion danger line sticker material paper conference presentation video hydrogen explosion sub channel members only backstory truth discovery reason densuru quote sodium explosion generation quantity mexico oxygen candle fire</t>
+  </si>
+  <si>
+    <t>favorite video youtube platform sounds liquid magnets work art experiment content respect house earth core magnet cutter magnetic levitation mind bread hands applause person video sound surface liquid nitrogen trail smoke trains minutes point music comments object thing quantum levitation subject chess setup engineering mounts chambers sensor housings research machining fabrication science hardware vehicles future hours geometry puck field magnetic games effect meissner effect demonstration rain phenomenon explanation led experience efforts fact principle bullet train tracks information magnets sound experiment times video hyperloop concept disc string head quantum locking experiment magnetism materials tricks spaceships movies fog idea chess pieces board rule side property game time questions space vacuum spin videos magic minutes block recommendation fingers physics likes materials device contact structure vehicle superconductors schools basics chess board prices scale weight arrangement life understanding scene compound magnet contact science</t>
+  </si>
+  <si>
+    <t>pre entry during entry post entry phrase momentum public organization underworld boundary composition video phenomenon time impression satisfaction dialect self introduction shouting contrast nuance situation occupation gap motion intensity impact surroundings stress effect interaction sense of safety presence wording mismatch appeal reaction indoors quality structure evaluation tempo tension humor example discovery content</t>
+  </si>
+  <si>
+    <t>video america audience photographers crowd clip history words stage players victory moment security detail officers shoes fan deal movement attempts books hero failure courage virtue hypocrisy victim peace attack service phones day agents backpack perimeter roof building authorities gunman slope place incident media week students politics woman camera safety times bodyguards case hat volume sound country files family memory light future event election tear podcast social media president rally cordon rifle shots police minutes advance agents seconds detail guards protection fingers hand scene evidence questions answers concern walk reaction history country</t>
+  </si>
+  <si>
+    <t>aki face heart self destruct feelings experience woman legs length style age boy acting man world actress actor script couple ideal reality gap tension day name despair expression emotion comments scenario direction role alice garden height weapon role truth year personality girlfriend actor older woman hell time tea side relationship sympathy photo scam experience courage traits setting guts beauty misconception happiness brother woman meal work consideration person romance app meeting era telephone club modern story location masterpiece taste big brother date partner consideration behavior problem chapter work audience empathy</t>
+  </si>
+  <si>
+    <t>dad fingers ai humans marker polydactyly message video commercial guy flips mob show humor cast friend generation plot movie skit videos film process twist stunts sounds marching detail people future internet bench trumpet village witch spells scene talent age art disbelief capacities pictures social media life stories images comparison attention algorithm production acting shots sound color grading alarm number creativity creation person screen world chance pulse mixing grade imagination commercials spot mother update defense short film minutes moth lamp moon culture reality term version family phone grandpa situation perspective scam feed eyes truth feature film fit years views censorship words crowd gymnastics trend room animators writing genius quality</t>
+  </si>
+  <si>
+    <t>2026 phones tech people music time crowd concert days life rock star legend freddie mercury feeling someone autotune event song internet moments history brand piano beer talent passion poetry world recording moment front father london heart message generations masterpiece hymn notes spine playback voice connection audience sound generation population response airwaves buckingham palace inspiration lyrics duality note register timing times entrance teacher school boy heaven emotion depth energy performance band age eyes february emotions years day fan highlight skills fame effects boarding school cry reasons train quarantine vocals car video laughter smile joy anthem memory stage registers singers taste genius love fans songs angel respect escape chaos worries thoughts clarity peace</t>
+  </si>
+  <si>
+    <t>1983 night performance birth king of pop effects dancers michael jackson world glove hat move time magnitude viewers chills artist jordan tyson decade stage presence views internet song crowd energy moonwalk outfit jacket award blueprint entertainer aura superstar icon papers morning toe stand dance moves singing perfection minutes history loss attendance idea level years sadness moment generation voice trance eyes reactions power talent songwriter skills autotune genius artists dance style music entertainer christmas eve production brilliance message tribulations soul era planet phenomenon prime legend records guinness book replacement spirit love night star thrill memory childhood television fans god peace friend arcade mall mtv videos roller rink birthday bikes atvs elvis presley freddie mercury performers dance lesson crown scepter midnight days gift memories metal bones fan</t>
+  </si>
+  <si>
+    <t>life teacher school calm videos sound agarwood india agartala incense wood ash healing woman soul music therapy mic mukbang powder snow mind migraine peace room meditation morning day class girl home mountain region place evening grandmother business money childhood stress asmr incense mood sandalwood price ritual tea ceremony structure beauty song sleep channel ease message video comfort edit anxiety center powder sensation potato starch relax country japan face materials process smoke culture patience</t>
+  </si>
+  <si>
+    <t>ladder record climb speedo life score hospital palms man risk judge dive height platform board comment section harness stress skull concrete stability years implication fear superman survival insanity book respect space movie moment bravery act world record mustache meters jump diver feet level tower audacity video recommendation youtube nerves steel fan diving legend memory childhood mind judges jealousy backward interview air water entry arms landing faith scale sportsman television history angle shot pool pixel ravine rating wobble spine props wife kids father family producer crowd surface thumbnail shake vertical money million mom friends cliff courage legend</t>
+  </si>
+  <si>
+    <t>mona lisa moment original years recommendation voice accent chicken meme comment mind algorithm youtube birth tutorial preparation food page mother asmr video cooking treasure bbc incognito mode reset smile face recipe title blender sound joy enthusiasm meal life teacher person chef gordon ramsay opponent earth history pull soap microorganisms bacteria brain night section</t>
+  </si>
+  <si>
+    <t>danger risk identification countermeasures responsibility video on site human caused disaster natural disaster warning residents government land fill water collapse cause investigation contractor petition permit victims firefighters advice speed scale fear filmer record news reality debris flow houses loss vehicles residents site rainband action disaster learning typical example recovery umbrella mountain tsunami destructive force expansion response sns spread on foot judgment panic empathy prayer location mountainous area sea area land selection restoration life evacuation delay living issues value risk awareness water flow sediment sense of scale event development world mourning nature humans sense of fear place preventive measures education scene seconds psychology delay multiple factors awareness victimhood urban development risk lessons heart miracle sense of ownership memory result regret anger accident hazardous area location background process disaster preparedness awareness</t>
+  </si>
+  <si>
+    <t>silhouette airborne blown away impact slow motion power safety blast shock astonishment words scene civilians collateral victims sorrow video life moment 21st century conflict meaninglessness film brutality reason fear explosion shockwave evasion tolerance unfairness world unstoppable breathing safety change tears tragedy life disregard realism memory replay range everyone impact time acoustics speed everyday place cause unknown aggression accidental underground gas possibility camera shake ground uplift precursor sudden scale anomaly understanding tracking weight era fact recognition explanation confrontation war happiness stakeholders value of life situation helplessness anger sadness acceptance justice confusion folly casualties increase record meaning first step parties number trembling calmness judgment life and death direction danger existence domain battlefield victimhood mental burden intensity habituation vulnerability resilience survivor imagination continuity issues attention reporting conclusion impression phenomenon shock intensity</t>
+  </si>
+  <si>
+    <t>stress anticipation moment head turn chills realization impact calm chaos split second woman reaction time tension crash awareness fear thought processing accident warning normalcy disaster anxiety uncertainty instinct delay speed unpredictability change memory shoulder glance sympathy survival miracle car adrenaline body pain resilience recovery insanity 911 presence mind leadership bystander effect action assumption frustration shock clarity delay response direction emergency example debris help response injury counter money escape behavior selfishness reaction animals sleep peace terror relief outcome death</t>
+  </si>
+  <si>
+    <t>youtube algorithm recommendation years minecraft world months earth thanos creation 2012 school childhood memory video movies humans aliens planet nature trees exam papers turtle teacher class animals treatment fear animation bowser gif man destruction timeline 2040 sadness comments timestamp moment elephant piano ivory tusks music composition mountain king guilt sheep summer plot twist virus truth vegans meat search google bing creator change jokes chicken fryer bucket kfc space technology missiles intelligence self destruction zoo mirror danger shirt logo chat snake boot editing homework dogs cats year wall e prequel countdown 2026 invasion creatures middle school uno reverse dislikes admission boots relevance 2019 expression server welcome mat duality ego progress wisdom speedrun robots extermination money pocket lesson beginning bug background nostalgia wine ocean direction path coronavirus body burial environment pollution water peta</t>
+  </si>
+  <si>
+    <t>cocaine sobriety addiction police school drugs animation emotion crying storytelling visuals genius translation shade darkness focus surroundings desire sobriety bird wings flight personality red bull choice cycle recovery model kiwi ground void recession indicator gambler feeling cycle video forms ending slurp decision sequel memory effect duration health state danger background contrast yellow clarity experience high desperation dependence music memories time enjoyment reality message symbolism documentary commercial regret darkness lesson education middle school adults alcoholic representation internet gambling forms loneliness substance meaning opioid recommendation episode heroin years reddit family son short reason presentation speaker life mcdonalds example effects children food street species endangered stages cartoon depression meth teacher class kids advertisement tattoo awareness overdose fentanyl bailout help defense program dare brain stomach feeling</t>
+  </si>
+  <si>
+    <t>oil gold lava dirt rarity mountain hill seed life doritos level crook godfather soil nature tree forest clapping growth water comparison uniqueness talent idea potential music rock instrument america property character fire animation meaning lesson masterpiece rain squirrel earthquake rainfall earth soul human story message child ability contentment flavor ink texture minecraft humanity emotion beauty geology landforms proof self love asmr recommendation interpretation focus worth visualization wisdom arrogance people freckles happiness thought light identity growth kiss question scale creator favorite film mind utilization creepiness eyes design healing power</t>
+  </si>
+  <si>
+    <t>videos website english learning ielts exam scholarship vlogs travel exploration uk japan harry potter premier league culture suitcase tapping tins jars hoodie queue photobooth double decker bus cab canal till barriers gap shenanigans handrail carousel deli terrace houses takeaways dream study countries switzerland faith taiwan london documents channel support iraq language pictures books city experience china warmth date october understanding lifestyle favorite year innovation vitality indonesia future new york cozy vibe vietnam book sign happiness museum subtitles beginners peace effect button airplane kazakhstan sweden sightseeing structure encouragement da nang malaysia thailand discovery notes practice accident vlog york india tour bangladesh content brazil teacher notebook notting hill memories ho chi minh city fluency education quality improvement gratitude joy travel britain</t>
+  </si>
+  <si>
+    <t>trip years excitement penguins content talent traveling vloggers airports hotels restaurants antarctica style minutes audience footage angles clarity commentary assignment school frames wallpaper photographer editor editing cinematography documentary bbc learning vlogging youtube suggestion tears student experience age videos world surreal treaty wildlife emotion effort colors visit beauty decade intro national geographic scenery safari storytelling production book ernest shackleton lifetime snow shivers solo travel bucket list words art shots fan cold importance capture quality love india place cow goosebumps motivation presentation seabourn iceland speechless journey sharing vibe awe inspiration visuals perfection congratulations peninsula hokkaido view spectacle favorite return opportunity luck solo awesome</t>
+  </si>
+  <si>
+    <t>explorer silence show discovery hood gorillas africa animal instincts respawn rwanda nature brothers question documentary light positivity mistake silverback trekking gang arsenal sleeve bench press tongue video opportunity south africa courage experiences vibe drumming warning son family pressure kigali roots base communication reunion fear moment quiet expectation chest twins streamer foam runners spawn wisdom ground collaboration side quests ancestors continent cousins exploration</t>
+  </si>
+  <si>
+    <t>thumbnail pool shot bike ghost rider time clips feats strength precision skill speed luck legend goal crowd deer celebration threat move moment gangsta john cena person motorcycle reaction gta vice city curry distance game anime double take crush girl scooter form animal culture vengeance buck football future badminton basketball league suspense goat sorcery friend house physics girlfriend instinct counter pirate people are awesome vote racing car reflexes science teacher runner race shohei ohtani home run shades vibes table realization brothers wrestler</t>
+  </si>
+  <si>
+    <t>racket video snakes opponent execution perfection wait boss game learning difficulty tutorial effort performance explanation channel pov vr table tennis editing match player kurta shot poster competition direction ball sports fans surprise defense sweden camera hand rubber spin india land ball size backhand vision mongoose</t>
+  </si>
+  <si>
+    <t>red bull logo competition injury work energy drink netherlands sport fierljeppen ankles sand grandparents bridge flood stick knees specialist distance bar climber tradition province friesland alcohol pronunciation trait jump mario level seconds announcer technology canal zip code rent traffic jam show microphone crocodiles water sponsor olympics wheelchair road shirt flag river timing execution acl pain camera channel survivor bones medal can difference creativity success foot top grass drink</t>
+  </si>
+  <si>
+    <t>jarvis alcohol video netflix valentine facts ending city people david maine trigger song episode arasaka tower trauma team anime moon cyberpsychosis edgerunners santa schedule steel ball run years emotion lucy genre dream man eyes story series season depression kiss scene character aspirations levels stance cigarettes update editor protagonist disappearance moment game definition insanity radio christmas rebecca mom interest comment collab wuthering waves guilty gear humanity belief expectation age legend romance boyfriend jacket time life reality fantasy simulation world characters properties view love</t>
+  </si>
+  <si>
+    <t>home school afternoon room street scene encounter stare confrontation tension men appearance clothing outfit coat hat pants chain accessory fashion style price currency usd pose posture expression face eyes glance aura presence confidence dominance intimidation energy atmosphere silence distance approach movement step timing reaction instinct strategy thinking mind calculation psychology dialogue quote line voice tone performance acting sound effect impact punch attack power strength ability stand range limit battle fight duel showdown rival enemy protagonist antagonist generation legacy reference meme internet culture community fan discussion comment video clip timestamp moment highlight transition adaptation panel animation anime genre story plot episode sequence emotion excitement fear shock respect admiration humor satire parody comparison celebrity mask pandemic family parent child brother friend cat mirror locker food grade teacher memory reenactment experience icon classic masterpiece</t>
+  </si>
+  <si>
+    <t>real name matikane tannhauser nickname mambo mango omatsuri song festival mambo voice father teaching lyric music melody background escalation performance singing clip video moment timestamp line phrase pronunciation japanese meme internet culture community fans global release banner character girl idol uma musume game cygames player playable collection gacha anime adaptation horse design appearance cuteness adorableness personality expression emotion happiness excitement reaction replay addiction obsession brain head heart healing impact damage legend trend reference raden familiarity recognition ringtone playlist gym life feeling sentiment cinema content discovery search timing arrival year day</t>
+  </si>
+  <si>
+    <t>madagascar island africa travel trip journey destination country nature landscape ecosystem biodiversity wildlife animals lemur chameleon baobab forest rainforest jungle desert savanna coast beach ocean water river lake isolation evolution species endemism environment habitat conservation deforestation climate geography terrain plateau gorge bridge rope bridge mountain valley scenery view photography filming cinematography 4k image picture visual documentary video production editing presentation narration voice accent writing description information education storytelling content experience adventure exploration discovery culture people malagasy community history tradition life beauty creation planet world uniqueness inspiration emotion enjoyment fascination interest memory viewer audience gratitude thanks opportunity planning visit</t>
+  </si>
+  <si>
+    <t>canoe boat gun net fish food room life sea ocean water island coast reef coral diving breath lungs ability skill tradition culture tribe bajau bajo bajonese people community family father children parenthood education teacher student anthropology ecology science research reality portrayal film movie short film documentary production cinematography shot visual narration narrator storytelling content sharing audience viewer emotion feeling sadness pride inspiration memory childhood experience identity country indonesia png borneo wakatobi philippines korea easter island language english voice culture preservation heritage tradition lifestyle simplicity independence survival livelihood fishing commercial fishing industry pressure struggle poverty oppression problem issue government policy punishment support assistance protection conservation sustainability awareness environment ecosystem nature resource coral farming reef space balance connection respect honesty love family bond community life daily life hard work effort strength grace swimming diver traditional diver health habit smoking adaptation change modernity contrast opportunity cycle concept production value execution recommendation recognition award oscar nomination viral content value</t>
+  </si>
+  <si>
+    <t>human health body fitness physique age strength lifestyle life way of life simplicity peace harmony balance happiness freedom independence self sufficiency nature land earth forest island jamaica trelawny orange hill country environment greenery food ackee diet nutrition organic food junk food subsistence harvest cultivation smoking spliff weed blunt habit routine morning ritual rasta rastafari belief faith jah spirituality spirit soul wisdom culture tradition community people locals man elder figure role model accent language voice sound tone vibe energy aura presence respect love unity brotherhood attitude mindset philosophy society modern society contrast criticism reflection question dream desire envy jealousy motivation inspiration memory experience visit travel return perspective documentary video content quality 4k production scene view landscape audience viewer comment message phrase meaning interpretation misunderstanding office worker robot health condition overweight illness healing longevity lifespan community support growth success</t>
+  </si>
+  <si>
+    <t>china imperial throne emperor yuan emperor puyi aisin gioro full name surname given name sun yat sen tokugawa yoshinobu yoshiteru john lone tokyo trial courtroom trial interpreter testimony response language english chinese japanese beijing dialect mandarin manchu pronunciation native pronunciation comprehension translation japanese translation notation peking conversation speaking style resonance voice audio recording video black and white footage archival film historical footage preservation video technology recording technology high resolution image quality smartphone youtube video streaming viewing free release era 100 years modern manchukuo period historical background history world history class textbook historical figure characterization realism presence comparison film the last emperor drama work evaluation perspective debate causality reality winners losers imperial army victims life turbulent dramatic hardship melancholy fate dignity image of emperor later years gardener descendants doctor family mother name pronunciation court palace palace culture food favorite food instant noodles episode interaction behind the scenes memo problem trial anecdotes culture manchu culture inheritance beijing scenery library archival value information knowledge learning chinese language learning understanding impression interest surprise emotion familiarity unexpected cuteness healing likability poignancy excitement shock irony comments expression dragon traces prank episode humor</t>
+  </si>
+  <si>
+    <t>speech orator public speaking rhetoric persuasion charisma voice tone delivery crowd audience reaction applause emotion atmosphere energy influence leader politician figure hitler goebbels patton voltaire germany europe weimar republic regime government power authority control elite clique globalism globalists interventionism international finance businessmen society distortion conflict division hatred struggle people nation culture identity propaganda ideology doctrine belief narrative history world history interpretation perspective revisionism censorship ban restriction translation subtitles language german english speech fragment recording audio video archive footage documentary education school class teacher textbook learning lesson awareness context timeline nov 33 period war world war ii enemy victor defeat unemployment economy recovery policy promise achievement support popularity interest view million views youtube channel algorithm search download internet discussion comment debate controversy demonization label antisemitism freedom free speech opinion truth fact evidence analysis comparison modern times 2020s events relevance prediction future past memory ancestor experience test exam curiosity mystery forbidden content hidden history rewrite manipulation bias side coin winner loser spirit grave legacy idea will individual change course crowd psychology mass psychology</t>
+  </si>
+  <si>
+    <t>youtube time machine video footage recording camera clip scene street new york nyc manhattan queens city world trade center twin towers north tower tower building attack tragedy september 11 2001 event aftermath day after week months years timeline history memory recollection story experience family father mother uncle friend tourist worker commuter train cart workplace office interview birthday flight plane sky noise silence sound horn saxophone music performance camera pan view skyline absence gap loss death victim soul missing persons poster sign message forgiveness never conflict emotion grief sadness shock trauma anxiety fear confusion emptiness heaviness atmosphere energy vibe crowd people pedestrian movement wandering purpose thought expression face look mask dust asbestos air pollution health cancer rubble debris rescue firefighter officer emt digging body survivor miracle escape car dog owner pet separation bond theater cinema movie poster offer cab taxi cabbie transport service kindness community support unity connection gratitude documentation documentary narrative storytelling raw footage reality normalcy contrast change impact moment hours transformation end of era 1990s future nostalgia recommendation algorithm anniversary date september viewer audience reflection life value peace</t>
+  </si>
+  <si>
+    <t>high street fashion fashion channel trend trend explanation wearability styling outfit look wardrobe clothing fashion creator content video part 2 suggestion feedback visuals model window screen layout presentation layering layering trend layering video layering tutorial layering ideas layering hacks lace layering scarf layering scarf styling accessories accessory trends bag bag trends footwear footwear styling trench coat coat wool coat leather jacket blazer shoulder pads jacket turtleneck top lace top tee shirt plaid shirt mini skirt denim dark denim maxi length skirt jeans skinny jeans slim jeans wide leg pants balloon pants parachute pants harem pants trousers pants high rise waist boots knee high boots flats oversized top color palette winter palette navy color block colors tailored cuts silhouette fit body type petite body tall body proportion style fashion cycle vintage clothing thrift thrifted items closet collection outfit recreation brand luxury brand design detail quality small brand rue sloane zara prada headphones wired headphones trip stockholm copenhagen season fall winter holiday climate warm climate california canada age fashion experience personal style signature style inspiration idea pinterest pinterest board trend return trend change comfort elegance femininity confidence flattery practicality functionality</t>
+  </si>
+  <si>
+    <t>tokyo japan osaka streetwear street fashion tokyo fashion japanese fashion style outfit fit look wardrobe clothing fashion inspiration fashion video channel content creator dev kamero hana kiki naomi xameleon yatta dachai fruits frugal aesthetic destroy lonely brand upcoming brand boutique shein phat farm streetwear brand fashion week paris fashion week trend 2000s grunge comeback aesthetic vibe energy personality creativity individuality identity diversity lifestyle culture cultural mix japanese language conversation learning travel trip visit tourism summer august may germany italy brazil dmv american foreigner local people crowd background smile interaction friend group couple girls guys nails hairstyle dreadlocks bag blue bag pants striped outfit orange outfit black skull outfit italian inspired look summer outfit street interview question moment scene clip camera close up video length editing consistency inspiration source work week daily life social media thrifting thrift culture shopping boutique shopping area location district harajuku shibuya aura respect attitude taste style sense confidence positivity good vibes happiness motivation</t>
+  </si>
+  <si>
+    <t>victorias secret victorias secret fashion show vs show vs 2013 vs 2014 vs 2024 fashion show runway runway walk catwalk model supermodel vs angels angel wings fantasy bra diamond dress outfit styling stylist british style costume segment snow angels parisian nights opening finale performance stage choreography lighting music song lineup energy interaction reaction adam levine behati prinsloo couple support taylor swift singer performance artist fall out boy collaboration cara delevingne candice swanepoel adriana lima sui he doutzen kroes miranda kerr lily aldridge asian model model lineup beauty appearance face facial expression smile body physique fitness muscle tone abs strength confidence courage personality presence charisma aura grace elegance style fashion trend era peak era nostalgia memory moment highlight clip scene timestamp crowd audience fan viewer comment section youtube video rewatch comparison difference upgrade downgrade criticism opinion inspiration motivation hard time emotion goosebumps excitement beauty standard body image health training athleticism slimness confidence image fashion industry entertainment show production stage design visuals experience</t>
+  </si>
+  <si>
+    <t>culture heritage ethnicity identity personality values beliefs core values social circle friends family environment surroundings region customs traditions lifestyle circumstances formative years childhood teen years upbringing background society community multiculturalism diversity integration foreigner name language speech accent label stereotype assumption discrimination alienation acceptance belonging home country migration immigration russia belgium eastern europe vacation grandmother cultural difference social perception collectivism individualism collectivist culture individualist culture group individual team nation self self improvement self reliance interdependence cooperation competition mindset worldview behavior habits decision adaptation change influence impact psychology cross cultural psychology personality development habitat population density urban area rural area city society structure leadership collective leadership authority rules tradition system family system education school assignment presentation knowledge learning video content topic discussion argument counterargument perspective opinion theory model spectrum contrast extremism balance tolerance conservatism liberalism uncertainty avoidance social norms politics brexit united kingdom ireland india hinduism islam judaism catholicism shintoism religion faith philosophy yoga eastern christianity orthodoxy gender inequality authority questioning activism political engagement teamwork collaboration independence ego collective ego self awareness herd mentality manipulation leaders politicians corporations globalization culture change cultural evolution art civilization nation human individual existence immortality mortality life experience emotion spirituality intellect distinction identity formation self identity cultural identity personal identity authenticity true self constraint freedom choice agency control algorithm belief system social construct environment influence external factor internal factor genetics emotional experience blockage limitation future decision adaptability transition cultural shock assimilation acculturation difference similarity communication interaction expression behavior pattern norm standard reference data literature research source analysis criticism feedback typo spelling application drawing animation art style channel livestream creator kreativevein assignment help english learning listening skill vocabulary translation subtitle vietnamese terms extrovert introvert small town big city</t>
+  </si>
+  <si>
+    <t>spain europe italy germany france madrid barcelona malaga basque galicia uzbekistan russia japan okinawa asia latin christianity culture culturaldifference cultureshock nationality lifestyle habit values common sense unconventional lifestyle atmosphere vibe margin restaurant dining meal dinner lunch cuisine servingtime service hospitality waiter chef customer tourist local staff businesshours sunday closed open departmentstore supermarket convenience store gasstation chainstore mcdonalds kfc siesta nap breaktime workinghours work dailyrhythm senseoftime sunset clock soccer laliga nightgame match kickoff sports kubo messi travel sightseeing stay hotel reservation elbulli conversation interpretation communication interaction excitement family friend partner relationship loneliness discrimination racism prejudice asian foreigner architecture classicalarchitecture sagradafamilia builder director transportation train toilet publictoilet fee climate daylighthours morning night strike shopping foodculture foamcuisine influencer korea video beauty girl ramen jiro ramen culturalcomparison overseas japaneseculture servicequality expectation ageofdiscovery history nightclub streetlive locker luggage bag sauce</t>
+  </si>
+  <si>
+    <t>japan usa uk sweden canada australia europe tokyo cambridge culture cultural differences manners rules customs values lifestyle daily life travel tourism residency study abroad language english japanese channel video content advice tips knowledge learning movie cinema audience screening end credits credits production crew actors director music soundtrack aftertaste silence applause respect appreciation work scene marvel star wars bonus scene entertainment viewing experience transport train station platform exit traffic signal crosswalk guidance sound bird chirping audio guide accessibility visually impaired safety tactile paving navigation block transport system household sink drain garbage disposal waste disposal drainage oil food waste trash bin filter metal strainer utility tool kitchen hygiene food convenience store 7 eleven limited edition collaboration product popcorn snack kitkat sandwich egg sandwich tuna sandwich dessert mochi cinnamoroll mcdonalds milkshake flavor inventory restock sold out fashion outfit style coordination scarf bag design appearance hairstyle sound notification sound effect humor joke reaction laughter impression comment experience memory atmosphere cultural understanding</t>
+  </si>
+  <si>
+    <t>original meme original video recommendation algorithm youtube nostalgia 2026 feed fyp january time years childhood og source clip short video trend viral gem classic legend iconic meme internet culture speedrun speedrunner game gameplay getting over it keyboard mouse gaming chair microphone mic quality sound quality earrape noise audio breathing shouting reaction rage stress performance timing rng frames pixels run record level progress failure success ending good ending achievement unlock moment clip timestamp pov fnaf 2 tom cruise carriminati markiplier mewtwo picasso mona lisa museum art asmr headphones volume ears trauma experience emotion laughter entertainment viewer audience comment caption subtitle autogenerated subtitles music tag japanese comments korean comments language translation editing sound distortion meme origin internet history</t>
+  </si>
+  <si>
+    <t>money 10k balloons space aliens astronauts plane pilot sky backyard bag credit cheque international space station environment ocean nature wildlife air travel weapon target range balloon confetti forecast weather birthday land tether plastic climate subscriber video</t>
+  </si>
+  <si>
+    <t>honor fans moment silence 2025 19 nov 26 lifetime gta trailer trailer 2 trailer 3 lucia reason days rewatching tradition nostalgia hype january april release delay waiting views months years time reminder existence chills childhood week work december 3rd 2024 predictions money revolution npcs detail reflex goosebumps health shape mar 26 october song announcement dream impatience november prayer pov times comments industry</t>
+  </si>
+  <si>
+    <t>dance dancers trio performance moves footwork talent style rhythm sync music song staying alive bee gees barry gibb gibb brothers saturday night fever disco glass wine drink control balance smoothness elegance flexibility confidence energy passion practice effort skill artists group gentlemen young men handsome memories nostalgia generation era soundtrack movie harmonies vocals band classic steps routine groove dexterity</t>
+  </si>
+  <si>
+    <t>song alien green alien dance lyrics moan brainrot generation childhood nostalgia memories trend 2018 2025 2026 april views spotify playlist stephen colbert desert mars school middle school first grade teacher music banger vibe innocence translation spanish language kids new gen skibidi toilet hip movement nightmare room tv trend part</t>
+  </si>
+  <si>
+    <t>michael jackson fans 1985 2024 apr 26 halloween anthem thriller billboard hot 100 artist decades music video movie song masterpiece kids fear room art lifetime king of pop performance tv premiere dance choreography mtv event october banger beat dead zombie transformation makeup werewolf effects history generation memory cinema theater popcorn smile comment section release season flash mobs urge scene meme</t>
   </si>
 </sst>
 </file>
@@ -1686,7 +1987,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1F33D89-B294-DA4A-BC93-23DA94125CD3}">
-  <dimension ref="A1:J100"/>
+  <dimension ref="A1:K100"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="5.6640625" bestFit="1" customWidth="1"/>
@@ -1695,7 +1996,7 @@
     <col min="4" max="10" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="18">
+    <row r="1" spans="1:11" ht="18">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1726,8 +2027,11 @@
       <c r="J1" s="4" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" ht="18">
+      <c r="K1" s="4" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="18">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1758,8 +2062,11 @@
       <c r="J2" s="2">
         <v>0.94868329799999995</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" ht="21">
+      <c r="K2" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="21">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1790,8 +2097,11 @@
       <c r="J3" s="2">
         <v>0.70710678100000002</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" ht="28">
+      <c r="K3" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="28">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1822,8 +2132,11 @@
       <c r="J4" s="2">
         <v>0.89442719100000001</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" ht="18">
+      <c r="K4" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="18">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1854,8 +2167,11 @@
       <c r="J5" s="2">
         <v>0.63245553200000004</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" ht="18">
+      <c r="K5" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="18">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -1886,8 +2202,11 @@
       <c r="J6" s="2">
         <v>0.72760687499999999</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" ht="18">
+      <c r="K6" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="18">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -1918,8 +2237,11 @@
       <c r="J7" s="2">
         <v>0.44721359500000002</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" ht="18">
+      <c r="K7" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="18">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -1950,8 +2272,11 @@
       <c r="J8" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" ht="28">
+      <c r="K8" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="28">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -1982,8 +2307,11 @@
       <c r="J9" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" ht="18">
+      <c r="K9" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="18">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -2014,8 +2342,11 @@
       <c r="J10" s="2">
         <v>0.37796447300000002</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" ht="18">
+      <c r="K10" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="18">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -2046,8 +2377,11 @@
       <c r="J11" s="2">
         <v>0.28867513500000003</v>
       </c>
-    </row>
-    <row r="12" spans="1:10" ht="18">
+      <c r="K11" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="18">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -2078,8 +2412,11 @@
       <c r="J12" s="2">
         <v>0.57735026899999997</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" ht="18">
+      <c r="K12" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="18">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -2110,8 +2447,11 @@
       <c r="J13" s="2">
         <v>0.80178372600000003</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" ht="18">
+      <c r="K13" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="18">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -2142,8 +2482,11 @@
       <c r="J14" s="2">
         <v>0.28867513500000003</v>
       </c>
-    </row>
-    <row r="15" spans="1:10" ht="18">
+      <c r="K14" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="18">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -2174,8 +2517,11 @@
       <c r="J15" s="2">
         <v>0.89442719100000001</v>
       </c>
-    </row>
-    <row r="16" spans="1:10" ht="18">
+      <c r="K15" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="18">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -2206,8 +2552,11 @@
       <c r="J16" s="2">
         <v>0.70710678100000002</v>
       </c>
-    </row>
-    <row r="17" spans="1:10" ht="18">
+      <c r="K16" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="18">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -2238,8 +2587,11 @@
       <c r="J17" s="2">
         <v>0.45883146800000002</v>
       </c>
-    </row>
-    <row r="18" spans="1:10" ht="28">
+      <c r="K17" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="28">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -2270,8 +2622,11 @@
       <c r="J18" s="2">
         <v>0.625543242</v>
       </c>
-    </row>
-    <row r="19" spans="1:10" ht="18">
+      <c r="K18" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="18">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -2302,8 +2657,11 @@
       <c r="J19" s="2">
         <v>0.15430335000000001</v>
       </c>
-    </row>
-    <row r="20" spans="1:10" ht="21">
+      <c r="K19" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="21">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -2334,8 +2692,11 @@
       <c r="J20" s="2">
         <v>0.30151134499999999</v>
       </c>
-    </row>
-    <row r="21" spans="1:10" ht="18">
+      <c r="K20" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="18">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -2366,8 +2727,11 @@
       <c r="J21" s="2">
         <v>0.70710678100000002</v>
       </c>
-    </row>
-    <row r="22" spans="1:10" ht="18">
+      <c r="K21" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="18">
       <c r="A22" s="1">
         <v>21</v>
       </c>
@@ -2398,8 +2762,11 @@
       <c r="J22" s="2">
         <v>0.688247202</v>
       </c>
-    </row>
-    <row r="23" spans="1:10" ht="28">
+      <c r="K22" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="28">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -2430,8 +2797,11 @@
       <c r="J23" s="2">
         <v>0.48507125000000001</v>
       </c>
-    </row>
-    <row r="24" spans="1:10" ht="18">
+      <c r="K23" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="18">
       <c r="A24" s="1">
         <v>23</v>
       </c>
@@ -2462,8 +2832,11 @@
       <c r="J24" s="2">
         <v>0.25819889000000001</v>
       </c>
-    </row>
-    <row r="25" spans="1:10" ht="18">
+      <c r="K24" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" ht="18">
       <c r="A25" s="1">
         <v>24</v>
       </c>
@@ -2494,8 +2867,11 @@
       <c r="J25" s="2">
         <v>0.57735026899999997</v>
       </c>
-    </row>
-    <row r="26" spans="1:10" ht="18">
+      <c r="K25" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="18">
       <c r="A26" s="1">
         <v>25</v>
       </c>
@@ -2526,8 +2902,11 @@
       <c r="J26" s="2">
         <v>0.43643578</v>
       </c>
-    </row>
-    <row r="27" spans="1:10" ht="18">
+      <c r="K26" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" ht="18">
       <c r="A27" s="1">
         <v>26</v>
       </c>
@@ -2558,8 +2937,11 @@
       <c r="J27" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:10" ht="18">
+      <c r="K27" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" ht="18">
       <c r="A28" s="1">
         <v>27</v>
       </c>
@@ -2590,8 +2972,11 @@
       <c r="J28" s="2">
         <v>0.78446454099999996</v>
       </c>
-    </row>
-    <row r="29" spans="1:10" ht="18">
+      <c r="K28" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="18">
       <c r="A29" s="1">
         <v>28</v>
       </c>
@@ -2622,8 +3007,11 @@
       <c r="J29" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="1:10" ht="18">
+      <c r="K29" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="18">
       <c r="A30" s="1">
         <v>29</v>
       </c>
@@ -2654,8 +3042,11 @@
       <c r="J30" s="2">
         <v>0.55470019599999998</v>
       </c>
-    </row>
-    <row r="31" spans="1:10" ht="18">
+      <c r="K30" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="18">
       <c r="A31" s="1">
         <v>30</v>
       </c>
@@ -2686,8 +3077,11 @@
       <c r="J31" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="1:10" ht="18">
+      <c r="K31" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" ht="18">
       <c r="A32" s="1">
         <v>31</v>
       </c>
@@ -2718,8 +3112,11 @@
       <c r="J32" s="2">
         <v>0.688247202</v>
       </c>
-    </row>
-    <row r="33" spans="1:10" ht="18">
+      <c r="K32" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" ht="18">
       <c r="A33" s="1">
         <v>32</v>
       </c>
@@ -2750,8 +3147,11 @@
       <c r="J33" s="2">
         <v>0.35355339099999999</v>
       </c>
-    </row>
-    <row r="34" spans="1:10" ht="18">
+      <c r="K33" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" ht="18">
       <c r="A34" s="1">
         <v>33</v>
       </c>
@@ -2782,8 +3182,11 @@
       <c r="J34" s="2">
         <v>0.55470019599999998</v>
       </c>
-    </row>
-    <row r="35" spans="1:10" ht="18">
+      <c r="K34" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" ht="18">
       <c r="A35" s="1">
         <v>34</v>
       </c>
@@ -2814,8 +3217,11 @@
       <c r="J35" s="2">
         <v>0.26726124200000001</v>
       </c>
-    </row>
-    <row r="36" spans="1:10" ht="18">
+      <c r="K35" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" ht="18">
       <c r="A36" s="1">
         <v>35</v>
       </c>
@@ -2846,8 +3252,11 @@
       <c r="J36" s="2">
         <v>0.53452248400000002</v>
       </c>
-    </row>
-    <row r="37" spans="1:10" ht="18">
+      <c r="K36" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" ht="18">
       <c r="A37" s="1">
         <v>36</v>
       </c>
@@ -2878,8 +3287,11 @@
       <c r="J37" s="2">
         <v>0.426401433</v>
       </c>
-    </row>
-    <row r="38" spans="1:10" ht="18">
+      <c r="K37" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" ht="18">
       <c r="A38" s="1">
         <v>37</v>
       </c>
@@ -2910,8 +3322,11 @@
       <c r="J38" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="39" spans="1:10" ht="18">
+      <c r="K38" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" ht="18">
       <c r="A39" s="1">
         <v>38</v>
       </c>
@@ -2942,8 +3357,11 @@
       <c r="J39" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="40" spans="1:10" ht="18">
+      <c r="K39" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" ht="18">
       <c r="A40" s="1">
         <v>39</v>
       </c>
@@ -2974,8 +3392,11 @@
       <c r="J40" s="2">
         <v>0.57735026899999997</v>
       </c>
-    </row>
-    <row r="41" spans="1:10" ht="24">
+      <c r="K40" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" ht="24">
       <c r="A41" s="1">
         <v>40</v>
       </c>
@@ -3006,8 +3427,11 @@
       <c r="J41" s="2">
         <v>0.53452248400000002</v>
       </c>
-    </row>
-    <row r="42" spans="1:10" ht="18">
+      <c r="K41" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" ht="18">
       <c r="A42" s="1">
         <v>41</v>
       </c>
@@ -3038,8 +3462,11 @@
       <c r="J42" s="2">
         <v>0.23570226</v>
       </c>
-    </row>
-    <row r="43" spans="1:10" ht="18">
+      <c r="K42" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" ht="18">
       <c r="A43" s="1">
         <v>42</v>
       </c>
@@ -3070,8 +3497,11 @@
       <c r="J43" s="2">
         <v>0.365148372</v>
       </c>
-    </row>
-    <row r="44" spans="1:10" ht="18">
+      <c r="K43" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" ht="18">
       <c r="A44" s="1">
         <v>43</v>
       </c>
@@ -3102,8 +3532,11 @@
       <c r="J44" s="2">
         <v>0.57735026899999997</v>
       </c>
-    </row>
-    <row r="45" spans="1:10" ht="18">
+      <c r="K44" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" ht="18">
       <c r="A45" s="1">
         <v>44</v>
       </c>
@@ -3134,8 +3567,11 @@
       <c r="J45" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="1:10" ht="18">
+      <c r="K45" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" ht="18">
       <c r="A46" s="1">
         <v>45</v>
       </c>
@@ -3166,8 +3602,11 @@
       <c r="J46" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="1:10" ht="18">
+      <c r="K46" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" ht="18">
       <c r="A47" s="1">
         <v>46</v>
       </c>
@@ -3198,8 +3637,11 @@
       <c r="J47" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="1:10" ht="18">
+      <c r="K47" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" ht="18">
       <c r="A48" s="1">
         <v>47</v>
       </c>
@@ -3230,8 +3672,11 @@
       <c r="J48" s="2">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="49" spans="1:10" ht="18">
+      <c r="K48" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" ht="18">
       <c r="A49" s="1">
         <v>48</v>
       </c>
@@ -3262,8 +3707,11 @@
       <c r="J49" s="2">
         <v>0.174077656</v>
       </c>
-    </row>
-    <row r="50" spans="1:10" ht="21">
+      <c r="K49" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" ht="21">
       <c r="A50" s="1">
         <v>49</v>
       </c>
@@ -3294,8 +3742,11 @@
       <c r="J50" s="2">
         <v>0.174077656</v>
       </c>
-    </row>
-    <row r="51" spans="1:10" ht="18">
+      <c r="K50" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" ht="18">
       <c r="A51" s="1">
         <v>50</v>
       </c>
@@ -3326,8 +3777,11 @@
       <c r="J51" s="2">
         <v>0.27735009799999999</v>
       </c>
-    </row>
-    <row r="52" spans="1:10" ht="18">
+      <c r="K51" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" ht="18">
       <c r="A52" s="1">
         <v>51</v>
       </c>
@@ -3358,8 +3812,11 @@
       <c r="J52" s="2">
         <v>0.80178372600000003</v>
       </c>
-    </row>
-    <row r="53" spans="1:10" ht="18">
+      <c r="K52" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" ht="18">
       <c r="A53" s="1">
         <v>52</v>
       </c>
@@ -3390,8 +3847,11 @@
       <c r="J53" s="2">
         <v>0.514495755</v>
       </c>
-    </row>
-    <row r="54" spans="1:10" ht="18">
+      <c r="K53" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" ht="18">
       <c r="A54" s="1">
         <v>53</v>
       </c>
@@ -3422,8 +3882,11 @@
       <c r="J54" s="2">
         <v>0.514495755</v>
       </c>
-    </row>
-    <row r="55" spans="1:10" ht="18">
+      <c r="K54" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" ht="18">
       <c r="A55" s="1">
         <v>54</v>
       </c>
@@ -3454,8 +3917,11 @@
       <c r="J55" s="2">
         <v>0.63960214900000001</v>
       </c>
-    </row>
-    <row r="56" spans="1:10" ht="18">
+      <c r="K55" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" ht="18">
       <c r="A56" s="1">
         <v>55</v>
       </c>
@@ -3486,8 +3952,11 @@
       <c r="J56" s="2">
         <v>0.68599434100000001</v>
       </c>
-    </row>
-    <row r="57" spans="1:10" ht="18">
+      <c r="K56" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" ht="18">
       <c r="A57" s="1">
         <v>56</v>
       </c>
@@ -3518,8 +3987,11 @@
       <c r="J57" s="2">
         <v>0.47140452100000002</v>
       </c>
-    </row>
-    <row r="58" spans="1:10" ht="18">
+      <c r="K57" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" ht="18">
       <c r="A58" s="1">
         <v>57</v>
       </c>
@@ -3550,8 +4022,11 @@
       <c r="J58" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="1:10" ht="18">
+      <c r="K58" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" ht="18">
       <c r="A59" s="1">
         <v>58</v>
       </c>
@@ -3582,8 +4057,11 @@
       <c r="J59" s="2">
         <v>0.53881590599999996</v>
       </c>
-    </row>
-    <row r="60" spans="1:10" ht="18">
+      <c r="K59" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" ht="18">
       <c r="A60" s="1">
         <v>59</v>
       </c>
@@ -3614,8 +4092,11 @@
       <c r="J60" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="1:10" ht="18">
+      <c r="K60" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" ht="18">
       <c r="A61" s="1">
         <v>60</v>
       </c>
@@ -3646,8 +4127,11 @@
       <c r="J61" s="2">
         <v>0.196116135</v>
       </c>
-    </row>
-    <row r="62" spans="1:10" ht="18">
+      <c r="K61" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" ht="18">
       <c r="A62" s="1">
         <v>61</v>
       </c>
@@ -3678,8 +4162,11 @@
       <c r="J62" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="1:10" ht="18">
+      <c r="K62" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" ht="18">
       <c r="A63" s="1">
         <v>62</v>
       </c>
@@ -3710,8 +4197,11 @@
       <c r="J63" s="2">
         <v>0.39223226999999999</v>
       </c>
-    </row>
-    <row r="64" spans="1:10" ht="18">
+      <c r="K63" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" ht="18">
       <c r="A64" s="1">
         <v>63</v>
       </c>
@@ -3742,8 +4232,11 @@
       <c r="J64" s="2">
         <v>0.39223226999999999</v>
       </c>
-    </row>
-    <row r="65" spans="1:10" ht="18">
+      <c r="K64" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" ht="18">
       <c r="A65" s="1">
         <v>64</v>
       </c>
@@ -3774,8 +4267,11 @@
       <c r="J65" s="2">
         <v>0.31622776600000002</v>
       </c>
-    </row>
-    <row r="66" spans="1:10" ht="18">
+      <c r="K65" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" ht="18">
       <c r="A66" s="1">
         <v>65</v>
       </c>
@@ -3806,8 +4302,11 @@
       <c r="J66" s="2">
         <v>0.174077656</v>
       </c>
-    </row>
-    <row r="67" spans="1:10" ht="18">
+      <c r="K66" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" ht="18">
       <c r="A67" s="1">
         <v>66</v>
       </c>
@@ -3838,8 +4337,11 @@
       <c r="J67" s="2">
         <v>0.816496581</v>
       </c>
-    </row>
-    <row r="68" spans="1:10" ht="18">
+      <c r="K67" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" ht="18">
       <c r="A68" s="1">
         <v>67</v>
       </c>
@@ -3870,8 +4372,11 @@
       <c r="J68" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="1:10" ht="18">
+      <c r="K68" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" ht="18">
       <c r="A69" s="1">
         <v>68</v>
       </c>
@@ -3902,8 +4407,11 @@
       <c r="J69" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="1:10" ht="18">
+      <c r="K69" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" ht="18">
       <c r="A70" s="1">
         <v>69</v>
       </c>
@@ -3934,8 +4442,11 @@
       <c r="J70" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="1:10" ht="18">
+      <c r="K70" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" ht="18">
       <c r="A71" s="1">
         <v>70</v>
       </c>
@@ -3966,8 +4477,11 @@
       <c r="J71" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="1:10" ht="18">
+      <c r="K71" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" ht="18">
       <c r="A72" s="1">
         <v>71</v>
       </c>
@@ -3998,8 +4512,11 @@
       <c r="J72" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="1:10" ht="18">
+      <c r="K72" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" ht="18">
       <c r="A73" s="1">
         <v>72</v>
       </c>
@@ -4030,8 +4547,11 @@
       <c r="J73" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="1:10" ht="18">
+      <c r="K73" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" ht="18">
       <c r="A74" s="1">
         <v>73</v>
       </c>
@@ -4062,8 +4582,11 @@
       <c r="J74" s="2">
         <v>0.66666666699999999</v>
       </c>
-    </row>
-    <row r="75" spans="1:10" ht="18">
+      <c r="K74" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" ht="18">
       <c r="A75" s="1">
         <v>74</v>
       </c>
@@ -4094,8 +4617,11 @@
       <c r="J75" s="2">
         <v>0.47140452100000002</v>
       </c>
-    </row>
-    <row r="76" spans="1:10" ht="28">
+      <c r="K75" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" ht="28">
       <c r="A76" s="1">
         <v>75</v>
       </c>
@@ -4126,8 +4652,11 @@
       <c r="J76" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="77" spans="1:10" ht="18">
+      <c r="K76" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" ht="18">
       <c r="A77" s="1">
         <v>76</v>
       </c>
@@ -4158,8 +4687,11 @@
       <c r="J77" s="2">
         <v>0.26726124200000001</v>
       </c>
-    </row>
-    <row r="78" spans="1:10" ht="28">
+      <c r="K77" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" ht="28">
       <c r="A78" s="1">
         <v>77</v>
       </c>
@@ -4190,8 +4722,11 @@
       <c r="J78" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="1:10" ht="28">
+      <c r="K78" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" ht="28">
       <c r="A79" s="1">
         <v>78</v>
       </c>
@@ -4222,8 +4757,11 @@
       <c r="J79" s="2">
         <v>0.57735026899999997</v>
       </c>
-    </row>
-    <row r="80" spans="1:10" ht="18">
+      <c r="K79" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" ht="18">
       <c r="A80" s="1">
         <v>79</v>
       </c>
@@ -4254,8 +4792,11 @@
       <c r="J80" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="81" spans="1:10" ht="18">
+      <c r="K80" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" ht="18">
       <c r="A81" s="1">
         <v>80</v>
       </c>
@@ -4286,8 +4827,11 @@
       <c r="J81" s="2">
         <v>0.70710678100000002</v>
       </c>
-    </row>
-    <row r="82" spans="1:10" ht="18">
+      <c r="K81" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" ht="18">
       <c r="A82" s="1">
         <v>81</v>
       </c>
@@ -4318,8 +4862,11 @@
       <c r="J82" s="2">
         <v>0.70710678100000002</v>
       </c>
-    </row>
-    <row r="83" spans="1:10" ht="18">
+      <c r="K82" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" ht="18">
       <c r="A83" s="1">
         <v>82</v>
       </c>
@@ -4350,8 +4897,11 @@
       <c r="J83" s="2">
         <v>0.30151134499999999</v>
       </c>
-    </row>
-    <row r="84" spans="1:10" ht="18">
+      <c r="K83" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11" ht="18">
       <c r="A84" s="1">
         <v>83</v>
       </c>
@@ -4382,8 +4932,11 @@
       <c r="J84" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="1:10" ht="18">
+      <c r="K84" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" ht="18">
       <c r="A85" s="1">
         <v>84</v>
       </c>
@@ -4414,8 +4967,11 @@
       <c r="J85" s="2">
         <v>0.57735026899999997</v>
       </c>
-    </row>
-    <row r="86" spans="1:10" ht="18">
+      <c r="K85" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" ht="18">
       <c r="A86" s="1">
         <v>85</v>
       </c>
@@ -4446,8 +5002,11 @@
       <c r="J86" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="1:10" ht="18">
+      <c r="K86" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" ht="18">
       <c r="A87" s="1">
         <v>86</v>
       </c>
@@ -4478,8 +5037,11 @@
       <c r="J87" s="2">
         <v>0.29488391200000003</v>
       </c>
-    </row>
-    <row r="88" spans="1:10" ht="18">
+      <c r="K87" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11" ht="18">
       <c r="A88" s="1">
         <v>87</v>
       </c>
@@ -4510,8 +5072,11 @@
       <c r="J88" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="1:10" ht="18">
+      <c r="K88" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11" ht="18">
       <c r="A89" s="1">
         <v>88</v>
       </c>
@@ -4542,8 +5107,11 @@
       <c r="J89" s="2">
         <v>0.51639777899999995</v>
       </c>
-    </row>
-    <row r="90" spans="1:10" ht="18">
+      <c r="K89" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11" ht="18">
       <c r="A90" s="1">
         <v>89</v>
       </c>
@@ -4574,8 +5142,11 @@
       <c r="J90" s="2">
         <v>0.31622776600000002</v>
       </c>
-    </row>
-    <row r="91" spans="1:10" ht="18">
+      <c r="K90" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11" ht="18">
       <c r="A91" s="1">
         <v>90</v>
       </c>
@@ -4606,8 +5177,11 @@
       <c r="J91" s="2">
         <v>0.43643578</v>
       </c>
-    </row>
-    <row r="92" spans="1:10" ht="18">
+      <c r="K91" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11" ht="18">
       <c r="A92" s="1">
         <v>91</v>
       </c>
@@ -4638,8 +5212,11 @@
       <c r="J92" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="1:10" ht="18">
+      <c r="K92" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11" ht="18">
       <c r="A93" s="1">
         <v>92</v>
       </c>
@@ -4670,8 +5247,11 @@
       <c r="J93" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="1:10" ht="18">
+      <c r="K93" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11" ht="18">
       <c r="A94" s="1">
         <v>93</v>
       </c>
@@ -4702,8 +5282,11 @@
       <c r="J94" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="1:10" ht="18">
+      <c r="K94" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11" ht="18">
       <c r="A95" s="1">
         <v>94</v>
       </c>
@@ -4734,8 +5317,11 @@
       <c r="J95" s="2">
         <v>0.53033008599999998</v>
       </c>
-    </row>
-    <row r="96" spans="1:10" ht="18">
+      <c r="K95" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11" ht="18">
       <c r="A96" s="1">
         <v>95</v>
       </c>
@@ -4766,8 +5352,11 @@
       <c r="J96" s="2">
         <v>0.48507125000000001</v>
       </c>
-    </row>
-    <row r="97" spans="1:10" ht="18">
+      <c r="K96" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11" ht="18">
       <c r="A97" s="1">
         <v>96</v>
       </c>
@@ -4798,8 +5387,11 @@
       <c r="J97" s="2">
         <v>0.56568542499999996</v>
       </c>
-    </row>
-    <row r="98" spans="1:10" ht="18">
+      <c r="K97" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11" ht="18">
       <c r="A98" s="1">
         <v>97</v>
       </c>
@@ -4830,8 +5422,11 @@
       <c r="J98" s="2">
         <v>0.78446454099999996</v>
       </c>
-    </row>
-    <row r="99" spans="1:10" ht="18">
+      <c r="K98" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11" ht="18">
       <c r="A99" s="1">
         <v>98</v>
       </c>
@@ -4862,8 +5457,11 @@
       <c r="J99" s="2">
         <v>0.63960214900000001</v>
       </c>
-    </row>
-    <row r="100" spans="1:10" ht="18">
+      <c r="K99" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11" ht="18">
       <c r="A100" s="1">
         <v>99</v>
       </c>
@@ -4893,6 +5491,9 @@
       </c>
       <c r="J100" s="2">
         <v>0.54433105400000004</v>
+      </c>
+      <c r="K100" t="s">
+        <v>307</v>
       </c>
     </row>
   </sheetData>

--- a/library.xlsx
+++ b/library.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F0163BA-716F-EF4F-88BE-4EAD1C61A6A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{F40E9203-8E2D-9949-9A4C-F506F7C93633}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15920" xr2:uid="{F40E9203-8E2D-9949-9A4C-F506F7C93633}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/library.xlsx
+++ b/library.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xxc/Desktop/xxc/拓殖大学/研究室/評価実験/video-recommend-system/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F0163BA-716F-EF4F-88BE-4EAD1C61A6A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B60A9EB6-A2F7-0343-AD95-3703B306B7A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15920" xr2:uid="{F40E9203-8E2D-9949-9A4C-F506F7C93633}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="343">
   <si>
     <t>No.</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -1461,6 +1461,112 @@
   </si>
   <si>
     <t>michael jackson fans 1985 2024 apr 26 halloween anthem thriller billboard hot 100 artist decades music video movie song masterpiece kids fear room art lifetime king of pop performance tv premiere dance choreography mtv event october banger beat dead zombie transformation makeup werewolf effects history generation memory cinema theater popcorn smile comment section release season flash mobs urge scene meme</t>
+  </si>
+  <si>
+    <t>tags</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ペット</t>
+  </si>
+  <si>
+    <t>自然</t>
+  </si>
+  <si>
+    <t>料理</t>
+  </si>
+  <si>
+    <t>夜景</t>
+  </si>
+  <si>
+    <t>園芸</t>
+  </si>
+  <si>
+    <t>レトロ</t>
+  </si>
+  <si>
+    <t>BGM</t>
+  </si>
+  <si>
+    <t>インタビュー</t>
+  </si>
+  <si>
+    <t>健康</t>
+  </si>
+  <si>
+    <t>科学</t>
+  </si>
+  <si>
+    <t>生活</t>
+  </si>
+  <si>
+    <t>チャレンジ</t>
+  </si>
+  <si>
+    <t>マジック</t>
+  </si>
+  <si>
+    <t>バーテンダー</t>
+  </si>
+  <si>
+    <t>実験</t>
+  </si>
+  <si>
+    <t>社会事件</t>
+  </si>
+  <si>
+    <t>短編映画</t>
+  </si>
+  <si>
+    <t>ライブ,音楽</t>
+  </si>
+  <si>
+    <t>癒し</t>
+  </si>
+  <si>
+    <t>極限チャレンジ</t>
+  </si>
+  <si>
+    <t>コメディ</t>
+  </si>
+  <si>
+    <t>災害</t>
+  </si>
+  <si>
+    <t>攻撃</t>
+  </si>
+  <si>
+    <t>ライブ</t>
+  </si>
+  <si>
+    <t>教育</t>
+  </si>
+  <si>
+    <t>旅行</t>
+  </si>
+  <si>
+    <t>スポーツ</t>
+  </si>
+  <si>
+    <t>アニメ</t>
+  </si>
+  <si>
+    <t>ドキュメンタリー</t>
+  </si>
+  <si>
+    <t>歴史</t>
+  </si>
+  <si>
+    <t>ファッション</t>
+  </si>
+  <si>
+    <t>文化</t>
+  </si>
+  <si>
+    <t>ゲーム</t>
+  </si>
+  <si>
+    <t>ダンス</t>
   </si>
 </sst>
 </file>
@@ -1987,7 +2093,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1F33D89-B294-DA4A-BC93-23DA94125CD3}">
-  <dimension ref="A1:K100"/>
+  <dimension ref="A1:L100"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="5.6640625" bestFit="1" customWidth="1"/>
@@ -1996,7 +2102,7 @@
     <col min="4" max="10" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="18">
+    <row r="1" spans="1:12" ht="18">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2028,10 +2134,13 @@
         <v>7</v>
       </c>
       <c r="K1" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="L1" s="4" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="18">
+    <row r="2" spans="1:12" ht="18">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -2062,11 +2171,14 @@
       <c r="J2" s="2">
         <v>0.94868329799999995</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K2" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="L2" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="21">
+    <row r="3" spans="1:12" ht="21">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -2097,11 +2209,14 @@
       <c r="J3" s="2">
         <v>0.70710678100000002</v>
       </c>
-      <c r="K3" t="s">
+      <c r="K3" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="L3" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="28">
+    <row r="4" spans="1:12" ht="28">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -2132,11 +2247,14 @@
       <c r="J4" s="2">
         <v>0.89442719100000001</v>
       </c>
-      <c r="K4" t="s">
+      <c r="K4" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="L4" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="18">
+    <row r="5" spans="1:12" ht="18">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -2167,11 +2285,14 @@
       <c r="J5" s="2">
         <v>0.63245553200000004</v>
       </c>
-      <c r="K5" t="s">
+      <c r="K5" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="L5" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="18">
+    <row r="6" spans="1:12" ht="18">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -2202,11 +2323,14 @@
       <c r="J6" s="2">
         <v>0.72760687499999999</v>
       </c>
-      <c r="K6" t="s">
+      <c r="K6" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="L6" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="18">
+    <row r="7" spans="1:12" ht="18">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -2237,11 +2361,14 @@
       <c r="J7" s="2">
         <v>0.44721359500000002</v>
       </c>
-      <c r="K7" t="s">
+      <c r="K7" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="L7" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="18">
+    <row r="8" spans="1:12" ht="18">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -2272,11 +2399,14 @@
       <c r="J8" s="2">
         <v>0</v>
       </c>
-      <c r="K8" t="s">
+      <c r="K8" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="L8" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="28">
+    <row r="9" spans="1:12" ht="28">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -2307,11 +2437,14 @@
       <c r="J9" s="2">
         <v>0</v>
       </c>
-      <c r="K9" t="s">
+      <c r="K9" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="L9" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="18">
+    <row r="10" spans="1:12" ht="18">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -2342,11 +2475,14 @@
       <c r="J10" s="2">
         <v>0.37796447300000002</v>
       </c>
-      <c r="K10" t="s">
+      <c r="K10" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="L10" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="18">
+    <row r="11" spans="1:12" ht="18">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -2377,11 +2513,14 @@
       <c r="J11" s="2">
         <v>0.28867513500000003</v>
       </c>
-      <c r="K11" t="s">
+      <c r="K11" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="L11" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="18">
+    <row r="12" spans="1:12" ht="18">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -2412,11 +2551,14 @@
       <c r="J12" s="2">
         <v>0.57735026899999997</v>
       </c>
-      <c r="K12" t="s">
+      <c r="K12" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="L12" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="18">
+    <row r="13" spans="1:12" ht="18">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -2447,11 +2589,14 @@
       <c r="J13" s="2">
         <v>0.80178372600000003</v>
       </c>
-      <c r="K13" t="s">
+      <c r="K13" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="L13" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="18">
+    <row r="14" spans="1:12" ht="18">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -2482,11 +2627,14 @@
       <c r="J14" s="2">
         <v>0.28867513500000003</v>
       </c>
-      <c r="K14" t="s">
+      <c r="K14" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="L14" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="18">
+    <row r="15" spans="1:12" ht="18">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -2517,11 +2665,14 @@
       <c r="J15" s="2">
         <v>0.89442719100000001</v>
       </c>
-      <c r="K15" t="s">
+      <c r="K15" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="L15" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="18">
+    <row r="16" spans="1:12" ht="18">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -2552,11 +2703,14 @@
       <c r="J16" s="2">
         <v>0.70710678100000002</v>
       </c>
-      <c r="K16" t="s">
+      <c r="K16" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="L16" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="18">
+    <row r="17" spans="1:12" ht="18">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -2587,11 +2741,14 @@
       <c r="J17" s="2">
         <v>0.45883146800000002</v>
       </c>
-      <c r="K17" t="s">
+      <c r="K17" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="L17" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="28">
+    <row r="18" spans="1:12" ht="28">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -2622,11 +2779,14 @@
       <c r="J18" s="2">
         <v>0.625543242</v>
       </c>
-      <c r="K18" t="s">
+      <c r="K18" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="L18" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="18">
+    <row r="19" spans="1:12" ht="18">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -2657,11 +2817,14 @@
       <c r="J19" s="2">
         <v>0.15430335000000001</v>
       </c>
-      <c r="K19" t="s">
+      <c r="K19" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="L19" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="20" spans="1:11" ht="21">
+    <row r="20" spans="1:12" ht="21">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -2692,11 +2855,14 @@
       <c r="J20" s="2">
         <v>0.30151134499999999</v>
       </c>
-      <c r="K20" t="s">
+      <c r="K20" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="L20" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="18">
+    <row r="21" spans="1:12" ht="18">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -2727,11 +2893,14 @@
       <c r="J21" s="2">
         <v>0.70710678100000002</v>
       </c>
-      <c r="K21" t="s">
+      <c r="K21" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="L21" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="18">
+    <row r="22" spans="1:12" ht="18">
       <c r="A22" s="1">
         <v>21</v>
       </c>
@@ -2762,11 +2931,14 @@
       <c r="J22" s="2">
         <v>0.688247202</v>
       </c>
-      <c r="K22" t="s">
+      <c r="K22" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="L22" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="28">
+    <row r="23" spans="1:12" ht="28">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -2797,11 +2969,14 @@
       <c r="J23" s="2">
         <v>0.48507125000000001</v>
       </c>
-      <c r="K23" t="s">
+      <c r="K23" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="L23" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="18">
+    <row r="24" spans="1:12" ht="18">
       <c r="A24" s="1">
         <v>23</v>
       </c>
@@ -2832,11 +3007,14 @@
       <c r="J24" s="2">
         <v>0.25819889000000001</v>
       </c>
-      <c r="K24" t="s">
+      <c r="K24" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="L24" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="25" spans="1:11" ht="18">
+    <row r="25" spans="1:12" ht="18">
       <c r="A25" s="1">
         <v>24</v>
       </c>
@@ -2867,11 +3045,14 @@
       <c r="J25" s="2">
         <v>0.57735026899999997</v>
       </c>
-      <c r="K25" t="s">
+      <c r="K25" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="L25" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="26" spans="1:11" ht="18">
+    <row r="26" spans="1:12" ht="18">
       <c r="A26" s="1">
         <v>25</v>
       </c>
@@ -2902,11 +3083,14 @@
       <c r="J26" s="2">
         <v>0.43643578</v>
       </c>
-      <c r="K26" t="s">
+      <c r="K26" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="L26" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="27" spans="1:11" ht="18">
+    <row r="27" spans="1:12" ht="18">
       <c r="A27" s="1">
         <v>26</v>
       </c>
@@ -2937,11 +3121,14 @@
       <c r="J27" s="2">
         <v>0</v>
       </c>
-      <c r="K27" t="s">
+      <c r="K27" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="L27" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="28" spans="1:11" ht="18">
+    <row r="28" spans="1:12" ht="18">
       <c r="A28" s="1">
         <v>27</v>
       </c>
@@ -2972,11 +3159,14 @@
       <c r="J28" s="2">
         <v>0.78446454099999996</v>
       </c>
-      <c r="K28" t="s">
+      <c r="K28" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="L28" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="29" spans="1:11" ht="18">
+    <row r="29" spans="1:12" ht="18">
       <c r="A29" s="1">
         <v>28</v>
       </c>
@@ -3007,11 +3197,14 @@
       <c r="J29" s="2">
         <v>0</v>
       </c>
-      <c r="K29" t="s">
+      <c r="K29" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="L29" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="30" spans="1:11" ht="18">
+    <row r="30" spans="1:12" ht="18">
       <c r="A30" s="1">
         <v>29</v>
       </c>
@@ -3042,11 +3235,14 @@
       <c r="J30" s="2">
         <v>0.55470019599999998</v>
       </c>
-      <c r="K30" t="s">
+      <c r="K30" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="L30" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="31" spans="1:11" ht="18">
+    <row r="31" spans="1:12" ht="18">
       <c r="A31" s="1">
         <v>30</v>
       </c>
@@ -3077,11 +3273,14 @@
       <c r="J31" s="2">
         <v>0</v>
       </c>
-      <c r="K31" t="s">
+      <c r="K31" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="L31" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="32" spans="1:11" ht="18">
+    <row r="32" spans="1:12" ht="18">
       <c r="A32" s="1">
         <v>31</v>
       </c>
@@ -3112,11 +3311,14 @@
       <c r="J32" s="2">
         <v>0.688247202</v>
       </c>
-      <c r="K32" t="s">
+      <c r="K32" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="L32" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="33" spans="1:11" ht="18">
+    <row r="33" spans="1:12" ht="18">
       <c r="A33" s="1">
         <v>32</v>
       </c>
@@ -3147,11 +3349,14 @@
       <c r="J33" s="2">
         <v>0.35355339099999999</v>
       </c>
-      <c r="K33" t="s">
+      <c r="K33" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="L33" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="34" spans="1:11" ht="18">
+    <row r="34" spans="1:12" ht="18">
       <c r="A34" s="1">
         <v>33</v>
       </c>
@@ -3182,11 +3387,14 @@
       <c r="J34" s="2">
         <v>0.55470019599999998</v>
       </c>
-      <c r="K34" t="s">
+      <c r="K34" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="L34" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="35" spans="1:11" ht="18">
+    <row r="35" spans="1:12" ht="18">
       <c r="A35" s="1">
         <v>34</v>
       </c>
@@ -3217,11 +3425,14 @@
       <c r="J35" s="2">
         <v>0.26726124200000001</v>
       </c>
-      <c r="K35" t="s">
+      <c r="K35" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="L35" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="36" spans="1:11" ht="18">
+    <row r="36" spans="1:12" ht="18">
       <c r="A36" s="1">
         <v>35</v>
       </c>
@@ -3252,11 +3463,14 @@
       <c r="J36" s="2">
         <v>0.53452248400000002</v>
       </c>
-      <c r="K36" t="s">
+      <c r="K36" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="L36" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="37" spans="1:11" ht="18">
+    <row r="37" spans="1:12" ht="18">
       <c r="A37" s="1">
         <v>36</v>
       </c>
@@ -3287,11 +3501,14 @@
       <c r="J37" s="2">
         <v>0.426401433</v>
       </c>
-      <c r="K37" t="s">
+      <c r="K37" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="L37" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="38" spans="1:11" ht="18">
+    <row r="38" spans="1:12" ht="18">
       <c r="A38" s="1">
         <v>37</v>
       </c>
@@ -3322,11 +3539,14 @@
       <c r="J38" s="2">
         <v>0</v>
       </c>
-      <c r="K38" t="s">
+      <c r="K38" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="L38" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="39" spans="1:11" ht="18">
+    <row r="39" spans="1:12" ht="18">
       <c r="A39" s="1">
         <v>38</v>
       </c>
@@ -3357,11 +3577,14 @@
       <c r="J39" s="2">
         <v>0</v>
       </c>
-      <c r="K39" t="s">
+      <c r="K39" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="L39" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="40" spans="1:11" ht="18">
+    <row r="40" spans="1:12" ht="18">
       <c r="A40" s="1">
         <v>39</v>
       </c>
@@ -3392,11 +3615,14 @@
       <c r="J40" s="2">
         <v>0.57735026899999997</v>
       </c>
-      <c r="K40" t="s">
+      <c r="K40" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="L40" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="41" spans="1:11" ht="24">
+    <row r="41" spans="1:12" ht="24">
       <c r="A41" s="1">
         <v>40</v>
       </c>
@@ -3427,11 +3653,14 @@
       <c r="J41" s="2">
         <v>0.53452248400000002</v>
       </c>
-      <c r="K41" t="s">
+      <c r="K41" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="L41" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="42" spans="1:11" ht="18">
+    <row r="42" spans="1:12" ht="18">
       <c r="A42" s="1">
         <v>41</v>
       </c>
@@ -3462,11 +3691,14 @@
       <c r="J42" s="2">
         <v>0.23570226</v>
       </c>
-      <c r="K42" t="s">
+      <c r="K42" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="L42" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="43" spans="1:11" ht="18">
+    <row r="43" spans="1:12" ht="18">
       <c r="A43" s="1">
         <v>42</v>
       </c>
@@ -3497,11 +3729,14 @@
       <c r="J43" s="2">
         <v>0.365148372</v>
       </c>
-      <c r="K43" t="s">
+      <c r="K43" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="L43" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="44" spans="1:11" ht="18">
+    <row r="44" spans="1:12" ht="18">
       <c r="A44" s="1">
         <v>43</v>
       </c>
@@ -3532,11 +3767,14 @@
       <c r="J44" s="2">
         <v>0.57735026899999997</v>
       </c>
-      <c r="K44" t="s">
+      <c r="K44" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="L44" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="45" spans="1:11" ht="18">
+    <row r="45" spans="1:12" ht="18">
       <c r="A45" s="1">
         <v>44</v>
       </c>
@@ -3567,11 +3805,14 @@
       <c r="J45" s="2">
         <v>0</v>
       </c>
-      <c r="K45" t="s">
+      <c r="K45" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="L45" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="46" spans="1:11" ht="18">
+    <row r="46" spans="1:12" ht="18">
       <c r="A46" s="1">
         <v>45</v>
       </c>
@@ -3602,11 +3843,14 @@
       <c r="J46" s="2">
         <v>0</v>
       </c>
-      <c r="K46" t="s">
+      <c r="K46" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="L46" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="47" spans="1:11" ht="18">
+    <row r="47" spans="1:12" ht="18">
       <c r="A47" s="1">
         <v>46</v>
       </c>
@@ -3637,11 +3881,14 @@
       <c r="J47" s="2">
         <v>0</v>
       </c>
-      <c r="K47" t="s">
+      <c r="K47" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="L47" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="48" spans="1:11" ht="18">
+    <row r="48" spans="1:12" ht="18">
       <c r="A48" s="1">
         <v>47</v>
       </c>
@@ -3672,11 +3919,14 @@
       <c r="J48" s="2">
         <v>0.5</v>
       </c>
-      <c r="K48" t="s">
+      <c r="K48" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="L48" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="18">
+    <row r="49" spans="1:12" ht="18">
       <c r="A49" s="1">
         <v>48</v>
       </c>
@@ -3707,11 +3957,14 @@
       <c r="J49" s="2">
         <v>0.174077656</v>
       </c>
-      <c r="K49" t="s">
+      <c r="K49" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="L49" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="21">
+    <row r="50" spans="1:12" ht="21">
       <c r="A50" s="1">
         <v>49</v>
       </c>
@@ -3742,11 +3995,14 @@
       <c r="J50" s="2">
         <v>0.174077656</v>
       </c>
-      <c r="K50" t="s">
+      <c r="K50" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="L50" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="51" spans="1:11" ht="18">
+    <row r="51" spans="1:12" ht="18">
       <c r="A51" s="1">
         <v>50</v>
       </c>
@@ -3777,11 +4033,14 @@
       <c r="J51" s="2">
         <v>0.27735009799999999</v>
       </c>
-      <c r="K51" t="s">
+      <c r="K51" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="L51" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="52" spans="1:11" ht="18">
+    <row r="52" spans="1:12" ht="18">
       <c r="A52" s="1">
         <v>51</v>
       </c>
@@ -3812,11 +4071,14 @@
       <c r="J52" s="2">
         <v>0.80178372600000003</v>
       </c>
-      <c r="K52" t="s">
+      <c r="K52" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="L52" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="53" spans="1:11" ht="18">
+    <row r="53" spans="1:12" ht="18">
       <c r="A53" s="1">
         <v>52</v>
       </c>
@@ -3847,11 +4109,14 @@
       <c r="J53" s="2">
         <v>0.514495755</v>
       </c>
-      <c r="K53" t="s">
+      <c r="K53" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="L53" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="54" spans="1:11" ht="18">
+    <row r="54" spans="1:12" ht="18">
       <c r="A54" s="1">
         <v>53</v>
       </c>
@@ -3882,11 +4147,14 @@
       <c r="J54" s="2">
         <v>0.514495755</v>
       </c>
-      <c r="K54" t="s">
+      <c r="K54" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="L54" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="55" spans="1:11" ht="18">
+    <row r="55" spans="1:12" ht="18">
       <c r="A55" s="1">
         <v>54</v>
       </c>
@@ -3917,11 +4185,14 @@
       <c r="J55" s="2">
         <v>0.63960214900000001</v>
       </c>
-      <c r="K55" t="s">
+      <c r="K55" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="L55" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="56" spans="1:11" ht="18">
+    <row r="56" spans="1:12" ht="18">
       <c r="A56" s="1">
         <v>55</v>
       </c>
@@ -3952,11 +4223,14 @@
       <c r="J56" s="2">
         <v>0.68599434100000001</v>
       </c>
-      <c r="K56" t="s">
+      <c r="K56" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="L56" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="57" spans="1:11" ht="18">
+    <row r="57" spans="1:12" ht="18">
       <c r="A57" s="1">
         <v>56</v>
       </c>
@@ -3987,11 +4261,14 @@
       <c r="J57" s="2">
         <v>0.47140452100000002</v>
       </c>
-      <c r="K57" t="s">
+      <c r="K57" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="L57" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="58" spans="1:11" ht="18">
+    <row r="58" spans="1:12" ht="18">
       <c r="A58" s="1">
         <v>57</v>
       </c>
@@ -4022,11 +4299,14 @@
       <c r="J58" s="2">
         <v>0</v>
       </c>
-      <c r="K58" t="s">
+      <c r="K58" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="L58" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="59" spans="1:11" ht="18">
+    <row r="59" spans="1:12" ht="18">
       <c r="A59" s="1">
         <v>58</v>
       </c>
@@ -4057,11 +4337,14 @@
       <c r="J59" s="2">
         <v>0.53881590599999996</v>
       </c>
-      <c r="K59" t="s">
+      <c r="K59" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="L59" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="60" spans="1:11" ht="18">
+    <row r="60" spans="1:12" ht="18">
       <c r="A60" s="1">
         <v>59</v>
       </c>
@@ -4092,11 +4375,14 @@
       <c r="J60" s="2">
         <v>0</v>
       </c>
-      <c r="K60" t="s">
+      <c r="K60" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="L60" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="61" spans="1:11" ht="18">
+    <row r="61" spans="1:12" ht="18">
       <c r="A61" s="1">
         <v>60</v>
       </c>
@@ -4127,11 +4413,14 @@
       <c r="J61" s="2">
         <v>0.196116135</v>
       </c>
-      <c r="K61" t="s">
+      <c r="K61" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="L61" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="62" spans="1:11" ht="18">
+    <row r="62" spans="1:12" ht="18">
       <c r="A62" s="1">
         <v>61</v>
       </c>
@@ -4162,11 +4451,14 @@
       <c r="J62" s="2">
         <v>0</v>
       </c>
-      <c r="K62" t="s">
+      <c r="K62" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="L62" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="63" spans="1:11" ht="18">
+    <row r="63" spans="1:12" ht="18">
       <c r="A63" s="1">
         <v>62</v>
       </c>
@@ -4197,11 +4489,14 @@
       <c r="J63" s="2">
         <v>0.39223226999999999</v>
       </c>
-      <c r="K63" t="s">
+      <c r="K63" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="L63" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="64" spans="1:11" ht="18">
+    <row r="64" spans="1:12" ht="18">
       <c r="A64" s="1">
         <v>63</v>
       </c>
@@ -4232,11 +4527,14 @@
       <c r="J64" s="2">
         <v>0.39223226999999999</v>
       </c>
-      <c r="K64" t="s">
+      <c r="K64" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="L64" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="65" spans="1:11" ht="18">
+    <row r="65" spans="1:12" ht="18">
       <c r="A65" s="1">
         <v>64</v>
       </c>
@@ -4267,11 +4565,14 @@
       <c r="J65" s="2">
         <v>0.31622776600000002</v>
       </c>
-      <c r="K65" t="s">
+      <c r="K65" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="L65" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="66" spans="1:11" ht="18">
+    <row r="66" spans="1:12" ht="18">
       <c r="A66" s="1">
         <v>65</v>
       </c>
@@ -4302,11 +4603,14 @@
       <c r="J66" s="2">
         <v>0.174077656</v>
       </c>
-      <c r="K66" t="s">
+      <c r="K66" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="L66" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="67" spans="1:11" ht="18">
+    <row r="67" spans="1:12" ht="18">
       <c r="A67" s="1">
         <v>66</v>
       </c>
@@ -4337,11 +4641,14 @@
       <c r="J67" s="2">
         <v>0.816496581</v>
       </c>
-      <c r="K67" t="s">
+      <c r="K67" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="L67" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="68" spans="1:11" ht="18">
+    <row r="68" spans="1:12" ht="18">
       <c r="A68" s="1">
         <v>67</v>
       </c>
@@ -4372,11 +4679,14 @@
       <c r="J68" s="2">
         <v>0</v>
       </c>
-      <c r="K68" t="s">
+      <c r="K68" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="L68" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="69" spans="1:11" ht="18">
+    <row r="69" spans="1:12" ht="18">
       <c r="A69" s="1">
         <v>68</v>
       </c>
@@ -4407,11 +4717,14 @@
       <c r="J69" s="2">
         <v>0</v>
       </c>
-      <c r="K69" t="s">
+      <c r="K69" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="L69" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="70" spans="1:11" ht="18">
+    <row r="70" spans="1:12" ht="18">
       <c r="A70" s="1">
         <v>69</v>
       </c>
@@ -4442,11 +4755,14 @@
       <c r="J70" s="2">
         <v>0</v>
       </c>
-      <c r="K70" t="s">
+      <c r="K70" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="L70" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="71" spans="1:11" ht="18">
+    <row r="71" spans="1:12" ht="18">
       <c r="A71" s="1">
         <v>70</v>
       </c>
@@ -4477,11 +4793,14 @@
       <c r="J71" s="2">
         <v>0</v>
       </c>
-      <c r="K71" t="s">
+      <c r="K71" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="L71" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="72" spans="1:11" ht="18">
+    <row r="72" spans="1:12" ht="18">
       <c r="A72" s="1">
         <v>71</v>
       </c>
@@ -4512,11 +4831,14 @@
       <c r="J72" s="2">
         <v>0</v>
       </c>
-      <c r="K72" t="s">
+      <c r="K72" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="L72" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="73" spans="1:11" ht="18">
+    <row r="73" spans="1:12" ht="18">
       <c r="A73" s="1">
         <v>72</v>
       </c>
@@ -4547,11 +4869,14 @@
       <c r="J73" s="2">
         <v>0</v>
       </c>
-      <c r="K73" t="s">
+      <c r="K73" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="L73" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="74" spans="1:11" ht="18">
+    <row r="74" spans="1:12" ht="18">
       <c r="A74" s="1">
         <v>73</v>
       </c>
@@ -4582,11 +4907,14 @@
       <c r="J74" s="2">
         <v>0.66666666699999999</v>
       </c>
-      <c r="K74" t="s">
+      <c r="K74" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="L74" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="75" spans="1:11" ht="18">
+    <row r="75" spans="1:12" ht="18">
       <c r="A75" s="1">
         <v>74</v>
       </c>
@@ -4617,11 +4945,14 @@
       <c r="J75" s="2">
         <v>0.47140452100000002</v>
       </c>
-      <c r="K75" t="s">
+      <c r="K75" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="L75" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="76" spans="1:11" ht="28">
+    <row r="76" spans="1:12" ht="28">
       <c r="A76" s="1">
         <v>75</v>
       </c>
@@ -4652,11 +4983,14 @@
       <c r="J76" s="2">
         <v>1</v>
       </c>
-      <c r="K76" t="s">
+      <c r="K76" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="L76" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="77" spans="1:11" ht="18">
+    <row r="77" spans="1:12" ht="18">
       <c r="A77" s="1">
         <v>76</v>
       </c>
@@ -4687,11 +5021,14 @@
       <c r="J77" s="2">
         <v>0.26726124200000001</v>
       </c>
-      <c r="K77" t="s">
+      <c r="K77" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="L77" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="78" spans="1:11" ht="28">
+    <row r="78" spans="1:12" ht="28">
       <c r="A78" s="1">
         <v>77</v>
       </c>
@@ -4722,11 +5059,14 @@
       <c r="J78" s="2">
         <v>0</v>
       </c>
-      <c r="K78" t="s">
+      <c r="K78" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="L78" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="79" spans="1:11" ht="28">
+    <row r="79" spans="1:12" ht="28">
       <c r="A79" s="1">
         <v>78</v>
       </c>
@@ -4757,11 +5097,14 @@
       <c r="J79" s="2">
         <v>0.57735026899999997</v>
       </c>
-      <c r="K79" t="s">
+      <c r="K79" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="L79" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="80" spans="1:11" ht="18">
+    <row r="80" spans="1:12" ht="18">
       <c r="A80" s="1">
         <v>79</v>
       </c>
@@ -4792,11 +5135,14 @@
       <c r="J80" s="2">
         <v>0</v>
       </c>
-      <c r="K80" t="s">
+      <c r="K80" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="L80" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="81" spans="1:11" ht="18">
+    <row r="81" spans="1:12" ht="18">
       <c r="A81" s="1">
         <v>80</v>
       </c>
@@ -4827,11 +5173,14 @@
       <c r="J81" s="2">
         <v>0.70710678100000002</v>
       </c>
-      <c r="K81" t="s">
+      <c r="K81" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="L81" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="82" spans="1:11" ht="18">
+    <row r="82" spans="1:12" ht="18">
       <c r="A82" s="1">
         <v>81</v>
       </c>
@@ -4862,11 +5211,14 @@
       <c r="J82" s="2">
         <v>0.70710678100000002</v>
       </c>
-      <c r="K82" t="s">
+      <c r="K82" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="L82" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="83" spans="1:11" ht="18">
+    <row r="83" spans="1:12" ht="18">
       <c r="A83" s="1">
         <v>82</v>
       </c>
@@ -4897,11 +5249,14 @@
       <c r="J83" s="2">
         <v>0.30151134499999999</v>
       </c>
-      <c r="K83" t="s">
+      <c r="K83" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="L83" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="84" spans="1:11" ht="18">
+    <row r="84" spans="1:12" ht="18">
       <c r="A84" s="1">
         <v>83</v>
       </c>
@@ -4932,11 +5287,14 @@
       <c r="J84" s="2">
         <v>0</v>
       </c>
-      <c r="K84" t="s">
+      <c r="K84" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="L84" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="85" spans="1:11" ht="18">
+    <row r="85" spans="1:12" ht="18">
       <c r="A85" s="1">
         <v>84</v>
       </c>
@@ -4967,11 +5325,14 @@
       <c r="J85" s="2">
         <v>0.57735026899999997</v>
       </c>
-      <c r="K85" t="s">
+      <c r="K85" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="L85" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="86" spans="1:11" ht="18">
+    <row r="86" spans="1:12" ht="18">
       <c r="A86" s="1">
         <v>85</v>
       </c>
@@ -5002,11 +5363,14 @@
       <c r="J86" s="2">
         <v>0</v>
       </c>
-      <c r="K86" t="s">
+      <c r="K86" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="L86" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="87" spans="1:11" ht="18">
+    <row r="87" spans="1:12" ht="18">
       <c r="A87" s="1">
         <v>86</v>
       </c>
@@ -5037,11 +5401,14 @@
       <c r="J87" s="2">
         <v>0.29488391200000003</v>
       </c>
-      <c r="K87" t="s">
+      <c r="K87" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="L87" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="88" spans="1:11" ht="18">
+    <row r="88" spans="1:12" ht="18">
       <c r="A88" s="1">
         <v>87</v>
       </c>
@@ -5072,11 +5439,14 @@
       <c r="J88" s="2">
         <v>0</v>
       </c>
-      <c r="K88" t="s">
+      <c r="K88" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="L88" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="89" spans="1:11" ht="18">
+    <row r="89" spans="1:12" ht="18">
       <c r="A89" s="1">
         <v>88</v>
       </c>
@@ -5107,11 +5477,14 @@
       <c r="J89" s="2">
         <v>0.51639777899999995</v>
       </c>
-      <c r="K89" t="s">
+      <c r="K89" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="L89" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="90" spans="1:11" ht="18">
+    <row r="90" spans="1:12" ht="18">
       <c r="A90" s="1">
         <v>89</v>
       </c>
@@ -5142,11 +5515,14 @@
       <c r="J90" s="2">
         <v>0.31622776600000002</v>
       </c>
-      <c r="K90" t="s">
+      <c r="K90" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="L90" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="91" spans="1:11" ht="18">
+    <row r="91" spans="1:12" ht="18">
       <c r="A91" s="1">
         <v>90</v>
       </c>
@@ -5177,11 +5553,14 @@
       <c r="J91" s="2">
         <v>0.43643578</v>
       </c>
-      <c r="K91" t="s">
+      <c r="K91" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="L91" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="92" spans="1:11" ht="18">
+    <row r="92" spans="1:12" ht="18">
       <c r="A92" s="1">
         <v>91</v>
       </c>
@@ -5212,11 +5591,14 @@
       <c r="J92" s="2">
         <v>0</v>
       </c>
-      <c r="K92" t="s">
+      <c r="K92" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="L92" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="93" spans="1:11" ht="18">
+    <row r="93" spans="1:12" ht="18">
       <c r="A93" s="1">
         <v>92</v>
       </c>
@@ -5247,11 +5629,14 @@
       <c r="J93" s="2">
         <v>0</v>
       </c>
-      <c r="K93" t="s">
+      <c r="K93" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="L93" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="94" spans="1:11" ht="18">
+    <row r="94" spans="1:12" ht="18">
       <c r="A94" s="1">
         <v>93</v>
       </c>
@@ -5282,11 +5667,14 @@
       <c r="J94" s="2">
         <v>0</v>
       </c>
-      <c r="K94" t="s">
+      <c r="K94" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="L94" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="95" spans="1:11" ht="18">
+    <row r="95" spans="1:12" ht="18">
       <c r="A95" s="1">
         <v>94</v>
       </c>
@@ -5317,11 +5705,14 @@
       <c r="J95" s="2">
         <v>0.53033008599999998</v>
       </c>
-      <c r="K95" t="s">
+      <c r="K95" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="L95" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="96" spans="1:11" ht="18">
+    <row r="96" spans="1:12" ht="18">
       <c r="A96" s="1">
         <v>95</v>
       </c>
@@ -5352,11 +5743,14 @@
       <c r="J96" s="2">
         <v>0.48507125000000001</v>
       </c>
-      <c r="K96" t="s">
+      <c r="K96" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="L96" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="97" spans="1:11" ht="18">
+    <row r="97" spans="1:12" ht="18">
       <c r="A97" s="1">
         <v>96</v>
       </c>
@@ -5387,11 +5781,14 @@
       <c r="J97" s="2">
         <v>0.56568542499999996</v>
       </c>
-      <c r="K97" t="s">
+      <c r="K97" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="L97" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="98" spans="1:11" ht="18">
+    <row r="98" spans="1:12" ht="18">
       <c r="A98" s="1">
         <v>97</v>
       </c>
@@ -5422,11 +5819,14 @@
       <c r="J98" s="2">
         <v>0.78446454099999996</v>
       </c>
-      <c r="K98" t="s">
+      <c r="K98" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="L98" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="99" spans="1:11" ht="18">
+    <row r="99" spans="1:12" ht="18">
       <c r="A99" s="1">
         <v>98</v>
       </c>
@@ -5457,11 +5857,14 @@
       <c r="J99" s="2">
         <v>0.63960214900000001</v>
       </c>
-      <c r="K99" t="s">
+      <c r="K99" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="L99" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="100" spans="1:11" ht="18">
+    <row r="100" spans="1:12" ht="18">
       <c r="A100" s="1">
         <v>99</v>
       </c>
@@ -5492,7 +5895,10 @@
       <c r="J100" s="2">
         <v>0.54433105400000004</v>
       </c>
-      <c r="K100" t="s">
+      <c r="K100" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="L100" t="s">
         <v>307</v>
       </c>
     </row>

--- a/library.xlsx
+++ b/library.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xxc/Desktop/xxc/拓殖大学/研究室/評価実験/video-recommend-system/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B60A9EB6-A2F7-0343-AD95-3703B306B7A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0040434-9F9F-294F-8EAA-72B178A63438}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15920" xr2:uid="{F40E9203-8E2D-9949-9A4C-F506F7C93633}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{F40E9203-8E2D-9949-9A4C-F506F7C93633}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="343">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="371">
   <si>
     <t>No.</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -140,39 +140,6 @@
         <scheme val="minor"/>
       </rPr>
       <t>リラックス効果、目覚めの朝に、または眠れない夜にもどうぞ。</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>アニメ料理復活|||宮崎駿のハウルの動く城、ベーコンの目玉焼き</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="Apple Color Emoji"/>
-      </rPr>
-      <t>🍳</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="等线"/>
-        <family val="4"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>、めっちゃ美味しい</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="Apple Color Emoji"/>
-      </rPr>
-      <t>😋</t>
     </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -871,9 +838,6 @@
     <t>pqUNX16D2Xs</t>
   </si>
   <si>
-    <t>vGHRq2zNI-c</t>
-  </si>
-  <si>
     <t>meD8BDtKYc0</t>
   </si>
   <si>
@@ -1172,9 +1136,6 @@
     <t>kamikochi shinshu karuizawa kamikochi nature mountain river scenery landscape breathtaking view air fresh greenery stream water sound bird sounds natural sound sound video audio quality atmosphere immersion clarity quietness peace healing relaxation sense of safety purification afterglow memories hometown nostalgia memory experience travel tourist spot trekking bridge place environment natural environment asset gratitude protection value appeal quality balance space time daily life extraordinary mood mind spirit body fatigue stress anxiety release recovery concentration study exam sleep paperwork work habit audio source video nature video healing video satisfaction happiness emotion beauty freshness coolness summer rainy season blue sky rain climate temperature perceived temperature overseas kyushu tateyama kurobe shinshu beef curry</t>
   </si>
   <si>
-    <t>ghibli hayao miyazaki director hayao miyazaki food meal scene breakfast bacon bacon and eggs thick cut bacon thin bacon fried egg egg eggshell frying pan fork seasoned salt calcifer howl markl kimutaku ryunosuke kamiki voice actor voice acting script character grandmother fire fire expression eating chewing sound sound audio design sense of life daily life distance warmth life preciousness worldview ghibli food food temptation animation drawing depiction realism detail direction movement gesture hand motion scene iconic scene representative scene quality appeal deliciousness appetite hunger happiness satisfaction emotion tension sensuality handsome cute rationality culture language umashikate umashi kate</t>
-  </si>
-  <si>
     <t>japan tokyo capital city world earth urban gdp landmark tokyo station tokyo tower odaiba night view illumination scenery cityscape architecture historical architecture skyscraper tradition kyoto edo development predecessors urban development coexistence diversity people life light lighting scale dynamic range video visual beauty video work bgm music quality completion angle work city video appeal pride gratitude love for japan return home overseas thailand region comparison disparity life student days work memory memories nostalgia farewell hope future growth maturity potential energy sense of safety security cleanliness order happiness excitement stimulation ecstasy healing relaxation meditation positivity motivation effort daily life travel tourism visit plan experience presence sense of scale urban power influence brand evaluation country japanese society</t>
   </si>
   <si>
@@ -1500,9 +1461,6 @@
     <t>生活</t>
   </si>
   <si>
-    <t>チャレンジ</t>
-  </si>
-  <si>
     <t>マジック</t>
   </si>
   <si>
@@ -1518,9 +1476,6 @@
     <t>短編映画</t>
   </si>
   <si>
-    <t>ライブ,音楽</t>
-  </si>
-  <si>
     <t>癒し</t>
   </si>
   <si>
@@ -1567,13 +1522,157 @@
   </si>
   <si>
     <t>ダンス</t>
+  </si>
+  <si>
+    <t>cook</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Quick &amp; Easy Recipes With Gordon Ramsay</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>mhDJNfV7hjk</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ペット,犬,猫,,動物,生活,可愛い</t>
+  </si>
+  <si>
+    <t>自然,景色,癒し,日本,ASMR,リラックス,山,上高地,河,鳥,名所,旅行</t>
+  </si>
+  <si>
+    <t>料理,Gordon Ramsay,教育,健康</t>
+  </si>
+  <si>
+    <t>夜景,景色,東京,日本,都市,名所,Time-lapse</t>
+  </si>
+  <si>
+    <t>園芸,植物,Time-lapse</t>
+  </si>
+  <si>
+    <t>レトロ,東京,都市,名所,夜景,景色,日本</t>
+  </si>
+  <si>
+    <t>ASMR,リラックス,喫茶店,勉強,仕事,雰囲気,集中</t>
+  </si>
+  <si>
+    <t>インタビュー,共感,野球,林琢真,感動,スポーツ</t>
+  </si>
+  <si>
+    <t>健康,運動,教育,筋肉,ダイエット,整体,柔軟体操</t>
+  </si>
+  <si>
+    <t>科学,体験,物理</t>
+  </si>
+  <si>
+    <t>生活,知恵,主婦,ライフハック</t>
+  </si>
+  <si>
+    <t>チャレンジ,Water Slide,体験,名所,IShowSpeed</t>
+  </si>
+  <si>
+    <t>マジック,コメディ</t>
+  </si>
+  <si>
+    <r>
+      <t>チャレンジ,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>‪</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="4"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>MrBeast</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>‬</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="4"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>,日本,コメディ</t>
+    </r>
+  </si>
+  <si>
+    <t>バーテンダー,日本,コメディ</t>
+  </si>
+  <si>
+    <t>体験,実験,科学,スライム,ダイラタンシー</t>
+  </si>
+  <si>
+    <t>IShowSpeed,危険,極限チャレンジ</t>
+  </si>
+  <si>
+    <t>社会事件,Will Smith,Oscars,俳優,喧嘩,エンタメ,Love,TV</t>
+  </si>
+  <si>
+    <t>短編映画,映画,感動,共感,Love,家族,父親,娘,離婚</t>
+  </si>
+  <si>
+    <t>ライブ,音楽,Pop,ドラム,rock,可愛い</t>
+  </si>
+  <si>
+    <t>癒し,Jazz,ライブ,音楽,牛,動物,自然,景色,雰囲気,リラックス,山,可愛い</t>
+  </si>
+  <si>
+    <t>極限チャレンジ,Base Jump,skydiving,危険,motorbike,崖,Red Bull</t>
+  </si>
+  <si>
+    <t>インタビュー,カラス,TV</t>
+  </si>
+  <si>
+    <t>コメディ,星野源,ドラム,音楽,Pop</t>
+  </si>
+  <si>
+    <t>チャレンジ,コメディ,料理,危険,牛丼</t>
+  </si>
+  <si>
+    <t>災害,攻撃,911,飛行機,terrorists,危険,America,死亡,恐怖,爆発,火災,world trade center,twin towers,crash,社会事件,hijack,政治,ビル,世界,消防</t>
+  </si>
+  <si>
+    <t>癒し,Lamb,動物,自然,可愛い,リラックス,ペット</t>
+  </si>
+  <si>
+    <t>攻撃,危険,熊,恐怖,逃げる,自然,森,自転車,hunter,GoPro</t>
+  </si>
+  <si>
+    <t>極限チャレンジ,World Record,宇宙,skydiving,Base Jump,危険,Freefall,Red Bull</t>
+  </si>
+  <si>
+    <t>災害,GoPro,火災,危険,消防,Raw POV</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14">
+  <fonts count="15">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1674,6 +1773,12 @@
       <name val="Menlo"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -1739,7 +1844,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1757,6 +1862,9 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2134,10 +2242,10 @@
         <v>7</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="18">
@@ -2148,7 +2256,7 @@
         <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D2" s="2">
         <v>0</v>
@@ -2171,11 +2279,11 @@
       <c r="J2" s="2">
         <v>0.94868329799999995</v>
       </c>
-      <c r="K2" s="2" t="s">
-        <v>309</v>
+      <c r="K2" s="6" t="s">
+        <v>341</v>
       </c>
       <c r="L2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="21">
@@ -2186,7 +2294,7 @@
         <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D3" s="2">
         <v>0</v>
@@ -2209,22 +2317,22 @@
       <c r="J3" s="2">
         <v>0.70710678100000002</v>
       </c>
-      <c r="K3" s="2" t="s">
-        <v>310</v>
+      <c r="K3" s="6" t="s">
+        <v>342</v>
       </c>
       <c r="L3" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" ht="28">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="18">
       <c r="A4" s="1">
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>12</v>
+        <v>339</v>
       </c>
       <c r="C4" t="s">
-        <v>111</v>
+        <v>340</v>
       </c>
       <c r="D4" s="2">
         <v>0</v>
@@ -2239,19 +2347,19 @@
         <v>0</v>
       </c>
       <c r="H4" s="2">
-        <v>0.44721359500000002</v>
+        <v>0.816496581</v>
       </c>
       <c r="I4" s="3">
-        <v>0</v>
+        <v>0.40824829000000001</v>
       </c>
       <c r="J4" s="2">
-        <v>0.89442719100000001</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>311</v>
+        <v>0.40824829000000001</v>
+      </c>
+      <c r="K4" s="6" t="s">
+        <v>343</v>
       </c>
       <c r="L4" t="s">
-        <v>211</v>
+        <v>338</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="18">
@@ -2259,10 +2367,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D5" s="2">
         <v>0</v>
@@ -2285,11 +2393,11 @@
       <c r="J5" s="2">
         <v>0.63245553200000004</v>
       </c>
-      <c r="K5" s="2" t="s">
-        <v>312</v>
+      <c r="K5" s="6" t="s">
+        <v>344</v>
       </c>
       <c r="L5" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="18">
@@ -2297,10 +2405,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D6" s="2">
         <v>0</v>
@@ -2323,11 +2431,11 @@
       <c r="J6" s="2">
         <v>0.72760687499999999</v>
       </c>
-      <c r="K6" s="2" t="s">
-        <v>313</v>
+      <c r="K6" s="6" t="s">
+        <v>345</v>
       </c>
       <c r="L6" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="18">
@@ -2335,10 +2443,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D7" s="2">
         <v>0</v>
@@ -2361,11 +2469,11 @@
       <c r="J7" s="2">
         <v>0.44721359500000002</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>314</v>
+      <c r="K7" s="6" t="s">
+        <v>346</v>
       </c>
       <c r="L7" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="18">
@@ -2373,10 +2481,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D8" s="2">
         <v>0</v>
@@ -2399,11 +2507,11 @@
       <c r="J8" s="2">
         <v>0</v>
       </c>
-      <c r="K8" s="2" t="s">
-        <v>315</v>
+      <c r="K8" s="6" t="s">
+        <v>347</v>
       </c>
       <c r="L8" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="28">
@@ -2411,10 +2519,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D9" s="2">
         <v>0.86602540400000005</v>
@@ -2437,11 +2545,11 @@
       <c r="J9" s="2">
         <v>0</v>
       </c>
-      <c r="K9" s="2" t="s">
-        <v>316</v>
+      <c r="K9" s="6" t="s">
+        <v>348</v>
       </c>
       <c r="L9" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="18">
@@ -2449,10 +2557,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D10" s="2">
         <v>0</v>
@@ -2475,11 +2583,11 @@
       <c r="J10" s="2">
         <v>0.37796447300000002</v>
       </c>
-      <c r="K10" s="2" t="s">
-        <v>317</v>
+      <c r="K10" s="6" t="s">
+        <v>349</v>
       </c>
       <c r="L10" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="18">
@@ -2487,10 +2595,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C11" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D11" s="2">
         <v>0</v>
@@ -2513,11 +2621,11 @@
       <c r="J11" s="2">
         <v>0.28867513500000003</v>
       </c>
-      <c r="K11" s="2" t="s">
-        <v>318</v>
+      <c r="K11" s="6" t="s">
+        <v>350</v>
       </c>
       <c r="L11" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="18">
@@ -2525,10 +2633,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C12" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D12" s="2">
         <v>0</v>
@@ -2551,11 +2659,11 @@
       <c r="J12" s="2">
         <v>0.57735026899999997</v>
       </c>
-      <c r="K12" s="2" t="s">
-        <v>319</v>
+      <c r="K12" s="6" t="s">
+        <v>351</v>
       </c>
       <c r="L12" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="18">
@@ -2563,10 +2671,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C13" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D13" s="2">
         <v>0</v>
@@ -2589,11 +2697,11 @@
       <c r="J13" s="2">
         <v>0.80178372600000003</v>
       </c>
-      <c r="K13" s="2" t="s">
-        <v>320</v>
+      <c r="K13" s="6" t="s">
+        <v>352</v>
       </c>
       <c r="L13" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="18">
@@ -2601,10 +2709,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C14" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D14" s="2">
         <v>0</v>
@@ -2627,11 +2735,11 @@
       <c r="J14" s="2">
         <v>0.28867513500000003</v>
       </c>
-      <c r="K14" s="2" t="s">
-        <v>321</v>
+      <c r="K14" s="6" t="s">
+        <v>353</v>
       </c>
       <c r="L14" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="18">
@@ -2639,10 +2747,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C15" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D15" s="2">
         <v>0</v>
@@ -2665,11 +2773,11 @@
       <c r="J15" s="2">
         <v>0.89442719100000001</v>
       </c>
-      <c r="K15" s="2" t="s">
-        <v>320</v>
+      <c r="K15" s="6" t="s">
+        <v>354</v>
       </c>
       <c r="L15" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="18">
@@ -2677,10 +2785,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C16" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D16" s="2">
         <v>0</v>
@@ -2703,11 +2811,11 @@
       <c r="J16" s="2">
         <v>0.70710678100000002</v>
       </c>
-      <c r="K16" s="2" t="s">
-        <v>322</v>
+      <c r="K16" s="6" t="s">
+        <v>355</v>
       </c>
       <c r="L16" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="18">
@@ -2715,10 +2823,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C17" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D17" s="2">
         <v>0</v>
@@ -2741,11 +2849,11 @@
       <c r="J17" s="2">
         <v>0.45883146800000002</v>
       </c>
-      <c r="K17" s="2" t="s">
-        <v>323</v>
+      <c r="K17" s="6" t="s">
+        <v>356</v>
       </c>
       <c r="L17" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="28">
@@ -2753,10 +2861,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C18" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D18" s="2">
         <v>0</v>
@@ -2779,11 +2887,11 @@
       <c r="J18" s="2">
         <v>0.625543242</v>
       </c>
-      <c r="K18" s="2" t="s">
-        <v>320</v>
+      <c r="K18" s="6" t="s">
+        <v>357</v>
       </c>
       <c r="L18" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="18">
@@ -2791,10 +2899,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C19" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D19" s="2">
         <v>0.30860670000000001</v>
@@ -2817,11 +2925,11 @@
       <c r="J19" s="2">
         <v>0.15430335000000001</v>
       </c>
-      <c r="K19" s="2" t="s">
-        <v>324</v>
+      <c r="K19" s="6" t="s">
+        <v>358</v>
       </c>
       <c r="L19" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="21">
@@ -2829,10 +2937,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C20" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D20" s="2">
         <v>0.603022689</v>
@@ -2855,11 +2963,11 @@
       <c r="J20" s="2">
         <v>0.30151134499999999</v>
       </c>
-      <c r="K20" s="2" t="s">
-        <v>325</v>
+      <c r="K20" s="6" t="s">
+        <v>359</v>
       </c>
       <c r="L20" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="18">
@@ -2867,10 +2975,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C21" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D21" s="2">
         <v>0</v>
@@ -2893,11 +3001,11 @@
       <c r="J21" s="2">
         <v>0.70710678100000002</v>
       </c>
-      <c r="K21" s="2" t="s">
-        <v>326</v>
+      <c r="K21" s="6" t="s">
+        <v>360</v>
       </c>
       <c r="L21" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="18">
@@ -2905,10 +3013,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C22" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D22" s="2">
         <v>0</v>
@@ -2931,11 +3039,11 @@
       <c r="J22" s="2">
         <v>0.688247202</v>
       </c>
-      <c r="K22" s="2" t="s">
-        <v>327</v>
+      <c r="K22" s="6" t="s">
+        <v>361</v>
       </c>
       <c r="L22" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="28">
@@ -2943,10 +3051,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C23" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D23" s="2">
         <v>0</v>
@@ -2969,11 +3077,11 @@
       <c r="J23" s="2">
         <v>0.48507125000000001</v>
       </c>
-      <c r="K23" s="2" t="s">
-        <v>328</v>
+      <c r="K23" s="6" t="s">
+        <v>362</v>
       </c>
       <c r="L23" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
     </row>
     <row r="24" spans="1:12" ht="18">
@@ -2981,10 +3089,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C24" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D24" s="2">
         <v>0</v>
@@ -3007,11 +3115,11 @@
       <c r="J24" s="2">
         <v>0.25819889000000001</v>
       </c>
-      <c r="K24" s="2" t="s">
-        <v>316</v>
+      <c r="K24" s="6" t="s">
+        <v>363</v>
       </c>
       <c r="L24" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="25" spans="1:12" ht="18">
@@ -3019,10 +3127,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C25" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D25" s="2">
         <v>0</v>
@@ -3045,11 +3153,11 @@
       <c r="J25" s="2">
         <v>0.57735026899999997</v>
       </c>
-      <c r="K25" s="2" t="s">
-        <v>329</v>
+      <c r="K25" s="6" t="s">
+        <v>364</v>
       </c>
       <c r="L25" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
     </row>
     <row r="26" spans="1:12" ht="18">
@@ -3057,37 +3165,37 @@
         <v>25</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C26" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D26" s="2">
         <v>0</v>
       </c>
       <c r="E26" s="3">
-        <v>0.43643578</v>
+        <v>0.46852128599999998</v>
       </c>
       <c r="F26" s="2">
         <v>0</v>
       </c>
       <c r="G26" s="3">
-        <v>0.43643578</v>
+        <v>0</v>
       </c>
       <c r="H26" s="2">
         <v>0</v>
       </c>
       <c r="I26" s="3">
-        <v>0.65465367100000005</v>
+        <v>0.62469504799999998</v>
       </c>
       <c r="J26" s="2">
-        <v>0.43643578</v>
-      </c>
-      <c r="K26" s="2" t="s">
-        <v>329</v>
+        <v>0.62469504799999998</v>
+      </c>
+      <c r="K26" s="6" t="s">
+        <v>365</v>
       </c>
       <c r="L26" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="18">
@@ -3095,10 +3203,10 @@
         <v>26</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C27" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D27" s="2">
         <v>0.36927447299999999</v>
@@ -3121,11 +3229,11 @@
       <c r="J27" s="2">
         <v>0</v>
       </c>
-      <c r="K27" s="2" t="s">
-        <v>330</v>
+      <c r="K27" s="6" t="s">
+        <v>366</v>
       </c>
       <c r="L27" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="28" spans="1:12" ht="18">
@@ -3133,10 +3241,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C28" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D28" s="2">
         <v>0</v>
@@ -3159,11 +3267,11 @@
       <c r="J28" s="2">
         <v>0.78446454099999996</v>
       </c>
-      <c r="K28" s="2" t="s">
-        <v>327</v>
+      <c r="K28" s="6" t="s">
+        <v>367</v>
       </c>
       <c r="L28" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
     </row>
     <row r="29" spans="1:12" ht="18">
@@ -3171,16 +3279,16 @@
         <v>28</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C29" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D29" s="2">
-        <v>0.196116135</v>
+        <v>0</v>
       </c>
       <c r="E29" s="3">
-        <v>0.58834840499999996</v>
+        <v>0.70710678118654746</v>
       </c>
       <c r="F29" s="2">
         <v>0</v>
@@ -3192,16 +3300,16 @@
         <v>0</v>
       </c>
       <c r="I29" s="3">
-        <v>0.78446454099999996</v>
+        <v>0.70710678118654746</v>
       </c>
       <c r="J29" s="2">
         <v>0</v>
       </c>
-      <c r="K29" s="2" t="s">
-        <v>331</v>
+      <c r="K29" s="6" t="s">
+        <v>368</v>
       </c>
       <c r="L29" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="18">
@@ -3209,10 +3317,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C30" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D30" s="2">
         <v>0</v>
@@ -3235,11 +3343,11 @@
       <c r="J30" s="2">
         <v>0.55470019599999998</v>
       </c>
-      <c r="K30" s="2" t="s">
-        <v>328</v>
+      <c r="K30" s="6" t="s">
+        <v>369</v>
       </c>
       <c r="L30" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
     </row>
     <row r="31" spans="1:12" ht="18">
@@ -3247,10 +3355,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C31" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D31" s="2">
         <v>0.52981294300000004</v>
@@ -3273,11 +3381,11 @@
       <c r="J31" s="2">
         <v>0</v>
       </c>
-      <c r="K31" s="2" t="s">
-        <v>330</v>
+      <c r="K31" s="6" t="s">
+        <v>370</v>
       </c>
       <c r="L31" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
     </row>
     <row r="32" spans="1:12" ht="18">
@@ -3285,10 +3393,10 @@
         <v>31</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C32" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D32" s="2">
         <v>0</v>
@@ -3312,10 +3420,10 @@
         <v>0.688247202</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="L32" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
     </row>
     <row r="33" spans="1:12" ht="18">
@@ -3323,10 +3431,10 @@
         <v>32</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C33" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D33" s="2">
         <v>0</v>
@@ -3350,10 +3458,10 @@
         <v>0.35355339099999999</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="L33" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
     </row>
     <row r="34" spans="1:12" ht="18">
@@ -3361,10 +3469,10 @@
         <v>33</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C34" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D34" s="2">
         <v>0.55470019599999998</v>
@@ -3388,10 +3496,10 @@
         <v>0.55470019599999998</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="L34" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
     </row>
     <row r="35" spans="1:12" ht="18">
@@ -3399,10 +3507,10 @@
         <v>34</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C35" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D35" s="2">
         <v>0.53452248400000002</v>
@@ -3426,10 +3534,10 @@
         <v>0.26726124200000001</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="L35" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
     </row>
     <row r="36" spans="1:12" ht="18">
@@ -3437,10 +3545,10 @@
         <v>35</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C36" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D36" s="2">
         <v>0</v>
@@ -3464,10 +3572,10 @@
         <v>0.53452248400000002</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="L36" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
     </row>
     <row r="37" spans="1:12" ht="18">
@@ -3475,10 +3583,10 @@
         <v>36</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C37" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D37" s="2">
         <v>0.21320071600000001</v>
@@ -3502,10 +3610,10 @@
         <v>0.426401433</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="L37" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
     </row>
     <row r="38" spans="1:12" ht="18">
@@ -3513,10 +3621,10 @@
         <v>37</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C38" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D38" s="2">
         <v>0</v>
@@ -3540,10 +3648,10 @@
         <v>0</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="L38" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
     </row>
     <row r="39" spans="1:12" ht="18">
@@ -3551,10 +3659,10 @@
         <v>38</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C39" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D39" s="2">
         <v>0</v>
@@ -3578,10 +3686,10 @@
         <v>0</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="L39" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
     </row>
     <row r="40" spans="1:12" ht="18">
@@ -3589,10 +3697,10 @@
         <v>39</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C40" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D40" s="2">
         <v>0</v>
@@ -3616,10 +3724,10 @@
         <v>0.57735026899999997</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="L40" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="41" spans="1:12" ht="24">
@@ -3627,10 +3735,10 @@
         <v>40</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C41" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D41" s="2">
         <v>0</v>
@@ -3654,10 +3762,10 @@
         <v>0.53452248400000002</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="L41" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
     </row>
     <row r="42" spans="1:12" ht="18">
@@ -3665,10 +3773,10 @@
         <v>41</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C42" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D42" s="2">
         <v>0.23570226</v>
@@ -3692,10 +3800,10 @@
         <v>0.23570226</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="L42" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="43" spans="1:12" ht="18">
@@ -3703,10 +3811,10 @@
         <v>42</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C43" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D43" s="2">
         <v>0.182574186</v>
@@ -3730,10 +3838,10 @@
         <v>0.365148372</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="L43" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
     </row>
     <row r="44" spans="1:12" ht="18">
@@ -3741,10 +3849,10 @@
         <v>43</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C44" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D44" s="2">
         <v>0.57735026899999997</v>
@@ -3768,10 +3876,10 @@
         <v>0.57735026899999997</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="L44" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="45" spans="1:12" ht="18">
@@ -3779,10 +3887,10 @@
         <v>44</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C45" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D45" s="2">
         <v>0.89442719100000001</v>
@@ -3806,10 +3914,10 @@
         <v>0</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="L45" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="46" spans="1:12" ht="18">
@@ -3817,10 +3925,10 @@
         <v>45</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C46" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D46" s="2">
         <v>0</v>
@@ -3844,10 +3952,10 @@
         <v>0</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="L46" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
     </row>
     <row r="47" spans="1:12" ht="18">
@@ -3855,10 +3963,10 @@
         <v>46</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C47" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D47" s="2">
         <v>0.25819889000000001</v>
@@ -3882,10 +3990,10 @@
         <v>0</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="L47" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
     </row>
     <row r="48" spans="1:12" ht="18">
@@ -3893,10 +4001,10 @@
         <v>47</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C48" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D48" s="2">
         <v>0.25</v>
@@ -3920,10 +4028,10 @@
         <v>0.5</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="L48" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
     </row>
     <row r="49" spans="1:12" ht="18">
@@ -3931,10 +4039,10 @@
         <v>48</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C49" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D49" s="2">
         <v>0</v>
@@ -3958,10 +4066,10 @@
         <v>0.174077656</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="L49" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
     </row>
     <row r="50" spans="1:12" ht="21">
@@ -3969,10 +4077,10 @@
         <v>49</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C50" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D50" s="2">
         <v>0</v>
@@ -3996,10 +4104,10 @@
         <v>0.174077656</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="L50" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
     </row>
     <row r="51" spans="1:12" ht="18">
@@ -4007,10 +4115,10 @@
         <v>50</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C51" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D51" s="2">
         <v>0.55470019599999998</v>
@@ -4034,10 +4142,10 @@
         <v>0.27735009799999999</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="L51" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
     </row>
     <row r="52" spans="1:12" ht="18">
@@ -4045,10 +4153,10 @@
         <v>51</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C52" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D52" s="2">
         <v>0</v>
@@ -4072,10 +4180,10 @@
         <v>0.80178372600000003</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="L52" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
     </row>
     <row r="53" spans="1:12" ht="18">
@@ -4083,10 +4191,10 @@
         <v>52</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C53" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D53" s="2">
         <v>0</v>
@@ -4110,10 +4218,10 @@
         <v>0.514495755</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="L53" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="54" spans="1:12" ht="18">
@@ -4121,10 +4229,10 @@
         <v>53</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C54" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D54" s="2">
         <v>0</v>
@@ -4148,10 +4256,10 @@
         <v>0.514495755</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="L54" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
     </row>
     <row r="55" spans="1:12" ht="18">
@@ -4159,10 +4267,10 @@
         <v>54</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C55" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D55" s="2">
         <v>0</v>
@@ -4186,10 +4294,10 @@
         <v>0.63960214900000001</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="L55" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
     </row>
     <row r="56" spans="1:12" ht="18">
@@ -4197,10 +4305,10 @@
         <v>55</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C56" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D56" s="2">
         <v>0</v>
@@ -4224,10 +4332,10 @@
         <v>0.68599434100000001</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="L56" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
     </row>
     <row r="57" spans="1:12" ht="18">
@@ -4235,10 +4343,10 @@
         <v>56</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C57" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D57" s="2">
         <v>0</v>
@@ -4262,10 +4370,10 @@
         <v>0.47140452100000002</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="L57" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
     </row>
     <row r="58" spans="1:12" ht="18">
@@ -4273,10 +4381,10 @@
         <v>57</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C58" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D58" s="2">
         <v>0</v>
@@ -4300,10 +4408,10 @@
         <v>0</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="L58" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
     </row>
     <row r="59" spans="1:12" ht="18">
@@ -4311,10 +4419,10 @@
         <v>58</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C59" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D59" s="2">
         <v>0</v>
@@ -4338,10 +4446,10 @@
         <v>0.53881590599999996</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="L59" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
     </row>
     <row r="60" spans="1:12" ht="18">
@@ -4349,10 +4457,10 @@
         <v>59</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C60" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D60" s="2">
         <v>0.188982237</v>
@@ -4376,10 +4484,10 @@
         <v>0</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="L60" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
     </row>
     <row r="61" spans="1:12" ht="18">
@@ -4387,10 +4495,10 @@
         <v>60</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C61" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D61" s="2">
         <v>0.39223226999999999</v>
@@ -4414,10 +4522,10 @@
         <v>0.196116135</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="L61" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
     </row>
     <row r="62" spans="1:12" ht="18">
@@ -4425,10 +4533,10 @@
         <v>61</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C62" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D62" s="2">
         <v>0.53452248400000002</v>
@@ -4452,10 +4560,10 @@
         <v>0</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="L62" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="63" spans="1:12" ht="18">
@@ -4463,10 +4571,10 @@
         <v>62</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C63" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D63" s="2">
         <v>0.58834840499999996</v>
@@ -4490,10 +4598,10 @@
         <v>0.39223226999999999</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="L63" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
     </row>
     <row r="64" spans="1:12" ht="18">
@@ -4501,10 +4609,10 @@
         <v>63</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C64" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D64" s="2">
         <v>0.39223226999999999</v>
@@ -4528,10 +4636,10 @@
         <v>0.39223226999999999</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="L64" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
     </row>
     <row r="65" spans="1:12" ht="18">
@@ -4539,10 +4647,10 @@
         <v>64</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C65" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D65" s="2">
         <v>0</v>
@@ -4566,10 +4674,10 @@
         <v>0.31622776600000002</v>
       </c>
       <c r="K65" s="2" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="L65" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
     </row>
     <row r="66" spans="1:12" ht="18">
@@ -4577,10 +4685,10 @@
         <v>65</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C66" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D66" s="2">
         <v>0</v>
@@ -4604,10 +4712,10 @@
         <v>0.174077656</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="L66" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="67" spans="1:12" ht="18">
@@ -4615,10 +4723,10 @@
         <v>66</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C67" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D67" s="2">
         <v>0</v>
@@ -4642,10 +4750,10 @@
         <v>0.816496581</v>
       </c>
       <c r="K67" s="2" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="L67" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="68" spans="1:12" ht="18">
@@ -4653,10 +4761,10 @@
         <v>67</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C68" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D68" s="2">
         <v>0.51214751999999997</v>
@@ -4680,10 +4788,10 @@
         <v>0</v>
       </c>
       <c r="K68" s="2" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="L68" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
     </row>
     <row r="69" spans="1:12" ht="18">
@@ -4691,10 +4799,10 @@
         <v>68</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C69" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D69" s="2">
         <v>0.44721359500000002</v>
@@ -4718,10 +4826,10 @@
         <v>0</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="L69" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
     </row>
     <row r="70" spans="1:12" ht="18">
@@ -4729,10 +4837,10 @@
         <v>69</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C70" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D70" s="2">
         <v>0.21320071600000001</v>
@@ -4756,10 +4864,10 @@
         <v>0</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="L70" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
     </row>
     <row r="71" spans="1:12" ht="18">
@@ -4767,10 +4875,10 @@
         <v>70</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C71" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D71" s="2">
         <v>0.40824829000000001</v>
@@ -4794,10 +4902,10 @@
         <v>0</v>
       </c>
       <c r="K71" s="2" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="L71" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
     </row>
     <row r="72" spans="1:12" ht="18">
@@ -4805,10 +4913,10 @@
         <v>71</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C72" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D72" s="2">
         <v>0.47434164899999998</v>
@@ -4832,10 +4940,10 @@
         <v>0</v>
       </c>
       <c r="K72" s="2" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="L72" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="73" spans="1:12" ht="18">
@@ -4843,10 +4951,10 @@
         <v>72</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C73" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D73" s="2">
         <v>0.61237243600000002</v>
@@ -4870,10 +4978,10 @@
         <v>0</v>
       </c>
       <c r="K73" s="2" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="L73" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
     </row>
     <row r="74" spans="1:12" ht="18">
@@ -4881,10 +4989,10 @@
         <v>73</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C74" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D74" s="2">
         <v>0</v>
@@ -4908,10 +5016,10 @@
         <v>0.66666666699999999</v>
       </c>
       <c r="K74" s="2" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="L74" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
     </row>
     <row r="75" spans="1:12" ht="18">
@@ -4919,10 +5027,10 @@
         <v>74</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C75" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D75" s="2">
         <v>0</v>
@@ -4946,10 +5054,10 @@
         <v>0.47140452100000002</v>
       </c>
       <c r="K75" s="2" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="L75" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
     </row>
     <row r="76" spans="1:12" ht="28">
@@ -4957,10 +5065,10 @@
         <v>75</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C76" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D76" s="2">
         <v>0</v>
@@ -4984,10 +5092,10 @@
         <v>1</v>
       </c>
       <c r="K76" s="2" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="L76" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
     </row>
     <row r="77" spans="1:12" ht="18">
@@ -4995,10 +5103,10 @@
         <v>76</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C77" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D77" s="2">
         <v>0</v>
@@ -5022,10 +5130,10 @@
         <v>0.26726124200000001</v>
       </c>
       <c r="K77" s="2" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="L77" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
     </row>
     <row r="78" spans="1:12" ht="28">
@@ -5033,10 +5141,10 @@
         <v>77</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C78" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D78" s="2">
         <v>0</v>
@@ -5060,10 +5168,10 @@
         <v>0</v>
       </c>
       <c r="K78" s="2" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="L78" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
     </row>
     <row r="79" spans="1:12" ht="28">
@@ -5071,10 +5179,10 @@
         <v>78</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C79" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D79" s="2">
         <v>0</v>
@@ -5098,10 +5206,10 @@
         <v>0.57735026899999997</v>
       </c>
       <c r="K79" s="2" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="L79" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
     </row>
     <row r="80" spans="1:12" ht="18">
@@ -5109,10 +5217,10 @@
         <v>79</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C80" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D80" s="2">
         <v>0.55470019599999998</v>
@@ -5136,10 +5244,10 @@
         <v>0</v>
       </c>
       <c r="K80" s="2" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="L80" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
     </row>
     <row r="81" spans="1:12" ht="18">
@@ -5147,10 +5255,10 @@
         <v>80</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C81" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D81" s="2">
         <v>0</v>
@@ -5174,10 +5282,10 @@
         <v>0.70710678100000002</v>
       </c>
       <c r="K81" s="2" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="L81" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
     </row>
     <row r="82" spans="1:12" ht="18">
@@ -5185,10 +5293,10 @@
         <v>81</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C82" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D82" s="2">
         <v>0</v>
@@ -5212,10 +5320,10 @@
         <v>0.70710678100000002</v>
       </c>
       <c r="K82" s="2" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="L82" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
     </row>
     <row r="83" spans="1:12" ht="18">
@@ -5223,10 +5331,10 @@
         <v>82</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C83" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D83" s="2">
         <v>0.30151134499999999</v>
@@ -5250,10 +5358,10 @@
         <v>0.30151134499999999</v>
       </c>
       <c r="K83" s="2" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="L83" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
     </row>
     <row r="84" spans="1:12" ht="18">
@@ -5261,10 +5369,10 @@
         <v>83</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C84" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D84" s="2">
         <v>0.75592894600000005</v>
@@ -5288,10 +5396,10 @@
         <v>0</v>
       </c>
       <c r="K84" s="2" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="L84" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
     </row>
     <row r="85" spans="1:12" ht="18">
@@ -5299,10 +5407,10 @@
         <v>84</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C85" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D85" s="2">
         <v>0</v>
@@ -5326,10 +5434,10 @@
         <v>0.57735026899999997</v>
       </c>
       <c r="K85" s="2" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="L85" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
     </row>
     <row r="86" spans="1:12" ht="18">
@@ -5337,10 +5445,10 @@
         <v>85</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C86" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D86" s="2">
         <v>0.47434164899999998</v>
@@ -5364,10 +5472,10 @@
         <v>0</v>
       </c>
       <c r="K86" s="2" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="L86" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
     </row>
     <row r="87" spans="1:12" ht="18">
@@ -5375,10 +5483,10 @@
         <v>86</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C87" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D87" s="2">
         <v>0.29488391200000003</v>
@@ -5402,10 +5510,10 @@
         <v>0.29488391200000003</v>
       </c>
       <c r="K87" s="2" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="L87" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
     </row>
     <row r="88" spans="1:12" ht="18">
@@ -5413,10 +5521,10 @@
         <v>87</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C88" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D88" s="2">
         <v>0.44721359500000002</v>
@@ -5440,10 +5548,10 @@
         <v>0</v>
       </c>
       <c r="K88" s="2" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="L88" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
     </row>
     <row r="89" spans="1:12" ht="18">
@@ -5451,10 +5559,10 @@
         <v>88</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C89" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D89" s="2">
         <v>0</v>
@@ -5478,10 +5586,10 @@
         <v>0.51639777899999995</v>
       </c>
       <c r="K89" s="2" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="L89" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
     </row>
     <row r="90" spans="1:12" ht="18">
@@ -5489,10 +5597,10 @@
         <v>89</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C90" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D90" s="2">
         <v>0</v>
@@ -5516,10 +5624,10 @@
         <v>0.31622776600000002</v>
       </c>
       <c r="K90" s="2" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="L90" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
     </row>
     <row r="91" spans="1:12" ht="18">
@@ -5527,10 +5635,10 @@
         <v>90</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C91" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D91" s="2">
         <v>0.43643578</v>
@@ -5554,10 +5662,10 @@
         <v>0.43643578</v>
       </c>
       <c r="K91" s="2" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="L91" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
     </row>
     <row r="92" spans="1:12" ht="18">
@@ -5565,10 +5673,10 @@
         <v>91</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C92" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D92" s="2">
         <v>0</v>
@@ -5592,10 +5700,10 @@
         <v>0</v>
       </c>
       <c r="K92" s="2" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="L92" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
     </row>
     <row r="93" spans="1:12" ht="18">
@@ -5603,10 +5711,10 @@
         <v>92</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C93" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D93" s="2">
         <v>0.45883146800000002</v>
@@ -5630,10 +5738,10 @@
         <v>0</v>
       </c>
       <c r="K93" s="2" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="L93" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
     </row>
     <row r="94" spans="1:12" ht="18">
@@ -5641,10 +5749,10 @@
         <v>93</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C94" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D94" s="2">
         <v>0.37796447300000002</v>
@@ -5668,10 +5776,10 @@
         <v>0</v>
       </c>
       <c r="K94" s="2" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="L94" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
     </row>
     <row r="95" spans="1:12" ht="18">
@@ -5679,10 +5787,10 @@
         <v>94</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C95" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D95" s="2">
         <v>0.17677669500000001</v>
@@ -5706,10 +5814,10 @@
         <v>0.53033008599999998</v>
       </c>
       <c r="K95" s="2" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="L95" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
     </row>
     <row r="96" spans="1:12" ht="18">
@@ -5717,10 +5825,10 @@
         <v>95</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C96" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D96" s="2">
         <v>0.48507125000000001</v>
@@ -5744,10 +5852,10 @@
         <v>0.48507125000000001</v>
       </c>
       <c r="K96" s="2" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="L96" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
     </row>
     <row r="97" spans="1:12" ht="18">
@@ -5755,10 +5863,10 @@
         <v>96</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C97" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D97" s="2">
         <v>0.141421356</v>
@@ -5782,10 +5890,10 @@
         <v>0.56568542499999996</v>
       </c>
       <c r="K97" s="2" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="L97" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
     </row>
     <row r="98" spans="1:12" ht="18">
@@ -5793,10 +5901,10 @@
         <v>97</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C98" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D98" s="2">
         <v>0</v>
@@ -5820,10 +5928,10 @@
         <v>0.78446454099999996</v>
       </c>
       <c r="K98" s="2" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="L98" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
     </row>
     <row r="99" spans="1:12" ht="18">
@@ -5831,10 +5939,10 @@
         <v>98</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C99" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D99" s="2">
         <v>0</v>
@@ -5858,10 +5966,10 @@
         <v>0.63960214900000001</v>
       </c>
       <c r="K99" s="2" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="L99" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
     </row>
     <row r="100" spans="1:12" ht="18">
@@ -5869,10 +5977,10 @@
         <v>99</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C100" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="D100" s="2">
         <v>0.40824829000000001</v>
@@ -5896,10 +6004,10 @@
         <v>0.54433105400000004</v>
       </c>
       <c r="K100" s="2" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="L100" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
     </row>
   </sheetData>

--- a/library.xlsx
+++ b/library.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xxc/Desktop/xxc/拓殖大学/研究室/評価実験/video-recommend-system/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0040434-9F9F-294F-8EAA-72B178A63438}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2864F4F0-D155-ED41-82BC-46D19CC5BEA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{F40E9203-8E2D-9949-9A4C-F506F7C93633}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="371">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="385">
   <si>
     <t>No.</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -1428,54 +1428,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>ペット</t>
-  </si>
-  <si>
-    <t>自然</t>
-  </si>
-  <si>
-    <t>料理</t>
-  </si>
-  <si>
-    <t>夜景</t>
-  </si>
-  <si>
-    <t>園芸</t>
-  </si>
-  <si>
-    <t>レトロ</t>
-  </si>
-  <si>
-    <t>BGM</t>
-  </si>
-  <si>
-    <t>インタビュー</t>
-  </si>
-  <si>
-    <t>健康</t>
-  </si>
-  <si>
-    <t>科学</t>
-  </si>
-  <si>
-    <t>生活</t>
-  </si>
-  <si>
-    <t>マジック</t>
-  </si>
-  <si>
-    <t>バーテンダー</t>
-  </si>
-  <si>
-    <t>実験</t>
-  </si>
-  <si>
-    <t>社会事件</t>
-  </si>
-  <si>
-    <t>短編映画</t>
-  </si>
-  <si>
     <t>癒し</t>
   </si>
   <si>
@@ -1539,9 +1491,6 @@
     <t>ペット,犬,猫,,動物,生活,可愛い</t>
   </si>
   <si>
-    <t>自然,景色,癒し,日本,ASMR,リラックス,山,上高地,河,鳥,名所,旅行</t>
-  </si>
-  <si>
     <t>料理,Gordon Ramsay,教育,健康</t>
   </si>
   <si>
@@ -1564,9 +1513,6 @@
   </si>
   <si>
     <t>科学,体験,物理</t>
-  </si>
-  <si>
-    <t>生活,知恵,主婦,ライフハック</t>
   </si>
   <si>
     <t>チャレンジ,Water Slide,体験,名所,IShowSpeed</t>
@@ -1620,21 +1566,12 @@
     </r>
   </si>
   <si>
-    <t>バーテンダー,日本,コメディ</t>
-  </si>
-  <si>
-    <t>体験,実験,科学,スライム,ダイラタンシー</t>
-  </si>
-  <si>
     <t>IShowSpeed,危険,極限チャレンジ</t>
   </si>
   <si>
     <t>社会事件,Will Smith,Oscars,俳優,喧嘩,エンタメ,Love,TV</t>
   </si>
   <si>
-    <t>短編映画,映画,感動,共感,Love,家族,父親,娘,離婚</t>
-  </si>
-  <si>
     <t>ライブ,音楽,Pop,ドラム,rock,可愛い</t>
   </si>
   <si>
@@ -1653,9 +1590,6 @@
     <t>チャレンジ,コメディ,料理,危険,牛丼</t>
   </si>
   <si>
-    <t>災害,攻撃,911,飛行機,terrorists,危険,America,死亡,恐怖,爆発,火災,world trade center,twin towers,crash,社会事件,hijack,政治,ビル,世界,消防</t>
-  </si>
-  <si>
     <t>癒し,Lamb,動物,自然,可愛い,リラックス,ペット</t>
   </si>
   <si>
@@ -1666,6 +1600,115 @@
   </si>
   <si>
     <t>災害,GoPro,火災,危険,消防,Raw POV</t>
+  </si>
+  <si>
+    <t>自然,景色,癒し,日本,ASMR,リラックス,山,上高地,河,鳥,名所,旅行,雰囲気</t>
+  </si>
+  <si>
+    <t>生活,主婦,ライフハック</t>
+  </si>
+  <si>
+    <t>バーテンダー,日本,コメディ,bar</t>
+  </si>
+  <si>
+    <t>実験,化学,スライム,ダイラタンシー</t>
+  </si>
+  <si>
+    <t>短編映画,感動,共感,Love,家族,父親,娘,離婚</t>
+  </si>
+  <si>
+    <t>災害,攻撃,911,飛行機,terrorists,危険,USA,死亡,恐怖,爆発,火災,world trade center,twin towers,crash,社会事件,hijack,政治,ビル,世界,消防</t>
+  </si>
+  <si>
+    <t>ペット,犬,動物,生活,可愛い,家族,子供,癒し,Love</t>
+  </si>
+  <si>
+    <t>ペット,チンチラ,ペット,動物,可愛い,教育</t>
+  </si>
+  <si>
+    <t>自然,景色,癒し,日本,ASMR,BGM,リラックス,鳥,花,桜,リラックス,雰囲気,集中,勉強,仕事,,植物,ピアノ</t>
+  </si>
+  <si>
+    <t>自然,景色,癒し,日本,BGM,リラックス,リラックス,雰囲気,集中,勉強,仕事,夜空,夜景,極光</t>
+  </si>
+  <si>
+    <t>料理,主婦,教育,健康,生活,vlog,日本,家族,癒し,雰囲気</t>
+  </si>
+  <si>
+    <t>料理,camp,癒し,雰囲気,冬</t>
+  </si>
+  <si>
+    <t>夜景,dji,上海,都市,中国,景色,名所</t>
+  </si>
+  <si>
+    <t>夜景,Hong Kong,都市,中国,景色,名所</t>
+  </si>
+  <si>
+    <t>園芸,癒し,BGM,リラックス,花,リラックス,雰囲気,集中,植物,ピアノ</t>
+  </si>
+  <si>
+    <t>園芸,教育,植物</t>
+  </si>
+  <si>
+    <t>レトロ,東京,都市,日本</t>
+  </si>
+  <si>
+    <t>レトロ,NY,USA,都市,生活,夜景,Jazz,音楽</t>
+  </si>
+  <si>
+    <t>BGM,リラックス,勉強,仕事,雰囲気,集中,ピアノ</t>
+  </si>
+  <si>
+    <t>BGM,坂本龍一,ピアノ,名作,勉強,仕事,リラックス,雰囲気,集中,Theme song</t>
+  </si>
+  <si>
+    <t>インタビュー,Donald Trump,政治,USA,Iran,世界</t>
+  </si>
+  <si>
+    <t>健康,医療,科学,教育</t>
+  </si>
+  <si>
+    <t>健康,教育,料理</t>
+  </si>
+  <si>
+    <t>科学,物理,宇宙,物理,教育</t>
+  </si>
+  <si>
+    <t>生活,vlog,日本,大阪,料理,掃除,reading,運動</t>
+  </si>
+  <si>
+    <t>生活,vlog,撮影,結婚,子供,共感,感動</t>
+  </si>
+  <si>
+    <t>マジック,GT,Eden Choi</t>
+  </si>
+  <si>
+    <t>バーテンダー,bar,雰囲気</t>
+  </si>
+  <si>
+    <t>バーテンダー,whiskey,コメディ</t>
+  </si>
+  <si>
+    <t>実験,TV,科学,化学,ナトリウム</t>
+  </si>
+  <si>
+    <t>実験,材料,物理,化学,magneticgames,quantumphysics,magnets</t>
+  </si>
+  <si>
+    <t>社会事件,暴力団,警察,大阪,山口組,コメディ</t>
+  </si>
+  <si>
+    <t>社会事件,Donald Trump,政治,USA,攻撃,暗殺,Shooter,MAGA,世界,危険</t>
+  </si>
+  <si>
+    <t>短編映画,マッチングアプリ,マッチング,アプリ,コメディ,社会事件,生活</t>
+  </si>
+  <si>
+    <t>短編映画,AI,科学,社会事件</t>
+  </si>
+  <si>
+    <t>マジック,GT,Shin Lim</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1844,7 +1887,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1865,6 +1908,15 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2210,7 +2262,7 @@
     <col min="4" max="10" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="18">
+    <row r="1" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2248,2321 +2300,2321 @@
         <v>207</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="18">
+    <row r="2" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="7" t="s">
         <v>108</v>
       </c>
       <c r="D2" s="2">
         <v>0</v>
       </c>
-      <c r="E2" s="3">
+      <c r="E2" s="9">
         <v>0</v>
       </c>
       <c r="F2" s="2">
         <v>0</v>
       </c>
-      <c r="G2" s="3">
+      <c r="G2" s="9">
         <v>0</v>
       </c>
       <c r="H2" s="2">
         <v>0.31622776600000002</v>
       </c>
-      <c r="I2" s="3">
+      <c r="I2" s="9">
         <v>0</v>
       </c>
       <c r="J2" s="2">
         <v>0.94868329799999995</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>341</v>
-      </c>
-      <c r="L2" t="s">
+        <v>325</v>
+      </c>
+      <c r="L2" s="7" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="21">
+    <row r="3" spans="1:12" s="7" customFormat="1" ht="21">
       <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="7" t="s">
         <v>109</v>
       </c>
       <c r="D3" s="2">
         <v>0</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3" s="9">
         <v>0</v>
       </c>
       <c r="F3" s="2">
         <v>0</v>
       </c>
-      <c r="G3" s="3">
+      <c r="G3" s="9">
         <v>0</v>
       </c>
       <c r="H3" s="2">
         <v>0.70710678100000002</v>
       </c>
-      <c r="I3" s="3">
+      <c r="I3" s="9">
         <v>0</v>
       </c>
       <c r="J3" s="2">
         <v>0.70710678100000002</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>342</v>
-      </c>
-      <c r="L3" t="s">
+        <v>349</v>
+      </c>
+      <c r="L3" s="7" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="18">
+    <row r="4" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A4" s="1">
         <v>3</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>339</v>
-      </c>
-      <c r="C4" t="s">
-        <v>340</v>
+      <c r="B4" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>324</v>
       </c>
       <c r="D4" s="2">
         <v>0</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="9">
         <v>0</v>
       </c>
       <c r="F4" s="2">
         <v>0</v>
       </c>
-      <c r="G4" s="3">
+      <c r="G4" s="9">
         <v>0</v>
       </c>
       <c r="H4" s="2">
         <v>0.816496581</v>
       </c>
-      <c r="I4" s="3">
+      <c r="I4" s="9">
         <v>0.40824829000000001</v>
       </c>
       <c r="J4" s="2">
         <v>0.40824829000000001</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>343</v>
-      </c>
-      <c r="L4" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="18">
+        <v>326</v>
+      </c>
+      <c r="L4" s="7" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A5" s="1">
         <v>4</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="7" t="s">
         <v>110</v>
       </c>
       <c r="D5" s="2">
         <v>0</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="9">
         <v>0.31622776600000002</v>
       </c>
       <c r="F5" s="2">
         <v>0</v>
       </c>
-      <c r="G5" s="3">
+      <c r="G5" s="9">
         <v>0</v>
       </c>
       <c r="H5" s="2">
         <v>0.31622776600000002</v>
       </c>
-      <c r="I5" s="3">
+      <c r="I5" s="9">
         <v>0.63245553200000004</v>
       </c>
       <c r="J5" s="2">
         <v>0.63245553200000004</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>344</v>
-      </c>
-      <c r="L5" t="s">
+        <v>327</v>
+      </c>
+      <c r="L5" s="7" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="18">
+    <row r="6" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A6" s="1">
         <v>5</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="7" t="s">
         <v>111</v>
       </c>
       <c r="D6" s="2">
         <v>0</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6" s="9">
         <v>0</v>
       </c>
       <c r="F6" s="2">
         <v>0</v>
       </c>
-      <c r="G6" s="3">
+      <c r="G6" s="9">
         <v>0</v>
       </c>
       <c r="H6" s="2">
         <v>0.48507125000000001</v>
       </c>
-      <c r="I6" s="3">
+      <c r="I6" s="9">
         <v>0.48507125000000001</v>
       </c>
       <c r="J6" s="2">
         <v>0.72760687499999999</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>345</v>
-      </c>
-      <c r="L6" t="s">
+        <v>328</v>
+      </c>
+      <c r="L6" s="7" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="18">
+    <row r="7" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A7" s="1">
         <v>6</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="7" t="s">
         <v>112</v>
       </c>
       <c r="D7" s="2">
         <v>0</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7" s="9">
         <v>0</v>
       </c>
       <c r="F7" s="2">
         <v>0</v>
       </c>
-      <c r="G7" s="3">
+      <c r="G7" s="9">
         <v>0</v>
       </c>
       <c r="H7" s="2">
         <v>0</v>
       </c>
-      <c r="I7" s="3">
+      <c r="I7" s="9">
         <v>0.89442719100000001</v>
       </c>
       <c r="J7" s="2">
         <v>0.44721359500000002</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>346</v>
-      </c>
-      <c r="L7" t="s">
+        <v>329</v>
+      </c>
+      <c r="L7" s="7" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="18">
+    <row r="8" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A8" s="1">
         <v>7</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="7" t="s">
         <v>113</v>
       </c>
       <c r="D8" s="2">
         <v>0</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8" s="9">
         <v>0.57735026899999997</v>
       </c>
       <c r="F8" s="2">
         <v>0</v>
       </c>
-      <c r="G8" s="3">
+      <c r="G8" s="9">
         <v>0.57735026899999997</v>
       </c>
       <c r="H8" s="2">
         <v>0.57735026899999997</v>
       </c>
-      <c r="I8" s="3">
+      <c r="I8" s="9">
         <v>0</v>
       </c>
       <c r="J8" s="2">
         <v>0</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>347</v>
-      </c>
-      <c r="L8" t="s">
+        <v>330</v>
+      </c>
+      <c r="L8" s="7" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="28">
+    <row r="9" spans="1:12" s="7" customFormat="1" ht="28">
       <c r="A9" s="1">
         <v>8</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="7" t="s">
         <v>114</v>
       </c>
       <c r="D9" s="2">
         <v>0.86602540400000005</v>
       </c>
-      <c r="E9" s="3">
+      <c r="E9" s="9">
         <v>0.28867513500000003</v>
       </c>
       <c r="F9" s="2">
         <v>0</v>
       </c>
-      <c r="G9" s="3">
+      <c r="G9" s="9">
         <v>0</v>
       </c>
       <c r="H9" s="2">
         <v>0.28867513500000003</v>
       </c>
-      <c r="I9" s="3">
+      <c r="I9" s="9">
         <v>0.28867513500000003</v>
       </c>
       <c r="J9" s="2">
         <v>0</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>348</v>
-      </c>
-      <c r="L9" t="s">
+        <v>331</v>
+      </c>
+      <c r="L9" s="7" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="18">
+    <row r="10" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A10" s="1">
         <v>9</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="7" t="s">
         <v>115</v>
       </c>
       <c r="D10" s="2">
         <v>0</v>
       </c>
-      <c r="E10" s="3">
+      <c r="E10" s="9">
         <v>0.37796447300000002</v>
       </c>
       <c r="F10" s="2">
         <v>0</v>
       </c>
-      <c r="G10" s="3">
+      <c r="G10" s="9">
         <v>0</v>
       </c>
       <c r="H10" s="2">
         <v>0.75592894600000005</v>
       </c>
-      <c r="I10" s="3">
+      <c r="I10" s="9">
         <v>0.37796447300000002</v>
       </c>
       <c r="J10" s="2">
         <v>0.37796447300000002</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>349</v>
-      </c>
-      <c r="L10" t="s">
+        <v>332</v>
+      </c>
+      <c r="L10" s="7" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="18">
+    <row r="11" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A11" s="1">
         <v>10</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="7" t="s">
         <v>116</v>
       </c>
       <c r="D11" s="2">
         <v>0</v>
       </c>
-      <c r="E11" s="3">
+      <c r="E11" s="9">
         <v>0.28867513500000003</v>
       </c>
       <c r="F11" s="2">
         <v>0</v>
       </c>
-      <c r="G11" s="3">
+      <c r="G11" s="9">
         <v>0</v>
       </c>
       <c r="H11" s="2">
         <v>0.28867513500000003</v>
       </c>
-      <c r="I11" s="3">
+      <c r="I11" s="9">
         <v>0.86602540400000005</v>
       </c>
       <c r="J11" s="2">
         <v>0.28867513500000003</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>350</v>
-      </c>
-      <c r="L11" t="s">
+        <v>333</v>
+      </c>
+      <c r="L11" s="7" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="18">
+    <row r="12" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A12" s="1">
         <v>11</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="7" t="s">
         <v>117</v>
       </c>
       <c r="D12" s="2">
         <v>0</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="9">
         <v>0</v>
       </c>
       <c r="F12" s="2">
         <v>0</v>
       </c>
-      <c r="G12" s="3">
+      <c r="G12" s="9">
         <v>0</v>
       </c>
       <c r="H12" s="2">
         <v>0.57735026899999997</v>
       </c>
-      <c r="I12" s="3">
+      <c r="I12" s="9">
         <v>0.57735026899999997</v>
       </c>
       <c r="J12" s="2">
         <v>0.57735026899999997</v>
       </c>
       <c r="K12" s="6" t="s">
-        <v>351</v>
-      </c>
-      <c r="L12" t="s">
+        <v>350</v>
+      </c>
+      <c r="L12" s="7" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="18">
+    <row r="13" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A13" s="1">
         <v>12</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="7" t="s">
         <v>118</v>
       </c>
       <c r="D13" s="2">
         <v>0</v>
       </c>
-      <c r="E13" s="3">
+      <c r="E13" s="9">
         <v>0</v>
       </c>
       <c r="F13" s="2">
         <v>0</v>
       </c>
-      <c r="G13" s="3">
+      <c r="G13" s="9">
         <v>0</v>
       </c>
       <c r="H13" s="2">
         <v>0.26726124200000001</v>
       </c>
-      <c r="I13" s="3">
+      <c r="I13" s="9">
         <v>0.53452248400000002</v>
       </c>
       <c r="J13" s="2">
         <v>0.80178372600000003</v>
       </c>
       <c r="K13" s="6" t="s">
-        <v>352</v>
-      </c>
-      <c r="L13" t="s">
+        <v>334</v>
+      </c>
+      <c r="L13" s="7" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="18">
+    <row r="14" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A14" s="1">
         <v>13</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="7" t="s">
         <v>119</v>
       </c>
       <c r="D14" s="2">
         <v>0</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="9">
         <v>0</v>
       </c>
       <c r="F14" s="2">
         <v>0</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="9">
         <v>0.28867513500000003</v>
       </c>
       <c r="H14" s="2">
         <v>0.28867513500000003</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="9">
         <v>0.86602540400000005</v>
       </c>
       <c r="J14" s="2">
         <v>0.28867513500000003</v>
       </c>
       <c r="K14" s="6" t="s">
-        <v>353</v>
-      </c>
-      <c r="L14" t="s">
+        <v>335</v>
+      </c>
+      <c r="L14" s="7" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="18">
+    <row r="15" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A15" s="1">
         <v>14</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="7" t="s">
         <v>120</v>
       </c>
       <c r="D15" s="2">
         <v>0</v>
       </c>
-      <c r="E15" s="3">
+      <c r="E15" s="9">
         <v>0</v>
       </c>
       <c r="F15" s="2">
         <v>0</v>
       </c>
-      <c r="G15" s="3">
+      <c r="G15" s="9">
         <v>0</v>
       </c>
       <c r="H15" s="2">
         <v>0</v>
       </c>
-      <c r="I15" s="3">
+      <c r="I15" s="9">
         <v>0.44721359500000002</v>
       </c>
       <c r="J15" s="2">
         <v>0.89442719100000001</v>
       </c>
       <c r="K15" s="6" t="s">
-        <v>354</v>
-      </c>
-      <c r="L15" t="s">
+        <v>336</v>
+      </c>
+      <c r="L15" s="7" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="18">
+    <row r="16" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A16" s="1">
         <v>15</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="7" t="s">
         <v>121</v>
       </c>
       <c r="D16" s="2">
         <v>0</v>
       </c>
-      <c r="E16" s="3">
+      <c r="E16" s="9">
         <v>0.23570226</v>
       </c>
       <c r="F16" s="2">
         <v>0</v>
       </c>
-      <c r="G16" s="3">
+      <c r="G16" s="9">
         <v>0</v>
       </c>
       <c r="H16" s="2">
         <v>0.47140452100000002</v>
       </c>
-      <c r="I16" s="3">
+      <c r="I16" s="9">
         <v>0.47140452100000002</v>
       </c>
       <c r="J16" s="2">
         <v>0.70710678100000002</v>
       </c>
       <c r="K16" s="6" t="s">
-        <v>355</v>
-      </c>
-      <c r="L16" t="s">
+        <v>351</v>
+      </c>
+      <c r="L16" s="7" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="18">
+    <row r="17" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A17" s="1">
         <v>16</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="7" t="s">
         <v>122</v>
       </c>
       <c r="D17" s="2">
         <v>0</v>
       </c>
-      <c r="E17" s="3">
+      <c r="E17" s="9">
         <v>0</v>
       </c>
       <c r="F17" s="2">
         <v>0.22941573400000001</v>
       </c>
-      <c r="G17" s="3">
+      <c r="G17" s="9">
         <v>0.688247202</v>
       </c>
       <c r="H17" s="2">
         <v>0.22941573400000001</v>
       </c>
-      <c r="I17" s="3">
+      <c r="I17" s="9">
         <v>0.45883146800000002</v>
       </c>
       <c r="J17" s="2">
         <v>0.45883146800000002</v>
       </c>
       <c r="K17" s="6" t="s">
-        <v>356</v>
-      </c>
-      <c r="L17" t="s">
+        <v>352</v>
+      </c>
+      <c r="L17" s="7" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="28">
+    <row r="18" spans="1:12" s="7" customFormat="1" ht="28">
       <c r="A18" s="1">
         <v>17</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="7" t="s">
         <v>123</v>
       </c>
       <c r="D18" s="2">
         <v>0</v>
       </c>
-      <c r="E18" s="3">
+      <c r="E18" s="9">
         <v>0.41702882800000002</v>
       </c>
       <c r="F18" s="2">
         <v>0</v>
       </c>
-      <c r="G18" s="3">
+      <c r="G18" s="9">
         <v>0.20851441400000001</v>
       </c>
       <c r="H18" s="2">
         <v>0</v>
       </c>
-      <c r="I18" s="3">
+      <c r="I18" s="9">
         <v>0.625543242</v>
       </c>
       <c r="J18" s="2">
         <v>0.625543242</v>
       </c>
       <c r="K18" s="6" t="s">
-        <v>357</v>
-      </c>
-      <c r="L18" t="s">
+        <v>337</v>
+      </c>
+      <c r="L18" s="7" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="18">
+    <row r="19" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A19" s="1">
         <v>18</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="7" t="s">
         <v>124</v>
       </c>
       <c r="D19" s="2">
         <v>0.30860670000000001</v>
       </c>
-      <c r="E19" s="3">
+      <c r="E19" s="9">
         <v>0.15430335000000001</v>
       </c>
       <c r="F19" s="2">
         <v>0.46291005000000002</v>
       </c>
-      <c r="G19" s="3">
+      <c r="G19" s="9">
         <v>0.46291005000000002</v>
       </c>
       <c r="H19" s="2">
         <v>0.46291005000000002</v>
       </c>
-      <c r="I19" s="3">
+      <c r="I19" s="9">
         <v>0.46291005000000002</v>
       </c>
       <c r="J19" s="2">
         <v>0.15430335000000001</v>
       </c>
       <c r="K19" s="6" t="s">
-        <v>358</v>
-      </c>
-      <c r="L19" t="s">
+        <v>338</v>
+      </c>
+      <c r="L19" s="7" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="21">
+    <row r="20" spans="1:12" s="7" customFormat="1" ht="21">
       <c r="A20" s="1">
         <v>19</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="7" t="s">
         <v>125</v>
       </c>
       <c r="D20" s="2">
         <v>0.603022689</v>
       </c>
-      <c r="E20" s="3">
+      <c r="E20" s="9">
         <v>0.30151134499999999</v>
       </c>
       <c r="F20" s="2">
         <v>0</v>
       </c>
-      <c r="G20" s="3">
+      <c r="G20" s="9">
         <v>0</v>
       </c>
       <c r="H20" s="2">
         <v>0.603022689</v>
       </c>
-      <c r="I20" s="3">
+      <c r="I20" s="9">
         <v>0.30151134499999999</v>
       </c>
       <c r="J20" s="2">
         <v>0.30151134499999999</v>
       </c>
       <c r="K20" s="6" t="s">
-        <v>359</v>
-      </c>
-      <c r="L20" t="s">
+        <v>353</v>
+      </c>
+      <c r="L20" s="7" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="18">
+    <row r="21" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A21" s="1">
         <v>20</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="7" t="s">
         <v>126</v>
       </c>
       <c r="D21" s="2">
         <v>0</v>
       </c>
-      <c r="E21" s="3">
+      <c r="E21" s="9">
         <v>0.23570226</v>
       </c>
       <c r="F21" s="2">
         <v>0</v>
       </c>
-      <c r="G21" s="3">
+      <c r="G21" s="9">
         <v>0</v>
       </c>
       <c r="H21" s="2">
         <v>0.47140452100000002</v>
       </c>
-      <c r="I21" s="3">
+      <c r="I21" s="9">
         <v>0.47140452100000002</v>
       </c>
       <c r="J21" s="2">
         <v>0.70710678100000002</v>
       </c>
       <c r="K21" s="6" t="s">
-        <v>360</v>
-      </c>
-      <c r="L21" t="s">
+        <v>339</v>
+      </c>
+      <c r="L21" s="7" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="18">
+    <row r="22" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A22" s="1">
         <v>21</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="7" t="s">
         <v>127</v>
       </c>
       <c r="D22" s="2">
         <v>0</v>
       </c>
-      <c r="E22" s="3">
+      <c r="E22" s="9">
         <v>0</v>
       </c>
       <c r="F22" s="2">
         <v>0</v>
       </c>
-      <c r="G22" s="3">
+      <c r="G22" s="9">
         <v>0</v>
       </c>
       <c r="H22" s="2">
         <v>0.688247202</v>
       </c>
-      <c r="I22" s="3">
+      <c r="I22" s="9">
         <v>0.22941573400000001</v>
       </c>
       <c r="J22" s="2">
         <v>0.688247202</v>
       </c>
       <c r="K22" s="6" t="s">
-        <v>361</v>
-      </c>
-      <c r="L22" t="s">
+        <v>340</v>
+      </c>
+      <c r="L22" s="7" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="28">
+    <row r="23" spans="1:12" s="7" customFormat="1" ht="28">
       <c r="A23" s="1">
         <v>22</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="7" t="s">
         <v>128</v>
       </c>
       <c r="D23" s="2">
         <v>0</v>
       </c>
-      <c r="E23" s="3">
+      <c r="E23" s="9">
         <v>0.48507125000000001</v>
       </c>
       <c r="F23" s="2">
         <v>0</v>
       </c>
-      <c r="G23" s="3">
+      <c r="G23" s="9">
         <v>0</v>
       </c>
       <c r="H23" s="2">
         <v>0</v>
       </c>
-      <c r="I23" s="3">
+      <c r="I23" s="9">
         <v>0.72760687499999999</v>
       </c>
       <c r="J23" s="2">
         <v>0.48507125000000001</v>
       </c>
       <c r="K23" s="6" t="s">
-        <v>362</v>
-      </c>
-      <c r="L23" t="s">
+        <v>341</v>
+      </c>
+      <c r="L23" s="7" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="18">
+    <row r="24" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A24" s="1">
         <v>23</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B24" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" s="7" t="s">
         <v>129</v>
       </c>
       <c r="D24" s="2">
         <v>0</v>
       </c>
-      <c r="E24" s="3">
+      <c r="E24" s="9">
         <v>0.51639777899999995</v>
       </c>
       <c r="F24" s="2">
         <v>0</v>
       </c>
-      <c r="G24" s="3">
+      <c r="G24" s="9">
         <v>0.25819889000000001</v>
       </c>
       <c r="H24" s="2">
         <v>0</v>
       </c>
-      <c r="I24" s="3">
+      <c r="I24" s="9">
         <v>0.77459666900000002</v>
       </c>
       <c r="J24" s="2">
         <v>0.25819889000000001</v>
       </c>
       <c r="K24" s="6" t="s">
-        <v>363</v>
-      </c>
-      <c r="L24" t="s">
+        <v>342</v>
+      </c>
+      <c r="L24" s="7" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="18">
+    <row r="25" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A25" s="1">
         <v>24</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C25" s="7" t="s">
         <v>130</v>
       </c>
       <c r="D25" s="2">
         <v>0</v>
       </c>
-      <c r="E25" s="3">
+      <c r="E25" s="9">
         <v>0</v>
       </c>
       <c r="F25" s="2">
         <v>0</v>
       </c>
-      <c r="G25" s="3">
+      <c r="G25" s="9">
         <v>0</v>
       </c>
       <c r="H25" s="2">
         <v>0.57735026899999997</v>
       </c>
-      <c r="I25" s="3">
+      <c r="I25" s="9">
         <v>0.57735026899999997</v>
       </c>
       <c r="J25" s="2">
         <v>0.57735026899999997</v>
       </c>
       <c r="K25" s="6" t="s">
-        <v>364</v>
-      </c>
-      <c r="L25" t="s">
+        <v>343</v>
+      </c>
+      <c r="L25" s="7" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="18">
+    <row r="26" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A26" s="1">
         <v>25</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C26" s="7" t="s">
         <v>131</v>
       </c>
       <c r="D26" s="2">
         <v>0</v>
       </c>
-      <c r="E26" s="3">
+      <c r="E26" s="9">
         <v>0.46852128599999998</v>
       </c>
       <c r="F26" s="2">
         <v>0</v>
       </c>
-      <c r="G26" s="3">
+      <c r="G26" s="9">
         <v>0</v>
       </c>
       <c r="H26" s="2">
         <v>0</v>
       </c>
-      <c r="I26" s="3">
+      <c r="I26" s="9">
         <v>0.62469504799999998</v>
       </c>
       <c r="J26" s="2">
         <v>0.62469504799999998</v>
       </c>
       <c r="K26" s="6" t="s">
-        <v>365</v>
-      </c>
-      <c r="L26" t="s">
+        <v>344</v>
+      </c>
+      <c r="L26" s="7" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="27" spans="1:12" ht="18">
+    <row r="27" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A27" s="1">
         <v>26</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B27" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C27" s="7" t="s">
         <v>132</v>
       </c>
       <c r="D27" s="2">
         <v>0.36927447299999999</v>
       </c>
-      <c r="E27" s="3">
+      <c r="E27" s="9">
         <v>0.36927447299999999</v>
       </c>
       <c r="F27" s="2">
         <v>0.49236596399999999</v>
       </c>
-      <c r="G27" s="3">
+      <c r="G27" s="9">
         <v>0.49236596399999999</v>
       </c>
       <c r="H27" s="2">
         <v>0</v>
       </c>
-      <c r="I27" s="3">
+      <c r="I27" s="9">
         <v>0.49236596399999999</v>
       </c>
       <c r="J27" s="2">
         <v>0</v>
       </c>
       <c r="K27" s="6" t="s">
-        <v>366</v>
-      </c>
-      <c r="L27" t="s">
+        <v>354</v>
+      </c>
+      <c r="L27" s="7" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="18">
+    <row r="28" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A28" s="1">
         <v>27</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B28" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C28" s="7" t="s">
         <v>133</v>
       </c>
       <c r="D28" s="2">
         <v>0</v>
       </c>
-      <c r="E28" s="3">
+      <c r="E28" s="9">
         <v>0</v>
       </c>
       <c r="F28" s="2">
         <v>0</v>
       </c>
-      <c r="G28" s="3">
+      <c r="G28" s="9">
         <v>0</v>
       </c>
       <c r="H28" s="2">
         <v>0.58834840499999996</v>
       </c>
-      <c r="I28" s="3">
+      <c r="I28" s="9">
         <v>0.196116135</v>
       </c>
       <c r="J28" s="2">
         <v>0.78446454099999996</v>
       </c>
       <c r="K28" s="6" t="s">
-        <v>367</v>
-      </c>
-      <c r="L28" t="s">
+        <v>345</v>
+      </c>
+      <c r="L28" s="7" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="29" spans="1:12" ht="18">
+    <row r="29" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A29" s="1">
         <v>28</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B29" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C29" s="7" t="s">
         <v>134</v>
       </c>
       <c r="D29" s="2">
         <v>0</v>
       </c>
-      <c r="E29" s="3">
+      <c r="E29" s="9">
         <v>0.70710678118654746</v>
       </c>
       <c r="F29" s="2">
         <v>0</v>
       </c>
-      <c r="G29" s="3">
+      <c r="G29" s="9">
         <v>0</v>
       </c>
       <c r="H29" s="2">
         <v>0</v>
       </c>
-      <c r="I29" s="3">
+      <c r="I29" s="9">
         <v>0.70710678118654746</v>
       </c>
       <c r="J29" s="2">
         <v>0</v>
       </c>
       <c r="K29" s="6" t="s">
-        <v>368</v>
-      </c>
-      <c r="L29" t="s">
+        <v>346</v>
+      </c>
+      <c r="L29" s="7" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="18">
+    <row r="30" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A30" s="1">
         <v>29</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="B30" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C30" s="7" t="s">
         <v>135</v>
       </c>
       <c r="D30" s="2">
         <v>0</v>
       </c>
-      <c r="E30" s="3">
+      <c r="E30" s="9">
         <v>0.55470019599999998</v>
       </c>
       <c r="F30" s="2">
         <v>0</v>
       </c>
-      <c r="G30" s="3">
+      <c r="G30" s="9">
         <v>0</v>
       </c>
       <c r="H30" s="2">
         <v>0.27735009799999999</v>
       </c>
-      <c r="I30" s="3">
+      <c r="I30" s="9">
         <v>0.55470019599999998</v>
       </c>
       <c r="J30" s="2">
         <v>0.55470019599999998</v>
       </c>
       <c r="K30" s="6" t="s">
-        <v>369</v>
-      </c>
-      <c r="L30" t="s">
+        <v>347</v>
+      </c>
+      <c r="L30" s="7" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="31" spans="1:12" ht="18">
+    <row r="31" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A31" s="1">
         <v>30</v>
       </c>
-      <c r="B31" s="5" t="s">
+      <c r="B31" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C31" s="7" t="s">
         <v>136</v>
       </c>
       <c r="D31" s="2">
         <v>0.52981294300000004</v>
       </c>
-      <c r="E31" s="3">
+      <c r="E31" s="9">
         <v>0.52981294300000004</v>
       </c>
       <c r="F31" s="2">
         <v>0</v>
       </c>
-      <c r="G31" s="3">
+      <c r="G31" s="9">
         <v>0</v>
       </c>
       <c r="H31" s="2">
         <v>0.52981294300000004</v>
       </c>
-      <c r="I31" s="3">
+      <c r="I31" s="9">
         <v>0.39735970700000001</v>
       </c>
       <c r="J31" s="2">
         <v>0</v>
       </c>
       <c r="K31" s="6" t="s">
-        <v>370</v>
-      </c>
-      <c r="L31" t="s">
+        <v>348</v>
+      </c>
+      <c r="L31" s="7" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="32" spans="1:12" ht="18">
+    <row r="32" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A32" s="1">
         <v>31</v>
       </c>
-      <c r="B32" s="5" t="s">
+      <c r="B32" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C32" s="7" t="s">
         <v>137</v>
       </c>
       <c r="D32" s="2">
         <v>0</v>
       </c>
-      <c r="E32" s="3">
+      <c r="E32" s="9">
         <v>0</v>
       </c>
       <c r="F32" s="2">
         <v>0</v>
       </c>
-      <c r="G32" s="3">
+      <c r="G32" s="9">
         <v>0</v>
       </c>
       <c r="H32" s="2">
         <v>0.688247202</v>
       </c>
-      <c r="I32" s="3">
+      <c r="I32" s="9">
         <v>0.22941573400000001</v>
       </c>
       <c r="J32" s="2">
         <v>0.688247202</v>
       </c>
-      <c r="K32" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="L32" t="s">
+      <c r="K32" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="L32" s="7" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="18">
+    <row r="33" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A33" s="1">
         <v>32</v>
       </c>
-      <c r="B33" s="5" t="s">
+      <c r="B33" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C33" s="7" t="s">
         <v>138</v>
       </c>
       <c r="D33" s="2">
         <v>0</v>
       </c>
-      <c r="E33" s="3">
+      <c r="E33" s="9">
         <v>0.70710678100000002</v>
       </c>
       <c r="F33" s="2">
         <v>0</v>
       </c>
-      <c r="G33" s="3">
+      <c r="G33" s="9">
         <v>0.35355339099999999</v>
       </c>
       <c r="H33" s="2">
         <v>0.35355339099999999</v>
       </c>
-      <c r="I33" s="3">
+      <c r="I33" s="9">
         <v>0.35355339099999999</v>
       </c>
       <c r="J33" s="2">
         <v>0.35355339099999999</v>
       </c>
-      <c r="K33" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="L33" t="s">
+      <c r="K33" s="6" t="s">
+        <v>356</v>
+      </c>
+      <c r="L33" s="7" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="34" spans="1:12" ht="18">
+    <row r="34" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A34" s="1">
         <v>33</v>
       </c>
-      <c r="B34" s="5" t="s">
+      <c r="B34" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C34" s="7" t="s">
         <v>139</v>
       </c>
       <c r="D34" s="2">
         <v>0.55470019599999998</v>
       </c>
-      <c r="E34" s="3">
+      <c r="E34" s="9">
         <v>0</v>
       </c>
       <c r="F34" s="2">
         <v>0</v>
       </c>
-      <c r="G34" s="3">
+      <c r="G34" s="9">
         <v>0</v>
       </c>
       <c r="H34" s="2">
         <v>0.55470019599999998</v>
       </c>
-      <c r="I34" s="3">
+      <c r="I34" s="9">
         <v>0.27735009799999999</v>
       </c>
       <c r="J34" s="2">
         <v>0.55470019599999998</v>
       </c>
-      <c r="K34" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="L34" t="s">
+      <c r="K34" s="6" t="s">
+        <v>357</v>
+      </c>
+      <c r="L34" s="7" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="35" spans="1:12" ht="18">
+    <row r="35" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A35" s="1">
         <v>34</v>
       </c>
-      <c r="B35" s="5" t="s">
+      <c r="B35" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C35" s="7" t="s">
         <v>140</v>
       </c>
       <c r="D35" s="2">
         <v>0.53452248400000002</v>
       </c>
-      <c r="E35" s="3">
+      <c r="E35" s="9">
         <v>0.53452248400000002</v>
       </c>
       <c r="F35" s="2">
         <v>0</v>
       </c>
-      <c r="G35" s="3">
+      <c r="G35" s="9">
         <v>0</v>
       </c>
       <c r="H35" s="2">
         <v>0.26726124200000001</v>
       </c>
-      <c r="I35" s="3">
+      <c r="I35" s="9">
         <v>0.53452248400000002</v>
       </c>
       <c r="J35" s="2">
         <v>0.26726124200000001</v>
       </c>
-      <c r="K35" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="L35" t="s">
+      <c r="K35" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="L35" s="7" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="36" spans="1:12" ht="18">
+    <row r="36" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A36" s="1">
         <v>35</v>
       </c>
-      <c r="B36" s="5" t="s">
+      <c r="B36" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C36" s="7" t="s">
         <v>141</v>
       </c>
       <c r="D36" s="2">
         <v>0</v>
       </c>
-      <c r="E36" s="3">
+      <c r="E36" s="9">
         <v>0</v>
       </c>
       <c r="F36" s="2">
         <v>0</v>
       </c>
-      <c r="G36" s="3">
+      <c r="G36" s="9">
         <v>0</v>
       </c>
       <c r="H36" s="2">
         <v>0.80178372600000003</v>
       </c>
-      <c r="I36" s="3">
+      <c r="I36" s="9">
         <v>0.26726124200000001</v>
       </c>
       <c r="J36" s="2">
         <v>0.53452248400000002</v>
       </c>
-      <c r="K36" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="L36" t="s">
+      <c r="K36" s="6" t="s">
+        <v>359</v>
+      </c>
+      <c r="L36" s="7" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="37" spans="1:12" ht="18">
+    <row r="37" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A37" s="1">
         <v>36</v>
       </c>
-      <c r="B37" s="5" t="s">
+      <c r="B37" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="C37" t="s">
+      <c r="C37" s="7" t="s">
         <v>142</v>
       </c>
       <c r="D37" s="2">
         <v>0.21320071600000001</v>
       </c>
-      <c r="E37" s="3">
+      <c r="E37" s="9">
         <v>0.426401433</v>
       </c>
       <c r="F37" s="2">
         <v>0</v>
       </c>
-      <c r="G37" s="3">
+      <c r="G37" s="9">
         <v>0</v>
       </c>
       <c r="H37" s="2">
         <v>0.63960214900000001</v>
       </c>
-      <c r="I37" s="3">
+      <c r="I37" s="9">
         <v>0.426401433</v>
       </c>
       <c r="J37" s="2">
         <v>0.426401433</v>
       </c>
-      <c r="K37" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="L37" t="s">
+      <c r="K37" s="6" t="s">
+        <v>360</v>
+      </c>
+      <c r="L37" s="7" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="38" spans="1:12" ht="18">
+    <row r="38" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A38" s="1">
         <v>37</v>
       </c>
-      <c r="B38" s="5" t="s">
+      <c r="B38" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C38" s="7" t="s">
         <v>143</v>
       </c>
       <c r="D38" s="2">
         <v>0</v>
       </c>
-      <c r="E38" s="3">
+      <c r="E38" s="9">
         <v>0.66666666699999999</v>
       </c>
       <c r="F38" s="2">
         <v>0</v>
       </c>
-      <c r="G38" s="3">
+      <c r="G38" s="9">
         <v>0.33333333300000001</v>
       </c>
       <c r="H38" s="2">
         <v>0</v>
       </c>
-      <c r="I38" s="3">
+      <c r="I38" s="9">
         <v>0.66666666699999999</v>
       </c>
       <c r="J38" s="2">
         <v>0</v>
       </c>
-      <c r="K38" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="L38" t="s">
+      <c r="K38" s="6" t="s">
+        <v>361</v>
+      </c>
+      <c r="L38" s="7" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="39" spans="1:12" ht="18">
+    <row r="39" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A39" s="1">
         <v>38</v>
       </c>
-      <c r="B39" s="5" t="s">
+      <c r="B39" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="C39" t="s">
+      <c r="C39" s="7" t="s">
         <v>144</v>
       </c>
       <c r="D39" s="2">
         <v>0</v>
       </c>
-      <c r="E39" s="3">
+      <c r="E39" s="9">
         <v>0.28867513500000003</v>
       </c>
       <c r="F39" s="2">
         <v>0</v>
       </c>
-      <c r="G39" s="3">
+      <c r="G39" s="9">
         <v>0.28867513500000003</v>
       </c>
       <c r="H39" s="2">
         <v>0.28867513500000003</v>
       </c>
-      <c r="I39" s="3">
+      <c r="I39" s="9">
         <v>0.86602540400000005</v>
       </c>
       <c r="J39" s="2">
         <v>0</v>
       </c>
-      <c r="K39" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="L39" t="s">
+      <c r="K39" s="6" t="s">
+        <v>362</v>
+      </c>
+      <c r="L39" s="7" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="40" spans="1:12" ht="18">
+    <row r="40" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A40" s="1">
         <v>39</v>
       </c>
-      <c r="B40" s="5" t="s">
+      <c r="B40" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="C40" t="s">
+      <c r="C40" s="7" t="s">
         <v>145</v>
       </c>
       <c r="D40" s="2">
         <v>0</v>
       </c>
-      <c r="E40" s="3">
+      <c r="E40" s="9">
         <v>0</v>
       </c>
       <c r="F40" s="2">
         <v>0</v>
       </c>
-      <c r="G40" s="3">
+      <c r="G40" s="9">
         <v>0</v>
       </c>
       <c r="H40" s="2">
         <v>0.57735026899999997</v>
       </c>
-      <c r="I40" s="3">
+      <c r="I40" s="9">
         <v>0.57735026899999997</v>
       </c>
       <c r="J40" s="2">
         <v>0.57735026899999997</v>
       </c>
-      <c r="K40" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="L40" t="s">
+      <c r="K40" s="6" t="s">
+        <v>363</v>
+      </c>
+      <c r="L40" s="7" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="41" spans="1:12" ht="24">
+    <row r="41" spans="1:12" s="7" customFormat="1" ht="24">
       <c r="A41" s="1">
         <v>40</v>
       </c>
-      <c r="B41" s="5" t="s">
+      <c r="B41" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="C41" t="s">
+      <c r="C41" s="7" t="s">
         <v>146</v>
       </c>
       <c r="D41" s="2">
         <v>0</v>
       </c>
-      <c r="E41" s="3">
+      <c r="E41" s="9">
         <v>0</v>
       </c>
       <c r="F41" s="2">
         <v>0</v>
       </c>
-      <c r="G41" s="3">
+      <c r="G41" s="9">
         <v>0</v>
       </c>
       <c r="H41" s="2">
         <v>0.80178372600000003</v>
       </c>
-      <c r="I41" s="3">
+      <c r="I41" s="9">
         <v>0.26726124200000001</v>
       </c>
       <c r="J41" s="2">
         <v>0.53452248400000002</v>
       </c>
-      <c r="K41" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="L41" t="s">
+      <c r="K41" s="6" t="s">
+        <v>364</v>
+      </c>
+      <c r="L41" s="7" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="42" spans="1:12" ht="18">
+    <row r="42" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A42" s="1">
         <v>41</v>
       </c>
-      <c r="B42" s="5" t="s">
+      <c r="B42" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="C42" t="s">
+      <c r="C42" s="7" t="s">
         <v>147</v>
       </c>
       <c r="D42" s="2">
         <v>0.23570226</v>
       </c>
-      <c r="E42" s="3">
+      <c r="E42" s="9">
         <v>0.70710678100000002</v>
       </c>
       <c r="F42" s="2">
         <v>0.23570226</v>
       </c>
-      <c r="G42" s="3">
+      <c r="G42" s="9">
         <v>0.23570226</v>
       </c>
       <c r="H42" s="2">
         <v>0.23570226</v>
       </c>
-      <c r="I42" s="3">
+      <c r="I42" s="9">
         <v>0.47140452100000002</v>
       </c>
       <c r="J42" s="2">
         <v>0.23570226</v>
       </c>
-      <c r="K42" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="L42" t="s">
+      <c r="K42" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="L42" s="7" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="43" spans="1:12" ht="18">
+    <row r="43" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A43" s="1">
         <v>42</v>
       </c>
-      <c r="B43" s="5" t="s">
+      <c r="B43" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="C43" t="s">
+      <c r="C43" s="7" t="s">
         <v>148</v>
       </c>
       <c r="D43" s="2">
         <v>0.182574186</v>
       </c>
-      <c r="E43" s="3">
+      <c r="E43" s="9">
         <v>0</v>
       </c>
       <c r="F43" s="2">
         <v>0</v>
       </c>
-      <c r="G43" s="3">
+      <c r="G43" s="9">
         <v>0</v>
       </c>
       <c r="H43" s="2">
         <v>0.54772255800000003</v>
       </c>
-      <c r="I43" s="3">
+      <c r="I43" s="9">
         <v>0.73029674300000003</v>
       </c>
       <c r="J43" s="2">
         <v>0.365148372</v>
       </c>
-      <c r="K43" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="L43" t="s">
+      <c r="K43" s="6" t="s">
+        <v>366</v>
+      </c>
+      <c r="L43" s="7" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="44" spans="1:12" ht="18">
+    <row r="44" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A44" s="1">
         <v>43</v>
       </c>
-      <c r="B44" s="5" t="s">
+      <c r="B44" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="C44" t="s">
+      <c r="C44" s="7" t="s">
         <v>149</v>
       </c>
       <c r="D44" s="2">
         <v>0.57735026899999997</v>
       </c>
-      <c r="E44" s="3">
+      <c r="E44" s="9">
         <v>0</v>
       </c>
       <c r="F44" s="2">
         <v>0</v>
       </c>
-      <c r="G44" s="3">
+      <c r="G44" s="9">
         <v>0</v>
       </c>
       <c r="H44" s="2">
         <v>0.57735026899999997</v>
       </c>
-      <c r="I44" s="3">
+      <c r="I44" s="9">
         <v>0</v>
       </c>
       <c r="J44" s="2">
         <v>0.57735026899999997</v>
       </c>
-      <c r="K44" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="L44" t="s">
+      <c r="K44" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="L44" s="7" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="45" spans="1:12" ht="18">
+    <row r="45" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A45" s="1">
         <v>44</v>
       </c>
-      <c r="B45" s="5" t="s">
+      <c r="B45" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="C45" t="s">
+      <c r="C45" s="7" t="s">
         <v>150</v>
       </c>
       <c r="D45" s="2">
         <v>0.89442719100000001</v>
       </c>
-      <c r="E45" s="3">
+      <c r="E45" s="9">
         <v>0.44721359500000002</v>
       </c>
       <c r="F45" s="2">
         <v>0</v>
       </c>
-      <c r="G45" s="3">
+      <c r="G45" s="9">
         <v>0</v>
       </c>
       <c r="H45" s="2">
         <v>0</v>
       </c>
-      <c r="I45" s="3">
+      <c r="I45" s="9">
         <v>0</v>
       </c>
       <c r="J45" s="2">
         <v>0</v>
       </c>
-      <c r="K45" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="L45" t="s">
+      <c r="K45" s="6" t="s">
+        <v>368</v>
+      </c>
+      <c r="L45" s="7" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="46" spans="1:12" ht="18">
+    <row r="46" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A46" s="1">
         <v>45</v>
       </c>
-      <c r="B46" s="5" t="s">
+      <c r="B46" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="C46" t="s">
+      <c r="C46" s="7" t="s">
         <v>151</v>
       </c>
       <c r="D46" s="2">
         <v>0</v>
       </c>
-      <c r="E46" s="3">
+      <c r="E46" s="9">
         <v>0</v>
       </c>
       <c r="F46" s="2">
         <v>0</v>
       </c>
-      <c r="G46" s="3">
+      <c r="G46" s="9">
         <v>0</v>
       </c>
       <c r="H46" s="2">
         <v>0.70710678100000002</v>
       </c>
-      <c r="I46" s="3">
+      <c r="I46" s="9">
         <v>0.70710678100000002</v>
       </c>
       <c r="J46" s="2">
         <v>0</v>
       </c>
-      <c r="K46" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="L46" t="s">
+      <c r="K46" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="L46" s="7" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="47" spans="1:12" ht="18">
+    <row r="47" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A47" s="1">
         <v>46</v>
       </c>
-      <c r="B47" s="5" t="s">
+      <c r="B47" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="C47" t="s">
+      <c r="C47" s="7" t="s">
         <v>152</v>
       </c>
       <c r="D47" s="2">
         <v>0.25819889000000001</v>
       </c>
-      <c r="E47" s="3">
+      <c r="E47" s="9">
         <v>0.51639777899999995</v>
       </c>
       <c r="F47" s="2">
         <v>0.25819889000000001</v>
       </c>
-      <c r="G47" s="3">
+      <c r="G47" s="9">
         <v>0.25819889000000001</v>
       </c>
       <c r="H47" s="2">
         <v>0.51639777899999995</v>
       </c>
-      <c r="I47" s="3">
+      <c r="I47" s="9">
         <v>0.51639777899999995</v>
       </c>
       <c r="J47" s="2">
         <v>0</v>
       </c>
-      <c r="K47" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="L47" t="s">
+      <c r="K47" s="6" t="s">
+        <v>370</v>
+      </c>
+      <c r="L47" s="7" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="48" spans="1:12" ht="18">
+    <row r="48" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A48" s="1">
         <v>47</v>
       </c>
-      <c r="B48" s="5" t="s">
+      <c r="B48" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="C48" t="s">
+      <c r="C48" s="7" t="s">
         <v>153</v>
       </c>
       <c r="D48" s="2">
         <v>0.25</v>
       </c>
-      <c r="E48" s="3">
+      <c r="E48" s="9">
         <v>0.25</v>
       </c>
       <c r="F48" s="2">
         <v>0</v>
       </c>
-      <c r="G48" s="3">
+      <c r="G48" s="9">
         <v>0</v>
       </c>
       <c r="H48" s="2">
         <v>0.75</v>
       </c>
-      <c r="I48" s="3">
+      <c r="I48" s="9">
         <v>0.25</v>
       </c>
       <c r="J48" s="2">
         <v>0.5</v>
       </c>
-      <c r="K48" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="L48" t="s">
+      <c r="K48" s="6" t="s">
+        <v>371</v>
+      </c>
+      <c r="L48" s="7" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="49" spans="1:12" ht="18">
+    <row r="49" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A49" s="1">
         <v>48</v>
       </c>
-      <c r="B49" s="5" t="s">
+      <c r="B49" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="C49" t="s">
+      <c r="C49" s="7" t="s">
         <v>154</v>
       </c>
       <c r="D49" s="2">
         <v>0</v>
       </c>
-      <c r="E49" s="3">
+      <c r="E49" s="9">
         <v>0</v>
       </c>
       <c r="F49" s="2">
         <v>0</v>
       </c>
-      <c r="G49" s="3">
+      <c r="G49" s="9">
         <v>0</v>
       </c>
       <c r="H49" s="2">
         <v>0.69631062399999999</v>
       </c>
-      <c r="I49" s="3">
+      <c r="I49" s="9">
         <v>0.69631062399999999</v>
       </c>
       <c r="J49" s="2">
         <v>0.174077656</v>
       </c>
-      <c r="K49" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="L49" t="s">
+      <c r="K49" s="6" t="s">
+        <v>372</v>
+      </c>
+      <c r="L49" s="7" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="50" spans="1:12" ht="21">
+    <row r="50" spans="1:12" s="7" customFormat="1" ht="21">
       <c r="A50" s="1">
         <v>49</v>
       </c>
-      <c r="B50" s="5" t="s">
+      <c r="B50" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="C50" t="s">
+      <c r="C50" s="7" t="s">
         <v>155</v>
       </c>
       <c r="D50" s="2">
         <v>0</v>
       </c>
-      <c r="E50" s="3">
+      <c r="E50" s="9">
         <v>0</v>
       </c>
       <c r="F50" s="2">
         <v>0</v>
       </c>
-      <c r="G50" s="3">
+      <c r="G50" s="9">
         <v>0</v>
       </c>
       <c r="H50" s="2">
         <v>0.69631062399999999</v>
       </c>
-      <c r="I50" s="3">
+      <c r="I50" s="9">
         <v>0.69631062399999999</v>
       </c>
       <c r="J50" s="2">
         <v>0.174077656</v>
       </c>
-      <c r="K50" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="L50" t="s">
+      <c r="K50" s="6" t="s">
+        <v>372</v>
+      </c>
+      <c r="L50" s="7" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="51" spans="1:12" ht="18">
+    <row r="51" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A51" s="1">
         <v>50</v>
       </c>
-      <c r="B51" s="5" t="s">
+      <c r="B51" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="C51" t="s">
+      <c r="C51" s="7" t="s">
         <v>156</v>
       </c>
       <c r="D51" s="2">
         <v>0.55470019599999998</v>
       </c>
-      <c r="E51" s="3">
+      <c r="E51" s="9">
         <v>0</v>
       </c>
       <c r="F51" s="2">
         <v>0</v>
       </c>
-      <c r="G51" s="3">
+      <c r="G51" s="9">
         <v>0.55470019599999998</v>
       </c>
       <c r="H51" s="2">
         <v>0.55470019599999998</v>
       </c>
-      <c r="I51" s="3">
+      <c r="I51" s="9">
         <v>0</v>
       </c>
       <c r="J51" s="2">
         <v>0.27735009799999999</v>
       </c>
-      <c r="K51" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="L51" t="s">
+      <c r="K51" s="6" t="s">
+        <v>373</v>
+      </c>
+      <c r="L51" s="7" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="52" spans="1:12" ht="18">
+    <row r="52" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A52" s="1">
         <v>51</v>
       </c>
-      <c r="B52" s="5" t="s">
+      <c r="B52" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="C52" t="s">
+      <c r="C52" s="7" t="s">
         <v>157</v>
       </c>
       <c r="D52" s="2">
         <v>0</v>
       </c>
-      <c r="E52" s="3">
+      <c r="E52" s="9">
         <v>0</v>
       </c>
       <c r="F52" s="2">
         <v>0</v>
       </c>
-      <c r="G52" s="3">
+      <c r="G52" s="9">
         <v>0</v>
       </c>
       <c r="H52" s="2">
         <v>0.26726124200000001</v>
       </c>
-      <c r="I52" s="3">
+      <c r="I52" s="9">
         <v>0.53452248400000002</v>
       </c>
       <c r="J52" s="2">
         <v>0.80178372600000003</v>
       </c>
-      <c r="K52" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="L52" t="s">
+      <c r="K52" s="6" t="s">
+        <v>374</v>
+      </c>
+      <c r="L52" s="7" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="53" spans="1:12" ht="18">
+    <row r="53" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A53" s="1">
         <v>52</v>
       </c>
-      <c r="B53" s="5" t="s">
+      <c r="B53" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="C53" t="s">
+      <c r="C53" s="7" t="s">
         <v>158</v>
       </c>
       <c r="D53" s="2">
         <v>0</v>
       </c>
-      <c r="E53" s="3">
+      <c r="E53" s="9">
         <v>0</v>
       </c>
       <c r="F53" s="2">
         <v>0</v>
       </c>
-      <c r="G53" s="3">
+      <c r="G53" s="9">
         <v>0</v>
       </c>
       <c r="H53" s="2">
         <v>0.514495755</v>
       </c>
-      <c r="I53" s="3">
+      <c r="I53" s="9">
         <v>0.68599434100000001</v>
       </c>
       <c r="J53" s="2">
         <v>0.514495755</v>
       </c>
-      <c r="K53" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="L53" t="s">
+      <c r="K53" s="6" t="s">
+        <v>375</v>
+      </c>
+      <c r="L53" s="7" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="54" spans="1:12" ht="18">
+    <row r="54" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A54" s="1">
         <v>53</v>
       </c>
-      <c r="B54" s="5" t="s">
+      <c r="B54" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="C54" t="s">
+      <c r="C54" s="7" t="s">
         <v>159</v>
       </c>
       <c r="D54" s="2">
         <v>0</v>
       </c>
-      <c r="E54" s="3">
+      <c r="E54" s="9">
         <v>0</v>
       </c>
       <c r="F54" s="2">
         <v>0</v>
       </c>
-      <c r="G54" s="3">
+      <c r="G54" s="9">
         <v>0</v>
       </c>
       <c r="H54" s="2">
         <v>0.514495755</v>
       </c>
-      <c r="I54" s="3">
+      <c r="I54" s="9">
         <v>0.68599434100000001</v>
       </c>
       <c r="J54" s="2">
         <v>0.514495755</v>
       </c>
-      <c r="K54" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="L54" t="s">
+      <c r="K54" s="6" t="s">
+        <v>384</v>
+      </c>
+      <c r="L54" s="7" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="55" spans="1:12" ht="18">
+    <row r="55" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A55" s="1">
         <v>54</v>
       </c>
-      <c r="B55" s="5" t="s">
+      <c r="B55" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="C55" t="s">
+      <c r="C55" s="7" t="s">
         <v>160</v>
       </c>
       <c r="D55" s="2">
         <v>0</v>
       </c>
-      <c r="E55" s="3">
+      <c r="E55" s="9">
         <v>0</v>
       </c>
       <c r="F55" s="2">
         <v>0</v>
       </c>
-      <c r="G55" s="3">
+      <c r="G55" s="9">
         <v>0</v>
       </c>
       <c r="H55" s="2">
         <v>0.63960214900000001</v>
       </c>
-      <c r="I55" s="3">
+      <c r="I55" s="9">
         <v>0.426401433</v>
       </c>
       <c r="J55" s="2">
         <v>0.63960214900000001</v>
       </c>
-      <c r="K55" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="L55" t="s">
+      <c r="K55" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="L55" s="7" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="56" spans="1:12" ht="18">
+    <row r="56" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A56" s="1">
         <v>55</v>
       </c>
-      <c r="B56" s="5" t="s">
+      <c r="B56" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="C56" t="s">
+      <c r="C56" s="7" t="s">
         <v>161</v>
       </c>
       <c r="D56" s="2">
         <v>0</v>
       </c>
-      <c r="E56" s="3">
+      <c r="E56" s="9">
         <v>0</v>
       </c>
       <c r="F56" s="2">
         <v>0</v>
       </c>
-      <c r="G56" s="3">
+      <c r="G56" s="9">
         <v>0</v>
       </c>
       <c r="H56" s="2">
         <v>0.514495755</v>
       </c>
-      <c r="I56" s="3">
+      <c r="I56" s="9">
         <v>0.514495755</v>
       </c>
       <c r="J56" s="2">
         <v>0.68599434100000001</v>
       </c>
-      <c r="K56" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="L56" t="s">
+      <c r="K56" s="6" t="s">
+        <v>377</v>
+      </c>
+      <c r="L56" s="7" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="57" spans="1:12" ht="18">
+    <row r="57" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A57" s="1">
         <v>56</v>
       </c>
-      <c r="B57" s="5" t="s">
+      <c r="B57" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="C57" t="s">
+      <c r="C57" s="7" t="s">
         <v>162</v>
       </c>
       <c r="D57" s="2">
         <v>0</v>
       </c>
-      <c r="E57" s="3">
+      <c r="E57" s="9">
         <v>0.23570226</v>
       </c>
       <c r="F57" s="2">
         <v>0</v>
       </c>
-      <c r="G57" s="3">
+      <c r="G57" s="9">
         <v>0</v>
       </c>
       <c r="H57" s="2">
         <v>0.70710678100000002</v>
       </c>
-      <c r="I57" s="3">
+      <c r="I57" s="9">
         <v>0.47140452100000002</v>
       </c>
       <c r="J57" s="2">
         <v>0.47140452100000002</v>
       </c>
-      <c r="K57" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="L57" t="s">
+      <c r="K57" s="6" t="s">
+        <v>378</v>
+      </c>
+      <c r="L57" s="7" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="58" spans="1:12" ht="18">
+    <row r="58" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A58" s="1">
         <v>57</v>
       </c>
-      <c r="B58" s="5" t="s">
+      <c r="B58" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="C58" t="s">
+      <c r="C58" s="7" t="s">
         <v>163</v>
       </c>
       <c r="D58" s="2">
         <v>0</v>
       </c>
-      <c r="E58" s="3">
+      <c r="E58" s="9">
         <v>0</v>
       </c>
       <c r="F58" s="2">
         <v>0</v>
       </c>
-      <c r="G58" s="3">
+      <c r="G58" s="9">
         <v>0</v>
       </c>
       <c r="H58" s="2">
         <v>0</v>
       </c>
-      <c r="I58" s="3">
+      <c r="I58" s="9">
         <v>1</v>
       </c>
       <c r="J58" s="2">
         <v>0</v>
       </c>
-      <c r="K58" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="L58" t="s">
+      <c r="K58" s="6" t="s">
+        <v>379</v>
+      </c>
+      <c r="L58" s="7" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="59" spans="1:12" ht="18">
+    <row r="59" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A59" s="1">
         <v>58</v>
       </c>
-      <c r="B59" s="5" t="s">
+      <c r="B59" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="C59" t="s">
+      <c r="C59" s="7" t="s">
         <v>164</v>
       </c>
       <c r="D59" s="2">
         <v>0</v>
       </c>
-      <c r="E59" s="3">
+      <c r="E59" s="9">
         <v>0.35921060399999999</v>
       </c>
       <c r="F59" s="2">
         <v>0</v>
       </c>
-      <c r="G59" s="3">
+      <c r="G59" s="9">
         <v>0</v>
       </c>
       <c r="H59" s="2">
         <v>0.53881590599999996</v>
       </c>
-      <c r="I59" s="3">
+      <c r="I59" s="9">
         <v>0.53881590599999996</v>
       </c>
       <c r="J59" s="2">
         <v>0.53881590599999996</v>
       </c>
-      <c r="K59" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="L59" t="s">
+      <c r="K59" s="6" t="s">
+        <v>380</v>
+      </c>
+      <c r="L59" s="7" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="60" spans="1:12" ht="18">
+    <row r="60" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A60" s="1">
         <v>59</v>
       </c>
-      <c r="B60" s="5" t="s">
+      <c r="B60" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="C60" t="s">
+      <c r="C60" s="7" t="s">
         <v>165</v>
       </c>
       <c r="D60" s="2">
         <v>0.188982237</v>
       </c>
-      <c r="E60" s="3">
+      <c r="E60" s="9">
         <v>0.56694670999999996</v>
       </c>
       <c r="F60" s="2">
         <v>0</v>
       </c>
-      <c r="G60" s="3">
+      <c r="G60" s="9">
         <v>0</v>
       </c>
       <c r="H60" s="2">
         <v>0.56694670999999996</v>
       </c>
-      <c r="I60" s="3">
+      <c r="I60" s="9">
         <v>0.56694670999999996</v>
       </c>
       <c r="J60" s="2">
         <v>0</v>
       </c>
-      <c r="K60" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="L60" t="s">
+      <c r="K60" s="6" t="s">
+        <v>381</v>
+      </c>
+      <c r="L60" s="7" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="61" spans="1:12" ht="18">
+    <row r="61" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A61" s="1">
         <v>60</v>
       </c>
-      <c r="B61" s="5" t="s">
+      <c r="B61" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="C61" t="s">
+      <c r="C61" s="7" t="s">
         <v>166</v>
       </c>
       <c r="D61" s="2">
         <v>0.39223226999999999</v>
       </c>
-      <c r="E61" s="3">
+      <c r="E61" s="9">
         <v>0.39223226999999999</v>
       </c>
       <c r="F61" s="2">
         <v>0.39223226999999999</v>
       </c>
-      <c r="G61" s="3">
+      <c r="G61" s="9">
         <v>0.58834840499999996</v>
       </c>
       <c r="H61" s="2">
         <v>0</v>
       </c>
-      <c r="I61" s="3">
+      <c r="I61" s="9">
         <v>0.39223226999999999</v>
       </c>
       <c r="J61" s="2">
         <v>0.196116135</v>
       </c>
-      <c r="K61" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="L61" t="s">
+      <c r="K61" s="6" t="s">
+        <v>382</v>
+      </c>
+      <c r="L61" s="7" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="62" spans="1:12" ht="18">
+    <row r="62" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A62" s="1">
         <v>61</v>
       </c>
-      <c r="B62" s="5" t="s">
+      <c r="B62" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="C62" t="s">
+      <c r="C62" s="7" t="s">
         <v>167</v>
       </c>
       <c r="D62" s="2">
         <v>0.53452248400000002</v>
       </c>
-      <c r="E62" s="3">
+      <c r="E62" s="9">
         <v>0.53452248400000002</v>
       </c>
       <c r="F62" s="2">
         <v>0.26726124200000001</v>
       </c>
-      <c r="G62" s="3">
+      <c r="G62" s="9">
         <v>0.53452248400000002</v>
       </c>
       <c r="H62" s="2">
         <v>0</v>
       </c>
-      <c r="I62" s="3">
+      <c r="I62" s="9">
         <v>0.26726124200000001</v>
       </c>
       <c r="J62" s="2">
         <v>0</v>
       </c>
-      <c r="K62" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="L62" t="s">
+      <c r="K62" s="6" t="s">
+        <v>383</v>
+      </c>
+      <c r="L62" s="7" t="s">
         <v>266</v>
       </c>
     </row>
@@ -4598,7 +4650,7 @@
         <v>0.39223226999999999</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>327</v>
+        <v>311</v>
       </c>
       <c r="L63" t="s">
         <v>267</v>
@@ -4636,7 +4688,7 @@
         <v>0.39223226999999999</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>327</v>
+        <v>311</v>
       </c>
       <c r="L64" t="s">
         <v>268</v>
@@ -4674,7 +4726,7 @@
         <v>0.31622776600000002</v>
       </c>
       <c r="K65" s="2" t="s">
-        <v>322</v>
+        <v>306</v>
       </c>
       <c r="L65" t="s">
         <v>269</v>
@@ -4712,7 +4764,7 @@
         <v>0.174077656</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>323</v>
+        <v>307</v>
       </c>
       <c r="L66" t="s">
         <v>270</v>
@@ -4750,7 +4802,7 @@
         <v>0.816496581</v>
       </c>
       <c r="K67" s="2" t="s">
-        <v>324</v>
+        <v>308</v>
       </c>
       <c r="L67" t="s">
         <v>271</v>
@@ -4788,7 +4840,7 @@
         <v>0</v>
       </c>
       <c r="K68" s="2" t="s">
-        <v>325</v>
+        <v>309</v>
       </c>
       <c r="L68" t="s">
         <v>272</v>
@@ -4826,7 +4878,7 @@
         <v>0</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>326</v>
+        <v>310</v>
       </c>
       <c r="L69" t="s">
         <v>273</v>
@@ -4864,7 +4916,7 @@
         <v>0</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>326</v>
+        <v>310</v>
       </c>
       <c r="L70" t="s">
         <v>274</v>
@@ -4902,7 +4954,7 @@
         <v>0</v>
       </c>
       <c r="K71" s="2" t="s">
-        <v>328</v>
+        <v>312</v>
       </c>
       <c r="L71" t="s">
         <v>275</v>
@@ -4940,7 +4992,7 @@
         <v>0</v>
       </c>
       <c r="K72" s="2" t="s">
-        <v>328</v>
+        <v>312</v>
       </c>
       <c r="L72" t="s">
         <v>276</v>
@@ -4978,7 +5030,7 @@
         <v>0</v>
       </c>
       <c r="K73" s="2" t="s">
-        <v>328</v>
+        <v>312</v>
       </c>
       <c r="L73" t="s">
         <v>277</v>
@@ -5016,7 +5068,7 @@
         <v>0.66666666699999999</v>
       </c>
       <c r="K74" s="2" t="s">
-        <v>329</v>
+        <v>313</v>
       </c>
       <c r="L74" t="s">
         <v>278</v>
@@ -5054,7 +5106,7 @@
         <v>0.47140452100000002</v>
       </c>
       <c r="K75" s="2" t="s">
-        <v>329</v>
+        <v>313</v>
       </c>
       <c r="L75" t="s">
         <v>279</v>
@@ -5092,7 +5144,7 @@
         <v>1</v>
       </c>
       <c r="K76" s="2" t="s">
-        <v>329</v>
+        <v>313</v>
       </c>
       <c r="L76" t="s">
         <v>280</v>
@@ -5130,7 +5182,7 @@
         <v>0.26726124200000001</v>
       </c>
       <c r="K77" s="2" t="s">
-        <v>330</v>
+        <v>314</v>
       </c>
       <c r="L77" t="s">
         <v>281</v>
@@ -5168,7 +5220,7 @@
         <v>0</v>
       </c>
       <c r="K78" s="2" t="s">
-        <v>330</v>
+        <v>314</v>
       </c>
       <c r="L78" t="s">
         <v>282</v>
@@ -5206,7 +5258,7 @@
         <v>0.57735026899999997</v>
       </c>
       <c r="K79" s="2" t="s">
-        <v>330</v>
+        <v>314</v>
       </c>
       <c r="L79" t="s">
         <v>283</v>
@@ -5244,7 +5296,7 @@
         <v>0</v>
       </c>
       <c r="K80" s="2" t="s">
-        <v>331</v>
+        <v>315</v>
       </c>
       <c r="L80" t="s">
         <v>284</v>
@@ -5282,7 +5334,7 @@
         <v>0.70710678100000002</v>
       </c>
       <c r="K81" s="2" t="s">
-        <v>331</v>
+        <v>315</v>
       </c>
       <c r="L81" t="s">
         <v>285</v>
@@ -5320,7 +5372,7 @@
         <v>0.70710678100000002</v>
       </c>
       <c r="K82" s="2" t="s">
-        <v>331</v>
+        <v>315</v>
       </c>
       <c r="L82" t="s">
         <v>286</v>
@@ -5358,7 +5410,7 @@
         <v>0.30151134499999999</v>
       </c>
       <c r="K83" s="2" t="s">
-        <v>332</v>
+        <v>316</v>
       </c>
       <c r="L83" t="s">
         <v>287</v>
@@ -5396,7 +5448,7 @@
         <v>0</v>
       </c>
       <c r="K84" s="2" t="s">
-        <v>332</v>
+        <v>316</v>
       </c>
       <c r="L84" t="s">
         <v>288</v>
@@ -5434,7 +5486,7 @@
         <v>0.57735026899999997</v>
       </c>
       <c r="K85" s="2" t="s">
-        <v>332</v>
+        <v>316</v>
       </c>
       <c r="L85" t="s">
         <v>289</v>
@@ -5472,7 +5524,7 @@
         <v>0</v>
       </c>
       <c r="K86" s="2" t="s">
-        <v>333</v>
+        <v>317</v>
       </c>
       <c r="L86" t="s">
         <v>290</v>
@@ -5510,7 +5562,7 @@
         <v>0.29488391200000003</v>
       </c>
       <c r="K87" s="2" t="s">
-        <v>333</v>
+        <v>317</v>
       </c>
       <c r="L87" t="s">
         <v>291</v>
@@ -5548,7 +5600,7 @@
         <v>0</v>
       </c>
       <c r="K88" s="2" t="s">
-        <v>333</v>
+        <v>317</v>
       </c>
       <c r="L88" t="s">
         <v>292</v>
@@ -5586,7 +5638,7 @@
         <v>0.51639777899999995</v>
       </c>
       <c r="K89" s="2" t="s">
-        <v>334</v>
+        <v>318</v>
       </c>
       <c r="L89" t="s">
         <v>293</v>
@@ -5624,7 +5676,7 @@
         <v>0.31622776600000002</v>
       </c>
       <c r="K90" s="2" t="s">
-        <v>334</v>
+        <v>318</v>
       </c>
       <c r="L90" t="s">
         <v>294</v>
@@ -5662,7 +5714,7 @@
         <v>0.43643578</v>
       </c>
       <c r="K91" s="2" t="s">
-        <v>334</v>
+        <v>318</v>
       </c>
       <c r="L91" t="s">
         <v>295</v>
@@ -5700,7 +5752,7 @@
         <v>0</v>
       </c>
       <c r="K92" s="2" t="s">
-        <v>335</v>
+        <v>319</v>
       </c>
       <c r="L92" t="s">
         <v>296</v>
@@ -5738,7 +5790,7 @@
         <v>0</v>
       </c>
       <c r="K93" s="2" t="s">
-        <v>335</v>
+        <v>319</v>
       </c>
       <c r="L93" t="s">
         <v>297</v>
@@ -5776,7 +5828,7 @@
         <v>0</v>
       </c>
       <c r="K94" s="2" t="s">
-        <v>335</v>
+        <v>319</v>
       </c>
       <c r="L94" t="s">
         <v>298</v>
@@ -5814,7 +5866,7 @@
         <v>0.53033008599999998</v>
       </c>
       <c r="K95" s="2" t="s">
-        <v>336</v>
+        <v>320</v>
       </c>
       <c r="L95" t="s">
         <v>299</v>
@@ -5852,7 +5904,7 @@
         <v>0.48507125000000001</v>
       </c>
       <c r="K96" s="2" t="s">
-        <v>336</v>
+        <v>320</v>
       </c>
       <c r="L96" t="s">
         <v>300</v>
@@ -5890,7 +5942,7 @@
         <v>0.56568542499999996</v>
       </c>
       <c r="K97" s="2" t="s">
-        <v>336</v>
+        <v>320</v>
       </c>
       <c r="L97" t="s">
         <v>301</v>
@@ -5928,7 +5980,7 @@
         <v>0.78446454099999996</v>
       </c>
       <c r="K98" s="2" t="s">
-        <v>337</v>
+        <v>321</v>
       </c>
       <c r="L98" t="s">
         <v>302</v>
@@ -5966,7 +6018,7 @@
         <v>0.63960214900000001</v>
       </c>
       <c r="K99" s="2" t="s">
-        <v>337</v>
+        <v>321</v>
       </c>
       <c r="L99" t="s">
         <v>303</v>
@@ -6004,7 +6056,7 @@
         <v>0.54433105400000004</v>
       </c>
       <c r="K100" s="2" t="s">
-        <v>337</v>
+        <v>321</v>
       </c>
       <c r="L100" t="s">
         <v>304</v>

--- a/library.xlsx
+++ b/library.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xxc/Desktop/xxc/拓殖大学/研究室/評価実験/video-recommend-system/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2864F4F0-D155-ED41-82BC-46D19CC5BEA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{187DABC6-751B-1F45-ACF6-B771D3D2FA3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{F40E9203-8E2D-9949-9A4C-F506F7C93633}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="385">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="388">
   <si>
     <t>No.</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -1428,24 +1428,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>癒し</t>
-  </si>
-  <si>
-    <t>極限チャレンジ</t>
-  </si>
-  <si>
-    <t>コメディ</t>
-  </si>
-  <si>
-    <t>災害</t>
-  </si>
-  <si>
-    <t>攻撃</t>
-  </si>
-  <si>
-    <t>ライブ</t>
-  </si>
-  <si>
     <t>教育</t>
   </si>
   <si>
@@ -1491,9 +1473,6 @@
     <t>ペット,犬,猫,,動物,生活,可愛い</t>
   </si>
   <si>
-    <t>料理,Gordon Ramsay,教育,健康</t>
-  </si>
-  <si>
     <t>夜景,景色,東京,日本,都市,名所,Time-lapse</t>
   </si>
   <si>
@@ -1507,9 +1486,6 @@
   </si>
   <si>
     <t>インタビュー,共感,野球,林琢真,感動,スポーツ</t>
-  </si>
-  <si>
-    <t>健康,運動,教育,筋肉,ダイエット,整体,柔軟体操</t>
   </si>
   <si>
     <t>科学,体験,物理</t>
@@ -1569,12 +1545,6 @@
     <t>IShowSpeed,危険,極限チャレンジ</t>
   </si>
   <si>
-    <t>社会事件,Will Smith,Oscars,俳優,喧嘩,エンタメ,Love,TV</t>
-  </si>
-  <si>
-    <t>ライブ,音楽,Pop,ドラム,rock,可愛い</t>
-  </si>
-  <si>
     <t>癒し,Jazz,ライブ,音楽,牛,動物,自然,景色,雰囲気,リラックス,山,可愛い</t>
   </si>
   <si>
@@ -1587,9 +1557,6 @@
     <t>コメディ,星野源,ドラム,音楽,Pop</t>
   </si>
   <si>
-    <t>チャレンジ,コメディ,料理,危険,牛丼</t>
-  </si>
-  <si>
     <t>癒し,Lamb,動物,自然,可愛い,リラックス,ペット</t>
   </si>
   <si>
@@ -1608,33 +1575,21 @@
     <t>生活,主婦,ライフハック</t>
   </si>
   <si>
-    <t>バーテンダー,日本,コメディ,bar</t>
-  </si>
-  <si>
     <t>実験,化学,スライム,ダイラタンシー</t>
   </si>
   <si>
     <t>短編映画,感動,共感,Love,家族,父親,娘,離婚</t>
   </si>
   <si>
-    <t>災害,攻撃,911,飛行機,terrorists,危険,USA,死亡,恐怖,爆発,火災,world trade center,twin towers,crash,社会事件,hijack,政治,ビル,世界,消防</t>
-  </si>
-  <si>
     <t>ペット,犬,動物,生活,可愛い,家族,子供,癒し,Love</t>
   </si>
   <si>
-    <t>ペット,チンチラ,ペット,動物,可愛い,教育</t>
-  </si>
-  <si>
     <t>自然,景色,癒し,日本,ASMR,BGM,リラックス,鳥,花,桜,リラックス,雰囲気,集中,勉強,仕事,,植物,ピアノ</t>
   </si>
   <si>
     <t>自然,景色,癒し,日本,BGM,リラックス,リラックス,雰囲気,集中,勉強,仕事,夜空,夜景,極光</t>
   </si>
   <si>
-    <t>料理,主婦,教育,健康,生活,vlog,日本,家族,癒し,雰囲気</t>
-  </si>
-  <si>
     <t>料理,camp,癒し,雰囲気,冬</t>
   </si>
   <si>
@@ -1647,9 +1602,6 @@
     <t>園芸,癒し,BGM,リラックス,花,リラックス,雰囲気,集中,植物,ピアノ</t>
   </si>
   <si>
-    <t>園芸,教育,植物</t>
-  </si>
-  <si>
     <t>レトロ,東京,都市,日本</t>
   </si>
   <si>
@@ -1665,12 +1617,6 @@
     <t>インタビュー,Donald Trump,政治,USA,Iran,世界</t>
   </si>
   <si>
-    <t>健康,医療,科学,教育</t>
-  </si>
-  <si>
-    <t>健康,教育,料理</t>
-  </si>
-  <si>
     <t>科学,物理,宇宙,物理,教育</t>
   </si>
   <si>
@@ -1683,21 +1629,18 @@
     <t>マジック,GT,Eden Choi</t>
   </si>
   <si>
+    <t>マジック,GT,Shin Lim</t>
+  </si>
+  <si>
     <t>バーテンダー,bar,雰囲気</t>
   </si>
   <si>
-    <t>バーテンダー,whiskey,コメディ</t>
-  </si>
-  <si>
     <t>実験,TV,科学,化学,ナトリウム</t>
   </si>
   <si>
     <t>実験,材料,物理,化学,magneticgames,quantumphysics,magnets</t>
   </si>
   <si>
-    <t>社会事件,暴力団,警察,大阪,山口組,コメディ</t>
-  </si>
-  <si>
     <t>社会事件,Donald Trump,政治,USA,攻撃,暗殺,Shooter,MAGA,世界,危険</t>
   </si>
   <si>
@@ -1707,8 +1650,73 @@
     <t>短編映画,AI,科学,社会事件</t>
   </si>
   <si>
-    <t>マジック,GT,Shin Lim</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <t>料理,Gordon Ramsay,紹介,健康</t>
+  </si>
+  <si>
+    <t>健康,運動,紹介,筋肉,ダイエット,整体,柔軟体操</t>
+  </si>
+  <si>
+    <t>バーテンダー,日本,コメディ,bar,meme</t>
+  </si>
+  <si>
+    <t>社会事件,Will Smith,Oscars,俳優,喧嘩,エンタメ,Love,TV,meme</t>
+  </si>
+  <si>
+    <t>ライブ,音楽,Pop,ドラム,rock,可愛い,meme</t>
+  </si>
+  <si>
+    <t>チャレンジ,コメディ,料理,危険,牛丼,meme</t>
+  </si>
+  <si>
+    <t>攻撃,911,飛行機,terrorists,危険,USA,死亡,恐怖,爆発,火災,world trade center,twin towers,crash,社会事件,hijack,政治,ビル,世界,消防,戦争</t>
+  </si>
+  <si>
+    <t>ペット,チンチラ,ペット,動物,可愛い,紹介</t>
+  </si>
+  <si>
+    <t>料理,主婦,紹介,健康,生活,vlog,日本,家族,癒し,雰囲気</t>
+  </si>
+  <si>
+    <t>園芸,紹介,植物</t>
+  </si>
+  <si>
+    <t>健康,医療,科学,教育,病院</t>
+  </si>
+  <si>
+    <t>健康,紹介,料理</t>
+  </si>
+  <si>
+    <t>バーテンダー,whiskey,コメディ,紹介,meme</t>
+  </si>
+  <si>
+    <t>社会事件,暴力団,警察,大阪,山口組,コメディ,meme</t>
+  </si>
+  <si>
+    <t>ライブ,Queen,音楽,rock,名作,慈善,共感</t>
+  </si>
+  <si>
+    <t>ライブ,MJ,音楽,Pop,名作,共感,ダンス</t>
+  </si>
+  <si>
+    <t>癒し,Agarwood,Incense,瞑想,癒し,リラックス,雰囲気,ASMR</t>
+  </si>
+  <si>
+    <t>極限チャレンジ,World Record,High Dive,diving,危険,Freefall</t>
+  </si>
+  <si>
+    <t>コメディ,BBQ,料理,紹介,meme</t>
+  </si>
+  <si>
+    <t>災害,土石流,危険,恐怖,自然,死亡,社会事件</t>
+  </si>
+  <si>
+    <t>攻撃,ガザ,イスラエル,爆発,恐怖,危険,政治,世界,ミサイル,死亡,戦争,病院</t>
+  </si>
+  <si>
+    <t>攻撃,car accident,ペット,病院,危険,Animal Clinic,事故</t>
+  </si>
+  <si>
+    <t>教育,生活,環境,人類,地球,社会,アニメ</t>
   </si>
 </sst>
 </file>
@@ -2332,7 +2340,7 @@
         <v>0.94868329799999995</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="L2" s="7" t="s">
         <v>206</v>
@@ -2370,7 +2378,7 @@
         <v>0.70710678100000002</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>349</v>
+        <v>338</v>
       </c>
       <c r="L3" s="7" t="s">
         <v>208</v>
@@ -2381,10 +2389,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="D4" s="2">
         <v>0</v>
@@ -2408,10 +2416,10 @@
         <v>0.40824829000000001</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>326</v>
+        <v>365</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
     </row>
     <row r="5" spans="1:12" s="7" customFormat="1" ht="18">
@@ -2446,7 +2454,7 @@
         <v>0.63245553200000004</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="L5" s="7" t="s">
         <v>209</v>
@@ -2484,7 +2492,7 @@
         <v>0.72760687499999999</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="L6" s="7" t="s">
         <v>210</v>
@@ -2522,7 +2530,7 @@
         <v>0.44721359500000002</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="L7" s="7" t="s">
         <v>211</v>
@@ -2560,7 +2568,7 @@
         <v>0</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="L8" s="7" t="s">
         <v>212</v>
@@ -2598,7 +2606,7 @@
         <v>0</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="L9" s="7" t="s">
         <v>213</v>
@@ -2636,7 +2644,7 @@
         <v>0.37796447300000002</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>332</v>
+        <v>366</v>
       </c>
       <c r="L10" s="7" t="s">
         <v>214</v>
@@ -2674,7 +2682,7 @@
         <v>0.28867513500000003</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="L11" s="7" t="s">
         <v>215</v>
@@ -2712,7 +2720,7 @@
         <v>0.57735026899999997</v>
       </c>
       <c r="K12" s="6" t="s">
-        <v>350</v>
+        <v>339</v>
       </c>
       <c r="L12" s="7" t="s">
         <v>216</v>
@@ -2750,7 +2758,7 @@
         <v>0.80178372600000003</v>
       </c>
       <c r="K13" s="6" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="L13" s="7" t="s">
         <v>217</v>
@@ -2788,7 +2796,7 @@
         <v>0.28867513500000003</v>
       </c>
       <c r="K14" s="6" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="L14" s="7" t="s">
         <v>218</v>
@@ -2826,7 +2834,7 @@
         <v>0.89442719100000001</v>
       </c>
       <c r="K15" s="6" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="L15" s="7" t="s">
         <v>219</v>
@@ -2864,7 +2872,7 @@
         <v>0.70710678100000002</v>
       </c>
       <c r="K16" s="6" t="s">
-        <v>351</v>
+        <v>367</v>
       </c>
       <c r="L16" s="7" t="s">
         <v>220</v>
@@ -2902,7 +2910,7 @@
         <v>0.45883146800000002</v>
       </c>
       <c r="K17" s="6" t="s">
-        <v>352</v>
+        <v>340</v>
       </c>
       <c r="L17" s="7" t="s">
         <v>221</v>
@@ -2940,7 +2948,7 @@
         <v>0.625543242</v>
       </c>
       <c r="K18" s="6" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="L18" s="7" t="s">
         <v>222</v>
@@ -2978,7 +2986,7 @@
         <v>0.15430335000000001</v>
       </c>
       <c r="K19" s="6" t="s">
-        <v>338</v>
+        <v>368</v>
       </c>
       <c r="L19" s="7" t="s">
         <v>223</v>
@@ -3016,7 +3024,7 @@
         <v>0.30151134499999999</v>
       </c>
       <c r="K20" s="6" t="s">
-        <v>353</v>
+        <v>341</v>
       </c>
       <c r="L20" s="7" t="s">
         <v>224</v>
@@ -3054,7 +3062,7 @@
         <v>0.70710678100000002</v>
       </c>
       <c r="K21" s="6" t="s">
-        <v>339</v>
+        <v>369</v>
       </c>
       <c r="L21" s="7" t="s">
         <v>225</v>
@@ -3092,7 +3100,7 @@
         <v>0.688247202</v>
       </c>
       <c r="K22" s="6" t="s">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="L22" s="7" t="s">
         <v>226</v>
@@ -3130,7 +3138,7 @@
         <v>0.48507125000000001</v>
       </c>
       <c r="K23" s="6" t="s">
-        <v>341</v>
+        <v>331</v>
       </c>
       <c r="L23" s="7" t="s">
         <v>227</v>
@@ -3168,7 +3176,7 @@
         <v>0.25819889000000001</v>
       </c>
       <c r="K24" s="6" t="s">
-        <v>342</v>
+        <v>332</v>
       </c>
       <c r="L24" s="7" t="s">
         <v>228</v>
@@ -3206,7 +3214,7 @@
         <v>0.57735026899999997</v>
       </c>
       <c r="K25" s="6" t="s">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="L25" s="7" t="s">
         <v>229</v>
@@ -3244,7 +3252,7 @@
         <v>0.62469504799999998</v>
       </c>
       <c r="K26" s="6" t="s">
-        <v>344</v>
+        <v>370</v>
       </c>
       <c r="L26" s="7" t="s">
         <v>230</v>
@@ -3282,7 +3290,7 @@
         <v>0</v>
       </c>
       <c r="K27" s="6" t="s">
-        <v>354</v>
+        <v>371</v>
       </c>
       <c r="L27" s="7" t="s">
         <v>231</v>
@@ -3320,7 +3328,7 @@
         <v>0.78446454099999996</v>
       </c>
       <c r="K28" s="6" t="s">
-        <v>345</v>
+        <v>334</v>
       </c>
       <c r="L28" s="7" t="s">
         <v>232</v>
@@ -3358,7 +3366,7 @@
         <v>0</v>
       </c>
       <c r="K29" s="6" t="s">
-        <v>346</v>
+        <v>335</v>
       </c>
       <c r="L29" s="7" t="s">
         <v>233</v>
@@ -3396,7 +3404,7 @@
         <v>0.55470019599999998</v>
       </c>
       <c r="K30" s="6" t="s">
-        <v>347</v>
+        <v>336</v>
       </c>
       <c r="L30" s="7" t="s">
         <v>234</v>
@@ -3434,7 +3442,7 @@
         <v>0</v>
       </c>
       <c r="K31" s="6" t="s">
-        <v>348</v>
+        <v>337</v>
       </c>
       <c r="L31" s="7" t="s">
         <v>235</v>
@@ -3472,7 +3480,7 @@
         <v>0.688247202</v>
       </c>
       <c r="K32" s="6" t="s">
-        <v>355</v>
+        <v>342</v>
       </c>
       <c r="L32" s="7" t="s">
         <v>236</v>
@@ -3510,7 +3518,7 @@
         <v>0.35355339099999999</v>
       </c>
       <c r="K33" s="6" t="s">
-        <v>356</v>
+        <v>372</v>
       </c>
       <c r="L33" s="7" t="s">
         <v>237</v>
@@ -3548,7 +3556,7 @@
         <v>0.55470019599999998</v>
       </c>
       <c r="K34" s="6" t="s">
-        <v>357</v>
+        <v>343</v>
       </c>
       <c r="L34" s="7" t="s">
         <v>238</v>
@@ -3586,7 +3594,7 @@
         <v>0.26726124200000001</v>
       </c>
       <c r="K35" s="6" t="s">
-        <v>358</v>
+        <v>344</v>
       </c>
       <c r="L35" s="7" t="s">
         <v>239</v>
@@ -3624,7 +3632,7 @@
         <v>0.53452248400000002</v>
       </c>
       <c r="K36" s="6" t="s">
-        <v>359</v>
+        <v>373</v>
       </c>
       <c r="L36" s="7" t="s">
         <v>240</v>
@@ -3662,7 +3670,7 @@
         <v>0.426401433</v>
       </c>
       <c r="K37" s="6" t="s">
-        <v>360</v>
+        <v>345</v>
       </c>
       <c r="L37" s="7" t="s">
         <v>241</v>
@@ -3700,7 +3708,7 @@
         <v>0</v>
       </c>
       <c r="K38" s="6" t="s">
-        <v>361</v>
+        <v>346</v>
       </c>
       <c r="L38" s="7" t="s">
         <v>242</v>
@@ -3738,7 +3746,7 @@
         <v>0</v>
       </c>
       <c r="K39" s="6" t="s">
-        <v>362</v>
+        <v>347</v>
       </c>
       <c r="L39" s="7" t="s">
         <v>243</v>
@@ -3776,7 +3784,7 @@
         <v>0.57735026899999997</v>
       </c>
       <c r="K40" s="6" t="s">
-        <v>363</v>
+        <v>348</v>
       </c>
       <c r="L40" s="7" t="s">
         <v>244</v>
@@ -3814,7 +3822,7 @@
         <v>0.53452248400000002</v>
       </c>
       <c r="K41" s="6" t="s">
-        <v>364</v>
+        <v>374</v>
       </c>
       <c r="L41" s="7" t="s">
         <v>245</v>
@@ -3852,7 +3860,7 @@
         <v>0.23570226</v>
       </c>
       <c r="K42" s="6" t="s">
-        <v>365</v>
+        <v>349</v>
       </c>
       <c r="L42" s="7" t="s">
         <v>246</v>
@@ -3890,7 +3898,7 @@
         <v>0.365148372</v>
       </c>
       <c r="K43" s="6" t="s">
-        <v>366</v>
+        <v>350</v>
       </c>
       <c r="L43" s="7" t="s">
         <v>247</v>
@@ -3928,7 +3936,7 @@
         <v>0.57735026899999997</v>
       </c>
       <c r="K44" s="6" t="s">
-        <v>367</v>
+        <v>351</v>
       </c>
       <c r="L44" s="7" t="s">
         <v>248</v>
@@ -3966,7 +3974,7 @@
         <v>0</v>
       </c>
       <c r="K45" s="6" t="s">
-        <v>368</v>
+        <v>352</v>
       </c>
       <c r="L45" s="7" t="s">
         <v>249</v>
@@ -4004,7 +4012,7 @@
         <v>0</v>
       </c>
       <c r="K46" s="6" t="s">
-        <v>369</v>
+        <v>353</v>
       </c>
       <c r="L46" s="7" t="s">
         <v>250</v>
@@ -4042,7 +4050,7 @@
         <v>0</v>
       </c>
       <c r="K47" s="6" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="L47" s="7" t="s">
         <v>251</v>
@@ -4080,7 +4088,7 @@
         <v>0.5</v>
       </c>
       <c r="K48" s="6" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="L48" s="7" t="s">
         <v>252</v>
@@ -4118,7 +4126,7 @@
         <v>0.174077656</v>
       </c>
       <c r="K49" s="6" t="s">
-        <v>372</v>
+        <v>354</v>
       </c>
       <c r="L49" s="7" t="s">
         <v>253</v>
@@ -4156,7 +4164,7 @@
         <v>0.174077656</v>
       </c>
       <c r="K50" s="6" t="s">
-        <v>372</v>
+        <v>354</v>
       </c>
       <c r="L50" s="7" t="s">
         <v>254</v>
@@ -4194,7 +4202,7 @@
         <v>0.27735009799999999</v>
       </c>
       <c r="K51" s="6" t="s">
-        <v>373</v>
+        <v>355</v>
       </c>
       <c r="L51" s="7" t="s">
         <v>255</v>
@@ -4232,7 +4240,7 @@
         <v>0.80178372600000003</v>
       </c>
       <c r="K52" s="6" t="s">
-        <v>374</v>
+        <v>356</v>
       </c>
       <c r="L52" s="7" t="s">
         <v>256</v>
@@ -4270,7 +4278,7 @@
         <v>0.514495755</v>
       </c>
       <c r="K53" s="6" t="s">
-        <v>375</v>
+        <v>357</v>
       </c>
       <c r="L53" s="7" t="s">
         <v>257</v>
@@ -4308,7 +4316,7 @@
         <v>0.514495755</v>
       </c>
       <c r="K54" s="6" t="s">
-        <v>384</v>
+        <v>358</v>
       </c>
       <c r="L54" s="7" t="s">
         <v>258</v>
@@ -4346,7 +4354,7 @@
         <v>0.63960214900000001</v>
       </c>
       <c r="K55" s="6" t="s">
-        <v>376</v>
+        <v>359</v>
       </c>
       <c r="L55" s="7" t="s">
         <v>259</v>
@@ -4422,7 +4430,7 @@
         <v>0.47140452100000002</v>
       </c>
       <c r="K57" s="6" t="s">
-        <v>378</v>
+        <v>360</v>
       </c>
       <c r="L57" s="7" t="s">
         <v>261</v>
@@ -4460,7 +4468,7 @@
         <v>0</v>
       </c>
       <c r="K58" s="6" t="s">
-        <v>379</v>
+        <v>361</v>
       </c>
       <c r="L58" s="7" t="s">
         <v>262</v>
@@ -4498,7 +4506,7 @@
         <v>0.53881590599999996</v>
       </c>
       <c r="K59" s="6" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="L59" s="7" t="s">
         <v>263</v>
@@ -4536,7 +4544,7 @@
         <v>0</v>
       </c>
       <c r="K60" s="6" t="s">
-        <v>381</v>
+        <v>362</v>
       </c>
       <c r="L60" s="7" t="s">
         <v>264</v>
@@ -4574,7 +4582,7 @@
         <v>0.196116135</v>
       </c>
       <c r="K61" s="6" t="s">
-        <v>382</v>
+        <v>363</v>
       </c>
       <c r="L61" s="7" t="s">
         <v>265</v>
@@ -4612,7 +4620,7 @@
         <v>0</v>
       </c>
       <c r="K62" s="6" t="s">
-        <v>383</v>
+        <v>364</v>
       </c>
       <c r="L62" s="7" t="s">
         <v>266</v>
@@ -4649,8 +4657,8 @@
       <c r="J63" s="2">
         <v>0.39223226999999999</v>
       </c>
-      <c r="K63" s="2" t="s">
-        <v>311</v>
+      <c r="K63" s="6" t="s">
+        <v>379</v>
       </c>
       <c r="L63" t="s">
         <v>267</v>
@@ -4687,8 +4695,8 @@
       <c r="J64" s="2">
         <v>0.39223226999999999</v>
       </c>
-      <c r="K64" s="2" t="s">
-        <v>311</v>
+      <c r="K64" s="6" t="s">
+        <v>380</v>
       </c>
       <c r="L64" t="s">
         <v>268</v>
@@ -4725,8 +4733,8 @@
       <c r="J65" s="2">
         <v>0.31622776600000002</v>
       </c>
-      <c r="K65" s="2" t="s">
-        <v>306</v>
+      <c r="K65" s="6" t="s">
+        <v>381</v>
       </c>
       <c r="L65" t="s">
         <v>269</v>
@@ -4763,8 +4771,8 @@
       <c r="J66" s="2">
         <v>0.174077656</v>
       </c>
-      <c r="K66" s="2" t="s">
-        <v>307</v>
+      <c r="K66" s="6" t="s">
+        <v>382</v>
       </c>
       <c r="L66" t="s">
         <v>270</v>
@@ -4801,8 +4809,8 @@
       <c r="J67" s="2">
         <v>0.816496581</v>
       </c>
-      <c r="K67" s="2" t="s">
-        <v>308</v>
+      <c r="K67" s="6" t="s">
+        <v>383</v>
       </c>
       <c r="L67" t="s">
         <v>271</v>
@@ -4839,8 +4847,8 @@
       <c r="J68" s="2">
         <v>0</v>
       </c>
-      <c r="K68" s="2" t="s">
-        <v>309</v>
+      <c r="K68" s="6" t="s">
+        <v>384</v>
       </c>
       <c r="L68" t="s">
         <v>272</v>
@@ -4877,8 +4885,8 @@
       <c r="J69" s="2">
         <v>0</v>
       </c>
-      <c r="K69" s="2" t="s">
-        <v>310</v>
+      <c r="K69" s="6" t="s">
+        <v>385</v>
       </c>
       <c r="L69" t="s">
         <v>273</v>
@@ -4915,8 +4923,8 @@
       <c r="J70" s="2">
         <v>0</v>
       </c>
-      <c r="K70" s="2" t="s">
-        <v>310</v>
+      <c r="K70" s="6" t="s">
+        <v>386</v>
       </c>
       <c r="L70" t="s">
         <v>274</v>
@@ -4953,8 +4961,8 @@
       <c r="J71" s="2">
         <v>0</v>
       </c>
-      <c r="K71" s="2" t="s">
-        <v>312</v>
+      <c r="K71" s="6" t="s">
+        <v>387</v>
       </c>
       <c r="L71" t="s">
         <v>275</v>
@@ -4992,7 +5000,7 @@
         <v>0</v>
       </c>
       <c r="K72" s="2" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="L72" t="s">
         <v>276</v>
@@ -5030,7 +5038,7 @@
         <v>0</v>
       </c>
       <c r="K73" s="2" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="L73" t="s">
         <v>277</v>
@@ -5068,7 +5076,7 @@
         <v>0.66666666699999999</v>
       </c>
       <c r="K74" s="2" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="L74" t="s">
         <v>278</v>
@@ -5106,7 +5114,7 @@
         <v>0.47140452100000002</v>
       </c>
       <c r="K75" s="2" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="L75" t="s">
         <v>279</v>
@@ -5144,7 +5152,7 @@
         <v>1</v>
       </c>
       <c r="K76" s="2" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="L76" t="s">
         <v>280</v>
@@ -5182,7 +5190,7 @@
         <v>0.26726124200000001</v>
       </c>
       <c r="K77" s="2" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="L77" t="s">
         <v>281</v>
@@ -5220,7 +5228,7 @@
         <v>0</v>
       </c>
       <c r="K78" s="2" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="L78" t="s">
         <v>282</v>
@@ -5258,7 +5266,7 @@
         <v>0.57735026899999997</v>
       </c>
       <c r="K79" s="2" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="L79" t="s">
         <v>283</v>
@@ -5296,7 +5304,7 @@
         <v>0</v>
       </c>
       <c r="K80" s="2" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="L80" t="s">
         <v>284</v>
@@ -5334,7 +5342,7 @@
         <v>0.70710678100000002</v>
       </c>
       <c r="K81" s="2" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="L81" t="s">
         <v>285</v>
@@ -5372,7 +5380,7 @@
         <v>0.70710678100000002</v>
       </c>
       <c r="K82" s="2" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="L82" t="s">
         <v>286</v>
@@ -5410,7 +5418,7 @@
         <v>0.30151134499999999</v>
       </c>
       <c r="K83" s="2" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="L83" t="s">
         <v>287</v>
@@ -5448,7 +5456,7 @@
         <v>0</v>
       </c>
       <c r="K84" s="2" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="L84" t="s">
         <v>288</v>
@@ -5486,7 +5494,7 @@
         <v>0.57735026899999997</v>
       </c>
       <c r="K85" s="2" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="L85" t="s">
         <v>289</v>
@@ -5524,7 +5532,7 @@
         <v>0</v>
       </c>
       <c r="K86" s="2" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="L86" t="s">
         <v>290</v>
@@ -5562,7 +5570,7 @@
         <v>0.29488391200000003</v>
       </c>
       <c r="K87" s="2" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="L87" t="s">
         <v>291</v>
@@ -5600,7 +5608,7 @@
         <v>0</v>
       </c>
       <c r="K88" s="2" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="L88" t="s">
         <v>292</v>
@@ -5638,7 +5646,7 @@
         <v>0.51639777899999995</v>
       </c>
       <c r="K89" s="2" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="L89" t="s">
         <v>293</v>
@@ -5676,7 +5684,7 @@
         <v>0.31622776600000002</v>
       </c>
       <c r="K90" s="2" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="L90" t="s">
         <v>294</v>
@@ -5714,7 +5722,7 @@
         <v>0.43643578</v>
       </c>
       <c r="K91" s="2" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="L91" t="s">
         <v>295</v>
@@ -5752,7 +5760,7 @@
         <v>0</v>
       </c>
       <c r="K92" s="2" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="L92" t="s">
         <v>296</v>
@@ -5790,7 +5798,7 @@
         <v>0</v>
       </c>
       <c r="K93" s="2" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="L93" t="s">
         <v>297</v>
@@ -5828,7 +5836,7 @@
         <v>0</v>
       </c>
       <c r="K94" s="2" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="L94" t="s">
         <v>298</v>
@@ -5866,7 +5874,7 @@
         <v>0.53033008599999998</v>
       </c>
       <c r="K95" s="2" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="L95" t="s">
         <v>299</v>
@@ -5904,7 +5912,7 @@
         <v>0.48507125000000001</v>
       </c>
       <c r="K96" s="2" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="L96" t="s">
         <v>300</v>
@@ -5942,7 +5950,7 @@
         <v>0.56568542499999996</v>
       </c>
       <c r="K97" s="2" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="L97" t="s">
         <v>301</v>
@@ -5980,7 +5988,7 @@
         <v>0.78446454099999996</v>
       </c>
       <c r="K98" s="2" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="L98" t="s">
         <v>302</v>
@@ -6018,7 +6026,7 @@
         <v>0.63960214900000001</v>
       </c>
       <c r="K99" s="2" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="L99" t="s">
         <v>303</v>
@@ -6056,7 +6064,7 @@
         <v>0.54433105400000004</v>
       </c>
       <c r="K100" s="2" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="L100" t="s">
         <v>304</v>

--- a/library.xlsx
+++ b/library.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xxc/Desktop/xxc/拓殖大学/研究室/評価実験/video-recommend-system/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{187DABC6-751B-1F45-ACF6-B771D3D2FA3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AEDC096-B148-B54E-877C-2AF58100F138}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{F40E9203-8E2D-9949-9A4C-F506F7C93633}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="388">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="397">
   <si>
     <t>No.</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -1428,21 +1428,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>教育</t>
-  </si>
-  <si>
-    <t>旅行</t>
-  </si>
-  <si>
-    <t>スポーツ</t>
-  </si>
-  <si>
-    <t>アニメ</t>
-  </si>
-  <si>
-    <t>ドキュメンタリー</t>
-  </si>
-  <si>
     <t>歴史</t>
   </si>
   <si>
@@ -1483,9 +1468,6 @@
   </si>
   <si>
     <t>ASMR,リラックス,喫茶店,勉強,仕事,雰囲気,集中</t>
-  </si>
-  <si>
-    <t>インタビュー,共感,野球,林琢真,感動,スポーツ</t>
   </si>
   <si>
     <t>科学,体験,物理</t>
@@ -1560,9 +1542,6 @@
     <t>癒し,Lamb,動物,自然,可愛い,リラックス,ペット</t>
   </si>
   <si>
-    <t>攻撃,危険,熊,恐怖,逃げる,自然,森,自転車,hunter,GoPro</t>
-  </si>
-  <si>
     <t>極限チャレンジ,World Record,宇宙,skydiving,Base Jump,危険,Freefall,Red Bull</t>
   </si>
   <si>
@@ -1629,25 +1608,26 @@
     <t>マジック,GT,Eden Choi</t>
   </si>
   <si>
+    <t>バーテンダー,bar,雰囲気</t>
+  </si>
+  <si>
+    <t>実験,TV,科学,化学,ナトリウム</t>
+  </si>
+  <si>
+    <t>実験,材料,物理,化学,magneticgames,quantumphysics,magnets</t>
+  </si>
+  <si>
+    <t>社会事件,Donald Trump,政治,USA,攻撃,暗殺,Shooter,MAGA,世界,危険</t>
+  </si>
+  <si>
+    <t>短編映画,マッチングアプリ,マッチング,アプリ,コメディ,社会事件,生活</t>
+  </si>
+  <si>
+    <t>短編映画,AI,科学,社会事件</t>
+  </si>
+  <si>
     <t>マジック,GT,Shin Lim</t>
-  </si>
-  <si>
-    <t>バーテンダー,bar,雰囲気</t>
-  </si>
-  <si>
-    <t>実験,TV,科学,化学,ナトリウム</t>
-  </si>
-  <si>
-    <t>実験,材料,物理,化学,magneticgames,quantumphysics,magnets</t>
-  </si>
-  <si>
-    <t>社会事件,Donald Trump,政治,USA,攻撃,暗殺,Shooter,MAGA,世界,危険</t>
-  </si>
-  <si>
-    <t>短編映画,マッチングアプリ,マッチング,アプリ,コメディ,社会事件,生活</t>
-  </si>
-  <si>
-    <t>短編映画,AI,科学,社会事件</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>料理,Gordon Ramsay,紹介,健康</t>
@@ -1686,9 +1666,6 @@
     <t>健康,紹介,料理</t>
   </si>
   <si>
-    <t>バーテンダー,whiskey,コメディ,紹介,meme</t>
-  </si>
-  <si>
     <t>社会事件,暴力団,警察,大阪,山口組,コメディ,meme</t>
   </si>
   <si>
@@ -1698,9 +1675,6 @@
     <t>ライブ,MJ,音楽,Pop,名作,共感,ダンス</t>
   </si>
   <si>
-    <t>癒し,Agarwood,Incense,瞑想,癒し,リラックス,雰囲気,ASMR</t>
-  </si>
-  <si>
     <t>極限チャレンジ,World Record,High Dive,diving,危険,Freefall</t>
   </si>
   <si>
@@ -1716,7 +1690,62 @@
     <t>攻撃,car accident,ペット,病院,危険,Animal Clinic,事故</t>
   </si>
   <si>
-    <t>教育,生活,環境,人類,地球,社会,アニメ</t>
+    <t>インタビュー,共感,野球,林琢真,感動,スポーツ,competition</t>
+  </si>
+  <si>
+    <t>攻撃,危険,熊,恐怖,逃げる,自然,森,自転車,hunter,GoPro,POV</t>
+  </si>
+  <si>
+    <t>バーテンダー,whiskey,コメディ,紹介,meme,文化</t>
+  </si>
+  <si>
+    <t>癒し,Agarwood,Incense,瞑想,癒し,リラックス,雰囲気,ASMR,文化</t>
+  </si>
+  <si>
+    <t>教育,生活,環境,人類,地球,社会,アニメ,資源,文化</t>
+  </si>
+  <si>
+    <t>教育,drug,アニメ</t>
+  </si>
+  <si>
+    <t>教育,アニメ,資源,文化</t>
+  </si>
+  <si>
+    <t>旅行,London,UK,紹介,vlog,英語,勉強,都市,生活,名所,文化</t>
+  </si>
+  <si>
+    <t>旅行,vlog,動物,南極,海,船,紹介,冒険</t>
+  </si>
+  <si>
+    <t>旅行,Rwanda,ゴリラ,動物,自然,危険,IShowSpeed</t>
+  </si>
+  <si>
+    <t>スポーツ,歴史,共感,competition</t>
+  </si>
+  <si>
+    <t>スポーツ,GoPro,POV,共感,Table Tennis,competition</t>
+  </si>
+  <si>
+    <t>スポーツ,Fierste Ljepper,competition,Netherlands,紹介,文化</t>
+  </si>
+  <si>
+    <t>アニメ,ゲーム,Cyberpunk: Edgerunners,Cyberpunk,Cyberpunk 2077,Netflix,音楽,MV,共感,感動,文化,都市,宇宙,月,Rosa Walton,Love,家族,名作,Movieclips,Theme song,宇宙飛行士,未来,戦い,夜景,Lucy,David</t>
+  </si>
+  <si>
+    <t>アニメ,JOJO,Movieclips,共感,名作,DIO,戦い,空条承太郎</t>
+  </si>
+  <si>
+    <t>アニメ,ゲーム,可愛い,お祭り,ウマ娘</t>
+  </si>
+  <si>
+    <t>ドキュメンタリー,MADAGASCAR,島,地球,自然,動物,海,World Record,砂浜,紹介,教育,植物</t>
+  </si>
+  <si>
+    <t>ドキュメンタリー,砂浜,海,生活,文化,東南アジア,fishing,船,自然,共感,塩,Bajo,紹介</t>
+  </si>
+  <si>
+    <t>ドキュメンタリー,Jamaica,Reggae,文化,紹介,自然,山,森,植物,音楽</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2340,7 +2369,7 @@
         <v>0.94868329799999995</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="L2" s="7" t="s">
         <v>206</v>
@@ -2378,7 +2407,7 @@
         <v>0.70710678100000002</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="L3" s="7" t="s">
         <v>208</v>
@@ -2389,10 +2418,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="D4" s="2">
         <v>0</v>
@@ -2416,10 +2445,10 @@
         <v>0.40824829000000001</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>365</v>
+        <v>358</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
     </row>
     <row r="5" spans="1:12" s="7" customFormat="1" ht="18">
@@ -2454,7 +2483,7 @@
         <v>0.63245553200000004</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="L5" s="7" t="s">
         <v>209</v>
@@ -2492,7 +2521,7 @@
         <v>0.72760687499999999</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="L6" s="7" t="s">
         <v>210</v>
@@ -2530,7 +2559,7 @@
         <v>0.44721359500000002</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="L7" s="7" t="s">
         <v>211</v>
@@ -2568,7 +2597,7 @@
         <v>0</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="L8" s="7" t="s">
         <v>212</v>
@@ -2606,7 +2635,7 @@
         <v>0</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>324</v>
+        <v>378</v>
       </c>
       <c r="L9" s="7" t="s">
         <v>213</v>
@@ -2644,7 +2673,7 @@
         <v>0.37796447300000002</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="L10" s="7" t="s">
         <v>214</v>
@@ -2682,7 +2711,7 @@
         <v>0.28867513500000003</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="L11" s="7" t="s">
         <v>215</v>
@@ -2720,7 +2749,7 @@
         <v>0.57735026899999997</v>
       </c>
       <c r="K12" s="6" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="L12" s="7" t="s">
         <v>216</v>
@@ -2758,7 +2787,7 @@
         <v>0.80178372600000003</v>
       </c>
       <c r="K13" s="6" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="L13" s="7" t="s">
         <v>217</v>
@@ -2796,7 +2825,7 @@
         <v>0.28867513500000003</v>
       </c>
       <c r="K14" s="6" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="L14" s="7" t="s">
         <v>218</v>
@@ -2834,7 +2863,7 @@
         <v>0.89442719100000001</v>
       </c>
       <c r="K15" s="6" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="L15" s="7" t="s">
         <v>219</v>
@@ -2872,7 +2901,7 @@
         <v>0.70710678100000002</v>
       </c>
       <c r="K16" s="6" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="L16" s="7" t="s">
         <v>220</v>
@@ -2910,7 +2939,7 @@
         <v>0.45883146800000002</v>
       </c>
       <c r="K17" s="6" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="L17" s="7" t="s">
         <v>221</v>
@@ -2948,7 +2977,7 @@
         <v>0.625543242</v>
       </c>
       <c r="K18" s="6" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="L18" s="7" t="s">
         <v>222</v>
@@ -2986,7 +3015,7 @@
         <v>0.15430335000000001</v>
       </c>
       <c r="K19" s="6" t="s">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="L19" s="7" t="s">
         <v>223</v>
@@ -3024,7 +3053,7 @@
         <v>0.30151134499999999</v>
       </c>
       <c r="K20" s="6" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="L20" s="7" t="s">
         <v>224</v>
@@ -3062,7 +3091,7 @@
         <v>0.70710678100000002</v>
       </c>
       <c r="K21" s="6" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="L21" s="7" t="s">
         <v>225</v>
@@ -3100,7 +3129,7 @@
         <v>0.688247202</v>
       </c>
       <c r="K22" s="6" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="L22" s="7" t="s">
         <v>226</v>
@@ -3138,7 +3167,7 @@
         <v>0.48507125000000001</v>
       </c>
       <c r="K23" s="6" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="L23" s="7" t="s">
         <v>227</v>
@@ -3176,7 +3205,7 @@
         <v>0.25819889000000001</v>
       </c>
       <c r="K24" s="6" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="L24" s="7" t="s">
         <v>228</v>
@@ -3214,7 +3243,7 @@
         <v>0.57735026899999997</v>
       </c>
       <c r="K25" s="6" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="L25" s="7" t="s">
         <v>229</v>
@@ -3252,7 +3281,7 @@
         <v>0.62469504799999998</v>
       </c>
       <c r="K26" s="6" t="s">
-        <v>370</v>
+        <v>363</v>
       </c>
       <c r="L26" s="7" t="s">
         <v>230</v>
@@ -3290,7 +3319,7 @@
         <v>0</v>
       </c>
       <c r="K27" s="6" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="L27" s="7" t="s">
         <v>231</v>
@@ -3328,7 +3357,7 @@
         <v>0.78446454099999996</v>
       </c>
       <c r="K28" s="6" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="L28" s="7" t="s">
         <v>232</v>
@@ -3366,7 +3395,7 @@
         <v>0</v>
       </c>
       <c r="K29" s="6" t="s">
-        <v>335</v>
+        <v>379</v>
       </c>
       <c r="L29" s="7" t="s">
         <v>233</v>
@@ -3404,7 +3433,7 @@
         <v>0.55470019599999998</v>
       </c>
       <c r="K30" s="6" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="L30" s="7" t="s">
         <v>234</v>
@@ -3442,7 +3471,7 @@
         <v>0</v>
       </c>
       <c r="K31" s="6" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="L31" s="7" t="s">
         <v>235</v>
@@ -3480,7 +3509,7 @@
         <v>0.688247202</v>
       </c>
       <c r="K32" s="6" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="L32" s="7" t="s">
         <v>236</v>
@@ -3518,7 +3547,7 @@
         <v>0.35355339099999999</v>
       </c>
       <c r="K33" s="6" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="L33" s="7" t="s">
         <v>237</v>
@@ -3556,7 +3585,7 @@
         <v>0.55470019599999998</v>
       </c>
       <c r="K34" s="6" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="L34" s="7" t="s">
         <v>238</v>
@@ -3594,7 +3623,7 @@
         <v>0.26726124200000001</v>
       </c>
       <c r="K35" s="6" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="L35" s="7" t="s">
         <v>239</v>
@@ -3632,7 +3661,7 @@
         <v>0.53452248400000002</v>
       </c>
       <c r="K36" s="6" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="L36" s="7" t="s">
         <v>240</v>
@@ -3670,7 +3699,7 @@
         <v>0.426401433</v>
       </c>
       <c r="K37" s="6" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="L37" s="7" t="s">
         <v>241</v>
@@ -3708,7 +3737,7 @@
         <v>0</v>
       </c>
       <c r="K38" s="6" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="L38" s="7" t="s">
         <v>242</v>
@@ -3746,7 +3775,7 @@
         <v>0</v>
       </c>
       <c r="K39" s="6" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="L39" s="7" t="s">
         <v>243</v>
@@ -3784,7 +3813,7 @@
         <v>0.57735026899999997</v>
       </c>
       <c r="K40" s="6" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="L40" s="7" t="s">
         <v>244</v>
@@ -3822,7 +3851,7 @@
         <v>0.53452248400000002</v>
       </c>
       <c r="K41" s="6" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="L41" s="7" t="s">
         <v>245</v>
@@ -3860,7 +3889,7 @@
         <v>0.23570226</v>
       </c>
       <c r="K42" s="6" t="s">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="L42" s="7" t="s">
         <v>246</v>
@@ -3898,7 +3927,7 @@
         <v>0.365148372</v>
       </c>
       <c r="K43" s="6" t="s">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="L43" s="7" t="s">
         <v>247</v>
@@ -3936,7 +3965,7 @@
         <v>0.57735026899999997</v>
       </c>
       <c r="K44" s="6" t="s">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="L44" s="7" t="s">
         <v>248</v>
@@ -3974,7 +4003,7 @@
         <v>0</v>
       </c>
       <c r="K45" s="6" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="L45" s="7" t="s">
         <v>249</v>
@@ -4012,7 +4041,7 @@
         <v>0</v>
       </c>
       <c r="K46" s="6" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="L46" s="7" t="s">
         <v>250</v>
@@ -4050,7 +4079,7 @@
         <v>0</v>
       </c>
       <c r="K47" s="6" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="L47" s="7" t="s">
         <v>251</v>
@@ -4088,7 +4117,7 @@
         <v>0.5</v>
       </c>
       <c r="K48" s="6" t="s">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="L48" s="7" t="s">
         <v>252</v>
@@ -4126,7 +4155,7 @@
         <v>0.174077656</v>
       </c>
       <c r="K49" s="6" t="s">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="L49" s="7" t="s">
         <v>253</v>
@@ -4164,7 +4193,7 @@
         <v>0.174077656</v>
       </c>
       <c r="K50" s="6" t="s">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="L50" s="7" t="s">
         <v>254</v>
@@ -4202,7 +4231,7 @@
         <v>0.27735009799999999</v>
       </c>
       <c r="K51" s="6" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="L51" s="7" t="s">
         <v>255</v>
@@ -4240,7 +4269,7 @@
         <v>0.80178372600000003</v>
       </c>
       <c r="K52" s="6" t="s">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="L52" s="7" t="s">
         <v>256</v>
@@ -4278,7 +4307,7 @@
         <v>0.514495755</v>
       </c>
       <c r="K53" s="6" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="L53" s="7" t="s">
         <v>257</v>
@@ -4316,7 +4345,7 @@
         <v>0.514495755</v>
       </c>
       <c r="K54" s="6" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="L54" s="7" t="s">
         <v>258</v>
@@ -4354,7 +4383,7 @@
         <v>0.63960214900000001</v>
       </c>
       <c r="K55" s="6" t="s">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="L55" s="7" t="s">
         <v>259</v>
@@ -4392,7 +4421,7 @@
         <v>0.68599434100000001</v>
       </c>
       <c r="K56" s="6" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="L56" s="7" t="s">
         <v>260</v>
@@ -4430,7 +4459,7 @@
         <v>0.47140452100000002</v>
       </c>
       <c r="K57" s="6" t="s">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="L57" s="7" t="s">
         <v>261</v>
@@ -4468,7 +4497,7 @@
         <v>0</v>
       </c>
       <c r="K58" s="6" t="s">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="L58" s="7" t="s">
         <v>262</v>
@@ -4506,7 +4535,7 @@
         <v>0.53881590599999996</v>
       </c>
       <c r="K59" s="6" t="s">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="L59" s="7" t="s">
         <v>263</v>
@@ -4544,7 +4573,7 @@
         <v>0</v>
       </c>
       <c r="K60" s="6" t="s">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="L60" s="7" t="s">
         <v>264</v>
@@ -4582,7 +4611,7 @@
         <v>0.196116135</v>
       </c>
       <c r="K61" s="6" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="L61" s="7" t="s">
         <v>265</v>
@@ -4620,7 +4649,7 @@
         <v>0</v>
       </c>
       <c r="K62" s="6" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="L62" s="7" t="s">
         <v>266</v>
@@ -4658,7 +4687,7 @@
         <v>0.39223226999999999</v>
       </c>
       <c r="K63" s="6" t="s">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="L63" t="s">
         <v>267</v>
@@ -4696,7 +4725,7 @@
         <v>0.39223226999999999</v>
       </c>
       <c r="K64" s="6" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="L64" t="s">
         <v>268</v>
@@ -4772,7 +4801,7 @@
         <v>0.174077656</v>
       </c>
       <c r="K66" s="6" t="s">
-        <v>382</v>
+        <v>373</v>
       </c>
       <c r="L66" t="s">
         <v>270</v>
@@ -4810,7 +4839,7 @@
         <v>0.816496581</v>
       </c>
       <c r="K67" s="6" t="s">
-        <v>383</v>
+        <v>374</v>
       </c>
       <c r="L67" t="s">
         <v>271</v>
@@ -4848,7 +4877,7 @@
         <v>0</v>
       </c>
       <c r="K68" s="6" t="s">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="L68" t="s">
         <v>272</v>
@@ -4886,7 +4915,7 @@
         <v>0</v>
       </c>
       <c r="K69" s="6" t="s">
-        <v>385</v>
+        <v>376</v>
       </c>
       <c r="L69" t="s">
         <v>273</v>
@@ -4924,7 +4953,7 @@
         <v>0</v>
       </c>
       <c r="K70" s="6" t="s">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="L70" t="s">
         <v>274</v>
@@ -4962,7 +4991,7 @@
         <v>0</v>
       </c>
       <c r="K71" s="6" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="L71" t="s">
         <v>275</v>
@@ -4999,8 +5028,8 @@
       <c r="J72" s="2">
         <v>0</v>
       </c>
-      <c r="K72" s="2" t="s">
-        <v>306</v>
+      <c r="K72" s="6" t="s">
+        <v>383</v>
       </c>
       <c r="L72" t="s">
         <v>276</v>
@@ -5037,8 +5066,8 @@
       <c r="J73" s="2">
         <v>0</v>
       </c>
-      <c r="K73" s="2" t="s">
-        <v>306</v>
+      <c r="K73" s="6" t="s">
+        <v>384</v>
       </c>
       <c r="L73" t="s">
         <v>277</v>
@@ -5075,8 +5104,8 @@
       <c r="J74" s="2">
         <v>0.66666666699999999</v>
       </c>
-      <c r="K74" s="2" t="s">
-        <v>307</v>
+      <c r="K74" s="6" t="s">
+        <v>385</v>
       </c>
       <c r="L74" t="s">
         <v>278</v>
@@ -5113,8 +5142,8 @@
       <c r="J75" s="2">
         <v>0.47140452100000002</v>
       </c>
-      <c r="K75" s="2" t="s">
-        <v>307</v>
+      <c r="K75" s="6" t="s">
+        <v>386</v>
       </c>
       <c r="L75" t="s">
         <v>279</v>
@@ -5151,8 +5180,8 @@
       <c r="J76" s="2">
         <v>1</v>
       </c>
-      <c r="K76" s="2" t="s">
-        <v>307</v>
+      <c r="K76" s="6" t="s">
+        <v>387</v>
       </c>
       <c r="L76" t="s">
         <v>280</v>
@@ -5189,8 +5218,8 @@
       <c r="J77" s="2">
         <v>0.26726124200000001</v>
       </c>
-      <c r="K77" s="2" t="s">
-        <v>308</v>
+      <c r="K77" s="6" t="s">
+        <v>388</v>
       </c>
       <c r="L77" t="s">
         <v>281</v>
@@ -5227,8 +5256,8 @@
       <c r="J78" s="2">
         <v>0</v>
       </c>
-      <c r="K78" s="2" t="s">
-        <v>308</v>
+      <c r="K78" s="6" t="s">
+        <v>389</v>
       </c>
       <c r="L78" t="s">
         <v>282</v>
@@ -5265,8 +5294,8 @@
       <c r="J79" s="2">
         <v>0.57735026899999997</v>
       </c>
-      <c r="K79" s="2" t="s">
-        <v>308</v>
+      <c r="K79" s="6" t="s">
+        <v>390</v>
       </c>
       <c r="L79" t="s">
         <v>283</v>
@@ -5303,8 +5332,8 @@
       <c r="J80" s="2">
         <v>0</v>
       </c>
-      <c r="K80" s="2" t="s">
-        <v>309</v>
+      <c r="K80" s="6" t="s">
+        <v>391</v>
       </c>
       <c r="L80" t="s">
         <v>284</v>
@@ -5341,8 +5370,8 @@
       <c r="J81" s="2">
         <v>0.70710678100000002</v>
       </c>
-      <c r="K81" s="2" t="s">
-        <v>309</v>
+      <c r="K81" s="6" t="s">
+        <v>392</v>
       </c>
       <c r="L81" t="s">
         <v>285</v>
@@ -5379,8 +5408,8 @@
       <c r="J82" s="2">
         <v>0.70710678100000002</v>
       </c>
-      <c r="K82" s="2" t="s">
-        <v>309</v>
+      <c r="K82" s="6" t="s">
+        <v>393</v>
       </c>
       <c r="L82" t="s">
         <v>286</v>
@@ -5417,8 +5446,8 @@
       <c r="J83" s="2">
         <v>0.30151134499999999</v>
       </c>
-      <c r="K83" s="2" t="s">
-        <v>310</v>
+      <c r="K83" s="6" t="s">
+        <v>394</v>
       </c>
       <c r="L83" t="s">
         <v>287</v>
@@ -5455,8 +5484,8 @@
       <c r="J84" s="2">
         <v>0</v>
       </c>
-      <c r="K84" s="2" t="s">
-        <v>310</v>
+      <c r="K84" s="6" t="s">
+        <v>395</v>
       </c>
       <c r="L84" t="s">
         <v>288</v>
@@ -5493,8 +5522,8 @@
       <c r="J85" s="2">
         <v>0.57735026899999997</v>
       </c>
-      <c r="K85" s="2" t="s">
-        <v>310</v>
+      <c r="K85" s="6" t="s">
+        <v>396</v>
       </c>
       <c r="L85" t="s">
         <v>289</v>
@@ -5532,7 +5561,7 @@
         <v>0</v>
       </c>
       <c r="K86" s="2" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="L86" t="s">
         <v>290</v>
@@ -5570,7 +5599,7 @@
         <v>0.29488391200000003</v>
       </c>
       <c r="K87" s="2" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="L87" t="s">
         <v>291</v>
@@ -5608,7 +5637,7 @@
         <v>0</v>
       </c>
       <c r="K88" s="2" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="L88" t="s">
         <v>292</v>
@@ -5646,7 +5675,7 @@
         <v>0.51639777899999995</v>
       </c>
       <c r="K89" s="2" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="L89" t="s">
         <v>293</v>
@@ -5684,7 +5713,7 @@
         <v>0.31622776600000002</v>
       </c>
       <c r="K90" s="2" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="L90" t="s">
         <v>294</v>
@@ -5722,7 +5751,7 @@
         <v>0.43643578</v>
       </c>
       <c r="K91" s="2" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="L91" t="s">
         <v>295</v>
@@ -5760,7 +5789,7 @@
         <v>0</v>
       </c>
       <c r="K92" s="2" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="L92" t="s">
         <v>296</v>
@@ -5798,7 +5827,7 @@
         <v>0</v>
       </c>
       <c r="K93" s="2" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="L93" t="s">
         <v>297</v>
@@ -5836,7 +5865,7 @@
         <v>0</v>
       </c>
       <c r="K94" s="2" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="L94" t="s">
         <v>298</v>
@@ -5874,7 +5903,7 @@
         <v>0.53033008599999998</v>
       </c>
       <c r="K95" s="2" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="L95" t="s">
         <v>299</v>
@@ -5912,7 +5941,7 @@
         <v>0.48507125000000001</v>
       </c>
       <c r="K96" s="2" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="L96" t="s">
         <v>300</v>
@@ -5950,7 +5979,7 @@
         <v>0.56568542499999996</v>
       </c>
       <c r="K97" s="2" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="L97" t="s">
         <v>301</v>
@@ -5988,7 +6017,7 @@
         <v>0.78446454099999996</v>
       </c>
       <c r="K98" s="2" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="L98" t="s">
         <v>302</v>
@@ -6026,7 +6055,7 @@
         <v>0.63960214900000001</v>
       </c>
       <c r="K99" s="2" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="L99" t="s">
         <v>303</v>
@@ -6064,7 +6093,7 @@
         <v>0.54433105400000004</v>
       </c>
       <c r="K100" s="2" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="L100" t="s">
         <v>304</v>

--- a/library.xlsx
+++ b/library.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xxc/Desktop/xxc/拓殖大学/研究室/評価実験/video-recommend-system/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AEDC096-B148-B54E-877C-2AF58100F138}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E51BCD9-B35F-3F4D-BA5D-68F028CF16B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{F40E9203-8E2D-9949-9A4C-F506F7C93633}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="397">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="407">
   <si>
     <t>No.</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -1428,21 +1428,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>歴史</t>
-  </si>
-  <si>
-    <t>ファッション</t>
-  </si>
-  <si>
-    <t>文化</t>
-  </si>
-  <si>
-    <t>ゲーム</t>
-  </si>
-  <si>
-    <t>ダンス</t>
-  </si>
-  <si>
     <t>cook</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1477,6 +1462,219 @@
   </si>
   <si>
     <t>マジック,コメディ</t>
+  </si>
+  <si>
+    <t>IShowSpeed,危険,極限チャレンジ</t>
+  </si>
+  <si>
+    <t>癒し,Jazz,ライブ,音楽,牛,動物,自然,景色,雰囲気,リラックス,山,可愛い</t>
+  </si>
+  <si>
+    <t>極限チャレンジ,Base Jump,skydiving,危険,motorbike,崖,Red Bull</t>
+  </si>
+  <si>
+    <t>インタビュー,カラス,TV</t>
+  </si>
+  <si>
+    <t>コメディ,星野源,ドラム,音楽,Pop</t>
+  </si>
+  <si>
+    <t>癒し,Lamb,動物,自然,可愛い,リラックス,ペット</t>
+  </si>
+  <si>
+    <t>極限チャレンジ,World Record,宇宙,skydiving,Base Jump,危険,Freefall,Red Bull</t>
+  </si>
+  <si>
+    <t>災害,GoPro,火災,危険,消防,Raw POV</t>
+  </si>
+  <si>
+    <t>自然,景色,癒し,日本,ASMR,リラックス,山,上高地,河,鳥,名所,旅行,雰囲気</t>
+  </si>
+  <si>
+    <t>生活,主婦,ライフハック</t>
+  </si>
+  <si>
+    <t>実験,化学,スライム,ダイラタンシー</t>
+  </si>
+  <si>
+    <t>短編映画,感動,共感,Love,家族,父親,娘,離婚</t>
+  </si>
+  <si>
+    <t>ペット,犬,動物,生活,可愛い,家族,子供,癒し,Love</t>
+  </si>
+  <si>
+    <t>自然,景色,癒し,日本,ASMR,BGM,リラックス,鳥,花,桜,リラックス,雰囲気,集中,勉強,仕事,,植物,ピアノ</t>
+  </si>
+  <si>
+    <t>自然,景色,癒し,日本,BGM,リラックス,リラックス,雰囲気,集中,勉強,仕事,夜空,夜景,極光</t>
+  </si>
+  <si>
+    <t>料理,camp,癒し,雰囲気,冬</t>
+  </si>
+  <si>
+    <t>夜景,dji,上海,都市,中国,景色,名所</t>
+  </si>
+  <si>
+    <t>夜景,Hong Kong,都市,中国,景色,名所</t>
+  </si>
+  <si>
+    <t>園芸,癒し,BGM,リラックス,花,リラックス,雰囲気,集中,植物,ピアノ</t>
+  </si>
+  <si>
+    <t>レトロ,東京,都市,日本</t>
+  </si>
+  <si>
+    <t>レトロ,NY,USA,都市,生活,夜景,Jazz,音楽</t>
+  </si>
+  <si>
+    <t>BGM,リラックス,勉強,仕事,雰囲気,集中,ピアノ</t>
+  </si>
+  <si>
+    <t>BGM,坂本龍一,ピアノ,名作,勉強,仕事,リラックス,雰囲気,集中,Theme song</t>
+  </si>
+  <si>
+    <t>インタビュー,Donald Trump,政治,USA,Iran,世界</t>
+  </si>
+  <si>
+    <t>科学,物理,宇宙,物理,教育</t>
+  </si>
+  <si>
+    <t>生活,vlog,日本,大阪,料理,掃除,reading,運動</t>
+  </si>
+  <si>
+    <t>生活,vlog,撮影,結婚,子供,共感,感動</t>
+  </si>
+  <si>
+    <t>マジック,GT,Eden Choi</t>
+  </si>
+  <si>
+    <t>マジック,GT,Shin Lim</t>
+  </si>
+  <si>
+    <t>バーテンダー,bar,雰囲気</t>
+  </si>
+  <si>
+    <t>実験,TV,科学,化学,ナトリウム</t>
+  </si>
+  <si>
+    <t>実験,材料,物理,化学,magneticgames,quantumphysics,magnets</t>
+  </si>
+  <si>
+    <t>社会事件,Donald Trump,政治,USA,攻撃,暗殺,Shooter,MAGA,世界,危険</t>
+  </si>
+  <si>
+    <t>短編映画,マッチングアプリ,マッチング,アプリ,コメディ,社会事件,生活</t>
+  </si>
+  <si>
+    <t>短編映画,AI,科学,社会事件</t>
+  </si>
+  <si>
+    <t>料理,Gordon Ramsay,紹介,健康</t>
+  </si>
+  <si>
+    <t>健康,運動,紹介,筋肉,ダイエット,整体,柔軟体操</t>
+  </si>
+  <si>
+    <t>バーテンダー,日本,コメディ,bar,meme</t>
+  </si>
+  <si>
+    <t>社会事件,Will Smith,Oscars,俳優,喧嘩,エンタメ,Love,TV,meme</t>
+  </si>
+  <si>
+    <t>ライブ,音楽,Pop,ドラム,rock,可愛い,meme</t>
+  </si>
+  <si>
+    <t>チャレンジ,コメディ,料理,危険,牛丼,meme</t>
+  </si>
+  <si>
+    <t>ペット,チンチラ,ペット,動物,可愛い,紹介</t>
+  </si>
+  <si>
+    <t>料理,主婦,紹介,健康,生活,vlog,日本,家族,癒し,雰囲気</t>
+  </si>
+  <si>
+    <t>園芸,紹介,植物</t>
+  </si>
+  <si>
+    <t>健康,医療,科学,教育,病院</t>
+  </si>
+  <si>
+    <t>健康,紹介,料理</t>
+  </si>
+  <si>
+    <t>社会事件,暴力団,警察,大阪,山口組,コメディ,meme</t>
+  </si>
+  <si>
+    <t>ライブ,Queen,音楽,rock,名作,慈善,共感</t>
+  </si>
+  <si>
+    <t>ライブ,MJ,音楽,Pop,名作,共感,ダンス</t>
+  </si>
+  <si>
+    <t>極限チャレンジ,World Record,High Dive,diving,危険,Freefall</t>
+  </si>
+  <si>
+    <t>コメディ,BBQ,料理,紹介,meme</t>
+  </si>
+  <si>
+    <t>災害,土石流,危険,恐怖,自然,死亡,社会事件</t>
+  </si>
+  <si>
+    <t>攻撃,ガザ,イスラエル,爆発,恐怖,危険,政治,世界,ミサイル,死亡,戦争,病院</t>
+  </si>
+  <si>
+    <t>攻撃,car accident,ペット,病院,危険,Animal Clinic,事故</t>
+  </si>
+  <si>
+    <t>インタビュー,共感,野球,林琢真,感動,スポーツ,competition</t>
+  </si>
+  <si>
+    <t>攻撃,危険,熊,恐怖,逃げる,自然,森,自転車,hunter,GoPro,POV</t>
+  </si>
+  <si>
+    <t>バーテンダー,whiskey,コメディ,紹介,meme,文化</t>
+  </si>
+  <si>
+    <t>癒し,Agarwood,Incense,瞑想,癒し,リラックス,雰囲気,ASMR,文化</t>
+  </si>
+  <si>
+    <t>教育,生活,環境,人類,地球,社会,アニメ,資源,文化</t>
+  </si>
+  <si>
+    <t>教育,drug,アニメ</t>
+  </si>
+  <si>
+    <t>教育,アニメ,資源,文化</t>
+  </si>
+  <si>
+    <t>旅行,London,UK,紹介,vlog,英語,勉強,都市,生活,名所,文化</t>
+  </si>
+  <si>
+    <t>旅行,vlog,動物,南極,海,船,紹介,冒険</t>
+  </si>
+  <si>
+    <t>旅行,Rwanda,ゴリラ,動物,自然,危険,IShowSpeed</t>
+  </si>
+  <si>
+    <t>スポーツ,GoPro,POV,共感,Table Tennis,competition</t>
+  </si>
+  <si>
+    <t>スポーツ,Fierste Ljepper,competition,Netherlands,紹介,文化</t>
+  </si>
+  <si>
+    <t>アニメ,JOJO,Movieclips,共感,名作,DIO,戦い,空条承太郎</t>
+  </si>
+  <si>
+    <t>アニメ,ゲーム,可愛い,お祭り,ウマ娘</t>
+  </si>
+  <si>
+    <t>ドキュメンタリー,MADAGASCAR,島,地球,自然,動物,海,World Record,砂浜,紹介,教育,植物</t>
+  </si>
+  <si>
+    <t>ドキュメンタリー,砂浜,海,生活,文化,東南アジア,fishing,船,自然,共感,塩,Bajo,紹介</t>
+  </si>
+  <si>
+    <t>ドキュメンタリー,Jamaica,Reggae,文化,紹介,自然,山,森,植物,音楽</t>
   </si>
   <si>
     <r>
@@ -1489,27 +1687,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>‪</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="等线"/>
-        <family val="4"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>MrBeast</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>‬</t>
+      <t>Mr.beast</t>
     </r>
     <r>
       <rPr>
@@ -1524,228 +1702,81 @@
     </r>
   </si>
   <si>
-    <t>IShowSpeed,危険,極限チャレンジ</t>
-  </si>
-  <si>
-    <t>癒し,Jazz,ライブ,音楽,牛,動物,自然,景色,雰囲気,リラックス,山,可愛い</t>
-  </si>
-  <si>
-    <t>極限チャレンジ,Base Jump,skydiving,危険,motorbike,崖,Red Bull</t>
-  </si>
-  <si>
-    <t>インタビュー,カラス,TV</t>
-  </si>
-  <si>
-    <t>コメディ,星野源,ドラム,音楽,Pop</t>
-  </si>
-  <si>
-    <t>癒し,Lamb,動物,自然,可愛い,リラックス,ペット</t>
-  </si>
-  <si>
-    <t>極限チャレンジ,World Record,宇宙,skydiving,Base Jump,危険,Freefall,Red Bull</t>
-  </si>
-  <si>
-    <t>災害,GoPro,火災,危険,消防,Raw POV</t>
-  </si>
-  <si>
-    <t>自然,景色,癒し,日本,ASMR,リラックス,山,上高地,河,鳥,名所,旅行,雰囲気</t>
-  </si>
-  <si>
-    <t>生活,主婦,ライフハック</t>
-  </si>
-  <si>
-    <t>実験,化学,スライム,ダイラタンシー</t>
-  </si>
-  <si>
-    <t>短編映画,感動,共感,Love,家族,父親,娘,離婚</t>
-  </si>
-  <si>
-    <t>ペット,犬,動物,生活,可愛い,家族,子供,癒し,Love</t>
-  </si>
-  <si>
-    <t>自然,景色,癒し,日本,ASMR,BGM,リラックス,鳥,花,桜,リラックス,雰囲気,集中,勉強,仕事,,植物,ピアノ</t>
-  </si>
-  <si>
-    <t>自然,景色,癒し,日本,BGM,リラックス,リラックス,雰囲気,集中,勉強,仕事,夜空,夜景,極光</t>
-  </si>
-  <si>
-    <t>料理,camp,癒し,雰囲気,冬</t>
-  </si>
-  <si>
-    <t>夜景,dji,上海,都市,中国,景色,名所</t>
-  </si>
-  <si>
-    <t>夜景,Hong Kong,都市,中国,景色,名所</t>
-  </si>
-  <si>
-    <t>園芸,癒し,BGM,リラックス,花,リラックス,雰囲気,集中,植物,ピアノ</t>
-  </si>
-  <si>
-    <t>レトロ,東京,都市,日本</t>
-  </si>
-  <si>
-    <t>レトロ,NY,USA,都市,生活,夜景,Jazz,音楽</t>
-  </si>
-  <si>
-    <t>BGM,リラックス,勉強,仕事,雰囲気,集中,ピアノ</t>
-  </si>
-  <si>
-    <t>BGM,坂本龍一,ピアノ,名作,勉強,仕事,リラックス,雰囲気,集中,Theme song</t>
-  </si>
-  <si>
-    <t>インタビュー,Donald Trump,政治,USA,Iran,世界</t>
-  </si>
-  <si>
-    <t>科学,物理,宇宙,物理,教育</t>
-  </si>
-  <si>
-    <t>生活,vlog,日本,大阪,料理,掃除,reading,運動</t>
-  </si>
-  <si>
-    <t>生活,vlog,撮影,結婚,子供,共感,感動</t>
-  </si>
-  <si>
-    <t>マジック,GT,Eden Choi</t>
-  </si>
-  <si>
-    <t>バーテンダー,bar,雰囲気</t>
-  </si>
-  <si>
-    <t>実験,TV,科学,化学,ナトリウム</t>
-  </si>
-  <si>
-    <t>実験,材料,物理,化学,magneticgames,quantumphysics,magnets</t>
-  </si>
-  <si>
-    <t>社会事件,Donald Trump,政治,USA,攻撃,暗殺,Shooter,MAGA,世界,危険</t>
-  </si>
-  <si>
-    <t>短編映画,マッチングアプリ,マッチング,アプリ,コメディ,社会事件,生活</t>
-  </si>
-  <si>
-    <t>短編映画,AI,科学,社会事件</t>
-  </si>
-  <si>
-    <t>マジック,GT,Shin Lim</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>料理,Gordon Ramsay,紹介,健康</t>
-  </si>
-  <si>
-    <t>健康,運動,紹介,筋肉,ダイエット,整体,柔軟体操</t>
-  </si>
-  <si>
-    <t>バーテンダー,日本,コメディ,bar,meme</t>
-  </si>
-  <si>
-    <t>社会事件,Will Smith,Oscars,俳優,喧嘩,エンタメ,Love,TV,meme</t>
-  </si>
-  <si>
-    <t>ライブ,音楽,Pop,ドラム,rock,可愛い,meme</t>
-  </si>
-  <si>
-    <t>チャレンジ,コメディ,料理,危険,牛丼,meme</t>
-  </si>
-  <si>
-    <t>攻撃,911,飛行機,terrorists,危険,USA,死亡,恐怖,爆発,火災,world trade center,twin towers,crash,社会事件,hijack,政治,ビル,世界,消防,戦争</t>
-  </si>
-  <si>
-    <t>ペット,チンチラ,ペット,動物,可愛い,紹介</t>
-  </si>
-  <si>
-    <t>料理,主婦,紹介,健康,生活,vlog,日本,家族,癒し,雰囲気</t>
-  </si>
-  <si>
-    <t>園芸,紹介,植物</t>
-  </si>
-  <si>
-    <t>健康,医療,科学,教育,病院</t>
-  </si>
-  <si>
-    <t>健康,紹介,料理</t>
-  </si>
-  <si>
-    <t>社会事件,暴力団,警察,大阪,山口組,コメディ,meme</t>
-  </si>
-  <si>
-    <t>ライブ,Queen,音楽,rock,名作,慈善,共感</t>
-  </si>
-  <si>
-    <t>ライブ,MJ,音楽,Pop,名作,共感,ダンス</t>
-  </si>
-  <si>
-    <t>極限チャレンジ,World Record,High Dive,diving,危険,Freefall</t>
-  </si>
-  <si>
-    <t>コメディ,BBQ,料理,紹介,meme</t>
-  </si>
-  <si>
-    <t>災害,土石流,危険,恐怖,自然,死亡,社会事件</t>
-  </si>
-  <si>
-    <t>攻撃,ガザ,イスラエル,爆発,恐怖,危険,政治,世界,ミサイル,死亡,戦争,病院</t>
-  </si>
-  <si>
-    <t>攻撃,car accident,ペット,病院,危険,Animal Clinic,事故</t>
-  </si>
-  <si>
-    <t>インタビュー,共感,野球,林琢真,感動,スポーツ,competition</t>
-  </si>
-  <si>
-    <t>攻撃,危険,熊,恐怖,逃げる,自然,森,自転車,hunter,GoPro,POV</t>
-  </si>
-  <si>
-    <t>バーテンダー,whiskey,コメディ,紹介,meme,文化</t>
-  </si>
-  <si>
-    <t>癒し,Agarwood,Incense,瞑想,癒し,リラックス,雰囲気,ASMR,文化</t>
-  </si>
-  <si>
-    <t>教育,生活,環境,人類,地球,社会,アニメ,資源,文化</t>
-  </si>
-  <si>
-    <t>教育,drug,アニメ</t>
-  </si>
-  <si>
-    <t>教育,アニメ,資源,文化</t>
-  </si>
-  <si>
-    <t>旅行,London,UK,紹介,vlog,英語,勉強,都市,生活,名所,文化</t>
-  </si>
-  <si>
-    <t>旅行,vlog,動物,南極,海,船,紹介,冒険</t>
-  </si>
-  <si>
-    <t>旅行,Rwanda,ゴリラ,動物,自然,危険,IShowSpeed</t>
-  </si>
-  <si>
-    <t>スポーツ,歴史,共感,competition</t>
-  </si>
-  <si>
-    <t>スポーツ,GoPro,POV,共感,Table Tennis,competition</t>
-  </si>
-  <si>
-    <t>スポーツ,Fierste Ljepper,competition,Netherlands,紹介,文化</t>
-  </si>
-  <si>
-    <t>アニメ,ゲーム,Cyberpunk: Edgerunners,Cyberpunk,Cyberpunk 2077,Netflix,音楽,MV,共感,感動,文化,都市,宇宙,月,Rosa Walton,Love,家族,名作,Movieclips,Theme song,宇宙飛行士,未来,戦い,夜景,Lucy,David</t>
-  </si>
-  <si>
-    <t>アニメ,JOJO,Movieclips,共感,名作,DIO,戦い,空条承太郎</t>
-  </si>
-  <si>
-    <t>アニメ,ゲーム,可愛い,お祭り,ウマ娘</t>
-  </si>
-  <si>
-    <t>ドキュメンタリー,MADAGASCAR,島,地球,自然,動物,海,World Record,砂浜,紹介,教育,植物</t>
-  </si>
-  <si>
-    <t>ドキュメンタリー,砂浜,海,生活,文化,東南アジア,fishing,船,自然,共感,塩,Bajo,紹介</t>
-  </si>
-  <si>
-    <t>ドキュメンタリー,Jamaica,Reggae,文化,紹介,自然,山,森,植物,音楽</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <t>攻撃,911,飛行機,terrorists,危険,USA,死亡,恐怖,爆発,火災,world trade center,twin towers,crash,社会事件,hijack,政治,ビル,世界,消防,都市</t>
+  </si>
+  <si>
+    <t>スポーツ,歴史,共感,competition,Video Highlights</t>
+  </si>
+  <si>
+    <t>アニメ,ゲーム,Cyberpunk: Edgerunners,Cyberpunk,Cyberpunk 2077,Netflix,音楽,MV,共感,感動,文化,都市,宇宙,月,Rosa Walton,Love,家族,名作,Movieclips,Theme song,宇宙飛行士,未来,戦い,夜景,Lucy,David,Video Highlights</t>
+  </si>
+  <si>
+    <t>歴史,溥儀,World War Two,共感,中国,皇帝,東京,裁判所,ドキュメンタリー,戦争</t>
+  </si>
+  <si>
+    <t>歴史,World War Two,共感,ドイツ,Siemens,ヒトラー,演説,Nazi,ドキュメンタリー,戦争</t>
+  </si>
+  <si>
+    <t>歴史,911,USA,死亡,恐怖,火災,world trade center,twin towers,社会事件,政治,世界,消防,生活,ドキュメンタリー,都市</t>
+  </si>
+  <si>
+    <t>ファッション,女性,紹介</t>
+  </si>
+  <si>
+    <t>ファッション,東京,生活,紹介,インタビュー,都市</t>
+  </si>
+  <si>
+    <r>
+      <t>ファッション,Victoria's Secret,Video Highlights,Taylor Swift,Pop,音楽,女性,ファッション</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="4"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>モデル,ライブ,共感,名作</t>
+    </r>
+  </si>
+  <si>
+    <t>文化,性格,心理学,教育,アニメ,紹介</t>
+  </si>
+  <si>
+    <t>文化,スペイン,日本,生活,紹介,比較</t>
+  </si>
+  <si>
+    <t>文化,規則,日本,生活,紹介,比較</t>
+  </si>
+  <si>
+    <t>ゲーム,Speedrun,meme,コメディ,共感</t>
+  </si>
+  <si>
+    <t>ゲーム,風船,Mr.beast,チャレンジ,コメディ</t>
+  </si>
+  <si>
+    <t>ゲーム,Video Highlights,GTA6,GTA,音楽,Pop,共感,感動,名作,紹介,USA,Rockstar,都市,海</t>
+  </si>
+  <si>
+    <t>ダンス,Pop,音楽,リラックス,Staying Alive,Trio</t>
+  </si>
+  <si>
+    <t>ダンス,アニメ,Pop,音楽,コメディ,宇宙人,宇宙,MV</t>
+  </si>
+  <si>
+    <t>ダンス,Michael Jackson,音楽,Pop,映画,名作,共感,MV,恐怖</t>
   </si>
 </sst>
 </file>
@@ -1924,7 +1955,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1945,6 +1976,9 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2299,7 +2333,7 @@
     <col min="4" max="10" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="1" spans="1:12" s="8" customFormat="1" ht="18">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2337,2321 +2371,2321 @@
         <v>207</v>
       </c>
     </row>
-    <row r="2" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="2" spans="1:12" s="8" customFormat="1" ht="18">
       <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="8" t="s">
         <v>108</v>
       </c>
       <c r="D2" s="2">
         <v>0</v>
       </c>
-      <c r="E2" s="9">
+      <c r="E2" s="10">
         <v>0</v>
       </c>
       <c r="F2" s="2">
         <v>0</v>
       </c>
-      <c r="G2" s="9">
+      <c r="G2" s="10">
         <v>0</v>
       </c>
       <c r="H2" s="2">
         <v>0.31622776600000002</v>
       </c>
-      <c r="I2" s="9">
+      <c r="I2" s="10">
         <v>0</v>
       </c>
       <c r="J2" s="2">
         <v>0.94868329799999995</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>314</v>
-      </c>
-      <c r="L2" s="7" t="s">
+        <v>309</v>
+      </c>
+      <c r="L2" s="8" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="3" spans="1:12" s="7" customFormat="1" ht="21">
+    <row r="3" spans="1:12" s="8" customFormat="1" ht="21">
       <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="8" t="s">
         <v>109</v>
       </c>
       <c r="D3" s="2">
         <v>0</v>
       </c>
-      <c r="E3" s="9">
+      <c r="E3" s="10">
         <v>0</v>
       </c>
       <c r="F3" s="2">
         <v>0</v>
       </c>
-      <c r="G3" s="9">
+      <c r="G3" s="10">
         <v>0</v>
       </c>
       <c r="H3" s="2">
         <v>0.70710678100000002</v>
       </c>
-      <c r="I3" s="9">
+      <c r="I3" s="10">
         <v>0</v>
       </c>
       <c r="J3" s="2">
         <v>0.70710678100000002</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>331</v>
-      </c>
-      <c r="L3" s="7" t="s">
+        <v>325</v>
+      </c>
+      <c r="L3" s="8" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="4" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="4" spans="1:12" s="8" customFormat="1" ht="18">
       <c r="A4" s="1">
         <v>3</v>
       </c>
-      <c r="B4" s="8" t="s">
-        <v>312</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>313</v>
+      <c r="B4" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>308</v>
       </c>
       <c r="D4" s="2">
         <v>0</v>
       </c>
-      <c r="E4" s="9">
+      <c r="E4" s="10">
         <v>0</v>
       </c>
       <c r="F4" s="2">
         <v>0</v>
       </c>
-      <c r="G4" s="9">
+      <c r="G4" s="10">
         <v>0</v>
       </c>
       <c r="H4" s="2">
         <v>0.816496581</v>
       </c>
-      <c r="I4" s="9">
+      <c r="I4" s="10">
         <v>0.40824829000000001</v>
       </c>
       <c r="J4" s="2">
         <v>0.40824829000000001</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>358</v>
-      </c>
-      <c r="L4" s="7" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" s="7" customFormat="1" ht="18">
+        <v>352</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" s="8" customFormat="1" ht="18">
       <c r="A5" s="1">
         <v>4</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="8" t="s">
         <v>110</v>
       </c>
       <c r="D5" s="2">
         <v>0</v>
       </c>
-      <c r="E5" s="9">
+      <c r="E5" s="10">
         <v>0.31622776600000002</v>
       </c>
       <c r="F5" s="2">
         <v>0</v>
       </c>
-      <c r="G5" s="9">
+      <c r="G5" s="10">
         <v>0</v>
       </c>
       <c r="H5" s="2">
         <v>0.31622776600000002</v>
       </c>
-      <c r="I5" s="9">
+      <c r="I5" s="10">
         <v>0.63245553200000004</v>
       </c>
       <c r="J5" s="2">
         <v>0.63245553200000004</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>315</v>
-      </c>
-      <c r="L5" s="7" t="s">
+        <v>310</v>
+      </c>
+      <c r="L5" s="8" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="6" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="6" spans="1:12" s="8" customFormat="1" ht="18">
       <c r="A6" s="1">
         <v>5</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="8" t="s">
         <v>111</v>
       </c>
       <c r="D6" s="2">
         <v>0</v>
       </c>
-      <c r="E6" s="9">
+      <c r="E6" s="10">
         <v>0</v>
       </c>
       <c r="F6" s="2">
         <v>0</v>
       </c>
-      <c r="G6" s="9">
+      <c r="G6" s="10">
         <v>0</v>
       </c>
       <c r="H6" s="2">
         <v>0.48507125000000001</v>
       </c>
-      <c r="I6" s="9">
+      <c r="I6" s="10">
         <v>0.48507125000000001</v>
       </c>
       <c r="J6" s="2">
         <v>0.72760687499999999</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>316</v>
-      </c>
-      <c r="L6" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="L6" s="8" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="7" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="7" spans="1:12" s="8" customFormat="1" ht="18">
       <c r="A7" s="1">
         <v>6</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="8" t="s">
         <v>112</v>
       </c>
       <c r="D7" s="2">
         <v>0</v>
       </c>
-      <c r="E7" s="9">
+      <c r="E7" s="10">
         <v>0</v>
       </c>
       <c r="F7" s="2">
         <v>0</v>
       </c>
-      <c r="G7" s="9">
+      <c r="G7" s="10">
         <v>0</v>
       </c>
       <c r="H7" s="2">
         <v>0</v>
       </c>
-      <c r="I7" s="9">
+      <c r="I7" s="10">
         <v>0.89442719100000001</v>
       </c>
       <c r="J7" s="2">
         <v>0.44721359500000002</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>317</v>
-      </c>
-      <c r="L7" s="7" t="s">
+        <v>312</v>
+      </c>
+      <c r="L7" s="8" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="8" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="8" spans="1:12" s="8" customFormat="1" ht="18">
       <c r="A8" s="1">
         <v>7</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="8" t="s">
         <v>113</v>
       </c>
       <c r="D8" s="2">
         <v>0</v>
       </c>
-      <c r="E8" s="9">
+      <c r="E8" s="10">
         <v>0.57735026899999997</v>
       </c>
       <c r="F8" s="2">
         <v>0</v>
       </c>
-      <c r="G8" s="9">
+      <c r="G8" s="10">
         <v>0.57735026899999997</v>
       </c>
       <c r="H8" s="2">
         <v>0.57735026899999997</v>
       </c>
-      <c r="I8" s="9">
+      <c r="I8" s="10">
         <v>0</v>
       </c>
       <c r="J8" s="2">
         <v>0</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>318</v>
-      </c>
-      <c r="L8" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="L8" s="8" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="9" spans="1:12" s="7" customFormat="1" ht="28">
+    <row r="9" spans="1:12" s="8" customFormat="1" ht="28">
       <c r="A9" s="1">
         <v>8</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D9" s="2">
         <v>0.86602540400000005</v>
       </c>
-      <c r="E9" s="9">
+      <c r="E9" s="10">
         <v>0.28867513500000003</v>
       </c>
       <c r="F9" s="2">
         <v>0</v>
       </c>
-      <c r="G9" s="9">
+      <c r="G9" s="10">
         <v>0</v>
       </c>
       <c r="H9" s="2">
         <v>0.28867513500000003</v>
       </c>
-      <c r="I9" s="9">
+      <c r="I9" s="10">
         <v>0.28867513500000003</v>
       </c>
       <c r="J9" s="2">
         <v>0</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>378</v>
-      </c>
-      <c r="L9" s="7" t="s">
+        <v>371</v>
+      </c>
+      <c r="L9" s="8" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="10" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="10" spans="1:12" s="8" customFormat="1" ht="18">
       <c r="A10" s="1">
         <v>9</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="8" t="s">
         <v>115</v>
       </c>
       <c r="D10" s="2">
         <v>0</v>
       </c>
-      <c r="E10" s="9">
+      <c r="E10" s="10">
         <v>0.37796447300000002</v>
       </c>
       <c r="F10" s="2">
         <v>0</v>
       </c>
-      <c r="G10" s="9">
+      <c r="G10" s="10">
         <v>0</v>
       </c>
       <c r="H10" s="2">
         <v>0.75592894600000005</v>
       </c>
-      <c r="I10" s="9">
+      <c r="I10" s="10">
         <v>0.37796447300000002</v>
       </c>
       <c r="J10" s="2">
         <v>0.37796447300000002</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>359</v>
-      </c>
-      <c r="L10" s="7" t="s">
+        <v>353</v>
+      </c>
+      <c r="L10" s="8" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="11" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="11" spans="1:12" s="8" customFormat="1" ht="18">
       <c r="A11" s="1">
         <v>10</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="8" t="s">
         <v>116</v>
       </c>
       <c r="D11" s="2">
         <v>0</v>
       </c>
-      <c r="E11" s="9">
+      <c r="E11" s="10">
         <v>0.28867513500000003</v>
       </c>
       <c r="F11" s="2">
         <v>0</v>
       </c>
-      <c r="G11" s="9">
+      <c r="G11" s="10">
         <v>0</v>
       </c>
       <c r="H11" s="2">
         <v>0.28867513500000003</v>
       </c>
-      <c r="I11" s="9">
+      <c r="I11" s="10">
         <v>0.86602540400000005</v>
       </c>
       <c r="J11" s="2">
         <v>0.28867513500000003</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>319</v>
-      </c>
-      <c r="L11" s="7" t="s">
+        <v>314</v>
+      </c>
+      <c r="L11" s="8" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="12" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="12" spans="1:12" s="8" customFormat="1" ht="18">
       <c r="A12" s="1">
         <v>11</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="8" t="s">
         <v>117</v>
       </c>
       <c r="D12" s="2">
         <v>0</v>
       </c>
-      <c r="E12" s="9">
+      <c r="E12" s="10">
         <v>0</v>
       </c>
       <c r="F12" s="2">
         <v>0</v>
       </c>
-      <c r="G12" s="9">
+      <c r="G12" s="10">
         <v>0</v>
       </c>
       <c r="H12" s="2">
         <v>0.57735026899999997</v>
       </c>
-      <c r="I12" s="9">
+      <c r="I12" s="10">
         <v>0.57735026899999997</v>
       </c>
       <c r="J12" s="2">
         <v>0.57735026899999997</v>
       </c>
       <c r="K12" s="6" t="s">
-        <v>332</v>
-      </c>
-      <c r="L12" s="7" t="s">
+        <v>326</v>
+      </c>
+      <c r="L12" s="8" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="13" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="13" spans="1:12" s="8" customFormat="1" ht="18">
       <c r="A13" s="1">
         <v>12</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="8" t="s">
         <v>118</v>
       </c>
       <c r="D13" s="2">
         <v>0</v>
       </c>
-      <c r="E13" s="9">
+      <c r="E13" s="10">
         <v>0</v>
       </c>
       <c r="F13" s="2">
         <v>0</v>
       </c>
-      <c r="G13" s="9">
+      <c r="G13" s="10">
         <v>0</v>
       </c>
       <c r="H13" s="2">
         <v>0.26726124200000001</v>
       </c>
-      <c r="I13" s="9">
+      <c r="I13" s="10">
         <v>0.53452248400000002</v>
       </c>
       <c r="J13" s="2">
         <v>0.80178372600000003</v>
       </c>
       <c r="K13" s="6" t="s">
-        <v>320</v>
-      </c>
-      <c r="L13" s="7" t="s">
+        <v>315</v>
+      </c>
+      <c r="L13" s="8" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="14" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="14" spans="1:12" s="8" customFormat="1" ht="18">
       <c r="A14" s="1">
         <v>13</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="8" t="s">
         <v>119</v>
       </c>
       <c r="D14" s="2">
         <v>0</v>
       </c>
-      <c r="E14" s="9">
+      <c r="E14" s="10">
         <v>0</v>
       </c>
       <c r="F14" s="2">
         <v>0</v>
       </c>
-      <c r="G14" s="9">
+      <c r="G14" s="10">
         <v>0.28867513500000003</v>
       </c>
       <c r="H14" s="2">
         <v>0.28867513500000003</v>
       </c>
-      <c r="I14" s="9">
+      <c r="I14" s="10">
         <v>0.86602540400000005</v>
       </c>
       <c r="J14" s="2">
         <v>0.28867513500000003</v>
       </c>
       <c r="K14" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="L14" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="L14" s="8" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="15" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="15" spans="1:12" s="8" customFormat="1" ht="18">
       <c r="A15" s="1">
         <v>14</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="B15" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="8" t="s">
         <v>120</v>
       </c>
       <c r="D15" s="2">
         <v>0</v>
       </c>
-      <c r="E15" s="9">
+      <c r="E15" s="10">
         <v>0</v>
       </c>
       <c r="F15" s="2">
         <v>0</v>
       </c>
-      <c r="G15" s="9">
+      <c r="G15" s="10">
         <v>0</v>
       </c>
       <c r="H15" s="2">
         <v>0</v>
       </c>
-      <c r="I15" s="9">
+      <c r="I15" s="10">
         <v>0.44721359500000002</v>
       </c>
       <c r="J15" s="2">
         <v>0.89442719100000001</v>
       </c>
       <c r="K15" s="6" t="s">
-        <v>322</v>
-      </c>
-      <c r="L15" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="L15" s="8" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="16" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="16" spans="1:12" s="8" customFormat="1" ht="18">
       <c r="A16" s="1">
         <v>15</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="B16" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="8" t="s">
         <v>121</v>
       </c>
       <c r="D16" s="2">
         <v>0</v>
       </c>
-      <c r="E16" s="9">
+      <c r="E16" s="10">
         <v>0.23570226</v>
       </c>
       <c r="F16" s="2">
         <v>0</v>
       </c>
-      <c r="G16" s="9">
+      <c r="G16" s="10">
         <v>0</v>
       </c>
       <c r="H16" s="2">
         <v>0.47140452100000002</v>
       </c>
-      <c r="I16" s="9">
+      <c r="I16" s="10">
         <v>0.47140452100000002</v>
       </c>
       <c r="J16" s="2">
         <v>0.70710678100000002</v>
       </c>
       <c r="K16" s="6" t="s">
-        <v>360</v>
-      </c>
-      <c r="L16" s="7" t="s">
+        <v>354</v>
+      </c>
+      <c r="L16" s="8" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="17" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="17" spans="1:12" s="8" customFormat="1" ht="18">
       <c r="A17" s="1">
         <v>16</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="B17" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C17" s="8" t="s">
         <v>122</v>
       </c>
       <c r="D17" s="2">
         <v>0</v>
       </c>
-      <c r="E17" s="9">
+      <c r="E17" s="10">
         <v>0</v>
       </c>
       <c r="F17" s="2">
         <v>0.22941573400000001</v>
       </c>
-      <c r="G17" s="9">
+      <c r="G17" s="10">
         <v>0.688247202</v>
       </c>
       <c r="H17" s="2">
         <v>0.22941573400000001</v>
       </c>
-      <c r="I17" s="9">
+      <c r="I17" s="10">
         <v>0.45883146800000002</v>
       </c>
       <c r="J17" s="2">
         <v>0.45883146800000002</v>
       </c>
       <c r="K17" s="6" t="s">
-        <v>333</v>
-      </c>
-      <c r="L17" s="7" t="s">
+        <v>327</v>
+      </c>
+      <c r="L17" s="8" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="18" spans="1:12" s="7" customFormat="1" ht="28">
+    <row r="18" spans="1:12" s="8" customFormat="1" ht="28">
       <c r="A18" s="1">
         <v>17</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="B18" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C18" s="8" t="s">
         <v>123</v>
       </c>
       <c r="D18" s="2">
         <v>0</v>
       </c>
-      <c r="E18" s="9">
+      <c r="E18" s="10">
         <v>0.41702882800000002</v>
       </c>
       <c r="F18" s="2">
         <v>0</v>
       </c>
-      <c r="G18" s="9">
+      <c r="G18" s="10">
         <v>0.20851441400000001</v>
       </c>
       <c r="H18" s="2">
         <v>0</v>
       </c>
-      <c r="I18" s="9">
+      <c r="I18" s="10">
         <v>0.625543242</v>
       </c>
       <c r="J18" s="2">
         <v>0.625543242</v>
       </c>
       <c r="K18" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="L18" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="L18" s="8" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="19" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="19" spans="1:12" s="8" customFormat="1" ht="18">
       <c r="A19" s="1">
         <v>18</v>
       </c>
-      <c r="B19" s="8" t="s">
+      <c r="B19" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="C19" s="8" t="s">
         <v>124</v>
       </c>
       <c r="D19" s="2">
         <v>0.30860670000000001</v>
       </c>
-      <c r="E19" s="9">
+      <c r="E19" s="10">
         <v>0.15430335000000001</v>
       </c>
       <c r="F19" s="2">
         <v>0.46291005000000002</v>
       </c>
-      <c r="G19" s="9">
+      <c r="G19" s="10">
         <v>0.46291005000000002</v>
       </c>
       <c r="H19" s="2">
         <v>0.46291005000000002</v>
       </c>
-      <c r="I19" s="9">
+      <c r="I19" s="10">
         <v>0.46291005000000002</v>
       </c>
       <c r="J19" s="2">
         <v>0.15430335000000001</v>
       </c>
       <c r="K19" s="6" t="s">
-        <v>361</v>
-      </c>
-      <c r="L19" s="7" t="s">
+        <v>355</v>
+      </c>
+      <c r="L19" s="8" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="20" spans="1:12" s="7" customFormat="1" ht="21">
+    <row r="20" spans="1:12" s="8" customFormat="1" ht="21">
       <c r="A20" s="1">
         <v>19</v>
       </c>
-      <c r="B20" s="8" t="s">
+      <c r="B20" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="7" t="s">
+      <c r="C20" s="8" t="s">
         <v>125</v>
       </c>
       <c r="D20" s="2">
         <v>0.603022689</v>
       </c>
-      <c r="E20" s="9">
+      <c r="E20" s="10">
         <v>0.30151134499999999</v>
       </c>
       <c r="F20" s="2">
         <v>0</v>
       </c>
-      <c r="G20" s="9">
+      <c r="G20" s="10">
         <v>0</v>
       </c>
       <c r="H20" s="2">
         <v>0.603022689</v>
       </c>
-      <c r="I20" s="9">
+      <c r="I20" s="10">
         <v>0.30151134499999999</v>
       </c>
       <c r="J20" s="2">
         <v>0.30151134499999999</v>
       </c>
       <c r="K20" s="6" t="s">
-        <v>334</v>
-      </c>
-      <c r="L20" s="7" t="s">
+        <v>328</v>
+      </c>
+      <c r="L20" s="8" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="21" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="21" spans="1:12" s="8" customFormat="1" ht="18">
       <c r="A21" s="1">
         <v>20</v>
       </c>
-      <c r="B21" s="8" t="s">
+      <c r="B21" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="C21" s="7" t="s">
+      <c r="C21" s="8" t="s">
         <v>126</v>
       </c>
       <c r="D21" s="2">
         <v>0</v>
       </c>
-      <c r="E21" s="9">
+      <c r="E21" s="10">
         <v>0.23570226</v>
       </c>
       <c r="F21" s="2">
         <v>0</v>
       </c>
-      <c r="G21" s="9">
+      <c r="G21" s="10">
         <v>0</v>
       </c>
       <c r="H21" s="2">
         <v>0.47140452100000002</v>
       </c>
-      <c r="I21" s="9">
+      <c r="I21" s="10">
         <v>0.47140452100000002</v>
       </c>
       <c r="J21" s="2">
         <v>0.70710678100000002</v>
       </c>
       <c r="K21" s="6" t="s">
-        <v>362</v>
-      </c>
-      <c r="L21" s="7" t="s">
+        <v>356</v>
+      </c>
+      <c r="L21" s="8" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="22" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="22" spans="1:12" s="8" customFormat="1" ht="18">
       <c r="A22" s="1">
         <v>21</v>
       </c>
-      <c r="B22" s="8" t="s">
+      <c r="B22" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="7" t="s">
+      <c r="C22" s="8" t="s">
         <v>127</v>
       </c>
       <c r="D22" s="2">
         <v>0</v>
       </c>
-      <c r="E22" s="9">
+      <c r="E22" s="10">
         <v>0</v>
       </c>
       <c r="F22" s="2">
         <v>0</v>
       </c>
-      <c r="G22" s="9">
+      <c r="G22" s="10">
         <v>0</v>
       </c>
       <c r="H22" s="2">
         <v>0.688247202</v>
       </c>
-      <c r="I22" s="9">
+      <c r="I22" s="10">
         <v>0.22941573400000001</v>
       </c>
       <c r="J22" s="2">
         <v>0.688247202</v>
       </c>
       <c r="K22" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="L22" s="7" t="s">
+        <v>318</v>
+      </c>
+      <c r="L22" s="8" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="23" spans="1:12" s="7" customFormat="1" ht="28">
+    <row r="23" spans="1:12" s="8" customFormat="1" ht="28">
       <c r="A23" s="1">
         <v>22</v>
       </c>
-      <c r="B23" s="8" t="s">
+      <c r="B23" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="7" t="s">
+      <c r="C23" s="8" t="s">
         <v>128</v>
       </c>
       <c r="D23" s="2">
         <v>0</v>
       </c>
-      <c r="E23" s="9">
+      <c r="E23" s="10">
         <v>0.48507125000000001</v>
       </c>
       <c r="F23" s="2">
         <v>0</v>
       </c>
-      <c r="G23" s="9">
+      <c r="G23" s="10">
         <v>0</v>
       </c>
       <c r="H23" s="2">
         <v>0</v>
       </c>
-      <c r="I23" s="9">
+      <c r="I23" s="10">
         <v>0.72760687499999999</v>
       </c>
       <c r="J23" s="2">
         <v>0.48507125000000001</v>
       </c>
       <c r="K23" s="6" t="s">
-        <v>325</v>
-      </c>
-      <c r="L23" s="7" t="s">
+        <v>319</v>
+      </c>
+      <c r="L23" s="8" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="24" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="24" spans="1:12" s="8" customFormat="1" ht="18">
       <c r="A24" s="1">
         <v>23</v>
       </c>
-      <c r="B24" s="8" t="s">
+      <c r="B24" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C24" s="7" t="s">
+      <c r="C24" s="8" t="s">
         <v>129</v>
       </c>
       <c r="D24" s="2">
         <v>0</v>
       </c>
-      <c r="E24" s="9">
+      <c r="E24" s="10">
         <v>0.51639777899999995</v>
       </c>
       <c r="F24" s="2">
         <v>0</v>
       </c>
-      <c r="G24" s="9">
+      <c r="G24" s="10">
         <v>0.25819889000000001</v>
       </c>
       <c r="H24" s="2">
         <v>0</v>
       </c>
-      <c r="I24" s="9">
+      <c r="I24" s="10">
         <v>0.77459666900000002</v>
       </c>
       <c r="J24" s="2">
         <v>0.25819889000000001</v>
       </c>
       <c r="K24" s="6" t="s">
-        <v>326</v>
-      </c>
-      <c r="L24" s="7" t="s">
+        <v>320</v>
+      </c>
+      <c r="L24" s="8" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="25" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="25" spans="1:12" s="8" customFormat="1" ht="18">
       <c r="A25" s="1">
         <v>24</v>
       </c>
-      <c r="B25" s="8" t="s">
+      <c r="B25" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="7" t="s">
+      <c r="C25" s="8" t="s">
         <v>130</v>
       </c>
       <c r="D25" s="2">
         <v>0</v>
       </c>
-      <c r="E25" s="9">
+      <c r="E25" s="10">
         <v>0</v>
       </c>
       <c r="F25" s="2">
         <v>0</v>
       </c>
-      <c r="G25" s="9">
+      <c r="G25" s="10">
         <v>0</v>
       </c>
       <c r="H25" s="2">
         <v>0.57735026899999997</v>
       </c>
-      <c r="I25" s="9">
+      <c r="I25" s="10">
         <v>0.57735026899999997</v>
       </c>
       <c r="J25" s="2">
         <v>0.57735026899999997</v>
       </c>
       <c r="K25" s="6" t="s">
-        <v>327</v>
-      </c>
-      <c r="L25" s="7" t="s">
+        <v>321</v>
+      </c>
+      <c r="L25" s="8" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="26" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="26" spans="1:12" s="8" customFormat="1" ht="18">
       <c r="A26" s="1">
         <v>25</v>
       </c>
-      <c r="B26" s="8" t="s">
+      <c r="B26" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="C26" s="7" t="s">
+      <c r="C26" s="8" t="s">
         <v>131</v>
       </c>
       <c r="D26" s="2">
         <v>0</v>
       </c>
-      <c r="E26" s="9">
+      <c r="E26" s="10">
         <v>0.46852128599999998</v>
       </c>
       <c r="F26" s="2">
         <v>0</v>
       </c>
-      <c r="G26" s="9">
+      <c r="G26" s="10">
         <v>0</v>
       </c>
       <c r="H26" s="2">
         <v>0</v>
       </c>
-      <c r="I26" s="9">
+      <c r="I26" s="10">
         <v>0.62469504799999998</v>
       </c>
       <c r="J26" s="2">
         <v>0.62469504799999998</v>
       </c>
       <c r="K26" s="6" t="s">
-        <v>363</v>
-      </c>
-      <c r="L26" s="7" t="s">
+        <v>357</v>
+      </c>
+      <c r="L26" s="8" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="27" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="27" spans="1:12" s="8" customFormat="1" ht="18">
       <c r="A27" s="1">
         <v>26</v>
       </c>
-      <c r="B27" s="8" t="s">
+      <c r="B27" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="7" t="s">
+      <c r="C27" s="8" t="s">
         <v>132</v>
       </c>
       <c r="D27" s="2">
         <v>0.36927447299999999</v>
       </c>
-      <c r="E27" s="9">
+      <c r="E27" s="10">
         <v>0.36927447299999999</v>
       </c>
       <c r="F27" s="2">
         <v>0.49236596399999999</v>
       </c>
-      <c r="G27" s="9">
+      <c r="G27" s="10">
         <v>0.49236596399999999</v>
       </c>
       <c r="H27" s="2">
         <v>0</v>
       </c>
-      <c r="I27" s="9">
+      <c r="I27" s="10">
         <v>0.49236596399999999</v>
       </c>
       <c r="J27" s="2">
         <v>0</v>
       </c>
       <c r="K27" s="6" t="s">
-        <v>364</v>
-      </c>
-      <c r="L27" s="7" t="s">
+        <v>389</v>
+      </c>
+      <c r="L27" s="8" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="28" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="28" spans="1:12" s="8" customFormat="1" ht="18">
       <c r="A28" s="1">
         <v>27</v>
       </c>
-      <c r="B28" s="8" t="s">
+      <c r="B28" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="7" t="s">
+      <c r="C28" s="8" t="s">
         <v>133</v>
       </c>
       <c r="D28" s="2">
         <v>0</v>
       </c>
-      <c r="E28" s="9">
+      <c r="E28" s="10">
         <v>0</v>
       </c>
       <c r="F28" s="2">
         <v>0</v>
       </c>
-      <c r="G28" s="9">
+      <c r="G28" s="10">
         <v>0</v>
       </c>
       <c r="H28" s="2">
         <v>0.58834840499999996</v>
       </c>
-      <c r="I28" s="9">
+      <c r="I28" s="10">
         <v>0.196116135</v>
       </c>
       <c r="J28" s="2">
         <v>0.78446454099999996</v>
       </c>
       <c r="K28" s="6" t="s">
-        <v>328</v>
-      </c>
-      <c r="L28" s="7" t="s">
+        <v>322</v>
+      </c>
+      <c r="L28" s="8" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="29" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="29" spans="1:12" s="8" customFormat="1" ht="18">
       <c r="A29" s="1">
         <v>28</v>
       </c>
-      <c r="B29" s="8" t="s">
+      <c r="B29" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="7" t="s">
+      <c r="C29" s="8" t="s">
         <v>134</v>
       </c>
       <c r="D29" s="2">
         <v>0</v>
       </c>
-      <c r="E29" s="9">
+      <c r="E29" s="10">
         <v>0.70710678118654746</v>
       </c>
       <c r="F29" s="2">
         <v>0</v>
       </c>
-      <c r="G29" s="9">
+      <c r="G29" s="10">
         <v>0</v>
       </c>
       <c r="H29" s="2">
         <v>0</v>
       </c>
-      <c r="I29" s="9">
+      <c r="I29" s="10">
         <v>0.70710678118654746</v>
       </c>
       <c r="J29" s="2">
         <v>0</v>
       </c>
       <c r="K29" s="6" t="s">
-        <v>379</v>
-      </c>
-      <c r="L29" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="L29" s="8" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="30" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="30" spans="1:12" s="8" customFormat="1" ht="18">
       <c r="A30" s="1">
         <v>29</v>
       </c>
-      <c r="B30" s="8" t="s">
+      <c r="B30" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="7" t="s">
+      <c r="C30" s="8" t="s">
         <v>135</v>
       </c>
       <c r="D30" s="2">
         <v>0</v>
       </c>
-      <c r="E30" s="9">
+      <c r="E30" s="10">
         <v>0.55470019599999998</v>
       </c>
       <c r="F30" s="2">
         <v>0</v>
       </c>
-      <c r="G30" s="9">
+      <c r="G30" s="10">
         <v>0</v>
       </c>
       <c r="H30" s="2">
         <v>0.27735009799999999</v>
       </c>
-      <c r="I30" s="9">
+      <c r="I30" s="10">
         <v>0.55470019599999998</v>
       </c>
       <c r="J30" s="2">
         <v>0.55470019599999998</v>
       </c>
       <c r="K30" s="6" t="s">
-        <v>329</v>
-      </c>
-      <c r="L30" s="7" t="s">
+        <v>323</v>
+      </c>
+      <c r="L30" s="8" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="31" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="31" spans="1:12" s="8" customFormat="1" ht="18">
       <c r="A31" s="1">
         <v>30</v>
       </c>
-      <c r="B31" s="8" t="s">
+      <c r="B31" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="7" t="s">
+      <c r="C31" s="8" t="s">
         <v>136</v>
       </c>
       <c r="D31" s="2">
         <v>0.52981294300000004</v>
       </c>
-      <c r="E31" s="9">
+      <c r="E31" s="10">
         <v>0.52981294300000004</v>
       </c>
       <c r="F31" s="2">
         <v>0</v>
       </c>
-      <c r="G31" s="9">
+      <c r="G31" s="10">
         <v>0</v>
       </c>
       <c r="H31" s="2">
         <v>0.52981294300000004</v>
       </c>
-      <c r="I31" s="9">
+      <c r="I31" s="10">
         <v>0.39735970700000001</v>
       </c>
       <c r="J31" s="2">
         <v>0</v>
       </c>
       <c r="K31" s="6" t="s">
-        <v>330</v>
-      </c>
-      <c r="L31" s="7" t="s">
+        <v>324</v>
+      </c>
+      <c r="L31" s="8" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="32" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="32" spans="1:12" s="8" customFormat="1" ht="18">
       <c r="A32" s="1">
         <v>31</v>
       </c>
-      <c r="B32" s="8" t="s">
+      <c r="B32" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="C32" s="7" t="s">
+      <c r="C32" s="8" t="s">
         <v>137</v>
       </c>
       <c r="D32" s="2">
         <v>0</v>
       </c>
-      <c r="E32" s="9">
+      <c r="E32" s="10">
         <v>0</v>
       </c>
       <c r="F32" s="2">
         <v>0</v>
       </c>
-      <c r="G32" s="9">
+      <c r="G32" s="10">
         <v>0</v>
       </c>
       <c r="H32" s="2">
         <v>0.688247202</v>
       </c>
-      <c r="I32" s="9">
+      <c r="I32" s="10">
         <v>0.22941573400000001</v>
       </c>
       <c r="J32" s="2">
         <v>0.688247202</v>
       </c>
       <c r="K32" s="6" t="s">
-        <v>335</v>
-      </c>
-      <c r="L32" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="L32" s="8" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="33" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="33" spans="1:12" s="8" customFormat="1" ht="18">
       <c r="A33" s="1">
         <v>32</v>
       </c>
-      <c r="B33" s="8" t="s">
+      <c r="B33" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="7" t="s">
+      <c r="C33" s="8" t="s">
         <v>138</v>
       </c>
       <c r="D33" s="2">
         <v>0</v>
       </c>
-      <c r="E33" s="9">
+      <c r="E33" s="10">
         <v>0.70710678100000002</v>
       </c>
       <c r="F33" s="2">
         <v>0</v>
       </c>
-      <c r="G33" s="9">
+      <c r="G33" s="10">
         <v>0.35355339099999999</v>
       </c>
       <c r="H33" s="2">
         <v>0.35355339099999999</v>
       </c>
-      <c r="I33" s="9">
+      <c r="I33" s="10">
         <v>0.35355339099999999</v>
       </c>
       <c r="J33" s="2">
         <v>0.35355339099999999</v>
       </c>
       <c r="K33" s="6" t="s">
-        <v>365</v>
-      </c>
-      <c r="L33" s="7" t="s">
+        <v>358</v>
+      </c>
+      <c r="L33" s="8" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="34" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="34" spans="1:12" s="8" customFormat="1" ht="18">
       <c r="A34" s="1">
         <v>33</v>
       </c>
-      <c r="B34" s="8" t="s">
+      <c r="B34" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="C34" s="7" t="s">
+      <c r="C34" s="8" t="s">
         <v>139</v>
       </c>
       <c r="D34" s="2">
         <v>0.55470019599999998</v>
       </c>
-      <c r="E34" s="9">
+      <c r="E34" s="10">
         <v>0</v>
       </c>
       <c r="F34" s="2">
         <v>0</v>
       </c>
-      <c r="G34" s="9">
+      <c r="G34" s="10">
         <v>0</v>
       </c>
       <c r="H34" s="2">
         <v>0.55470019599999998</v>
       </c>
-      <c r="I34" s="9">
+      <c r="I34" s="10">
         <v>0.27735009799999999</v>
       </c>
       <c r="J34" s="2">
         <v>0.55470019599999998</v>
       </c>
       <c r="K34" s="6" t="s">
-        <v>336</v>
-      </c>
-      <c r="L34" s="7" t="s">
+        <v>330</v>
+      </c>
+      <c r="L34" s="8" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="35" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="35" spans="1:12" s="8" customFormat="1" ht="18">
       <c r="A35" s="1">
         <v>34</v>
       </c>
-      <c r="B35" s="8" t="s">
+      <c r="B35" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="C35" s="7" t="s">
+      <c r="C35" s="8" t="s">
         <v>140</v>
       </c>
       <c r="D35" s="2">
         <v>0.53452248400000002</v>
       </c>
-      <c r="E35" s="9">
+      <c r="E35" s="10">
         <v>0.53452248400000002</v>
       </c>
       <c r="F35" s="2">
         <v>0</v>
       </c>
-      <c r="G35" s="9">
+      <c r="G35" s="10">
         <v>0</v>
       </c>
       <c r="H35" s="2">
         <v>0.26726124200000001</v>
       </c>
-      <c r="I35" s="9">
+      <c r="I35" s="10">
         <v>0.53452248400000002</v>
       </c>
       <c r="J35" s="2">
         <v>0.26726124200000001</v>
       </c>
       <c r="K35" s="6" t="s">
-        <v>337</v>
-      </c>
-      <c r="L35" s="7" t="s">
+        <v>331</v>
+      </c>
+      <c r="L35" s="8" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="36" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="36" spans="1:12" s="8" customFormat="1" ht="18">
       <c r="A36" s="1">
         <v>35</v>
       </c>
-      <c r="B36" s="8" t="s">
+      <c r="B36" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="C36" s="7" t="s">
+      <c r="C36" s="8" t="s">
         <v>141</v>
       </c>
       <c r="D36" s="2">
         <v>0</v>
       </c>
-      <c r="E36" s="9">
+      <c r="E36" s="10">
         <v>0</v>
       </c>
       <c r="F36" s="2">
         <v>0</v>
       </c>
-      <c r="G36" s="9">
+      <c r="G36" s="10">
         <v>0</v>
       </c>
       <c r="H36" s="2">
         <v>0.80178372600000003</v>
       </c>
-      <c r="I36" s="9">
+      <c r="I36" s="10">
         <v>0.26726124200000001</v>
       </c>
       <c r="J36" s="2">
         <v>0.53452248400000002</v>
       </c>
       <c r="K36" s="6" t="s">
-        <v>366</v>
-      </c>
-      <c r="L36" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="L36" s="8" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="37" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="37" spans="1:12" s="8" customFormat="1" ht="18">
       <c r="A37" s="1">
         <v>36</v>
       </c>
-      <c r="B37" s="8" t="s">
+      <c r="B37" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="C37" s="7" t="s">
+      <c r="C37" s="8" t="s">
         <v>142</v>
       </c>
       <c r="D37" s="2">
         <v>0.21320071600000001</v>
       </c>
-      <c r="E37" s="9">
+      <c r="E37" s="10">
         <v>0.426401433</v>
       </c>
       <c r="F37" s="2">
         <v>0</v>
       </c>
-      <c r="G37" s="9">
+      <c r="G37" s="10">
         <v>0</v>
       </c>
       <c r="H37" s="2">
         <v>0.63960214900000001</v>
       </c>
-      <c r="I37" s="9">
+      <c r="I37" s="10">
         <v>0.426401433</v>
       </c>
       <c r="J37" s="2">
         <v>0.426401433</v>
       </c>
       <c r="K37" s="6" t="s">
-        <v>338</v>
-      </c>
-      <c r="L37" s="7" t="s">
+        <v>332</v>
+      </c>
+      <c r="L37" s="8" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="38" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="38" spans="1:12" s="8" customFormat="1" ht="18">
       <c r="A38" s="1">
         <v>37</v>
       </c>
-      <c r="B38" s="8" t="s">
+      <c r="B38" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="C38" s="7" t="s">
+      <c r="C38" s="8" t="s">
         <v>143</v>
       </c>
       <c r="D38" s="2">
         <v>0</v>
       </c>
-      <c r="E38" s="9">
+      <c r="E38" s="10">
         <v>0.66666666699999999</v>
       </c>
       <c r="F38" s="2">
         <v>0</v>
       </c>
-      <c r="G38" s="9">
+      <c r="G38" s="10">
         <v>0.33333333300000001</v>
       </c>
       <c r="H38" s="2">
         <v>0</v>
       </c>
-      <c r="I38" s="9">
+      <c r="I38" s="10">
         <v>0.66666666699999999</v>
       </c>
       <c r="J38" s="2">
         <v>0</v>
       </c>
       <c r="K38" s="6" t="s">
-        <v>339</v>
-      </c>
-      <c r="L38" s="7" t="s">
+        <v>333</v>
+      </c>
+      <c r="L38" s="8" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="39" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="39" spans="1:12" s="8" customFormat="1" ht="18">
       <c r="A39" s="1">
         <v>38</v>
       </c>
-      <c r="B39" s="8" t="s">
+      <c r="B39" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="C39" s="7" t="s">
+      <c r="C39" s="8" t="s">
         <v>144</v>
       </c>
       <c r="D39" s="2">
         <v>0</v>
       </c>
-      <c r="E39" s="9">
+      <c r="E39" s="10">
         <v>0.28867513500000003</v>
       </c>
       <c r="F39" s="2">
         <v>0</v>
       </c>
-      <c r="G39" s="9">
+      <c r="G39" s="10">
         <v>0.28867513500000003</v>
       </c>
       <c r="H39" s="2">
         <v>0.28867513500000003</v>
       </c>
-      <c r="I39" s="9">
+      <c r="I39" s="10">
         <v>0.86602540400000005</v>
       </c>
       <c r="J39" s="2">
         <v>0</v>
       </c>
       <c r="K39" s="6" t="s">
-        <v>340</v>
-      </c>
-      <c r="L39" s="7" t="s">
+        <v>334</v>
+      </c>
+      <c r="L39" s="8" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="40" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="40" spans="1:12" s="8" customFormat="1" ht="18">
       <c r="A40" s="1">
         <v>39</v>
       </c>
-      <c r="B40" s="8" t="s">
+      <c r="B40" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="C40" s="7" t="s">
+      <c r="C40" s="8" t="s">
         <v>145</v>
       </c>
       <c r="D40" s="2">
         <v>0</v>
       </c>
-      <c r="E40" s="9">
+      <c r="E40" s="10">
         <v>0</v>
       </c>
       <c r="F40" s="2">
         <v>0</v>
       </c>
-      <c r="G40" s="9">
+      <c r="G40" s="10">
         <v>0</v>
       </c>
       <c r="H40" s="2">
         <v>0.57735026899999997</v>
       </c>
-      <c r="I40" s="9">
+      <c r="I40" s="10">
         <v>0.57735026899999997</v>
       </c>
       <c r="J40" s="2">
         <v>0.57735026899999997</v>
       </c>
       <c r="K40" s="6" t="s">
-        <v>341</v>
-      </c>
-      <c r="L40" s="7" t="s">
+        <v>335</v>
+      </c>
+      <c r="L40" s="8" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="41" spans="1:12" s="7" customFormat="1" ht="24">
+    <row r="41" spans="1:12" s="8" customFormat="1" ht="24">
       <c r="A41" s="1">
         <v>40</v>
       </c>
-      <c r="B41" s="8" t="s">
+      <c r="B41" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="C41" s="7" t="s">
+      <c r="C41" s="8" t="s">
         <v>146</v>
       </c>
       <c r="D41" s="2">
         <v>0</v>
       </c>
-      <c r="E41" s="9">
+      <c r="E41" s="10">
         <v>0</v>
       </c>
       <c r="F41" s="2">
         <v>0</v>
       </c>
-      <c r="G41" s="9">
+      <c r="G41" s="10">
         <v>0</v>
       </c>
       <c r="H41" s="2">
         <v>0.80178372600000003</v>
       </c>
-      <c r="I41" s="9">
+      <c r="I41" s="10">
         <v>0.26726124200000001</v>
       </c>
       <c r="J41" s="2">
         <v>0.53452248400000002</v>
       </c>
       <c r="K41" s="6" t="s">
-        <v>367</v>
-      </c>
-      <c r="L41" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="L41" s="8" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="42" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="42" spans="1:12" s="8" customFormat="1" ht="18">
       <c r="A42" s="1">
         <v>41</v>
       </c>
-      <c r="B42" s="8" t="s">
+      <c r="B42" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="C42" s="7" t="s">
+      <c r="C42" s="8" t="s">
         <v>147</v>
       </c>
       <c r="D42" s="2">
         <v>0.23570226</v>
       </c>
-      <c r="E42" s="9">
+      <c r="E42" s="10">
         <v>0.70710678100000002</v>
       </c>
       <c r="F42" s="2">
         <v>0.23570226</v>
       </c>
-      <c r="G42" s="9">
+      <c r="G42" s="10">
         <v>0.23570226</v>
       </c>
       <c r="H42" s="2">
         <v>0.23570226</v>
       </c>
-      <c r="I42" s="9">
+      <c r="I42" s="10">
         <v>0.47140452100000002</v>
       </c>
       <c r="J42" s="2">
         <v>0.23570226</v>
       </c>
       <c r="K42" s="6" t="s">
-        <v>342</v>
-      </c>
-      <c r="L42" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="L42" s="8" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="43" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="43" spans="1:12" s="8" customFormat="1" ht="18">
       <c r="A43" s="1">
         <v>42</v>
       </c>
-      <c r="B43" s="8" t="s">
+      <c r="B43" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="C43" s="7" t="s">
+      <c r="C43" s="8" t="s">
         <v>148</v>
       </c>
       <c r="D43" s="2">
         <v>0.182574186</v>
       </c>
-      <c r="E43" s="9">
+      <c r="E43" s="10">
         <v>0</v>
       </c>
       <c r="F43" s="2">
         <v>0</v>
       </c>
-      <c r="G43" s="9">
+      <c r="G43" s="10">
         <v>0</v>
       </c>
       <c r="H43" s="2">
         <v>0.54772255800000003</v>
       </c>
-      <c r="I43" s="9">
+      <c r="I43" s="10">
         <v>0.73029674300000003</v>
       </c>
       <c r="J43" s="2">
         <v>0.365148372</v>
       </c>
       <c r="K43" s="6" t="s">
-        <v>343</v>
-      </c>
-      <c r="L43" s="7" t="s">
+        <v>337</v>
+      </c>
+      <c r="L43" s="8" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="44" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="44" spans="1:12" s="8" customFormat="1" ht="18">
       <c r="A44" s="1">
         <v>43</v>
       </c>
-      <c r="B44" s="8" t="s">
+      <c r="B44" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="C44" s="7" t="s">
+      <c r="C44" s="8" t="s">
         <v>149</v>
       </c>
       <c r="D44" s="2">
         <v>0.57735026899999997</v>
       </c>
-      <c r="E44" s="9">
+      <c r="E44" s="10">
         <v>0</v>
       </c>
       <c r="F44" s="2">
         <v>0</v>
       </c>
-      <c r="G44" s="9">
+      <c r="G44" s="10">
         <v>0</v>
       </c>
       <c r="H44" s="2">
         <v>0.57735026899999997</v>
       </c>
-      <c r="I44" s="9">
+      <c r="I44" s="10">
         <v>0</v>
       </c>
       <c r="J44" s="2">
         <v>0.57735026899999997</v>
       </c>
       <c r="K44" s="6" t="s">
-        <v>344</v>
-      </c>
-      <c r="L44" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="L44" s="8" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="45" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="45" spans="1:12" s="8" customFormat="1" ht="18">
       <c r="A45" s="1">
         <v>44</v>
       </c>
-      <c r="B45" s="8" t="s">
+      <c r="B45" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="C45" s="7" t="s">
+      <c r="C45" s="8" t="s">
         <v>150</v>
       </c>
       <c r="D45" s="2">
         <v>0.89442719100000001</v>
       </c>
-      <c r="E45" s="9">
+      <c r="E45" s="10">
         <v>0.44721359500000002</v>
       </c>
       <c r="F45" s="2">
         <v>0</v>
       </c>
-      <c r="G45" s="9">
+      <c r="G45" s="10">
         <v>0</v>
       </c>
       <c r="H45" s="2">
         <v>0</v>
       </c>
-      <c r="I45" s="9">
+      <c r="I45" s="10">
         <v>0</v>
       </c>
       <c r="J45" s="2">
         <v>0</v>
       </c>
       <c r="K45" s="6" t="s">
-        <v>345</v>
-      </c>
-      <c r="L45" s="7" t="s">
+        <v>339</v>
+      </c>
+      <c r="L45" s="8" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="46" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="46" spans="1:12" s="8" customFormat="1" ht="18">
       <c r="A46" s="1">
         <v>45</v>
       </c>
-      <c r="B46" s="8" t="s">
+      <c r="B46" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="C46" s="7" t="s">
+      <c r="C46" s="8" t="s">
         <v>151</v>
       </c>
       <c r="D46" s="2">
         <v>0</v>
       </c>
-      <c r="E46" s="9">
+      <c r="E46" s="10">
         <v>0</v>
       </c>
       <c r="F46" s="2">
         <v>0</v>
       </c>
-      <c r="G46" s="9">
+      <c r="G46" s="10">
         <v>0</v>
       </c>
       <c r="H46" s="2">
         <v>0.70710678100000002</v>
       </c>
-      <c r="I46" s="9">
+      <c r="I46" s="10">
         <v>0.70710678100000002</v>
       </c>
       <c r="J46" s="2">
         <v>0</v>
       </c>
       <c r="K46" s="6" t="s">
-        <v>346</v>
-      </c>
-      <c r="L46" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="L46" s="8" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="47" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="47" spans="1:12" s="8" customFormat="1" ht="18">
       <c r="A47" s="1">
         <v>46</v>
       </c>
-      <c r="B47" s="8" t="s">
+      <c r="B47" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="C47" s="7" t="s">
+      <c r="C47" s="8" t="s">
         <v>152</v>
       </c>
       <c r="D47" s="2">
         <v>0.25819889000000001</v>
       </c>
-      <c r="E47" s="9">
+      <c r="E47" s="10">
         <v>0.51639777899999995</v>
       </c>
       <c r="F47" s="2">
         <v>0.25819889000000001</v>
       </c>
-      <c r="G47" s="9">
+      <c r="G47" s="10">
         <v>0.25819889000000001</v>
       </c>
       <c r="H47" s="2">
         <v>0.51639777899999995</v>
       </c>
-      <c r="I47" s="9">
+      <c r="I47" s="10">
         <v>0.51639777899999995</v>
       </c>
       <c r="J47" s="2">
         <v>0</v>
       </c>
       <c r="K47" s="6" t="s">
-        <v>368</v>
-      </c>
-      <c r="L47" s="7" t="s">
+        <v>361</v>
+      </c>
+      <c r="L47" s="8" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="48" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="48" spans="1:12" s="8" customFormat="1" ht="18">
       <c r="A48" s="1">
         <v>47</v>
       </c>
-      <c r="B48" s="8" t="s">
+      <c r="B48" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="C48" s="7" t="s">
+      <c r="C48" s="8" t="s">
         <v>153</v>
       </c>
       <c r="D48" s="2">
         <v>0.25</v>
       </c>
-      <c r="E48" s="9">
+      <c r="E48" s="10">
         <v>0.25</v>
       </c>
       <c r="F48" s="2">
         <v>0</v>
       </c>
-      <c r="G48" s="9">
+      <c r="G48" s="10">
         <v>0</v>
       </c>
       <c r="H48" s="2">
         <v>0.75</v>
       </c>
-      <c r="I48" s="9">
+      <c r="I48" s="10">
         <v>0.25</v>
       </c>
       <c r="J48" s="2">
         <v>0.5</v>
       </c>
       <c r="K48" s="6" t="s">
-        <v>369</v>
-      </c>
-      <c r="L48" s="7" t="s">
+        <v>362</v>
+      </c>
+      <c r="L48" s="8" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="49" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="49" spans="1:12" s="8" customFormat="1" ht="18">
       <c r="A49" s="1">
         <v>48</v>
       </c>
-      <c r="B49" s="8" t="s">
+      <c r="B49" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="C49" s="7" t="s">
+      <c r="C49" s="8" t="s">
         <v>154</v>
       </c>
       <c r="D49" s="2">
         <v>0</v>
       </c>
-      <c r="E49" s="9">
+      <c r="E49" s="10">
         <v>0</v>
       </c>
       <c r="F49" s="2">
         <v>0</v>
       </c>
-      <c r="G49" s="9">
+      <c r="G49" s="10">
         <v>0</v>
       </c>
       <c r="H49" s="2">
         <v>0.69631062399999999</v>
       </c>
-      <c r="I49" s="9">
+      <c r="I49" s="10">
         <v>0.69631062399999999</v>
       </c>
       <c r="J49" s="2">
         <v>0.174077656</v>
       </c>
       <c r="K49" s="6" t="s">
-        <v>347</v>
-      </c>
-      <c r="L49" s="7" t="s">
+        <v>341</v>
+      </c>
+      <c r="L49" s="8" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="50" spans="1:12" s="7" customFormat="1" ht="21">
+    <row r="50" spans="1:12" s="8" customFormat="1" ht="21">
       <c r="A50" s="1">
         <v>49</v>
       </c>
-      <c r="B50" s="8" t="s">
+      <c r="B50" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="C50" s="7" t="s">
+      <c r="C50" s="8" t="s">
         <v>155</v>
       </c>
       <c r="D50" s="2">
         <v>0</v>
       </c>
-      <c r="E50" s="9">
+      <c r="E50" s="10">
         <v>0</v>
       </c>
       <c r="F50" s="2">
         <v>0</v>
       </c>
-      <c r="G50" s="9">
+      <c r="G50" s="10">
         <v>0</v>
       </c>
       <c r="H50" s="2">
         <v>0.69631062399999999</v>
       </c>
-      <c r="I50" s="9">
+      <c r="I50" s="10">
         <v>0.69631062399999999</v>
       </c>
       <c r="J50" s="2">
         <v>0.174077656</v>
       </c>
       <c r="K50" s="6" t="s">
-        <v>347</v>
-      </c>
-      <c r="L50" s="7" t="s">
+        <v>341</v>
+      </c>
+      <c r="L50" s="8" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="51" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="51" spans="1:12" s="8" customFormat="1" ht="18">
       <c r="A51" s="1">
         <v>50</v>
       </c>
-      <c r="B51" s="8" t="s">
+      <c r="B51" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="C51" s="7" t="s">
+      <c r="C51" s="8" t="s">
         <v>156</v>
       </c>
       <c r="D51" s="2">
         <v>0.55470019599999998</v>
       </c>
-      <c r="E51" s="9">
+      <c r="E51" s="10">
         <v>0</v>
       </c>
       <c r="F51" s="2">
         <v>0</v>
       </c>
-      <c r="G51" s="9">
+      <c r="G51" s="10">
         <v>0.55470019599999998</v>
       </c>
       <c r="H51" s="2">
         <v>0.55470019599999998</v>
       </c>
-      <c r="I51" s="9">
+      <c r="I51" s="10">
         <v>0</v>
       </c>
       <c r="J51" s="2">
         <v>0.27735009799999999</v>
       </c>
       <c r="K51" s="6" t="s">
-        <v>348</v>
-      </c>
-      <c r="L51" s="7" t="s">
+        <v>342</v>
+      </c>
+      <c r="L51" s="8" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="52" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="52" spans="1:12" s="8" customFormat="1" ht="18">
       <c r="A52" s="1">
         <v>51</v>
       </c>
-      <c r="B52" s="8" t="s">
+      <c r="B52" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="C52" s="7" t="s">
+      <c r="C52" s="8" t="s">
         <v>157</v>
       </c>
       <c r="D52" s="2">
         <v>0</v>
       </c>
-      <c r="E52" s="9">
+      <c r="E52" s="10">
         <v>0</v>
       </c>
       <c r="F52" s="2">
         <v>0</v>
       </c>
-      <c r="G52" s="9">
+      <c r="G52" s="10">
         <v>0</v>
       </c>
       <c r="H52" s="2">
         <v>0.26726124200000001</v>
       </c>
-      <c r="I52" s="9">
+      <c r="I52" s="10">
         <v>0.53452248400000002</v>
       </c>
       <c r="J52" s="2">
         <v>0.80178372600000003</v>
       </c>
       <c r="K52" s="6" t="s">
-        <v>349</v>
-      </c>
-      <c r="L52" s="7" t="s">
+        <v>343</v>
+      </c>
+      <c r="L52" s="8" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="53" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="53" spans="1:12" s="8" customFormat="1" ht="18">
       <c r="A53" s="1">
         <v>52</v>
       </c>
-      <c r="B53" s="8" t="s">
+      <c r="B53" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="C53" s="7" t="s">
+      <c r="C53" s="8" t="s">
         <v>158</v>
       </c>
       <c r="D53" s="2">
         <v>0</v>
       </c>
-      <c r="E53" s="9">
+      <c r="E53" s="10">
         <v>0</v>
       </c>
       <c r="F53" s="2">
         <v>0</v>
       </c>
-      <c r="G53" s="9">
+      <c r="G53" s="10">
         <v>0</v>
       </c>
       <c r="H53" s="2">
         <v>0.514495755</v>
       </c>
-      <c r="I53" s="9">
+      <c r="I53" s="10">
         <v>0.68599434100000001</v>
       </c>
       <c r="J53" s="2">
         <v>0.514495755</v>
       </c>
       <c r="K53" s="6" t="s">
-        <v>350</v>
-      </c>
-      <c r="L53" s="7" t="s">
+        <v>344</v>
+      </c>
+      <c r="L53" s="8" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="54" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="54" spans="1:12" s="8" customFormat="1" ht="57">
       <c r="A54" s="1">
         <v>53</v>
       </c>
-      <c r="B54" s="8" t="s">
+      <c r="B54" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="C54" s="7" t="s">
+      <c r="C54" s="8" t="s">
         <v>159</v>
       </c>
       <c r="D54" s="2">
         <v>0</v>
       </c>
-      <c r="E54" s="9">
+      <c r="E54" s="10">
         <v>0</v>
       </c>
       <c r="F54" s="2">
         <v>0</v>
       </c>
-      <c r="G54" s="9">
+      <c r="G54" s="10">
         <v>0</v>
       </c>
       <c r="H54" s="2">
         <v>0.514495755</v>
       </c>
-      <c r="I54" s="9">
+      <c r="I54" s="10">
         <v>0.68599434100000001</v>
       </c>
       <c r="J54" s="2">
         <v>0.514495755</v>
       </c>
-      <c r="K54" s="6" t="s">
-        <v>357</v>
-      </c>
-      <c r="L54" s="7" t="s">
+      <c r="K54" s="7" t="s">
+        <v>345</v>
+      </c>
+      <c r="L54" s="8" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="55" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="55" spans="1:12" s="8" customFormat="1" ht="18">
       <c r="A55" s="1">
         <v>54</v>
       </c>
-      <c r="B55" s="8" t="s">
+      <c r="B55" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="C55" s="7" t="s">
+      <c r="C55" s="8" t="s">
         <v>160</v>
       </c>
       <c r="D55" s="2">
         <v>0</v>
       </c>
-      <c r="E55" s="9">
+      <c r="E55" s="10">
         <v>0</v>
       </c>
       <c r="F55" s="2">
         <v>0</v>
       </c>
-      <c r="G55" s="9">
+      <c r="G55" s="10">
         <v>0</v>
       </c>
       <c r="H55" s="2">
         <v>0.63960214900000001</v>
       </c>
-      <c r="I55" s="9">
+      <c r="I55" s="10">
         <v>0.426401433</v>
       </c>
       <c r="J55" s="2">
         <v>0.63960214900000001</v>
       </c>
       <c r="K55" s="6" t="s">
-        <v>351</v>
-      </c>
-      <c r="L55" s="7" t="s">
+        <v>346</v>
+      </c>
+      <c r="L55" s="8" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="56" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="56" spans="1:12" s="8" customFormat="1" ht="18">
       <c r="A56" s="1">
         <v>55</v>
       </c>
-      <c r="B56" s="8" t="s">
+      <c r="B56" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="C56" s="7" t="s">
+      <c r="C56" s="8" t="s">
         <v>161</v>
       </c>
       <c r="D56" s="2">
         <v>0</v>
       </c>
-      <c r="E56" s="9">
+      <c r="E56" s="10">
         <v>0</v>
       </c>
       <c r="F56" s="2">
         <v>0</v>
       </c>
-      <c r="G56" s="9">
+      <c r="G56" s="10">
         <v>0</v>
       </c>
       <c r="H56" s="2">
         <v>0.514495755</v>
       </c>
-      <c r="I56" s="9">
+      <c r="I56" s="10">
         <v>0.514495755</v>
       </c>
       <c r="J56" s="2">
         <v>0.68599434100000001</v>
       </c>
       <c r="K56" s="6" t="s">
-        <v>380</v>
-      </c>
-      <c r="L56" s="7" t="s">
+        <v>373</v>
+      </c>
+      <c r="L56" s="8" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="57" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="57" spans="1:12" s="8" customFormat="1" ht="18">
       <c r="A57" s="1">
         <v>56</v>
       </c>
-      <c r="B57" s="8" t="s">
+      <c r="B57" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="C57" s="7" t="s">
+      <c r="C57" s="8" t="s">
         <v>162</v>
       </c>
       <c r="D57" s="2">
         <v>0</v>
       </c>
-      <c r="E57" s="9">
+      <c r="E57" s="10">
         <v>0.23570226</v>
       </c>
       <c r="F57" s="2">
         <v>0</v>
       </c>
-      <c r="G57" s="9">
+      <c r="G57" s="10">
         <v>0</v>
       </c>
       <c r="H57" s="2">
         <v>0.70710678100000002</v>
       </c>
-      <c r="I57" s="9">
+      <c r="I57" s="10">
         <v>0.47140452100000002</v>
       </c>
       <c r="J57" s="2">
         <v>0.47140452100000002</v>
       </c>
       <c r="K57" s="6" t="s">
-        <v>352</v>
-      </c>
-      <c r="L57" s="7" t="s">
+        <v>347</v>
+      </c>
+      <c r="L57" s="8" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="58" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="58" spans="1:12" s="8" customFormat="1" ht="18">
       <c r="A58" s="1">
         <v>57</v>
       </c>
-      <c r="B58" s="8" t="s">
+      <c r="B58" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="C58" s="7" t="s">
+      <c r="C58" s="8" t="s">
         <v>163</v>
       </c>
       <c r="D58" s="2">
         <v>0</v>
       </c>
-      <c r="E58" s="9">
+      <c r="E58" s="10">
         <v>0</v>
       </c>
       <c r="F58" s="2">
         <v>0</v>
       </c>
-      <c r="G58" s="9">
+      <c r="G58" s="10">
         <v>0</v>
       </c>
       <c r="H58" s="2">
         <v>0</v>
       </c>
-      <c r="I58" s="9">
+      <c r="I58" s="10">
         <v>1</v>
       </c>
       <c r="J58" s="2">
         <v>0</v>
       </c>
       <c r="K58" s="6" t="s">
-        <v>353</v>
-      </c>
-      <c r="L58" s="7" t="s">
+        <v>348</v>
+      </c>
+      <c r="L58" s="8" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="59" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="59" spans="1:12" s="8" customFormat="1" ht="18">
       <c r="A59" s="1">
         <v>58</v>
       </c>
-      <c r="B59" s="8" t="s">
+      <c r="B59" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="C59" s="7" t="s">
+      <c r="C59" s="8" t="s">
         <v>164</v>
       </c>
       <c r="D59" s="2">
         <v>0</v>
       </c>
-      <c r="E59" s="9">
+      <c r="E59" s="10">
         <v>0.35921060399999999</v>
       </c>
       <c r="F59" s="2">
         <v>0</v>
       </c>
-      <c r="G59" s="9">
+      <c r="G59" s="10">
         <v>0</v>
       </c>
       <c r="H59" s="2">
         <v>0.53881590599999996</v>
       </c>
-      <c r="I59" s="9">
+      <c r="I59" s="10">
         <v>0.53881590599999996</v>
       </c>
       <c r="J59" s="2">
         <v>0.53881590599999996</v>
       </c>
       <c r="K59" s="6" t="s">
-        <v>370</v>
-      </c>
-      <c r="L59" s="7" t="s">
+        <v>363</v>
+      </c>
+      <c r="L59" s="8" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="60" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="60" spans="1:12" s="8" customFormat="1" ht="18">
       <c r="A60" s="1">
         <v>59</v>
       </c>
-      <c r="B60" s="8" t="s">
+      <c r="B60" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="C60" s="7" t="s">
+      <c r="C60" s="8" t="s">
         <v>165</v>
       </c>
       <c r="D60" s="2">
         <v>0.188982237</v>
       </c>
-      <c r="E60" s="9">
+      <c r="E60" s="10">
         <v>0.56694670999999996</v>
       </c>
       <c r="F60" s="2">
         <v>0</v>
       </c>
-      <c r="G60" s="9">
+      <c r="G60" s="10">
         <v>0</v>
       </c>
       <c r="H60" s="2">
         <v>0.56694670999999996</v>
       </c>
-      <c r="I60" s="9">
+      <c r="I60" s="10">
         <v>0.56694670999999996</v>
       </c>
       <c r="J60" s="2">
         <v>0</v>
       </c>
       <c r="K60" s="6" t="s">
-        <v>354</v>
-      </c>
-      <c r="L60" s="7" t="s">
+        <v>349</v>
+      </c>
+      <c r="L60" s="8" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="61" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="61" spans="1:12" s="8" customFormat="1" ht="18">
       <c r="A61" s="1">
         <v>60</v>
       </c>
-      <c r="B61" s="8" t="s">
+      <c r="B61" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="C61" s="7" t="s">
+      <c r="C61" s="8" t="s">
         <v>166</v>
       </c>
       <c r="D61" s="2">
         <v>0.39223226999999999</v>
       </c>
-      <c r="E61" s="9">
+      <c r="E61" s="10">
         <v>0.39223226999999999</v>
       </c>
       <c r="F61" s="2">
         <v>0.39223226999999999</v>
       </c>
-      <c r="G61" s="9">
+      <c r="G61" s="10">
         <v>0.58834840499999996</v>
       </c>
       <c r="H61" s="2">
         <v>0</v>
       </c>
-      <c r="I61" s="9">
+      <c r="I61" s="10">
         <v>0.39223226999999999</v>
       </c>
       <c r="J61" s="2">
         <v>0.196116135</v>
       </c>
       <c r="K61" s="6" t="s">
-        <v>355</v>
-      </c>
-      <c r="L61" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="L61" s="8" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="62" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="62" spans="1:12" s="8" customFormat="1" ht="18">
       <c r="A62" s="1">
         <v>61</v>
       </c>
-      <c r="B62" s="8" t="s">
+      <c r="B62" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="C62" s="7" t="s">
+      <c r="C62" s="8" t="s">
         <v>167</v>
       </c>
       <c r="D62" s="2">
         <v>0.53452248400000002</v>
       </c>
-      <c r="E62" s="9">
+      <c r="E62" s="10">
         <v>0.53452248400000002</v>
       </c>
       <c r="F62" s="2">
         <v>0.26726124200000001</v>
       </c>
-      <c r="G62" s="9">
+      <c r="G62" s="10">
         <v>0.53452248400000002</v>
       </c>
       <c r="H62" s="2">
         <v>0</v>
       </c>
-      <c r="I62" s="9">
+      <c r="I62" s="10">
         <v>0.26726124200000001</v>
       </c>
       <c r="J62" s="2">
         <v>0</v>
       </c>
       <c r="K62" s="6" t="s">
-        <v>356</v>
-      </c>
-      <c r="L62" s="7" t="s">
+        <v>351</v>
+      </c>
+      <c r="L62" s="8" t="s">
         <v>266</v>
       </c>
     </row>
@@ -4687,7 +4721,7 @@
         <v>0.39223226999999999</v>
       </c>
       <c r="K63" s="6" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="L63" t="s">
         <v>267</v>
@@ -4725,7 +4759,7 @@
         <v>0.39223226999999999</v>
       </c>
       <c r="K64" s="6" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="L64" t="s">
         <v>268</v>
@@ -4763,7 +4797,7 @@
         <v>0.31622776600000002</v>
       </c>
       <c r="K65" s="6" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="L65" t="s">
         <v>269</v>
@@ -4801,7 +4835,7 @@
         <v>0.174077656</v>
       </c>
       <c r="K66" s="6" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="L66" t="s">
         <v>270</v>
@@ -4839,7 +4873,7 @@
         <v>0.816496581</v>
       </c>
       <c r="K67" s="6" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="L67" t="s">
         <v>271</v>
@@ -4877,7 +4911,7 @@
         <v>0</v>
       </c>
       <c r="K68" s="6" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="L68" t="s">
         <v>272</v>
@@ -4915,7 +4949,7 @@
         <v>0</v>
       </c>
       <c r="K69" s="6" t="s">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="L69" t="s">
         <v>273</v>
@@ -4953,7 +4987,7 @@
         <v>0</v>
       </c>
       <c r="K70" s="6" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="L70" t="s">
         <v>274</v>
@@ -4991,7 +5025,7 @@
         <v>0</v>
       </c>
       <c r="K71" s="6" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="L71" t="s">
         <v>275</v>
@@ -5029,7 +5063,7 @@
         <v>0</v>
       </c>
       <c r="K72" s="6" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="L72" t="s">
         <v>276</v>
@@ -5067,7 +5101,7 @@
         <v>0</v>
       </c>
       <c r="K73" s="6" t="s">
-        <v>384</v>
+        <v>377</v>
       </c>
       <c r="L73" t="s">
         <v>277</v>
@@ -5105,7 +5139,7 @@
         <v>0.66666666699999999</v>
       </c>
       <c r="K74" s="6" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="L74" t="s">
         <v>278</v>
@@ -5143,7 +5177,7 @@
         <v>0.47140452100000002</v>
       </c>
       <c r="K75" s="6" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="L75" t="s">
         <v>279</v>
@@ -5181,7 +5215,7 @@
         <v>1</v>
       </c>
       <c r="K76" s="6" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="L76" t="s">
         <v>280</v>
@@ -5219,7 +5253,7 @@
         <v>0.26726124200000001</v>
       </c>
       <c r="K77" s="6" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="L77" t="s">
         <v>281</v>
@@ -5257,7 +5291,7 @@
         <v>0</v>
       </c>
       <c r="K78" s="6" t="s">
-        <v>389</v>
+        <v>381</v>
       </c>
       <c r="L78" t="s">
         <v>282</v>
@@ -5295,7 +5329,7 @@
         <v>0.57735026899999997</v>
       </c>
       <c r="K79" s="6" t="s">
-        <v>390</v>
+        <v>382</v>
       </c>
       <c r="L79" t="s">
         <v>283</v>
@@ -5371,7 +5405,7 @@
         <v>0.70710678100000002</v>
       </c>
       <c r="K81" s="6" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="L81" t="s">
         <v>285</v>
@@ -5409,7 +5443,7 @@
         <v>0.70710678100000002</v>
       </c>
       <c r="K82" s="6" t="s">
-        <v>393</v>
+        <v>384</v>
       </c>
       <c r="L82" t="s">
         <v>286</v>
@@ -5447,7 +5481,7 @@
         <v>0.30151134499999999</v>
       </c>
       <c r="K83" s="6" t="s">
-        <v>394</v>
+        <v>385</v>
       </c>
       <c r="L83" t="s">
         <v>287</v>
@@ -5485,7 +5519,7 @@
         <v>0</v>
       </c>
       <c r="K84" s="6" t="s">
-        <v>395</v>
+        <v>386</v>
       </c>
       <c r="L84" t="s">
         <v>288</v>
@@ -5523,7 +5557,7 @@
         <v>0.57735026899999997</v>
       </c>
       <c r="K85" s="6" t="s">
-        <v>396</v>
+        <v>387</v>
       </c>
       <c r="L85" t="s">
         <v>289</v>
@@ -5560,8 +5594,8 @@
       <c r="J86" s="2">
         <v>0</v>
       </c>
-      <c r="K86" s="2" t="s">
-        <v>306</v>
+      <c r="K86" s="6" t="s">
+        <v>392</v>
       </c>
       <c r="L86" t="s">
         <v>290</v>
@@ -5598,8 +5632,8 @@
       <c r="J87" s="2">
         <v>0.29488391200000003</v>
       </c>
-      <c r="K87" s="2" t="s">
-        <v>306</v>
+      <c r="K87" s="6" t="s">
+        <v>393</v>
       </c>
       <c r="L87" t="s">
         <v>291</v>
@@ -5636,8 +5670,8 @@
       <c r="J88" s="2">
         <v>0</v>
       </c>
-      <c r="K88" s="2" t="s">
-        <v>306</v>
+      <c r="K88" s="6" t="s">
+        <v>394</v>
       </c>
       <c r="L88" t="s">
         <v>292</v>
@@ -5674,8 +5708,8 @@
       <c r="J89" s="2">
         <v>0.51639777899999995</v>
       </c>
-      <c r="K89" s="2" t="s">
-        <v>307</v>
+      <c r="K89" s="6" t="s">
+        <v>395</v>
       </c>
       <c r="L89" t="s">
         <v>293</v>
@@ -5712,14 +5746,14 @@
       <c r="J90" s="2">
         <v>0.31622776600000002</v>
       </c>
-      <c r="K90" s="2" t="s">
-        <v>307</v>
+      <c r="K90" s="6" t="s">
+        <v>396</v>
       </c>
       <c r="L90" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="91" spans="1:12" ht="18">
+    <row r="91" spans="1:12" ht="21">
       <c r="A91" s="1">
         <v>90</v>
       </c>
@@ -5750,8 +5784,8 @@
       <c r="J91" s="2">
         <v>0.43643578</v>
       </c>
-      <c r="K91" s="2" t="s">
-        <v>307</v>
+      <c r="K91" s="6" t="s">
+        <v>397</v>
       </c>
       <c r="L91" t="s">
         <v>295</v>
@@ -5788,8 +5822,8 @@
       <c r="J92" s="2">
         <v>0</v>
       </c>
-      <c r="K92" s="2" t="s">
-        <v>308</v>
+      <c r="K92" s="6" t="s">
+        <v>398</v>
       </c>
       <c r="L92" t="s">
         <v>296</v>
@@ -5826,8 +5860,8 @@
       <c r="J93" s="2">
         <v>0</v>
       </c>
-      <c r="K93" s="2" t="s">
-        <v>308</v>
+      <c r="K93" s="6" t="s">
+        <v>399</v>
       </c>
       <c r="L93" t="s">
         <v>297</v>
@@ -5864,8 +5898,8 @@
       <c r="J94" s="2">
         <v>0</v>
       </c>
-      <c r="K94" s="2" t="s">
-        <v>308</v>
+      <c r="K94" s="6" t="s">
+        <v>400</v>
       </c>
       <c r="L94" t="s">
         <v>298</v>
@@ -5902,8 +5936,8 @@
       <c r="J95" s="2">
         <v>0.53033008599999998</v>
       </c>
-      <c r="K95" s="2" t="s">
-        <v>309</v>
+      <c r="K95" s="6" t="s">
+        <v>401</v>
       </c>
       <c r="L95" t="s">
         <v>299</v>
@@ -5940,8 +5974,8 @@
       <c r="J96" s="2">
         <v>0.48507125000000001</v>
       </c>
-      <c r="K96" s="2" t="s">
-        <v>309</v>
+      <c r="K96" s="6" t="s">
+        <v>402</v>
       </c>
       <c r="L96" t="s">
         <v>300</v>
@@ -5978,8 +6012,8 @@
       <c r="J97" s="2">
         <v>0.56568542499999996</v>
       </c>
-      <c r="K97" s="2" t="s">
-        <v>309</v>
+      <c r="K97" s="6" t="s">
+        <v>403</v>
       </c>
       <c r="L97" t="s">
         <v>301</v>
@@ -6016,8 +6050,8 @@
       <c r="J98" s="2">
         <v>0.78446454099999996</v>
       </c>
-      <c r="K98" s="2" t="s">
-        <v>310</v>
+      <c r="K98" s="6" t="s">
+        <v>404</v>
       </c>
       <c r="L98" t="s">
         <v>302</v>
@@ -6054,8 +6088,8 @@
       <c r="J99" s="2">
         <v>0.63960214900000001</v>
       </c>
-      <c r="K99" s="2" t="s">
-        <v>310</v>
+      <c r="K99" s="6" t="s">
+        <v>405</v>
       </c>
       <c r="L99" t="s">
         <v>303</v>
@@ -6092,8 +6126,8 @@
       <c r="J100" s="2">
         <v>0.54433105400000004</v>
       </c>
-      <c r="K100" s="2" t="s">
-        <v>310</v>
+      <c r="K100" s="6" t="s">
+        <v>406</v>
       </c>
       <c r="L100" t="s">
         <v>304</v>

--- a/library.xlsx
+++ b/library.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xxc/Desktop/xxc/拓殖大学/研究室/評価実験/video-recommend-system/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E51BCD9-B35F-3F4D-BA5D-68F028CF16B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B021C07-25FC-9444-9787-692769195CE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{F40E9203-8E2D-9949-9A4C-F506F7C93633}"/>
   </bookViews>
@@ -1708,9 +1708,6 @@
     <t>スポーツ,歴史,共感,competition,Video Highlights</t>
   </si>
   <si>
-    <t>アニメ,ゲーム,Cyberpunk: Edgerunners,Cyberpunk,Cyberpunk 2077,Netflix,音楽,MV,共感,感動,文化,都市,宇宙,月,Rosa Walton,Love,家族,名作,Movieclips,Theme song,宇宙飛行士,未来,戦い,夜景,Lucy,David,Video Highlights</t>
-  </si>
-  <si>
     <t>歴史,溥儀,World War Two,共感,中国,皇帝,東京,裁判所,ドキュメンタリー,戦争</t>
   </si>
   <si>
@@ -1777,6 +1774,10 @@
   </si>
   <si>
     <t>ダンス,Michael Jackson,音楽,Pop,映画,名作,共感,MV,恐怖</t>
+  </si>
+  <si>
+    <t>アニメ,ゲーム,Cyberpunk: Edgerunners,Cyberpunk,Cyberpunk 2077,Netflix,音楽,Pop,MV,共感,感動,文化,都市,宇宙,月,Rosa Walton,Love,名作,Movieclips,Theme song,宇宙飛行士,未来,戦い,夜景,Lucy,David,Video Highlights</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -5346,28 +5347,28 @@
         <v>185</v>
       </c>
       <c r="D80" s="2">
-        <v>0.55470019599999998</v>
+        <v>0.56568542499999996</v>
       </c>
       <c r="E80" s="3">
-        <v>0</v>
+        <v>0.282842712</v>
       </c>
       <c r="F80" s="2">
-        <v>0.55470019599999998</v>
+        <v>0.56568542499999996</v>
       </c>
       <c r="G80" s="3">
-        <v>0</v>
+        <v>0.282842712</v>
       </c>
       <c r="H80" s="2">
-        <v>0.55470019599999998</v>
+        <v>0</v>
       </c>
       <c r="I80" s="3">
-        <v>0.27735009799999999</v>
+        <v>0.42426406900000002</v>
       </c>
       <c r="J80" s="2">
-        <v>0</v>
+        <v>0.141421356</v>
       </c>
       <c r="K80" s="6" t="s">
-        <v>391</v>
+        <v>406</v>
       </c>
       <c r="L80" t="s">
         <v>284</v>
@@ -5595,7 +5596,7 @@
         <v>0</v>
       </c>
       <c r="K86" s="6" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="L86" t="s">
         <v>290</v>
@@ -5633,7 +5634,7 @@
         <v>0.29488391200000003</v>
       </c>
       <c r="K87" s="6" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="L87" t="s">
         <v>291</v>
@@ -5671,7 +5672,7 @@
         <v>0</v>
       </c>
       <c r="K88" s="6" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="L88" t="s">
         <v>292</v>
@@ -5709,7 +5710,7 @@
         <v>0.51639777899999995</v>
       </c>
       <c r="K89" s="6" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="L89" t="s">
         <v>293</v>
@@ -5747,7 +5748,7 @@
         <v>0.31622776600000002</v>
       </c>
       <c r="K90" s="6" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="L90" t="s">
         <v>294</v>
@@ -5785,7 +5786,7 @@
         <v>0.43643578</v>
       </c>
       <c r="K91" s="6" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="L91" t="s">
         <v>295</v>
@@ -5823,7 +5824,7 @@
         <v>0</v>
       </c>
       <c r="K92" s="6" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="L92" t="s">
         <v>296</v>
@@ -5861,7 +5862,7 @@
         <v>0</v>
       </c>
       <c r="K93" s="6" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="L93" t="s">
         <v>297</v>
@@ -5899,7 +5900,7 @@
         <v>0</v>
       </c>
       <c r="K94" s="6" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="L94" t="s">
         <v>298</v>
@@ -5937,7 +5938,7 @@
         <v>0.53033008599999998</v>
       </c>
       <c r="K95" s="6" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="L95" t="s">
         <v>299</v>
@@ -5975,7 +5976,7 @@
         <v>0.48507125000000001</v>
       </c>
       <c r="K96" s="6" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="L96" t="s">
         <v>300</v>
@@ -6013,7 +6014,7 @@
         <v>0.56568542499999996</v>
       </c>
       <c r="K97" s="6" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="L97" t="s">
         <v>301</v>
@@ -6051,7 +6052,7 @@
         <v>0.78446454099999996</v>
       </c>
       <c r="K98" s="6" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="L98" t="s">
         <v>302</v>
@@ -6089,7 +6090,7 @@
         <v>0.63960214900000001</v>
       </c>
       <c r="K99" s="6" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="L99" t="s">
         <v>303</v>
@@ -6127,7 +6128,7 @@
         <v>0.54433105400000004</v>
       </c>
       <c r="K100" s="6" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="L100" t="s">
         <v>304</v>

--- a/library.xlsx
+++ b/library.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xxc/Desktop/xxc/拓殖大学/研究室/評価実験/video-recommend-system/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B021C07-25FC-9444-9787-692769195CE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03E6FF0F-AA09-A845-88E9-BD86783CBE9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{F40E9203-8E2D-9949-9A4C-F506F7C93633}"/>
   </bookViews>
@@ -1770,13 +1770,14 @@
     <t>ダンス,Pop,音楽,リラックス,Staying Alive,Trio</t>
   </si>
   <si>
-    <t>ダンス,アニメ,Pop,音楽,コメディ,宇宙人,宇宙,MV</t>
-  </si>
-  <si>
     <t>ダンス,Michael Jackson,音楽,Pop,映画,名作,共感,MV,恐怖</t>
   </si>
   <si>
     <t>アニメ,ゲーム,Cyberpunk: Edgerunners,Cyberpunk,Cyberpunk 2077,Netflix,音楽,Pop,MV,共感,感動,文化,都市,宇宙,月,Rosa Walton,Love,名作,Movieclips,Theme song,宇宙飛行士,未来,戦い,夜景,Lucy,David,Video Highlights</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ダンス,アニメ,Pop,音楽,コメディ,宇宙人,MV</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -5368,7 +5369,7 @@
         <v>0.141421356</v>
       </c>
       <c r="K80" s="6" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="L80" t="s">
         <v>284</v>
@@ -6090,7 +6091,7 @@
         <v>0.63960214900000001</v>
       </c>
       <c r="K99" s="6" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="L99" t="s">
         <v>303</v>
@@ -6128,7 +6129,7 @@
         <v>0.54433105400000004</v>
       </c>
       <c r="K100" s="6" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="L100" t="s">
         <v>304</v>

--- a/library.xlsx
+++ b/library.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xxc/Desktop/xxc/拓殖大学/研究室/評価実験/video-recommend-system/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03E6FF0F-AA09-A845-88E9-BD86783CBE9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E1FBEB0-D4AB-A849-96E3-701B2317A722}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{F40E9203-8E2D-9949-9A4C-F506F7C93633}"/>
   </bookViews>
@@ -1777,7 +1777,7 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>ダンス,アニメ,Pop,音楽,コメディ,宇宙人,MV</t>
+    <t>ダンス,アニメ,音楽,コメディ,宇宙人,MV,meme</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1957,7 +1957,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1978,9 +1978,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2335,7 +2332,7 @@
     <col min="4" max="10" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="8" customFormat="1" ht="18">
+    <row r="1" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2373,32 +2370,32 @@
         <v>207</v>
       </c>
     </row>
-    <row r="2" spans="1:12" s="8" customFormat="1" ht="18">
+    <row r="2" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="7" t="s">
         <v>108</v>
       </c>
       <c r="D2" s="2">
         <v>0</v>
       </c>
-      <c r="E2" s="10">
+      <c r="E2" s="9">
         <v>0</v>
       </c>
       <c r="F2" s="2">
         <v>0</v>
       </c>
-      <c r="G2" s="10">
+      <c r="G2" s="9">
         <v>0</v>
       </c>
       <c r="H2" s="2">
         <v>0.31622776600000002</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="9">
         <v>0</v>
       </c>
       <c r="J2" s="2">
@@ -2407,36 +2404,36 @@
       <c r="K2" s="6" t="s">
         <v>309</v>
       </c>
-      <c r="L2" s="8" t="s">
+      <c r="L2" s="7" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="3" spans="1:12" s="8" customFormat="1" ht="21">
+    <row r="3" spans="1:12" s="7" customFormat="1" ht="21">
       <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="7" t="s">
         <v>109</v>
       </c>
       <c r="D3" s="2">
         <v>0</v>
       </c>
-      <c r="E3" s="10">
+      <c r="E3" s="9">
         <v>0</v>
       </c>
       <c r="F3" s="2">
         <v>0</v>
       </c>
-      <c r="G3" s="10">
+      <c r="G3" s="9">
         <v>0</v>
       </c>
       <c r="H3" s="2">
         <v>0.70710678100000002</v>
       </c>
-      <c r="I3" s="10">
+      <c r="I3" s="9">
         <v>0</v>
       </c>
       <c r="J3" s="2">
@@ -2445,36 +2442,36 @@
       <c r="K3" s="6" t="s">
         <v>325</v>
       </c>
-      <c r="L3" s="8" t="s">
+      <c r="L3" s="7" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="4" spans="1:12" s="8" customFormat="1" ht="18">
+    <row r="4" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A4" s="1">
         <v>3</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="8" t="s">
         <v>307</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="7" t="s">
         <v>308</v>
       </c>
       <c r="D4" s="2">
         <v>0</v>
       </c>
-      <c r="E4" s="10">
+      <c r="E4" s="9">
         <v>0</v>
       </c>
       <c r="F4" s="2">
         <v>0</v>
       </c>
-      <c r="G4" s="10">
+      <c r="G4" s="9">
         <v>0</v>
       </c>
       <c r="H4" s="2">
         <v>0.816496581</v>
       </c>
-      <c r="I4" s="10">
+      <c r="I4" s="9">
         <v>0.40824829000000001</v>
       </c>
       <c r="J4" s="2">
@@ -2483,36 +2480,36 @@
       <c r="K4" s="6" t="s">
         <v>352</v>
       </c>
-      <c r="L4" s="8" t="s">
+      <c r="L4" s="7" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="5" spans="1:12" s="8" customFormat="1" ht="18">
+    <row r="5" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A5" s="1">
         <v>4</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="7" t="s">
         <v>110</v>
       </c>
       <c r="D5" s="2">
         <v>0</v>
       </c>
-      <c r="E5" s="10">
+      <c r="E5" s="9">
         <v>0.31622776600000002</v>
       </c>
       <c r="F5" s="2">
         <v>0</v>
       </c>
-      <c r="G5" s="10">
+      <c r="G5" s="9">
         <v>0</v>
       </c>
       <c r="H5" s="2">
         <v>0.31622776600000002</v>
       </c>
-      <c r="I5" s="10">
+      <c r="I5" s="9">
         <v>0.63245553200000004</v>
       </c>
       <c r="J5" s="2">
@@ -2521,36 +2518,36 @@
       <c r="K5" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="L5" s="8" t="s">
+      <c r="L5" s="7" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="6" spans="1:12" s="8" customFormat="1" ht="18">
+    <row r="6" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A6" s="1">
         <v>5</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="7" t="s">
         <v>111</v>
       </c>
       <c r="D6" s="2">
         <v>0</v>
       </c>
-      <c r="E6" s="10">
+      <c r="E6" s="9">
         <v>0</v>
       </c>
       <c r="F6" s="2">
         <v>0</v>
       </c>
-      <c r="G6" s="10">
+      <c r="G6" s="9">
         <v>0</v>
       </c>
       <c r="H6" s="2">
         <v>0.48507125000000001</v>
       </c>
-      <c r="I6" s="10">
+      <c r="I6" s="9">
         <v>0.48507125000000001</v>
       </c>
       <c r="J6" s="2">
@@ -2559,36 +2556,36 @@
       <c r="K6" s="6" t="s">
         <v>311</v>
       </c>
-      <c r="L6" s="8" t="s">
+      <c r="L6" s="7" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="7" spans="1:12" s="8" customFormat="1" ht="18">
+    <row r="7" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A7" s="1">
         <v>6</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="7" t="s">
         <v>112</v>
       </c>
       <c r="D7" s="2">
         <v>0</v>
       </c>
-      <c r="E7" s="10">
+      <c r="E7" s="9">
         <v>0</v>
       </c>
       <c r="F7" s="2">
         <v>0</v>
       </c>
-      <c r="G7" s="10">
+      <c r="G7" s="9">
         <v>0</v>
       </c>
       <c r="H7" s="2">
         <v>0</v>
       </c>
-      <c r="I7" s="10">
+      <c r="I7" s="9">
         <v>0.89442719100000001</v>
       </c>
       <c r="J7" s="2">
@@ -2597,36 +2594,36 @@
       <c r="K7" s="6" t="s">
         <v>312</v>
       </c>
-      <c r="L7" s="8" t="s">
+      <c r="L7" s="7" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="8" spans="1:12" s="8" customFormat="1" ht="18">
+    <row r="8" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A8" s="1">
         <v>7</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="7" t="s">
         <v>113</v>
       </c>
       <c r="D8" s="2">
         <v>0</v>
       </c>
-      <c r="E8" s="10">
+      <c r="E8" s="9">
         <v>0.57735026899999997</v>
       </c>
       <c r="F8" s="2">
         <v>0</v>
       </c>
-      <c r="G8" s="10">
+      <c r="G8" s="9">
         <v>0.57735026899999997</v>
       </c>
       <c r="H8" s="2">
         <v>0.57735026899999997</v>
       </c>
-      <c r="I8" s="10">
+      <c r="I8" s="9">
         <v>0</v>
       </c>
       <c r="J8" s="2">
@@ -2635,36 +2632,36 @@
       <c r="K8" s="6" t="s">
         <v>313</v>
       </c>
-      <c r="L8" s="8" t="s">
+      <c r="L8" s="7" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="9" spans="1:12" s="8" customFormat="1" ht="28">
+    <row r="9" spans="1:12" s="7" customFormat="1" ht="28">
       <c r="A9" s="1">
         <v>8</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="7" t="s">
         <v>114</v>
       </c>
       <c r="D9" s="2">
         <v>0.86602540400000005</v>
       </c>
-      <c r="E9" s="10">
+      <c r="E9" s="9">
         <v>0.28867513500000003</v>
       </c>
       <c r="F9" s="2">
         <v>0</v>
       </c>
-      <c r="G9" s="10">
+      <c r="G9" s="9">
         <v>0</v>
       </c>
       <c r="H9" s="2">
         <v>0.28867513500000003</v>
       </c>
-      <c r="I9" s="10">
+      <c r="I9" s="9">
         <v>0.28867513500000003</v>
       </c>
       <c r="J9" s="2">
@@ -2673,36 +2670,36 @@
       <c r="K9" s="6" t="s">
         <v>371</v>
       </c>
-      <c r="L9" s="8" t="s">
+      <c r="L9" s="7" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="10" spans="1:12" s="8" customFormat="1" ht="18">
+    <row r="10" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A10" s="1">
         <v>9</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="7" t="s">
         <v>115</v>
       </c>
       <c r="D10" s="2">
         <v>0</v>
       </c>
-      <c r="E10" s="10">
+      <c r="E10" s="9">
         <v>0.37796447300000002</v>
       </c>
       <c r="F10" s="2">
         <v>0</v>
       </c>
-      <c r="G10" s="10">
+      <c r="G10" s="9">
         <v>0</v>
       </c>
       <c r="H10" s="2">
         <v>0.75592894600000005</v>
       </c>
-      <c r="I10" s="10">
+      <c r="I10" s="9">
         <v>0.37796447300000002</v>
       </c>
       <c r="J10" s="2">
@@ -2711,36 +2708,36 @@
       <c r="K10" s="6" t="s">
         <v>353</v>
       </c>
-      <c r="L10" s="8" t="s">
+      <c r="L10" s="7" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="11" spans="1:12" s="8" customFormat="1" ht="18">
+    <row r="11" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A11" s="1">
         <v>10</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="7" t="s">
         <v>116</v>
       </c>
       <c r="D11" s="2">
         <v>0</v>
       </c>
-      <c r="E11" s="10">
+      <c r="E11" s="9">
         <v>0.28867513500000003</v>
       </c>
       <c r="F11" s="2">
         <v>0</v>
       </c>
-      <c r="G11" s="10">
+      <c r="G11" s="9">
         <v>0</v>
       </c>
       <c r="H11" s="2">
         <v>0.28867513500000003</v>
       </c>
-      <c r="I11" s="10">
+      <c r="I11" s="9">
         <v>0.86602540400000005</v>
       </c>
       <c r="J11" s="2">
@@ -2749,36 +2746,36 @@
       <c r="K11" s="6" t="s">
         <v>314</v>
       </c>
-      <c r="L11" s="8" t="s">
+      <c r="L11" s="7" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="12" spans="1:12" s="8" customFormat="1" ht="18">
+    <row r="12" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A12" s="1">
         <v>11</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C12" s="7" t="s">
         <v>117</v>
       </c>
       <c r="D12" s="2">
         <v>0</v>
       </c>
-      <c r="E12" s="10">
+      <c r="E12" s="9">
         <v>0</v>
       </c>
       <c r="F12" s="2">
         <v>0</v>
       </c>
-      <c r="G12" s="10">
+      <c r="G12" s="9">
         <v>0</v>
       </c>
       <c r="H12" s="2">
         <v>0.57735026899999997</v>
       </c>
-      <c r="I12" s="10">
+      <c r="I12" s="9">
         <v>0.57735026899999997</v>
       </c>
       <c r="J12" s="2">
@@ -2787,36 +2784,36 @@
       <c r="K12" s="6" t="s">
         <v>326</v>
       </c>
-      <c r="L12" s="8" t="s">
+      <c r="L12" s="7" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="13" spans="1:12" s="8" customFormat="1" ht="18">
+    <row r="13" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A13" s="1">
         <v>12</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="B13" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="7" t="s">
         <v>118</v>
       </c>
       <c r="D13" s="2">
         <v>0</v>
       </c>
-      <c r="E13" s="10">
+      <c r="E13" s="9">
         <v>0</v>
       </c>
       <c r="F13" s="2">
         <v>0</v>
       </c>
-      <c r="G13" s="10">
+      <c r="G13" s="9">
         <v>0</v>
       </c>
       <c r="H13" s="2">
         <v>0.26726124200000001</v>
       </c>
-      <c r="I13" s="10">
+      <c r="I13" s="9">
         <v>0.53452248400000002</v>
       </c>
       <c r="J13" s="2">
@@ -2825,36 +2822,36 @@
       <c r="K13" s="6" t="s">
         <v>315</v>
       </c>
-      <c r="L13" s="8" t="s">
+      <c r="L13" s="7" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="14" spans="1:12" s="8" customFormat="1" ht="18">
+    <row r="14" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A14" s="1">
         <v>13</v>
       </c>
-      <c r="B14" s="9" t="s">
+      <c r="B14" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C14" s="7" t="s">
         <v>119</v>
       </c>
       <c r="D14" s="2">
         <v>0</v>
       </c>
-      <c r="E14" s="10">
+      <c r="E14" s="9">
         <v>0</v>
       </c>
       <c r="F14" s="2">
         <v>0</v>
       </c>
-      <c r="G14" s="10">
+      <c r="G14" s="9">
         <v>0.28867513500000003</v>
       </c>
       <c r="H14" s="2">
         <v>0.28867513500000003</v>
       </c>
-      <c r="I14" s="10">
+      <c r="I14" s="9">
         <v>0.86602540400000005</v>
       </c>
       <c r="J14" s="2">
@@ -2863,36 +2860,36 @@
       <c r="K14" s="6" t="s">
         <v>316</v>
       </c>
-      <c r="L14" s="8" t="s">
+      <c r="L14" s="7" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="15" spans="1:12" s="8" customFormat="1" ht="18">
+    <row r="15" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A15" s="1">
         <v>14</v>
       </c>
-      <c r="B15" s="9" t="s">
+      <c r="B15" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="7" t="s">
         <v>120</v>
       </c>
       <c r="D15" s="2">
         <v>0</v>
       </c>
-      <c r="E15" s="10">
+      <c r="E15" s="9">
         <v>0</v>
       </c>
       <c r="F15" s="2">
         <v>0</v>
       </c>
-      <c r="G15" s="10">
+      <c r="G15" s="9">
         <v>0</v>
       </c>
       <c r="H15" s="2">
         <v>0</v>
       </c>
-      <c r="I15" s="10">
+      <c r="I15" s="9">
         <v>0.44721359500000002</v>
       </c>
       <c r="J15" s="2">
@@ -2901,36 +2898,36 @@
       <c r="K15" s="6" t="s">
         <v>388</v>
       </c>
-      <c r="L15" s="8" t="s">
+      <c r="L15" s="7" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="16" spans="1:12" s="8" customFormat="1" ht="18">
+    <row r="16" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A16" s="1">
         <v>15</v>
       </c>
-      <c r="B16" s="9" t="s">
+      <c r="B16" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="C16" s="7" t="s">
         <v>121</v>
       </c>
       <c r="D16" s="2">
         <v>0</v>
       </c>
-      <c r="E16" s="10">
+      <c r="E16" s="9">
         <v>0.23570226</v>
       </c>
       <c r="F16" s="2">
         <v>0</v>
       </c>
-      <c r="G16" s="10">
+      <c r="G16" s="9">
         <v>0</v>
       </c>
       <c r="H16" s="2">
         <v>0.47140452100000002</v>
       </c>
-      <c r="I16" s="10">
+      <c r="I16" s="9">
         <v>0.47140452100000002</v>
       </c>
       <c r="J16" s="2">
@@ -2939,36 +2936,36 @@
       <c r="K16" s="6" t="s">
         <v>354</v>
       </c>
-      <c r="L16" s="8" t="s">
+      <c r="L16" s="7" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="17" spans="1:12" s="8" customFormat="1" ht="18">
+    <row r="17" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A17" s="1">
         <v>16</v>
       </c>
-      <c r="B17" s="9" t="s">
+      <c r="B17" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="C17" s="7" t="s">
         <v>122</v>
       </c>
       <c r="D17" s="2">
         <v>0</v>
       </c>
-      <c r="E17" s="10">
+      <c r="E17" s="9">
         <v>0</v>
       </c>
       <c r="F17" s="2">
         <v>0.22941573400000001</v>
       </c>
-      <c r="G17" s="10">
+      <c r="G17" s="9">
         <v>0.688247202</v>
       </c>
       <c r="H17" s="2">
         <v>0.22941573400000001</v>
       </c>
-      <c r="I17" s="10">
+      <c r="I17" s="9">
         <v>0.45883146800000002</v>
       </c>
       <c r="J17" s="2">
@@ -2977,36 +2974,36 @@
       <c r="K17" s="6" t="s">
         <v>327</v>
       </c>
-      <c r="L17" s="8" t="s">
+      <c r="L17" s="7" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="18" spans="1:12" s="8" customFormat="1" ht="28">
+    <row r="18" spans="1:12" s="7" customFormat="1" ht="28">
       <c r="A18" s="1">
         <v>17</v>
       </c>
-      <c r="B18" s="9" t="s">
+      <c r="B18" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="8" t="s">
+      <c r="C18" s="7" t="s">
         <v>123</v>
       </c>
       <c r="D18" s="2">
         <v>0</v>
       </c>
-      <c r="E18" s="10">
+      <c r="E18" s="9">
         <v>0.41702882800000002</v>
       </c>
       <c r="F18" s="2">
         <v>0</v>
       </c>
-      <c r="G18" s="10">
+      <c r="G18" s="9">
         <v>0.20851441400000001</v>
       </c>
       <c r="H18" s="2">
         <v>0</v>
       </c>
-      <c r="I18" s="10">
+      <c r="I18" s="9">
         <v>0.625543242</v>
       </c>
       <c r="J18" s="2">
@@ -3015,36 +3012,36 @@
       <c r="K18" s="6" t="s">
         <v>317</v>
       </c>
-      <c r="L18" s="8" t="s">
+      <c r="L18" s="7" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="19" spans="1:12" s="8" customFormat="1" ht="18">
+    <row r="19" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A19" s="1">
         <v>18</v>
       </c>
-      <c r="B19" s="9" t="s">
+      <c r="B19" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="C19" s="8" t="s">
+      <c r="C19" s="7" t="s">
         <v>124</v>
       </c>
       <c r="D19" s="2">
         <v>0.30860670000000001</v>
       </c>
-      <c r="E19" s="10">
+      <c r="E19" s="9">
         <v>0.15430335000000001</v>
       </c>
       <c r="F19" s="2">
         <v>0.46291005000000002</v>
       </c>
-      <c r="G19" s="10">
+      <c r="G19" s="9">
         <v>0.46291005000000002</v>
       </c>
       <c r="H19" s="2">
         <v>0.46291005000000002</v>
       </c>
-      <c r="I19" s="10">
+      <c r="I19" s="9">
         <v>0.46291005000000002</v>
       </c>
       <c r="J19" s="2">
@@ -3053,36 +3050,36 @@
       <c r="K19" s="6" t="s">
         <v>355</v>
       </c>
-      <c r="L19" s="8" t="s">
+      <c r="L19" s="7" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="20" spans="1:12" s="8" customFormat="1" ht="21">
+    <row r="20" spans="1:12" s="7" customFormat="1" ht="21">
       <c r="A20" s="1">
         <v>19</v>
       </c>
-      <c r="B20" s="9" t="s">
+      <c r="B20" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="8" t="s">
+      <c r="C20" s="7" t="s">
         <v>125</v>
       </c>
       <c r="D20" s="2">
         <v>0.603022689</v>
       </c>
-      <c r="E20" s="10">
+      <c r="E20" s="9">
         <v>0.30151134499999999</v>
       </c>
       <c r="F20" s="2">
         <v>0</v>
       </c>
-      <c r="G20" s="10">
+      <c r="G20" s="9">
         <v>0</v>
       </c>
       <c r="H20" s="2">
         <v>0.603022689</v>
       </c>
-      <c r="I20" s="10">
+      <c r="I20" s="9">
         <v>0.30151134499999999</v>
       </c>
       <c r="J20" s="2">
@@ -3091,36 +3088,36 @@
       <c r="K20" s="6" t="s">
         <v>328</v>
       </c>
-      <c r="L20" s="8" t="s">
+      <c r="L20" s="7" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="21" spans="1:12" s="8" customFormat="1" ht="18">
+    <row r="21" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A21" s="1">
         <v>20</v>
       </c>
-      <c r="B21" s="9" t="s">
+      <c r="B21" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="C21" s="8" t="s">
+      <c r="C21" s="7" t="s">
         <v>126</v>
       </c>
       <c r="D21" s="2">
         <v>0</v>
       </c>
-      <c r="E21" s="10">
+      <c r="E21" s="9">
         <v>0.23570226</v>
       </c>
       <c r="F21" s="2">
         <v>0</v>
       </c>
-      <c r="G21" s="10">
+      <c r="G21" s="9">
         <v>0</v>
       </c>
       <c r="H21" s="2">
         <v>0.47140452100000002</v>
       </c>
-      <c r="I21" s="10">
+      <c r="I21" s="9">
         <v>0.47140452100000002</v>
       </c>
       <c r="J21" s="2">
@@ -3129,36 +3126,36 @@
       <c r="K21" s="6" t="s">
         <v>356</v>
       </c>
-      <c r="L21" s="8" t="s">
+      <c r="L21" s="7" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="22" spans="1:12" s="8" customFormat="1" ht="18">
+    <row r="22" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A22" s="1">
         <v>21</v>
       </c>
-      <c r="B22" s="9" t="s">
+      <c r="B22" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="8" t="s">
+      <c r="C22" s="7" t="s">
         <v>127</v>
       </c>
       <c r="D22" s="2">
         <v>0</v>
       </c>
-      <c r="E22" s="10">
+      <c r="E22" s="9">
         <v>0</v>
       </c>
       <c r="F22" s="2">
         <v>0</v>
       </c>
-      <c r="G22" s="10">
+      <c r="G22" s="9">
         <v>0</v>
       </c>
       <c r="H22" s="2">
         <v>0.688247202</v>
       </c>
-      <c r="I22" s="10">
+      <c r="I22" s="9">
         <v>0.22941573400000001</v>
       </c>
       <c r="J22" s="2">
@@ -3167,36 +3164,36 @@
       <c r="K22" s="6" t="s">
         <v>318</v>
       </c>
-      <c r="L22" s="8" t="s">
+      <c r="L22" s="7" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="23" spans="1:12" s="8" customFormat="1" ht="28">
+    <row r="23" spans="1:12" s="7" customFormat="1" ht="28">
       <c r="A23" s="1">
         <v>22</v>
       </c>
-      <c r="B23" s="9" t="s">
+      <c r="B23" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="8" t="s">
+      <c r="C23" s="7" t="s">
         <v>128</v>
       </c>
       <c r="D23" s="2">
         <v>0</v>
       </c>
-      <c r="E23" s="10">
+      <c r="E23" s="9">
         <v>0.48507125000000001</v>
       </c>
       <c r="F23" s="2">
         <v>0</v>
       </c>
-      <c r="G23" s="10">
+      <c r="G23" s="9">
         <v>0</v>
       </c>
       <c r="H23" s="2">
         <v>0</v>
       </c>
-      <c r="I23" s="10">
+      <c r="I23" s="9">
         <v>0.72760687499999999</v>
       </c>
       <c r="J23" s="2">
@@ -3205,36 +3202,36 @@
       <c r="K23" s="6" t="s">
         <v>319</v>
       </c>
-      <c r="L23" s="8" t="s">
+      <c r="L23" s="7" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="24" spans="1:12" s="8" customFormat="1" ht="18">
+    <row r="24" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A24" s="1">
         <v>23</v>
       </c>
-      <c r="B24" s="9" t="s">
+      <c r="B24" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="C24" s="8" t="s">
+      <c r="C24" s="7" t="s">
         <v>129</v>
       </c>
       <c r="D24" s="2">
         <v>0</v>
       </c>
-      <c r="E24" s="10">
+      <c r="E24" s="9">
         <v>0.51639777899999995</v>
       </c>
       <c r="F24" s="2">
         <v>0</v>
       </c>
-      <c r="G24" s="10">
+      <c r="G24" s="9">
         <v>0.25819889000000001</v>
       </c>
       <c r="H24" s="2">
         <v>0</v>
       </c>
-      <c r="I24" s="10">
+      <c r="I24" s="9">
         <v>0.77459666900000002</v>
       </c>
       <c r="J24" s="2">
@@ -3243,36 +3240,36 @@
       <c r="K24" s="6" t="s">
         <v>320</v>
       </c>
-      <c r="L24" s="8" t="s">
+      <c r="L24" s="7" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="25" spans="1:12" s="8" customFormat="1" ht="18">
+    <row r="25" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A25" s="1">
         <v>24</v>
       </c>
-      <c r="B25" s="9" t="s">
+      <c r="B25" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="8" t="s">
+      <c r="C25" s="7" t="s">
         <v>130</v>
       </c>
       <c r="D25" s="2">
         <v>0</v>
       </c>
-      <c r="E25" s="10">
+      <c r="E25" s="9">
         <v>0</v>
       </c>
       <c r="F25" s="2">
         <v>0</v>
       </c>
-      <c r="G25" s="10">
+      <c r="G25" s="9">
         <v>0</v>
       </c>
       <c r="H25" s="2">
         <v>0.57735026899999997</v>
       </c>
-      <c r="I25" s="10">
+      <c r="I25" s="9">
         <v>0.57735026899999997</v>
       </c>
       <c r="J25" s="2">
@@ -3281,36 +3278,36 @@
       <c r="K25" s="6" t="s">
         <v>321</v>
       </c>
-      <c r="L25" s="8" t="s">
+      <c r="L25" s="7" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="26" spans="1:12" s="8" customFormat="1" ht="18">
+    <row r="26" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A26" s="1">
         <v>25</v>
       </c>
-      <c r="B26" s="9" t="s">
+      <c r="B26" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="C26" s="8" t="s">
+      <c r="C26" s="7" t="s">
         <v>131</v>
       </c>
       <c r="D26" s="2">
         <v>0</v>
       </c>
-      <c r="E26" s="10">
+      <c r="E26" s="9">
         <v>0.46852128599999998</v>
       </c>
       <c r="F26" s="2">
         <v>0</v>
       </c>
-      <c r="G26" s="10">
+      <c r="G26" s="9">
         <v>0</v>
       </c>
       <c r="H26" s="2">
         <v>0</v>
       </c>
-      <c r="I26" s="10">
+      <c r="I26" s="9">
         <v>0.62469504799999998</v>
       </c>
       <c r="J26" s="2">
@@ -3319,36 +3316,36 @@
       <c r="K26" s="6" t="s">
         <v>357</v>
       </c>
-      <c r="L26" s="8" t="s">
+      <c r="L26" s="7" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="27" spans="1:12" s="8" customFormat="1" ht="18">
+    <row r="27" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A27" s="1">
         <v>26</v>
       </c>
-      <c r="B27" s="9" t="s">
+      <c r="B27" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="8" t="s">
+      <c r="C27" s="7" t="s">
         <v>132</v>
       </c>
       <c r="D27" s="2">
         <v>0.36927447299999999</v>
       </c>
-      <c r="E27" s="10">
+      <c r="E27" s="9">
         <v>0.36927447299999999</v>
       </c>
       <c r="F27" s="2">
         <v>0.49236596399999999</v>
       </c>
-      <c r="G27" s="10">
+      <c r="G27" s="9">
         <v>0.49236596399999999</v>
       </c>
       <c r="H27" s="2">
         <v>0</v>
       </c>
-      <c r="I27" s="10">
+      <c r="I27" s="9">
         <v>0.49236596399999999</v>
       </c>
       <c r="J27" s="2">
@@ -3357,36 +3354,36 @@
       <c r="K27" s="6" t="s">
         <v>389</v>
       </c>
-      <c r="L27" s="8" t="s">
+      <c r="L27" s="7" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="28" spans="1:12" s="8" customFormat="1" ht="18">
+    <row r="28" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A28" s="1">
         <v>27</v>
       </c>
-      <c r="B28" s="9" t="s">
+      <c r="B28" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="8" t="s">
+      <c r="C28" s="7" t="s">
         <v>133</v>
       </c>
       <c r="D28" s="2">
         <v>0</v>
       </c>
-      <c r="E28" s="10">
+      <c r="E28" s="9">
         <v>0</v>
       </c>
       <c r="F28" s="2">
         <v>0</v>
       </c>
-      <c r="G28" s="10">
+      <c r="G28" s="9">
         <v>0</v>
       </c>
       <c r="H28" s="2">
         <v>0.58834840499999996</v>
       </c>
-      <c r="I28" s="10">
+      <c r="I28" s="9">
         <v>0.196116135</v>
       </c>
       <c r="J28" s="2">
@@ -3395,36 +3392,36 @@
       <c r="K28" s="6" t="s">
         <v>322</v>
       </c>
-      <c r="L28" s="8" t="s">
+      <c r="L28" s="7" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="29" spans="1:12" s="8" customFormat="1" ht="18">
+    <row r="29" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A29" s="1">
         <v>28</v>
       </c>
-      <c r="B29" s="9" t="s">
+      <c r="B29" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="8" t="s">
+      <c r="C29" s="7" t="s">
         <v>134</v>
       </c>
       <c r="D29" s="2">
         <v>0</v>
       </c>
-      <c r="E29" s="10">
+      <c r="E29" s="9">
         <v>0.70710678118654746</v>
       </c>
       <c r="F29" s="2">
         <v>0</v>
       </c>
-      <c r="G29" s="10">
+      <c r="G29" s="9">
         <v>0</v>
       </c>
       <c r="H29" s="2">
         <v>0</v>
       </c>
-      <c r="I29" s="10">
+      <c r="I29" s="9">
         <v>0.70710678118654746</v>
       </c>
       <c r="J29" s="2">
@@ -3433,36 +3430,36 @@
       <c r="K29" s="6" t="s">
         <v>372</v>
       </c>
-      <c r="L29" s="8" t="s">
+      <c r="L29" s="7" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="30" spans="1:12" s="8" customFormat="1" ht="18">
+    <row r="30" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A30" s="1">
         <v>29</v>
       </c>
-      <c r="B30" s="9" t="s">
+      <c r="B30" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="8" t="s">
+      <c r="C30" s="7" t="s">
         <v>135</v>
       </c>
       <c r="D30" s="2">
         <v>0</v>
       </c>
-      <c r="E30" s="10">
+      <c r="E30" s="9">
         <v>0.55470019599999998</v>
       </c>
       <c r="F30" s="2">
         <v>0</v>
       </c>
-      <c r="G30" s="10">
+      <c r="G30" s="9">
         <v>0</v>
       </c>
       <c r="H30" s="2">
         <v>0.27735009799999999</v>
       </c>
-      <c r="I30" s="10">
+      <c r="I30" s="9">
         <v>0.55470019599999998</v>
       </c>
       <c r="J30" s="2">
@@ -3471,36 +3468,36 @@
       <c r="K30" s="6" t="s">
         <v>323</v>
       </c>
-      <c r="L30" s="8" t="s">
+      <c r="L30" s="7" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="31" spans="1:12" s="8" customFormat="1" ht="18">
+    <row r="31" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A31" s="1">
         <v>30</v>
       </c>
-      <c r="B31" s="9" t="s">
+      <c r="B31" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="8" t="s">
+      <c r="C31" s="7" t="s">
         <v>136</v>
       </c>
       <c r="D31" s="2">
         <v>0.52981294300000004</v>
       </c>
-      <c r="E31" s="10">
+      <c r="E31" s="9">
         <v>0.52981294300000004</v>
       </c>
       <c r="F31" s="2">
         <v>0</v>
       </c>
-      <c r="G31" s="10">
+      <c r="G31" s="9">
         <v>0</v>
       </c>
       <c r="H31" s="2">
         <v>0.52981294300000004</v>
       </c>
-      <c r="I31" s="10">
+      <c r="I31" s="9">
         <v>0.39735970700000001</v>
       </c>
       <c r="J31" s="2">
@@ -3509,36 +3506,36 @@
       <c r="K31" s="6" t="s">
         <v>324</v>
       </c>
-      <c r="L31" s="8" t="s">
+      <c r="L31" s="7" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="32" spans="1:12" s="8" customFormat="1" ht="18">
+    <row r="32" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A32" s="1">
         <v>31</v>
       </c>
-      <c r="B32" s="9" t="s">
+      <c r="B32" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="C32" s="8" t="s">
+      <c r="C32" s="7" t="s">
         <v>137</v>
       </c>
       <c r="D32" s="2">
         <v>0</v>
       </c>
-      <c r="E32" s="10">
+      <c r="E32" s="9">
         <v>0</v>
       </c>
       <c r="F32" s="2">
         <v>0</v>
       </c>
-      <c r="G32" s="10">
+      <c r="G32" s="9">
         <v>0</v>
       </c>
       <c r="H32" s="2">
         <v>0.688247202</v>
       </c>
-      <c r="I32" s="10">
+      <c r="I32" s="9">
         <v>0.22941573400000001</v>
       </c>
       <c r="J32" s="2">
@@ -3547,36 +3544,36 @@
       <c r="K32" s="6" t="s">
         <v>329</v>
       </c>
-      <c r="L32" s="8" t="s">
+      <c r="L32" s="7" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="33" spans="1:12" s="8" customFormat="1" ht="18">
+    <row r="33" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A33" s="1">
         <v>32</v>
       </c>
-      <c r="B33" s="9" t="s">
+      <c r="B33" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="8" t="s">
+      <c r="C33" s="7" t="s">
         <v>138</v>
       </c>
       <c r="D33" s="2">
         <v>0</v>
       </c>
-      <c r="E33" s="10">
+      <c r="E33" s="9">
         <v>0.70710678100000002</v>
       </c>
       <c r="F33" s="2">
         <v>0</v>
       </c>
-      <c r="G33" s="10">
+      <c r="G33" s="9">
         <v>0.35355339099999999</v>
       </c>
       <c r="H33" s="2">
         <v>0.35355339099999999</v>
       </c>
-      <c r="I33" s="10">
+      <c r="I33" s="9">
         <v>0.35355339099999999</v>
       </c>
       <c r="J33" s="2">
@@ -3585,36 +3582,36 @@
       <c r="K33" s="6" t="s">
         <v>358</v>
       </c>
-      <c r="L33" s="8" t="s">
+      <c r="L33" s="7" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="34" spans="1:12" s="8" customFormat="1" ht="18">
+    <row r="34" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A34" s="1">
         <v>33</v>
       </c>
-      <c r="B34" s="9" t="s">
+      <c r="B34" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="C34" s="8" t="s">
+      <c r="C34" s="7" t="s">
         <v>139</v>
       </c>
       <c r="D34" s="2">
         <v>0.55470019599999998</v>
       </c>
-      <c r="E34" s="10">
+      <c r="E34" s="9">
         <v>0</v>
       </c>
       <c r="F34" s="2">
         <v>0</v>
       </c>
-      <c r="G34" s="10">
+      <c r="G34" s="9">
         <v>0</v>
       </c>
       <c r="H34" s="2">
         <v>0.55470019599999998</v>
       </c>
-      <c r="I34" s="10">
+      <c r="I34" s="9">
         <v>0.27735009799999999</v>
       </c>
       <c r="J34" s="2">
@@ -3623,36 +3620,36 @@
       <c r="K34" s="6" t="s">
         <v>330</v>
       </c>
-      <c r="L34" s="8" t="s">
+      <c r="L34" s="7" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="35" spans="1:12" s="8" customFormat="1" ht="18">
+    <row r="35" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A35" s="1">
         <v>34</v>
       </c>
-      <c r="B35" s="9" t="s">
+      <c r="B35" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="C35" s="8" t="s">
+      <c r="C35" s="7" t="s">
         <v>140</v>
       </c>
       <c r="D35" s="2">
         <v>0.53452248400000002</v>
       </c>
-      <c r="E35" s="10">
+      <c r="E35" s="9">
         <v>0.53452248400000002</v>
       </c>
       <c r="F35" s="2">
         <v>0</v>
       </c>
-      <c r="G35" s="10">
+      <c r="G35" s="9">
         <v>0</v>
       </c>
       <c r="H35" s="2">
         <v>0.26726124200000001</v>
       </c>
-      <c r="I35" s="10">
+      <c r="I35" s="9">
         <v>0.53452248400000002</v>
       </c>
       <c r="J35" s="2">
@@ -3661,36 +3658,36 @@
       <c r="K35" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="L35" s="8" t="s">
+      <c r="L35" s="7" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="36" spans="1:12" s="8" customFormat="1" ht="18">
+    <row r="36" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A36" s="1">
         <v>35</v>
       </c>
-      <c r="B36" s="9" t="s">
+      <c r="B36" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="C36" s="8" t="s">
+      <c r="C36" s="7" t="s">
         <v>141</v>
       </c>
       <c r="D36" s="2">
         <v>0</v>
       </c>
-      <c r="E36" s="10">
+      <c r="E36" s="9">
         <v>0</v>
       </c>
       <c r="F36" s="2">
         <v>0</v>
       </c>
-      <c r="G36" s="10">
+      <c r="G36" s="9">
         <v>0</v>
       </c>
       <c r="H36" s="2">
         <v>0.80178372600000003</v>
       </c>
-      <c r="I36" s="10">
+      <c r="I36" s="9">
         <v>0.26726124200000001</v>
       </c>
       <c r="J36" s="2">
@@ -3699,36 +3696,36 @@
       <c r="K36" s="6" t="s">
         <v>359</v>
       </c>
-      <c r="L36" s="8" t="s">
+      <c r="L36" s="7" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="37" spans="1:12" s="8" customFormat="1" ht="18">
+    <row r="37" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A37" s="1">
         <v>36</v>
       </c>
-      <c r="B37" s="9" t="s">
+      <c r="B37" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="C37" s="8" t="s">
+      <c r="C37" s="7" t="s">
         <v>142</v>
       </c>
       <c r="D37" s="2">
         <v>0.21320071600000001</v>
       </c>
-      <c r="E37" s="10">
+      <c r="E37" s="9">
         <v>0.426401433</v>
       </c>
       <c r="F37" s="2">
         <v>0</v>
       </c>
-      <c r="G37" s="10">
+      <c r="G37" s="9">
         <v>0</v>
       </c>
       <c r="H37" s="2">
         <v>0.63960214900000001</v>
       </c>
-      <c r="I37" s="10">
+      <c r="I37" s="9">
         <v>0.426401433</v>
       </c>
       <c r="J37" s="2">
@@ -3737,36 +3734,36 @@
       <c r="K37" s="6" t="s">
         <v>332</v>
       </c>
-      <c r="L37" s="8" t="s">
+      <c r="L37" s="7" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="38" spans="1:12" s="8" customFormat="1" ht="18">
+    <row r="38" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A38" s="1">
         <v>37</v>
       </c>
-      <c r="B38" s="9" t="s">
+      <c r="B38" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="C38" s="8" t="s">
+      <c r="C38" s="7" t="s">
         <v>143</v>
       </c>
       <c r="D38" s="2">
         <v>0</v>
       </c>
-      <c r="E38" s="10">
+      <c r="E38" s="9">
         <v>0.66666666699999999</v>
       </c>
       <c r="F38" s="2">
         <v>0</v>
       </c>
-      <c r="G38" s="10">
+      <c r="G38" s="9">
         <v>0.33333333300000001</v>
       </c>
       <c r="H38" s="2">
         <v>0</v>
       </c>
-      <c r="I38" s="10">
+      <c r="I38" s="9">
         <v>0.66666666699999999</v>
       </c>
       <c r="J38" s="2">
@@ -3775,36 +3772,36 @@
       <c r="K38" s="6" t="s">
         <v>333</v>
       </c>
-      <c r="L38" s="8" t="s">
+      <c r="L38" s="7" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="39" spans="1:12" s="8" customFormat="1" ht="18">
+    <row r="39" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A39" s="1">
         <v>38</v>
       </c>
-      <c r="B39" s="9" t="s">
+      <c r="B39" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="C39" s="8" t="s">
+      <c r="C39" s="7" t="s">
         <v>144</v>
       </c>
       <c r="D39" s="2">
         <v>0</v>
       </c>
-      <c r="E39" s="10">
+      <c r="E39" s="9">
         <v>0.28867513500000003</v>
       </c>
       <c r="F39" s="2">
         <v>0</v>
       </c>
-      <c r="G39" s="10">
+      <c r="G39" s="9">
         <v>0.28867513500000003</v>
       </c>
       <c r="H39" s="2">
         <v>0.28867513500000003</v>
       </c>
-      <c r="I39" s="10">
+      <c r="I39" s="9">
         <v>0.86602540400000005</v>
       </c>
       <c r="J39" s="2">
@@ -3813,36 +3810,36 @@
       <c r="K39" s="6" t="s">
         <v>334</v>
       </c>
-      <c r="L39" s="8" t="s">
+      <c r="L39" s="7" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="40" spans="1:12" s="8" customFormat="1" ht="18">
+    <row r="40" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A40" s="1">
         <v>39</v>
       </c>
-      <c r="B40" s="9" t="s">
+      <c r="B40" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="C40" s="8" t="s">
+      <c r="C40" s="7" t="s">
         <v>145</v>
       </c>
       <c r="D40" s="2">
         <v>0</v>
       </c>
-      <c r="E40" s="10">
+      <c r="E40" s="9">
         <v>0</v>
       </c>
       <c r="F40" s="2">
         <v>0</v>
       </c>
-      <c r="G40" s="10">
+      <c r="G40" s="9">
         <v>0</v>
       </c>
       <c r="H40" s="2">
         <v>0.57735026899999997</v>
       </c>
-      <c r="I40" s="10">
+      <c r="I40" s="9">
         <v>0.57735026899999997</v>
       </c>
       <c r="J40" s="2">
@@ -3851,36 +3848,36 @@
       <c r="K40" s="6" t="s">
         <v>335</v>
       </c>
-      <c r="L40" s="8" t="s">
+      <c r="L40" s="7" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="41" spans="1:12" s="8" customFormat="1" ht="24">
+    <row r="41" spans="1:12" s="7" customFormat="1" ht="24">
       <c r="A41" s="1">
         <v>40</v>
       </c>
-      <c r="B41" s="9" t="s">
+      <c r="B41" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="C41" s="8" t="s">
+      <c r="C41" s="7" t="s">
         <v>146</v>
       </c>
       <c r="D41" s="2">
         <v>0</v>
       </c>
-      <c r="E41" s="10">
+      <c r="E41" s="9">
         <v>0</v>
       </c>
       <c r="F41" s="2">
         <v>0</v>
       </c>
-      <c r="G41" s="10">
+      <c r="G41" s="9">
         <v>0</v>
       </c>
       <c r="H41" s="2">
         <v>0.80178372600000003</v>
       </c>
-      <c r="I41" s="10">
+      <c r="I41" s="9">
         <v>0.26726124200000001</v>
       </c>
       <c r="J41" s="2">
@@ -3889,36 +3886,36 @@
       <c r="K41" s="6" t="s">
         <v>360</v>
       </c>
-      <c r="L41" s="8" t="s">
+      <c r="L41" s="7" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="42" spans="1:12" s="8" customFormat="1" ht="18">
+    <row r="42" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A42" s="1">
         <v>41</v>
       </c>
-      <c r="B42" s="9" t="s">
+      <c r="B42" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="C42" s="8" t="s">
+      <c r="C42" s="7" t="s">
         <v>147</v>
       </c>
       <c r="D42" s="2">
         <v>0.23570226</v>
       </c>
-      <c r="E42" s="10">
+      <c r="E42" s="9">
         <v>0.70710678100000002</v>
       </c>
       <c r="F42" s="2">
         <v>0.23570226</v>
       </c>
-      <c r="G42" s="10">
+      <c r="G42" s="9">
         <v>0.23570226</v>
       </c>
       <c r="H42" s="2">
         <v>0.23570226</v>
       </c>
-      <c r="I42" s="10">
+      <c r="I42" s="9">
         <v>0.47140452100000002</v>
       </c>
       <c r="J42" s="2">
@@ -3927,36 +3924,36 @@
       <c r="K42" s="6" t="s">
         <v>336</v>
       </c>
-      <c r="L42" s="8" t="s">
+      <c r="L42" s="7" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="43" spans="1:12" s="8" customFormat="1" ht="18">
+    <row r="43" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A43" s="1">
         <v>42</v>
       </c>
-      <c r="B43" s="9" t="s">
+      <c r="B43" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="C43" s="8" t="s">
+      <c r="C43" s="7" t="s">
         <v>148</v>
       </c>
       <c r="D43" s="2">
         <v>0.182574186</v>
       </c>
-      <c r="E43" s="10">
+      <c r="E43" s="9">
         <v>0</v>
       </c>
       <c r="F43" s="2">
         <v>0</v>
       </c>
-      <c r="G43" s="10">
+      <c r="G43" s="9">
         <v>0</v>
       </c>
       <c r="H43" s="2">
         <v>0.54772255800000003</v>
       </c>
-      <c r="I43" s="10">
+      <c r="I43" s="9">
         <v>0.73029674300000003</v>
       </c>
       <c r="J43" s="2">
@@ -3965,36 +3962,36 @@
       <c r="K43" s="6" t="s">
         <v>337</v>
       </c>
-      <c r="L43" s="8" t="s">
+      <c r="L43" s="7" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="44" spans="1:12" s="8" customFormat="1" ht="18">
+    <row r="44" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A44" s="1">
         <v>43</v>
       </c>
-      <c r="B44" s="9" t="s">
+      <c r="B44" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="C44" s="8" t="s">
+      <c r="C44" s="7" t="s">
         <v>149</v>
       </c>
       <c r="D44" s="2">
         <v>0.57735026899999997</v>
       </c>
-      <c r="E44" s="10">
+      <c r="E44" s="9">
         <v>0</v>
       </c>
       <c r="F44" s="2">
         <v>0</v>
       </c>
-      <c r="G44" s="10">
+      <c r="G44" s="9">
         <v>0</v>
       </c>
       <c r="H44" s="2">
         <v>0.57735026899999997</v>
       </c>
-      <c r="I44" s="10">
+      <c r="I44" s="9">
         <v>0</v>
       </c>
       <c r="J44" s="2">
@@ -4003,36 +4000,36 @@
       <c r="K44" s="6" t="s">
         <v>338</v>
       </c>
-      <c r="L44" s="8" t="s">
+      <c r="L44" s="7" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="45" spans="1:12" s="8" customFormat="1" ht="18">
+    <row r="45" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A45" s="1">
         <v>44</v>
       </c>
-      <c r="B45" s="9" t="s">
+      <c r="B45" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="C45" s="8" t="s">
+      <c r="C45" s="7" t="s">
         <v>150</v>
       </c>
       <c r="D45" s="2">
         <v>0.89442719100000001</v>
       </c>
-      <c r="E45" s="10">
+      <c r="E45" s="9">
         <v>0.44721359500000002</v>
       </c>
       <c r="F45" s="2">
         <v>0</v>
       </c>
-      <c r="G45" s="10">
+      <c r="G45" s="9">
         <v>0</v>
       </c>
       <c r="H45" s="2">
         <v>0</v>
       </c>
-      <c r="I45" s="10">
+      <c r="I45" s="9">
         <v>0</v>
       </c>
       <c r="J45" s="2">
@@ -4041,36 +4038,36 @@
       <c r="K45" s="6" t="s">
         <v>339</v>
       </c>
-      <c r="L45" s="8" t="s">
+      <c r="L45" s="7" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="46" spans="1:12" s="8" customFormat="1" ht="18">
+    <row r="46" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A46" s="1">
         <v>45</v>
       </c>
-      <c r="B46" s="9" t="s">
+      <c r="B46" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="C46" s="8" t="s">
+      <c r="C46" s="7" t="s">
         <v>151</v>
       </c>
       <c r="D46" s="2">
         <v>0</v>
       </c>
-      <c r="E46" s="10">
+      <c r="E46" s="9">
         <v>0</v>
       </c>
       <c r="F46" s="2">
         <v>0</v>
       </c>
-      <c r="G46" s="10">
+      <c r="G46" s="9">
         <v>0</v>
       </c>
       <c r="H46" s="2">
         <v>0.70710678100000002</v>
       </c>
-      <c r="I46" s="10">
+      <c r="I46" s="9">
         <v>0.70710678100000002</v>
       </c>
       <c r="J46" s="2">
@@ -4079,36 +4076,36 @@
       <c r="K46" s="6" t="s">
         <v>340</v>
       </c>
-      <c r="L46" s="8" t="s">
+      <c r="L46" s="7" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="47" spans="1:12" s="8" customFormat="1" ht="18">
+    <row r="47" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A47" s="1">
         <v>46</v>
       </c>
-      <c r="B47" s="9" t="s">
+      <c r="B47" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="C47" s="8" t="s">
+      <c r="C47" s="7" t="s">
         <v>152</v>
       </c>
       <c r="D47" s="2">
         <v>0.25819889000000001</v>
       </c>
-      <c r="E47" s="10">
+      <c r="E47" s="9">
         <v>0.51639777899999995</v>
       </c>
       <c r="F47" s="2">
         <v>0.25819889000000001</v>
       </c>
-      <c r="G47" s="10">
+      <c r="G47" s="9">
         <v>0.25819889000000001</v>
       </c>
       <c r="H47" s="2">
         <v>0.51639777899999995</v>
       </c>
-      <c r="I47" s="10">
+      <c r="I47" s="9">
         <v>0.51639777899999995</v>
       </c>
       <c r="J47" s="2">
@@ -4117,36 +4114,36 @@
       <c r="K47" s="6" t="s">
         <v>361</v>
       </c>
-      <c r="L47" s="8" t="s">
+      <c r="L47" s="7" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="48" spans="1:12" s="8" customFormat="1" ht="18">
+    <row r="48" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A48" s="1">
         <v>47</v>
       </c>
-      <c r="B48" s="9" t="s">
+      <c r="B48" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="C48" s="8" t="s">
+      <c r="C48" s="7" t="s">
         <v>153</v>
       </c>
       <c r="D48" s="2">
         <v>0.25</v>
       </c>
-      <c r="E48" s="10">
+      <c r="E48" s="9">
         <v>0.25</v>
       </c>
       <c r="F48" s="2">
         <v>0</v>
       </c>
-      <c r="G48" s="10">
+      <c r="G48" s="9">
         <v>0</v>
       </c>
       <c r="H48" s="2">
         <v>0.75</v>
       </c>
-      <c r="I48" s="10">
+      <c r="I48" s="9">
         <v>0.25</v>
       </c>
       <c r="J48" s="2">
@@ -4155,36 +4152,36 @@
       <c r="K48" s="6" t="s">
         <v>362</v>
       </c>
-      <c r="L48" s="8" t="s">
+      <c r="L48" s="7" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="49" spans="1:12" s="8" customFormat="1" ht="18">
+    <row r="49" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A49" s="1">
         <v>48</v>
       </c>
-      <c r="B49" s="9" t="s">
+      <c r="B49" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="C49" s="8" t="s">
+      <c r="C49" s="7" t="s">
         <v>154</v>
       </c>
       <c r="D49" s="2">
         <v>0</v>
       </c>
-      <c r="E49" s="10">
+      <c r="E49" s="9">
         <v>0</v>
       </c>
       <c r="F49" s="2">
         <v>0</v>
       </c>
-      <c r="G49" s="10">
+      <c r="G49" s="9">
         <v>0</v>
       </c>
       <c r="H49" s="2">
         <v>0.69631062399999999</v>
       </c>
-      <c r="I49" s="10">
+      <c r="I49" s="9">
         <v>0.69631062399999999</v>
       </c>
       <c r="J49" s="2">
@@ -4193,36 +4190,36 @@
       <c r="K49" s="6" t="s">
         <v>341</v>
       </c>
-      <c r="L49" s="8" t="s">
+      <c r="L49" s="7" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="50" spans="1:12" s="8" customFormat="1" ht="21">
+    <row r="50" spans="1:12" s="7" customFormat="1" ht="21">
       <c r="A50" s="1">
         <v>49</v>
       </c>
-      <c r="B50" s="9" t="s">
+      <c r="B50" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="C50" s="8" t="s">
+      <c r="C50" s="7" t="s">
         <v>155</v>
       </c>
       <c r="D50" s="2">
         <v>0</v>
       </c>
-      <c r="E50" s="10">
+      <c r="E50" s="9">
         <v>0</v>
       </c>
       <c r="F50" s="2">
         <v>0</v>
       </c>
-      <c r="G50" s="10">
+      <c r="G50" s="9">
         <v>0</v>
       </c>
       <c r="H50" s="2">
         <v>0.69631062399999999</v>
       </c>
-      <c r="I50" s="10">
+      <c r="I50" s="9">
         <v>0.69631062399999999</v>
       </c>
       <c r="J50" s="2">
@@ -4231,36 +4228,36 @@
       <c r="K50" s="6" t="s">
         <v>341</v>
       </c>
-      <c r="L50" s="8" t="s">
+      <c r="L50" s="7" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="51" spans="1:12" s="8" customFormat="1" ht="18">
+    <row r="51" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A51" s="1">
         <v>50</v>
       </c>
-      <c r="B51" s="9" t="s">
+      <c r="B51" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="C51" s="8" t="s">
+      <c r="C51" s="7" t="s">
         <v>156</v>
       </c>
       <c r="D51" s="2">
         <v>0.55470019599999998</v>
       </c>
-      <c r="E51" s="10">
+      <c r="E51" s="9">
         <v>0</v>
       </c>
       <c r="F51" s="2">
         <v>0</v>
       </c>
-      <c r="G51" s="10">
+      <c r="G51" s="9">
         <v>0.55470019599999998</v>
       </c>
       <c r="H51" s="2">
         <v>0.55470019599999998</v>
       </c>
-      <c r="I51" s="10">
+      <c r="I51" s="9">
         <v>0</v>
       </c>
       <c r="J51" s="2">
@@ -4269,36 +4266,36 @@
       <c r="K51" s="6" t="s">
         <v>342</v>
       </c>
-      <c r="L51" s="8" t="s">
+      <c r="L51" s="7" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="52" spans="1:12" s="8" customFormat="1" ht="18">
+    <row r="52" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A52" s="1">
         <v>51</v>
       </c>
-      <c r="B52" s="9" t="s">
+      <c r="B52" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="C52" s="8" t="s">
+      <c r="C52" s="7" t="s">
         <v>157</v>
       </c>
       <c r="D52" s="2">
         <v>0</v>
       </c>
-      <c r="E52" s="10">
+      <c r="E52" s="9">
         <v>0</v>
       </c>
       <c r="F52" s="2">
         <v>0</v>
       </c>
-      <c r="G52" s="10">
+      <c r="G52" s="9">
         <v>0</v>
       </c>
       <c r="H52" s="2">
         <v>0.26726124200000001</v>
       </c>
-      <c r="I52" s="10">
+      <c r="I52" s="9">
         <v>0.53452248400000002</v>
       </c>
       <c r="J52" s="2">
@@ -4307,36 +4304,36 @@
       <c r="K52" s="6" t="s">
         <v>343</v>
       </c>
-      <c r="L52" s="8" t="s">
+      <c r="L52" s="7" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="53" spans="1:12" s="8" customFormat="1" ht="18">
+    <row r="53" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A53" s="1">
         <v>52</v>
       </c>
-      <c r="B53" s="9" t="s">
+      <c r="B53" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="C53" s="8" t="s">
+      <c r="C53" s="7" t="s">
         <v>158</v>
       </c>
       <c r="D53" s="2">
         <v>0</v>
       </c>
-      <c r="E53" s="10">
+      <c r="E53" s="9">
         <v>0</v>
       </c>
       <c r="F53" s="2">
         <v>0</v>
       </c>
-      <c r="G53" s="10">
+      <c r="G53" s="9">
         <v>0</v>
       </c>
       <c r="H53" s="2">
         <v>0.514495755</v>
       </c>
-      <c r="I53" s="10">
+      <c r="I53" s="9">
         <v>0.68599434100000001</v>
       </c>
       <c r="J53" s="2">
@@ -4345,74 +4342,74 @@
       <c r="K53" s="6" t="s">
         <v>344</v>
       </c>
-      <c r="L53" s="8" t="s">
+      <c r="L53" s="7" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="54" spans="1:12" s="8" customFormat="1" ht="57">
+    <row r="54" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A54" s="1">
         <v>53</v>
       </c>
-      <c r="B54" s="9" t="s">
+      <c r="B54" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="C54" s="8" t="s">
+      <c r="C54" s="7" t="s">
         <v>159</v>
       </c>
       <c r="D54" s="2">
         <v>0</v>
       </c>
-      <c r="E54" s="10">
+      <c r="E54" s="9">
         <v>0</v>
       </c>
       <c r="F54" s="2">
         <v>0</v>
       </c>
-      <c r="G54" s="10">
+      <c r="G54" s="9">
         <v>0</v>
       </c>
       <c r="H54" s="2">
         <v>0.514495755</v>
       </c>
-      <c r="I54" s="10">
+      <c r="I54" s="9">
         <v>0.68599434100000001</v>
       </c>
       <c r="J54" s="2">
         <v>0.514495755</v>
       </c>
-      <c r="K54" s="7" t="s">
+      <c r="K54" s="6" t="s">
         <v>345</v>
       </c>
-      <c r="L54" s="8" t="s">
+      <c r="L54" s="7" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="55" spans="1:12" s="8" customFormat="1" ht="18">
+    <row r="55" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A55" s="1">
         <v>54</v>
       </c>
-      <c r="B55" s="9" t="s">
+      <c r="B55" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="C55" s="8" t="s">
+      <c r="C55" s="7" t="s">
         <v>160</v>
       </c>
       <c r="D55" s="2">
         <v>0</v>
       </c>
-      <c r="E55" s="10">
+      <c r="E55" s="9">
         <v>0</v>
       </c>
       <c r="F55" s="2">
         <v>0</v>
       </c>
-      <c r="G55" s="10">
+      <c r="G55" s="9">
         <v>0</v>
       </c>
       <c r="H55" s="2">
         <v>0.63960214900000001</v>
       </c>
-      <c r="I55" s="10">
+      <c r="I55" s="9">
         <v>0.426401433</v>
       </c>
       <c r="J55" s="2">
@@ -4421,36 +4418,36 @@
       <c r="K55" s="6" t="s">
         <v>346</v>
       </c>
-      <c r="L55" s="8" t="s">
+      <c r="L55" s="7" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="56" spans="1:12" s="8" customFormat="1" ht="18">
+    <row r="56" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A56" s="1">
         <v>55</v>
       </c>
-      <c r="B56" s="9" t="s">
+      <c r="B56" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="C56" s="8" t="s">
+      <c r="C56" s="7" t="s">
         <v>161</v>
       </c>
       <c r="D56" s="2">
         <v>0</v>
       </c>
-      <c r="E56" s="10">
+      <c r="E56" s="9">
         <v>0</v>
       </c>
       <c r="F56" s="2">
         <v>0</v>
       </c>
-      <c r="G56" s="10">
+      <c r="G56" s="9">
         <v>0</v>
       </c>
       <c r="H56" s="2">
         <v>0.514495755</v>
       </c>
-      <c r="I56" s="10">
+      <c r="I56" s="9">
         <v>0.514495755</v>
       </c>
       <c r="J56" s="2">
@@ -4459,36 +4456,36 @@
       <c r="K56" s="6" t="s">
         <v>373</v>
       </c>
-      <c r="L56" s="8" t="s">
+      <c r="L56" s="7" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="57" spans="1:12" s="8" customFormat="1" ht="18">
+    <row r="57" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A57" s="1">
         <v>56</v>
       </c>
-      <c r="B57" s="9" t="s">
+      <c r="B57" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="C57" s="8" t="s">
+      <c r="C57" s="7" t="s">
         <v>162</v>
       </c>
       <c r="D57" s="2">
         <v>0</v>
       </c>
-      <c r="E57" s="10">
+      <c r="E57" s="9">
         <v>0.23570226</v>
       </c>
       <c r="F57" s="2">
         <v>0</v>
       </c>
-      <c r="G57" s="10">
+      <c r="G57" s="9">
         <v>0</v>
       </c>
       <c r="H57" s="2">
         <v>0.70710678100000002</v>
       </c>
-      <c r="I57" s="10">
+      <c r="I57" s="9">
         <v>0.47140452100000002</v>
       </c>
       <c r="J57" s="2">
@@ -4497,36 +4494,36 @@
       <c r="K57" s="6" t="s">
         <v>347</v>
       </c>
-      <c r="L57" s="8" t="s">
+      <c r="L57" s="7" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="58" spans="1:12" s="8" customFormat="1" ht="18">
+    <row r="58" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A58" s="1">
         <v>57</v>
       </c>
-      <c r="B58" s="9" t="s">
+      <c r="B58" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="C58" s="8" t="s">
+      <c r="C58" s="7" t="s">
         <v>163</v>
       </c>
       <c r="D58" s="2">
         <v>0</v>
       </c>
-      <c r="E58" s="10">
+      <c r="E58" s="9">
         <v>0</v>
       </c>
       <c r="F58" s="2">
         <v>0</v>
       </c>
-      <c r="G58" s="10">
+      <c r="G58" s="9">
         <v>0</v>
       </c>
       <c r="H58" s="2">
         <v>0</v>
       </c>
-      <c r="I58" s="10">
+      <c r="I58" s="9">
         <v>1</v>
       </c>
       <c r="J58" s="2">
@@ -4535,36 +4532,36 @@
       <c r="K58" s="6" t="s">
         <v>348</v>
       </c>
-      <c r="L58" s="8" t="s">
+      <c r="L58" s="7" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="59" spans="1:12" s="8" customFormat="1" ht="18">
+    <row r="59" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A59" s="1">
         <v>58</v>
       </c>
-      <c r="B59" s="9" t="s">
+      <c r="B59" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="C59" s="8" t="s">
+      <c r="C59" s="7" t="s">
         <v>164</v>
       </c>
       <c r="D59" s="2">
         <v>0</v>
       </c>
-      <c r="E59" s="10">
+      <c r="E59" s="9">
         <v>0.35921060399999999</v>
       </c>
       <c r="F59" s="2">
         <v>0</v>
       </c>
-      <c r="G59" s="10">
+      <c r="G59" s="9">
         <v>0</v>
       </c>
       <c r="H59" s="2">
         <v>0.53881590599999996</v>
       </c>
-      <c r="I59" s="10">
+      <c r="I59" s="9">
         <v>0.53881590599999996</v>
       </c>
       <c r="J59" s="2">
@@ -4573,36 +4570,36 @@
       <c r="K59" s="6" t="s">
         <v>363</v>
       </c>
-      <c r="L59" s="8" t="s">
+      <c r="L59" s="7" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="60" spans="1:12" s="8" customFormat="1" ht="18">
+    <row r="60" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A60" s="1">
         <v>59</v>
       </c>
-      <c r="B60" s="9" t="s">
+      <c r="B60" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="C60" s="8" t="s">
+      <c r="C60" s="7" t="s">
         <v>165</v>
       </c>
       <c r="D60" s="2">
         <v>0.188982237</v>
       </c>
-      <c r="E60" s="10">
+      <c r="E60" s="9">
         <v>0.56694670999999996</v>
       </c>
       <c r="F60" s="2">
         <v>0</v>
       </c>
-      <c r="G60" s="10">
+      <c r="G60" s="9">
         <v>0</v>
       </c>
       <c r="H60" s="2">
         <v>0.56694670999999996</v>
       </c>
-      <c r="I60" s="10">
+      <c r="I60" s="9">
         <v>0.56694670999999996</v>
       </c>
       <c r="J60" s="2">
@@ -4611,36 +4608,36 @@
       <c r="K60" s="6" t="s">
         <v>349</v>
       </c>
-      <c r="L60" s="8" t="s">
+      <c r="L60" s="7" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="61" spans="1:12" s="8" customFormat="1" ht="18">
+    <row r="61" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A61" s="1">
         <v>60</v>
       </c>
-      <c r="B61" s="9" t="s">
+      <c r="B61" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="C61" s="8" t="s">
+      <c r="C61" s="7" t="s">
         <v>166</v>
       </c>
       <c r="D61" s="2">
         <v>0.39223226999999999</v>
       </c>
-      <c r="E61" s="10">
+      <c r="E61" s="9">
         <v>0.39223226999999999</v>
       </c>
       <c r="F61" s="2">
         <v>0.39223226999999999</v>
       </c>
-      <c r="G61" s="10">
+      <c r="G61" s="9">
         <v>0.58834840499999996</v>
       </c>
       <c r="H61" s="2">
         <v>0</v>
       </c>
-      <c r="I61" s="10">
+      <c r="I61" s="9">
         <v>0.39223226999999999</v>
       </c>
       <c r="J61" s="2">
@@ -4649,36 +4646,36 @@
       <c r="K61" s="6" t="s">
         <v>350</v>
       </c>
-      <c r="L61" s="8" t="s">
+      <c r="L61" s="7" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="62" spans="1:12" s="8" customFormat="1" ht="18">
+    <row r="62" spans="1:12" s="7" customFormat="1" ht="18">
       <c r="A62" s="1">
         <v>61</v>
       </c>
-      <c r="B62" s="9" t="s">
+      <c r="B62" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="C62" s="8" t="s">
+      <c r="C62" s="7" t="s">
         <v>167</v>
       </c>
       <c r="D62" s="2">
         <v>0.53452248400000002</v>
       </c>
-      <c r="E62" s="10">
+      <c r="E62" s="9">
         <v>0.53452248400000002</v>
       </c>
       <c r="F62" s="2">
         <v>0.26726124200000001</v>
       </c>
-      <c r="G62" s="10">
+      <c r="G62" s="9">
         <v>0.53452248400000002</v>
       </c>
       <c r="H62" s="2">
         <v>0</v>
       </c>
-      <c r="I62" s="10">
+      <c r="I62" s="9">
         <v>0.26726124200000001</v>
       </c>
       <c r="J62" s="2">
@@ -4687,7 +4684,7 @@
       <c r="K62" s="6" t="s">
         <v>351</v>
       </c>
-      <c r="L62" s="8" t="s">
+      <c r="L62" s="7" t="s">
         <v>266</v>
       </c>
     </row>

--- a/library.xlsx
+++ b/library.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xxc/Desktop/xxc/拓殖大学/研究室/評価実験/video-recommend-system/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E1FBEB0-D4AB-A849-96E3-701B2317A722}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E9FAA5C-89FA-004B-89D6-8A2C777E66B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{F40E9203-8E2D-9949-9A4C-F506F7C93633}"/>
   </bookViews>

--- a/library.xlsx
+++ b/library.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E9FAA5C-89FA-004B-89D6-8A2C777E66B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{F40E9203-8E2D-9949-9A4C-F506F7C93633}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15920" xr2:uid="{F40E9203-8E2D-9949-9A4C-F506F7C93633}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1957,7 +1957,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1978,15 +1978,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2332,7 +2323,7 @@
     <col min="4" max="10" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="1" spans="1:12" ht="18">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2370,32 +2361,32 @@
         <v>207</v>
       </c>
     </row>
-    <row r="2" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="2" spans="1:12" ht="18">
       <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" t="s">
         <v>108</v>
       </c>
       <c r="D2" s="2">
         <v>0</v>
       </c>
-      <c r="E2" s="9">
+      <c r="E2" s="3">
         <v>0</v>
       </c>
       <c r="F2" s="2">
         <v>0</v>
       </c>
-      <c r="G2" s="9">
+      <c r="G2" s="3">
         <v>0</v>
       </c>
       <c r="H2" s="2">
         <v>0.31622776600000002</v>
       </c>
-      <c r="I2" s="9">
+      <c r="I2" s="3">
         <v>0</v>
       </c>
       <c r="J2" s="2">
@@ -2404,36 +2395,36 @@
       <c r="K2" s="6" t="s">
         <v>309</v>
       </c>
-      <c r="L2" s="7" t="s">
+      <c r="L2" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="3" spans="1:12" s="7" customFormat="1" ht="21">
+    <row r="3" spans="1:12" ht="21">
       <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" t="s">
         <v>109</v>
       </c>
       <c r="D3" s="2">
         <v>0</v>
       </c>
-      <c r="E3" s="9">
+      <c r="E3" s="3">
         <v>0</v>
       </c>
       <c r="F3" s="2">
         <v>0</v>
       </c>
-      <c r="G3" s="9">
+      <c r="G3" s="3">
         <v>0</v>
       </c>
       <c r="H3" s="2">
         <v>0.70710678100000002</v>
       </c>
-      <c r="I3" s="9">
+      <c r="I3" s="3">
         <v>0</v>
       </c>
       <c r="J3" s="2">
@@ -2442,36 +2433,36 @@
       <c r="K3" s="6" t="s">
         <v>325</v>
       </c>
-      <c r="L3" s="7" t="s">
+      <c r="L3" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="4" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="4" spans="1:12" ht="18">
       <c r="A4" s="1">
         <v>3</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="5" t="s">
         <v>307</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" t="s">
         <v>308</v>
       </c>
       <c r="D4" s="2">
         <v>0</v>
       </c>
-      <c r="E4" s="9">
+      <c r="E4" s="3">
         <v>0</v>
       </c>
       <c r="F4" s="2">
         <v>0</v>
       </c>
-      <c r="G4" s="9">
+      <c r="G4" s="3">
         <v>0</v>
       </c>
       <c r="H4" s="2">
         <v>0.816496581</v>
       </c>
-      <c r="I4" s="9">
+      <c r="I4" s="3">
         <v>0.40824829000000001</v>
       </c>
       <c r="J4" s="2">
@@ -2480,36 +2471,36 @@
       <c r="K4" s="6" t="s">
         <v>352</v>
       </c>
-      <c r="L4" s="7" t="s">
+      <c r="L4" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="5" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="5" spans="1:12" ht="18">
       <c r="A5" s="1">
         <v>4</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" t="s">
         <v>110</v>
       </c>
       <c r="D5" s="2">
         <v>0</v>
       </c>
-      <c r="E5" s="9">
+      <c r="E5" s="3">
         <v>0.31622776600000002</v>
       </c>
       <c r="F5" s="2">
         <v>0</v>
       </c>
-      <c r="G5" s="9">
+      <c r="G5" s="3">
         <v>0</v>
       </c>
       <c r="H5" s="2">
         <v>0.31622776600000002</v>
       </c>
-      <c r="I5" s="9">
+      <c r="I5" s="3">
         <v>0.63245553200000004</v>
       </c>
       <c r="J5" s="2">
@@ -2518,36 +2509,36 @@
       <c r="K5" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="L5" s="7" t="s">
+      <c r="L5" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="6" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="6" spans="1:12" ht="18">
       <c r="A6" s="1">
         <v>5</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" t="s">
         <v>111</v>
       </c>
       <c r="D6" s="2">
         <v>0</v>
       </c>
-      <c r="E6" s="9">
+      <c r="E6" s="3">
         <v>0</v>
       </c>
       <c r="F6" s="2">
         <v>0</v>
       </c>
-      <c r="G6" s="9">
+      <c r="G6" s="3">
         <v>0</v>
       </c>
       <c r="H6" s="2">
         <v>0.48507125000000001</v>
       </c>
-      <c r="I6" s="9">
+      <c r="I6" s="3">
         <v>0.48507125000000001</v>
       </c>
       <c r="J6" s="2">
@@ -2556,36 +2547,36 @@
       <c r="K6" s="6" t="s">
         <v>311</v>
       </c>
-      <c r="L6" s="7" t="s">
+      <c r="L6" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="7" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="7" spans="1:12" ht="18">
       <c r="A7" s="1">
         <v>6</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" t="s">
         <v>112</v>
       </c>
       <c r="D7" s="2">
         <v>0</v>
       </c>
-      <c r="E7" s="9">
+      <c r="E7" s="3">
         <v>0</v>
       </c>
       <c r="F7" s="2">
         <v>0</v>
       </c>
-      <c r="G7" s="9">
+      <c r="G7" s="3">
         <v>0</v>
       </c>
       <c r="H7" s="2">
         <v>0</v>
       </c>
-      <c r="I7" s="9">
+      <c r="I7" s="3">
         <v>0.89442719100000001</v>
       </c>
       <c r="J7" s="2">
@@ -2594,36 +2585,36 @@
       <c r="K7" s="6" t="s">
         <v>312</v>
       </c>
-      <c r="L7" s="7" t="s">
+      <c r="L7" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="8" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="8" spans="1:12" ht="18">
       <c r="A8" s="1">
         <v>7</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" t="s">
         <v>113</v>
       </c>
       <c r="D8" s="2">
         <v>0</v>
       </c>
-      <c r="E8" s="9">
+      <c r="E8" s="3">
         <v>0.57735026899999997</v>
       </c>
       <c r="F8" s="2">
         <v>0</v>
       </c>
-      <c r="G8" s="9">
+      <c r="G8" s="3">
         <v>0.57735026899999997</v>
       </c>
       <c r="H8" s="2">
         <v>0.57735026899999997</v>
       </c>
-      <c r="I8" s="9">
+      <c r="I8" s="3">
         <v>0</v>
       </c>
       <c r="J8" s="2">
@@ -2632,36 +2623,36 @@
       <c r="K8" s="6" t="s">
         <v>313</v>
       </c>
-      <c r="L8" s="7" t="s">
+      <c r="L8" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="9" spans="1:12" s="7" customFormat="1" ht="28">
+    <row r="9" spans="1:12" ht="28">
       <c r="A9" s="1">
         <v>8</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" t="s">
         <v>114</v>
       </c>
       <c r="D9" s="2">
         <v>0.86602540400000005</v>
       </c>
-      <c r="E9" s="9">
+      <c r="E9" s="3">
         <v>0.28867513500000003</v>
       </c>
       <c r="F9" s="2">
         <v>0</v>
       </c>
-      <c r="G9" s="9">
+      <c r="G9" s="3">
         <v>0</v>
       </c>
       <c r="H9" s="2">
         <v>0.28867513500000003</v>
       </c>
-      <c r="I9" s="9">
+      <c r="I9" s="3">
         <v>0.28867513500000003</v>
       </c>
       <c r="J9" s="2">
@@ -2670,36 +2661,36 @@
       <c r="K9" s="6" t="s">
         <v>371</v>
       </c>
-      <c r="L9" s="7" t="s">
+      <c r="L9" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="10" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="10" spans="1:12" ht="18">
       <c r="A10" s="1">
         <v>9</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" t="s">
         <v>115</v>
       </c>
       <c r="D10" s="2">
         <v>0</v>
       </c>
-      <c r="E10" s="9">
+      <c r="E10" s="3">
         <v>0.37796447300000002</v>
       </c>
       <c r="F10" s="2">
         <v>0</v>
       </c>
-      <c r="G10" s="9">
+      <c r="G10" s="3">
         <v>0</v>
       </c>
       <c r="H10" s="2">
         <v>0.75592894600000005</v>
       </c>
-      <c r="I10" s="9">
+      <c r="I10" s="3">
         <v>0.37796447300000002</v>
       </c>
       <c r="J10" s="2">
@@ -2708,36 +2699,36 @@
       <c r="K10" s="6" t="s">
         <v>353</v>
       </c>
-      <c r="L10" s="7" t="s">
+      <c r="L10" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="11" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="11" spans="1:12" ht="18">
       <c r="A11" s="1">
         <v>10</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" t="s">
         <v>116</v>
       </c>
       <c r="D11" s="2">
         <v>0</v>
       </c>
-      <c r="E11" s="9">
+      <c r="E11" s="3">
         <v>0.28867513500000003</v>
       </c>
       <c r="F11" s="2">
         <v>0</v>
       </c>
-      <c r="G11" s="9">
+      <c r="G11" s="3">
         <v>0</v>
       </c>
       <c r="H11" s="2">
         <v>0.28867513500000003</v>
       </c>
-      <c r="I11" s="9">
+      <c r="I11" s="3">
         <v>0.86602540400000005</v>
       </c>
       <c r="J11" s="2">
@@ -2746,36 +2737,36 @@
       <c r="K11" s="6" t="s">
         <v>314</v>
       </c>
-      <c r="L11" s="7" t="s">
+      <c r="L11" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="12" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="12" spans="1:12" ht="18">
       <c r="A12" s="1">
         <v>11</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" t="s">
         <v>117</v>
       </c>
       <c r="D12" s="2">
         <v>0</v>
       </c>
-      <c r="E12" s="9">
+      <c r="E12" s="3">
         <v>0</v>
       </c>
       <c r="F12" s="2">
         <v>0</v>
       </c>
-      <c r="G12" s="9">
+      <c r="G12" s="3">
         <v>0</v>
       </c>
       <c r="H12" s="2">
         <v>0.57735026899999997</v>
       </c>
-      <c r="I12" s="9">
+      <c r="I12" s="3">
         <v>0.57735026899999997</v>
       </c>
       <c r="J12" s="2">
@@ -2784,36 +2775,36 @@
       <c r="K12" s="6" t="s">
         <v>326</v>
       </c>
-      <c r="L12" s="7" t="s">
+      <c r="L12" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="13" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="13" spans="1:12" ht="18">
       <c r="A13" s="1">
         <v>12</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" t="s">
         <v>118</v>
       </c>
       <c r="D13" s="2">
         <v>0</v>
       </c>
-      <c r="E13" s="9">
+      <c r="E13" s="3">
         <v>0</v>
       </c>
       <c r="F13" s="2">
         <v>0</v>
       </c>
-      <c r="G13" s="9">
+      <c r="G13" s="3">
         <v>0</v>
       </c>
       <c r="H13" s="2">
         <v>0.26726124200000001</v>
       </c>
-      <c r="I13" s="9">
+      <c r="I13" s="3">
         <v>0.53452248400000002</v>
       </c>
       <c r="J13" s="2">
@@ -2822,36 +2813,36 @@
       <c r="K13" s="6" t="s">
         <v>315</v>
       </c>
-      <c r="L13" s="7" t="s">
+      <c r="L13" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="14" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="14" spans="1:12" ht="18">
       <c r="A14" s="1">
         <v>13</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" t="s">
         <v>119</v>
       </c>
       <c r="D14" s="2">
         <v>0</v>
       </c>
-      <c r="E14" s="9">
+      <c r="E14" s="3">
         <v>0</v>
       </c>
       <c r="F14" s="2">
         <v>0</v>
       </c>
-      <c r="G14" s="9">
+      <c r="G14" s="3">
         <v>0.28867513500000003</v>
       </c>
       <c r="H14" s="2">
         <v>0.28867513500000003</v>
       </c>
-      <c r="I14" s="9">
+      <c r="I14" s="3">
         <v>0.86602540400000005</v>
       </c>
       <c r="J14" s="2">
@@ -2860,36 +2851,36 @@
       <c r="K14" s="6" t="s">
         <v>316</v>
       </c>
-      <c r="L14" s="7" t="s">
+      <c r="L14" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="15" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="15" spans="1:12" ht="18">
       <c r="A15" s="1">
         <v>14</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="B15" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" t="s">
         <v>120</v>
       </c>
       <c r="D15" s="2">
         <v>0</v>
       </c>
-      <c r="E15" s="9">
+      <c r="E15" s="3">
         <v>0</v>
       </c>
       <c r="F15" s="2">
         <v>0</v>
       </c>
-      <c r="G15" s="9">
+      <c r="G15" s="3">
         <v>0</v>
       </c>
       <c r="H15" s="2">
         <v>0</v>
       </c>
-      <c r="I15" s="9">
+      <c r="I15" s="3">
         <v>0.44721359500000002</v>
       </c>
       <c r="J15" s="2">
@@ -2898,36 +2889,36 @@
       <c r="K15" s="6" t="s">
         <v>388</v>
       </c>
-      <c r="L15" s="7" t="s">
+      <c r="L15" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="16" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="16" spans="1:12" ht="18">
       <c r="A16" s="1">
         <v>15</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="B16" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" t="s">
         <v>121</v>
       </c>
       <c r="D16" s="2">
         <v>0</v>
       </c>
-      <c r="E16" s="9">
+      <c r="E16" s="3">
         <v>0.23570226</v>
       </c>
       <c r="F16" s="2">
         <v>0</v>
       </c>
-      <c r="G16" s="9">
+      <c r="G16" s="3">
         <v>0</v>
       </c>
       <c r="H16" s="2">
         <v>0.47140452100000002</v>
       </c>
-      <c r="I16" s="9">
+      <c r="I16" s="3">
         <v>0.47140452100000002</v>
       </c>
       <c r="J16" s="2">
@@ -2936,36 +2927,36 @@
       <c r="K16" s="6" t="s">
         <v>354</v>
       </c>
-      <c r="L16" s="7" t="s">
+      <c r="L16" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="17" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="17" spans="1:12" ht="18">
       <c r="A17" s="1">
         <v>16</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="B17" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C17" t="s">
         <v>122</v>
       </c>
       <c r="D17" s="2">
         <v>0</v>
       </c>
-      <c r="E17" s="9">
+      <c r="E17" s="3">
         <v>0</v>
       </c>
       <c r="F17" s="2">
         <v>0.22941573400000001</v>
       </c>
-      <c r="G17" s="9">
+      <c r="G17" s="3">
         <v>0.688247202</v>
       </c>
       <c r="H17" s="2">
         <v>0.22941573400000001</v>
       </c>
-      <c r="I17" s="9">
+      <c r="I17" s="3">
         <v>0.45883146800000002</v>
       </c>
       <c r="J17" s="2">
@@ -2974,36 +2965,36 @@
       <c r="K17" s="6" t="s">
         <v>327</v>
       </c>
-      <c r="L17" s="7" t="s">
+      <c r="L17" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="18" spans="1:12" s="7" customFormat="1" ht="28">
+    <row r="18" spans="1:12" ht="28">
       <c r="A18" s="1">
         <v>17</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="B18" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C18" t="s">
         <v>123</v>
       </c>
       <c r="D18" s="2">
         <v>0</v>
       </c>
-      <c r="E18" s="9">
+      <c r="E18" s="3">
         <v>0.41702882800000002</v>
       </c>
       <c r="F18" s="2">
         <v>0</v>
       </c>
-      <c r="G18" s="9">
+      <c r="G18" s="3">
         <v>0.20851441400000001</v>
       </c>
       <c r="H18" s="2">
         <v>0</v>
       </c>
-      <c r="I18" s="9">
+      <c r="I18" s="3">
         <v>0.625543242</v>
       </c>
       <c r="J18" s="2">
@@ -3012,36 +3003,36 @@
       <c r="K18" s="6" t="s">
         <v>317</v>
       </c>
-      <c r="L18" s="7" t="s">
+      <c r="L18" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="19" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="19" spans="1:12" ht="18">
       <c r="A19" s="1">
         <v>18</v>
       </c>
-      <c r="B19" s="8" t="s">
+      <c r="B19" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="C19" t="s">
         <v>124</v>
       </c>
       <c r="D19" s="2">
         <v>0.30860670000000001</v>
       </c>
-      <c r="E19" s="9">
+      <c r="E19" s="3">
         <v>0.15430335000000001</v>
       </c>
       <c r="F19" s="2">
         <v>0.46291005000000002</v>
       </c>
-      <c r="G19" s="9">
+      <c r="G19" s="3">
         <v>0.46291005000000002</v>
       </c>
       <c r="H19" s="2">
         <v>0.46291005000000002</v>
       </c>
-      <c r="I19" s="9">
+      <c r="I19" s="3">
         <v>0.46291005000000002</v>
       </c>
       <c r="J19" s="2">
@@ -3050,36 +3041,36 @@
       <c r="K19" s="6" t="s">
         <v>355</v>
       </c>
-      <c r="L19" s="7" t="s">
+      <c r="L19" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="20" spans="1:12" s="7" customFormat="1" ht="21">
+    <row r="20" spans="1:12" ht="21">
       <c r="A20" s="1">
         <v>19</v>
       </c>
-      <c r="B20" s="8" t="s">
+      <c r="B20" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="7" t="s">
+      <c r="C20" t="s">
         <v>125</v>
       </c>
       <c r="D20" s="2">
         <v>0.603022689</v>
       </c>
-      <c r="E20" s="9">
+      <c r="E20" s="3">
         <v>0.30151134499999999</v>
       </c>
       <c r="F20" s="2">
         <v>0</v>
       </c>
-      <c r="G20" s="9">
+      <c r="G20" s="3">
         <v>0</v>
       </c>
       <c r="H20" s="2">
         <v>0.603022689</v>
       </c>
-      <c r="I20" s="9">
+      <c r="I20" s="3">
         <v>0.30151134499999999</v>
       </c>
       <c r="J20" s="2">
@@ -3088,36 +3079,36 @@
       <c r="K20" s="6" t="s">
         <v>328</v>
       </c>
-      <c r="L20" s="7" t="s">
+      <c r="L20" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="21" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="21" spans="1:12" ht="18">
       <c r="A21" s="1">
         <v>20</v>
       </c>
-      <c r="B21" s="8" t="s">
+      <c r="B21" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="C21" s="7" t="s">
+      <c r="C21" t="s">
         <v>126</v>
       </c>
       <c r="D21" s="2">
         <v>0</v>
       </c>
-      <c r="E21" s="9">
+      <c r="E21" s="3">
         <v>0.23570226</v>
       </c>
       <c r="F21" s="2">
         <v>0</v>
       </c>
-      <c r="G21" s="9">
+      <c r="G21" s="3">
         <v>0</v>
       </c>
       <c r="H21" s="2">
         <v>0.47140452100000002</v>
       </c>
-      <c r="I21" s="9">
+      <c r="I21" s="3">
         <v>0.47140452100000002</v>
       </c>
       <c r="J21" s="2">
@@ -3126,36 +3117,36 @@
       <c r="K21" s="6" t="s">
         <v>356</v>
       </c>
-      <c r="L21" s="7" t="s">
+      <c r="L21" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="22" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="22" spans="1:12" ht="18">
       <c r="A22" s="1">
         <v>21</v>
       </c>
-      <c r="B22" s="8" t="s">
+      <c r="B22" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="7" t="s">
+      <c r="C22" t="s">
         <v>127</v>
       </c>
       <c r="D22" s="2">
         <v>0</v>
       </c>
-      <c r="E22" s="9">
+      <c r="E22" s="3">
         <v>0</v>
       </c>
       <c r="F22" s="2">
         <v>0</v>
       </c>
-      <c r="G22" s="9">
+      <c r="G22" s="3">
         <v>0</v>
       </c>
       <c r="H22" s="2">
         <v>0.688247202</v>
       </c>
-      <c r="I22" s="9">
+      <c r="I22" s="3">
         <v>0.22941573400000001</v>
       </c>
       <c r="J22" s="2">
@@ -3164,36 +3155,36 @@
       <c r="K22" s="6" t="s">
         <v>318</v>
       </c>
-      <c r="L22" s="7" t="s">
+      <c r="L22" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="23" spans="1:12" s="7" customFormat="1" ht="28">
+    <row r="23" spans="1:12" ht="28">
       <c r="A23" s="1">
         <v>22</v>
       </c>
-      <c r="B23" s="8" t="s">
+      <c r="B23" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="7" t="s">
+      <c r="C23" t="s">
         <v>128</v>
       </c>
       <c r="D23" s="2">
         <v>0</v>
       </c>
-      <c r="E23" s="9">
+      <c r="E23" s="3">
         <v>0.48507125000000001</v>
       </c>
       <c r="F23" s="2">
         <v>0</v>
       </c>
-      <c r="G23" s="9">
+      <c r="G23" s="3">
         <v>0</v>
       </c>
       <c r="H23" s="2">
         <v>0</v>
       </c>
-      <c r="I23" s="9">
+      <c r="I23" s="3">
         <v>0.72760687499999999</v>
       </c>
       <c r="J23" s="2">
@@ -3202,36 +3193,36 @@
       <c r="K23" s="6" t="s">
         <v>319</v>
       </c>
-      <c r="L23" s="7" t="s">
+      <c r="L23" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="24" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="24" spans="1:12" ht="18">
       <c r="A24" s="1">
         <v>23</v>
       </c>
-      <c r="B24" s="8" t="s">
+      <c r="B24" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C24" s="7" t="s">
+      <c r="C24" t="s">
         <v>129</v>
       </c>
       <c r="D24" s="2">
         <v>0</v>
       </c>
-      <c r="E24" s="9">
+      <c r="E24" s="3">
         <v>0.51639777899999995</v>
       </c>
       <c r="F24" s="2">
         <v>0</v>
       </c>
-      <c r="G24" s="9">
+      <c r="G24" s="3">
         <v>0.25819889000000001</v>
       </c>
       <c r="H24" s="2">
         <v>0</v>
       </c>
-      <c r="I24" s="9">
+      <c r="I24" s="3">
         <v>0.77459666900000002</v>
       </c>
       <c r="J24" s="2">
@@ -3240,36 +3231,36 @@
       <c r="K24" s="6" t="s">
         <v>320</v>
       </c>
-      <c r="L24" s="7" t="s">
+      <c r="L24" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="25" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="25" spans="1:12" ht="18">
       <c r="A25" s="1">
         <v>24</v>
       </c>
-      <c r="B25" s="8" t="s">
+      <c r="B25" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="7" t="s">
+      <c r="C25" t="s">
         <v>130</v>
       </c>
       <c r="D25" s="2">
         <v>0</v>
       </c>
-      <c r="E25" s="9">
+      <c r="E25" s="3">
         <v>0</v>
       </c>
       <c r="F25" s="2">
         <v>0</v>
       </c>
-      <c r="G25" s="9">
+      <c r="G25" s="3">
         <v>0</v>
       </c>
       <c r="H25" s="2">
         <v>0.57735026899999997</v>
       </c>
-      <c r="I25" s="9">
+      <c r="I25" s="3">
         <v>0.57735026899999997</v>
       </c>
       <c r="J25" s="2">
@@ -3278,36 +3269,36 @@
       <c r="K25" s="6" t="s">
         <v>321</v>
       </c>
-      <c r="L25" s="7" t="s">
+      <c r="L25" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="26" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="26" spans="1:12" ht="18">
       <c r="A26" s="1">
         <v>25</v>
       </c>
-      <c r="B26" s="8" t="s">
+      <c r="B26" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C26" s="7" t="s">
+      <c r="C26" t="s">
         <v>131</v>
       </c>
       <c r="D26" s="2">
         <v>0</v>
       </c>
-      <c r="E26" s="9">
+      <c r="E26" s="3">
         <v>0.46852128599999998</v>
       </c>
       <c r="F26" s="2">
         <v>0</v>
       </c>
-      <c r="G26" s="9">
+      <c r="G26" s="3">
         <v>0</v>
       </c>
       <c r="H26" s="2">
         <v>0</v>
       </c>
-      <c r="I26" s="9">
+      <c r="I26" s="3">
         <v>0.62469504799999998</v>
       </c>
       <c r="J26" s="2">
@@ -3316,36 +3307,36 @@
       <c r="K26" s="6" t="s">
         <v>357</v>
       </c>
-      <c r="L26" s="7" t="s">
+      <c r="L26" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="27" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="27" spans="1:12" ht="18">
       <c r="A27" s="1">
         <v>26</v>
       </c>
-      <c r="B27" s="8" t="s">
+      <c r="B27" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="7" t="s">
+      <c r="C27" t="s">
         <v>132</v>
       </c>
       <c r="D27" s="2">
         <v>0.36927447299999999</v>
       </c>
-      <c r="E27" s="9">
+      <c r="E27" s="3">
         <v>0.36927447299999999</v>
       </c>
       <c r="F27" s="2">
         <v>0.49236596399999999</v>
       </c>
-      <c r="G27" s="9">
+      <c r="G27" s="3">
         <v>0.49236596399999999</v>
       </c>
       <c r="H27" s="2">
         <v>0</v>
       </c>
-      <c r="I27" s="9">
+      <c r="I27" s="3">
         <v>0.49236596399999999</v>
       </c>
       <c r="J27" s="2">
@@ -3354,36 +3345,36 @@
       <c r="K27" s="6" t="s">
         <v>389</v>
       </c>
-      <c r="L27" s="7" t="s">
+      <c r="L27" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="28" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="28" spans="1:12" ht="18">
       <c r="A28" s="1">
         <v>27</v>
       </c>
-      <c r="B28" s="8" t="s">
+      <c r="B28" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="7" t="s">
+      <c r="C28" t="s">
         <v>133</v>
       </c>
       <c r="D28" s="2">
         <v>0</v>
       </c>
-      <c r="E28" s="9">
+      <c r="E28" s="3">
         <v>0</v>
       </c>
       <c r="F28" s="2">
         <v>0</v>
       </c>
-      <c r="G28" s="9">
+      <c r="G28" s="3">
         <v>0</v>
       </c>
       <c r="H28" s="2">
         <v>0.58834840499999996</v>
       </c>
-      <c r="I28" s="9">
+      <c r="I28" s="3">
         <v>0.196116135</v>
       </c>
       <c r="J28" s="2">
@@ -3392,36 +3383,36 @@
       <c r="K28" s="6" t="s">
         <v>322</v>
       </c>
-      <c r="L28" s="7" t="s">
+      <c r="L28" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="29" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="29" spans="1:12" ht="18">
       <c r="A29" s="1">
         <v>28</v>
       </c>
-      <c r="B29" s="8" t="s">
+      <c r="B29" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="7" t="s">
+      <c r="C29" t="s">
         <v>134</v>
       </c>
       <c r="D29" s="2">
         <v>0</v>
       </c>
-      <c r="E29" s="9">
+      <c r="E29" s="3">
         <v>0.70710678118654746</v>
       </c>
       <c r="F29" s="2">
         <v>0</v>
       </c>
-      <c r="G29" s="9">
+      <c r="G29" s="3">
         <v>0</v>
       </c>
       <c r="H29" s="2">
         <v>0</v>
       </c>
-      <c r="I29" s="9">
+      <c r="I29" s="3">
         <v>0.70710678118654746</v>
       </c>
       <c r="J29" s="2">
@@ -3430,36 +3421,36 @@
       <c r="K29" s="6" t="s">
         <v>372</v>
       </c>
-      <c r="L29" s="7" t="s">
+      <c r="L29" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="30" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="30" spans="1:12" ht="18">
       <c r="A30" s="1">
         <v>29</v>
       </c>
-      <c r="B30" s="8" t="s">
+      <c r="B30" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="7" t="s">
+      <c r="C30" t="s">
         <v>135</v>
       </c>
       <c r="D30" s="2">
         <v>0</v>
       </c>
-      <c r="E30" s="9">
+      <c r="E30" s="3">
         <v>0.55470019599999998</v>
       </c>
       <c r="F30" s="2">
         <v>0</v>
       </c>
-      <c r="G30" s="9">
+      <c r="G30" s="3">
         <v>0</v>
       </c>
       <c r="H30" s="2">
         <v>0.27735009799999999</v>
       </c>
-      <c r="I30" s="9">
+      <c r="I30" s="3">
         <v>0.55470019599999998</v>
       </c>
       <c r="J30" s="2">
@@ -3468,36 +3459,36 @@
       <c r="K30" s="6" t="s">
         <v>323</v>
       </c>
-      <c r="L30" s="7" t="s">
+      <c r="L30" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="31" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="31" spans="1:12" ht="18">
       <c r="A31" s="1">
         <v>30</v>
       </c>
-      <c r="B31" s="8" t="s">
+      <c r="B31" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="7" t="s">
+      <c r="C31" t="s">
         <v>136</v>
       </c>
       <c r="D31" s="2">
         <v>0.52981294300000004</v>
       </c>
-      <c r="E31" s="9">
+      <c r="E31" s="3">
         <v>0.52981294300000004</v>
       </c>
       <c r="F31" s="2">
         <v>0</v>
       </c>
-      <c r="G31" s="9">
+      <c r="G31" s="3">
         <v>0</v>
       </c>
       <c r="H31" s="2">
         <v>0.52981294300000004</v>
       </c>
-      <c r="I31" s="9">
+      <c r="I31" s="3">
         <v>0.39735970700000001</v>
       </c>
       <c r="J31" s="2">
@@ -3506,36 +3497,36 @@
       <c r="K31" s="6" t="s">
         <v>324</v>
       </c>
-      <c r="L31" s="7" t="s">
+      <c r="L31" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="32" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="32" spans="1:12" ht="18">
       <c r="A32" s="1">
         <v>31</v>
       </c>
-      <c r="B32" s="8" t="s">
+      <c r="B32" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="C32" s="7" t="s">
+      <c r="C32" t="s">
         <v>137</v>
       </c>
       <c r="D32" s="2">
         <v>0</v>
       </c>
-      <c r="E32" s="9">
+      <c r="E32" s="3">
         <v>0</v>
       </c>
       <c r="F32" s="2">
         <v>0</v>
       </c>
-      <c r="G32" s="9">
+      <c r="G32" s="3">
         <v>0</v>
       </c>
       <c r="H32" s="2">
         <v>0.688247202</v>
       </c>
-      <c r="I32" s="9">
+      <c r="I32" s="3">
         <v>0.22941573400000001</v>
       </c>
       <c r="J32" s="2">
@@ -3544,36 +3535,36 @@
       <c r="K32" s="6" t="s">
         <v>329</v>
       </c>
-      <c r="L32" s="7" t="s">
+      <c r="L32" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="33" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="33" spans="1:12" ht="18">
       <c r="A33" s="1">
         <v>32</v>
       </c>
-      <c r="B33" s="8" t="s">
+      <c r="B33" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="7" t="s">
+      <c r="C33" t="s">
         <v>138</v>
       </c>
       <c r="D33" s="2">
         <v>0</v>
       </c>
-      <c r="E33" s="9">
+      <c r="E33" s="3">
         <v>0.70710678100000002</v>
       </c>
       <c r="F33" s="2">
         <v>0</v>
       </c>
-      <c r="G33" s="9">
+      <c r="G33" s="3">
         <v>0.35355339099999999</v>
       </c>
       <c r="H33" s="2">
         <v>0.35355339099999999</v>
       </c>
-      <c r="I33" s="9">
+      <c r="I33" s="3">
         <v>0.35355339099999999</v>
       </c>
       <c r="J33" s="2">
@@ -3582,36 +3573,36 @@
       <c r="K33" s="6" t="s">
         <v>358</v>
       </c>
-      <c r="L33" s="7" t="s">
+      <c r="L33" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="34" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="34" spans="1:12" ht="18">
       <c r="A34" s="1">
         <v>33</v>
       </c>
-      <c r="B34" s="8" t="s">
+      <c r="B34" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="C34" s="7" t="s">
+      <c r="C34" t="s">
         <v>139</v>
       </c>
       <c r="D34" s="2">
         <v>0.55470019599999998</v>
       </c>
-      <c r="E34" s="9">
+      <c r="E34" s="3">
         <v>0</v>
       </c>
       <c r="F34" s="2">
         <v>0</v>
       </c>
-      <c r="G34" s="9">
+      <c r="G34" s="3">
         <v>0</v>
       </c>
       <c r="H34" s="2">
         <v>0.55470019599999998</v>
       </c>
-      <c r="I34" s="9">
+      <c r="I34" s="3">
         <v>0.27735009799999999</v>
       </c>
       <c r="J34" s="2">
@@ -3620,36 +3611,36 @@
       <c r="K34" s="6" t="s">
         <v>330</v>
       </c>
-      <c r="L34" s="7" t="s">
+      <c r="L34" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="35" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="35" spans="1:12" ht="18">
       <c r="A35" s="1">
         <v>34</v>
       </c>
-      <c r="B35" s="8" t="s">
+      <c r="B35" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C35" s="7" t="s">
+      <c r="C35" t="s">
         <v>140</v>
       </c>
       <c r="D35" s="2">
         <v>0.53452248400000002</v>
       </c>
-      <c r="E35" s="9">
+      <c r="E35" s="3">
         <v>0.53452248400000002</v>
       </c>
       <c r="F35" s="2">
         <v>0</v>
       </c>
-      <c r="G35" s="9">
+      <c r="G35" s="3">
         <v>0</v>
       </c>
       <c r="H35" s="2">
         <v>0.26726124200000001</v>
       </c>
-      <c r="I35" s="9">
+      <c r="I35" s="3">
         <v>0.53452248400000002</v>
       </c>
       <c r="J35" s="2">
@@ -3658,36 +3649,36 @@
       <c r="K35" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="L35" s="7" t="s">
+      <c r="L35" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="36" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="36" spans="1:12" ht="18">
       <c r="A36" s="1">
         <v>35</v>
       </c>
-      <c r="B36" s="8" t="s">
+      <c r="B36" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C36" s="7" t="s">
+      <c r="C36" t="s">
         <v>141</v>
       </c>
       <c r="D36" s="2">
         <v>0</v>
       </c>
-      <c r="E36" s="9">
+      <c r="E36" s="3">
         <v>0</v>
       </c>
       <c r="F36" s="2">
         <v>0</v>
       </c>
-      <c r="G36" s="9">
+      <c r="G36" s="3">
         <v>0</v>
       </c>
       <c r="H36" s="2">
         <v>0.80178372600000003</v>
       </c>
-      <c r="I36" s="9">
+      <c r="I36" s="3">
         <v>0.26726124200000001</v>
       </c>
       <c r="J36" s="2">
@@ -3696,36 +3687,36 @@
       <c r="K36" s="6" t="s">
         <v>359</v>
       </c>
-      <c r="L36" s="7" t="s">
+      <c r="L36" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="37" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="37" spans="1:12" ht="18">
       <c r="A37" s="1">
         <v>36</v>
       </c>
-      <c r="B37" s="8" t="s">
+      <c r="B37" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="C37" s="7" t="s">
+      <c r="C37" t="s">
         <v>142</v>
       </c>
       <c r="D37" s="2">
         <v>0.21320071600000001</v>
       </c>
-      <c r="E37" s="9">
+      <c r="E37" s="3">
         <v>0.426401433</v>
       </c>
       <c r="F37" s="2">
         <v>0</v>
       </c>
-      <c r="G37" s="9">
+      <c r="G37" s="3">
         <v>0</v>
       </c>
       <c r="H37" s="2">
         <v>0.63960214900000001</v>
       </c>
-      <c r="I37" s="9">
+      <c r="I37" s="3">
         <v>0.426401433</v>
       </c>
       <c r="J37" s="2">
@@ -3734,36 +3725,36 @@
       <c r="K37" s="6" t="s">
         <v>332</v>
       </c>
-      <c r="L37" s="7" t="s">
+      <c r="L37" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="38" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="38" spans="1:12" ht="18">
       <c r="A38" s="1">
         <v>37</v>
       </c>
-      <c r="B38" s="8" t="s">
+      <c r="B38" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C38" s="7" t="s">
+      <c r="C38" t="s">
         <v>143</v>
       </c>
       <c r="D38" s="2">
         <v>0</v>
       </c>
-      <c r="E38" s="9">
+      <c r="E38" s="3">
         <v>0.66666666699999999</v>
       </c>
       <c r="F38" s="2">
         <v>0</v>
       </c>
-      <c r="G38" s="9">
+      <c r="G38" s="3">
         <v>0.33333333300000001</v>
       </c>
       <c r="H38" s="2">
         <v>0</v>
       </c>
-      <c r="I38" s="9">
+      <c r="I38" s="3">
         <v>0.66666666699999999</v>
       </c>
       <c r="J38" s="2">
@@ -3772,36 +3763,36 @@
       <c r="K38" s="6" t="s">
         <v>333</v>
       </c>
-      <c r="L38" s="7" t="s">
+      <c r="L38" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="39" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="39" spans="1:12" ht="18">
       <c r="A39" s="1">
         <v>38</v>
       </c>
-      <c r="B39" s="8" t="s">
+      <c r="B39" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C39" s="7" t="s">
+      <c r="C39" t="s">
         <v>144</v>
       </c>
       <c r="D39" s="2">
         <v>0</v>
       </c>
-      <c r="E39" s="9">
+      <c r="E39" s="3">
         <v>0.28867513500000003</v>
       </c>
       <c r="F39" s="2">
         <v>0</v>
       </c>
-      <c r="G39" s="9">
+      <c r="G39" s="3">
         <v>0.28867513500000003</v>
       </c>
       <c r="H39" s="2">
         <v>0.28867513500000003</v>
       </c>
-      <c r="I39" s="9">
+      <c r="I39" s="3">
         <v>0.86602540400000005</v>
       </c>
       <c r="J39" s="2">
@@ -3810,36 +3801,36 @@
       <c r="K39" s="6" t="s">
         <v>334</v>
       </c>
-      <c r="L39" s="7" t="s">
+      <c r="L39" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="40" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="40" spans="1:12" ht="18">
       <c r="A40" s="1">
         <v>39</v>
       </c>
-      <c r="B40" s="8" t="s">
+      <c r="B40" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C40" s="7" t="s">
+      <c r="C40" t="s">
         <v>145</v>
       </c>
       <c r="D40" s="2">
         <v>0</v>
       </c>
-      <c r="E40" s="9">
+      <c r="E40" s="3">
         <v>0</v>
       </c>
       <c r="F40" s="2">
         <v>0</v>
       </c>
-      <c r="G40" s="9">
+      <c r="G40" s="3">
         <v>0</v>
       </c>
       <c r="H40" s="2">
         <v>0.57735026899999997</v>
       </c>
-      <c r="I40" s="9">
+      <c r="I40" s="3">
         <v>0.57735026899999997</v>
       </c>
       <c r="J40" s="2">
@@ -3848,36 +3839,36 @@
       <c r="K40" s="6" t="s">
         <v>335</v>
       </c>
-      <c r="L40" s="7" t="s">
+      <c r="L40" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="41" spans="1:12" s="7" customFormat="1" ht="24">
+    <row r="41" spans="1:12" ht="24">
       <c r="A41" s="1">
         <v>40</v>
       </c>
-      <c r="B41" s="8" t="s">
+      <c r="B41" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C41" s="7" t="s">
+      <c r="C41" t="s">
         <v>146</v>
       </c>
       <c r="D41" s="2">
         <v>0</v>
       </c>
-      <c r="E41" s="9">
+      <c r="E41" s="3">
         <v>0</v>
       </c>
       <c r="F41" s="2">
         <v>0</v>
       </c>
-      <c r="G41" s="9">
+      <c r="G41" s="3">
         <v>0</v>
       </c>
       <c r="H41" s="2">
         <v>0.80178372600000003</v>
       </c>
-      <c r="I41" s="9">
+      <c r="I41" s="3">
         <v>0.26726124200000001</v>
       </c>
       <c r="J41" s="2">
@@ -3886,36 +3877,36 @@
       <c r="K41" s="6" t="s">
         <v>360</v>
       </c>
-      <c r="L41" s="7" t="s">
+      <c r="L41" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="42" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="42" spans="1:12" ht="18">
       <c r="A42" s="1">
         <v>41</v>
       </c>
-      <c r="B42" s="8" t="s">
+      <c r="B42" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="C42" s="7" t="s">
+      <c r="C42" t="s">
         <v>147</v>
       </c>
       <c r="D42" s="2">
         <v>0.23570226</v>
       </c>
-      <c r="E42" s="9">
+      <c r="E42" s="3">
         <v>0.70710678100000002</v>
       </c>
       <c r="F42" s="2">
         <v>0.23570226</v>
       </c>
-      <c r="G42" s="9">
+      <c r="G42" s="3">
         <v>0.23570226</v>
       </c>
       <c r="H42" s="2">
         <v>0.23570226</v>
       </c>
-      <c r="I42" s="9">
+      <c r="I42" s="3">
         <v>0.47140452100000002</v>
       </c>
       <c r="J42" s="2">
@@ -3924,36 +3915,36 @@
       <c r="K42" s="6" t="s">
         <v>336</v>
       </c>
-      <c r="L42" s="7" t="s">
+      <c r="L42" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="43" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="43" spans="1:12" ht="18">
       <c r="A43" s="1">
         <v>42</v>
       </c>
-      <c r="B43" s="8" t="s">
+      <c r="B43" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="C43" s="7" t="s">
+      <c r="C43" t="s">
         <v>148</v>
       </c>
       <c r="D43" s="2">
         <v>0.182574186</v>
       </c>
-      <c r="E43" s="9">
+      <c r="E43" s="3">
         <v>0</v>
       </c>
       <c r="F43" s="2">
         <v>0</v>
       </c>
-      <c r="G43" s="9">
+      <c r="G43" s="3">
         <v>0</v>
       </c>
       <c r="H43" s="2">
         <v>0.54772255800000003</v>
       </c>
-      <c r="I43" s="9">
+      <c r="I43" s="3">
         <v>0.73029674300000003</v>
       </c>
       <c r="J43" s="2">
@@ -3962,36 +3953,36 @@
       <c r="K43" s="6" t="s">
         <v>337</v>
       </c>
-      <c r="L43" s="7" t="s">
+      <c r="L43" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="44" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="44" spans="1:12" ht="18">
       <c r="A44" s="1">
         <v>43</v>
       </c>
-      <c r="B44" s="8" t="s">
+      <c r="B44" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="C44" s="7" t="s">
+      <c r="C44" t="s">
         <v>149</v>
       </c>
       <c r="D44" s="2">
         <v>0.57735026899999997</v>
       </c>
-      <c r="E44" s="9">
+      <c r="E44" s="3">
         <v>0</v>
       </c>
       <c r="F44" s="2">
         <v>0</v>
       </c>
-      <c r="G44" s="9">
+      <c r="G44" s="3">
         <v>0</v>
       </c>
       <c r="H44" s="2">
         <v>0.57735026899999997</v>
       </c>
-      <c r="I44" s="9">
+      <c r="I44" s="3">
         <v>0</v>
       </c>
       <c r="J44" s="2">
@@ -4000,36 +3991,36 @@
       <c r="K44" s="6" t="s">
         <v>338</v>
       </c>
-      <c r="L44" s="7" t="s">
+      <c r="L44" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="45" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="45" spans="1:12" ht="18">
       <c r="A45" s="1">
         <v>44</v>
       </c>
-      <c r="B45" s="8" t="s">
+      <c r="B45" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="C45" s="7" t="s">
+      <c r="C45" t="s">
         <v>150</v>
       </c>
       <c r="D45" s="2">
         <v>0.89442719100000001</v>
       </c>
-      <c r="E45" s="9">
+      <c r="E45" s="3">
         <v>0.44721359500000002</v>
       </c>
       <c r="F45" s="2">
         <v>0</v>
       </c>
-      <c r="G45" s="9">
+      <c r="G45" s="3">
         <v>0</v>
       </c>
       <c r="H45" s="2">
         <v>0</v>
       </c>
-      <c r="I45" s="9">
+      <c r="I45" s="3">
         <v>0</v>
       </c>
       <c r="J45" s="2">
@@ -4038,36 +4029,36 @@
       <c r="K45" s="6" t="s">
         <v>339</v>
       </c>
-      <c r="L45" s="7" t="s">
+      <c r="L45" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="46" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="46" spans="1:12" ht="18">
       <c r="A46" s="1">
         <v>45</v>
       </c>
-      <c r="B46" s="8" t="s">
+      <c r="B46" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="C46" s="7" t="s">
+      <c r="C46" t="s">
         <v>151</v>
       </c>
       <c r="D46" s="2">
         <v>0</v>
       </c>
-      <c r="E46" s="9">
+      <c r="E46" s="3">
         <v>0</v>
       </c>
       <c r="F46" s="2">
         <v>0</v>
       </c>
-      <c r="G46" s="9">
+      <c r="G46" s="3">
         <v>0</v>
       </c>
       <c r="H46" s="2">
         <v>0.70710678100000002</v>
       </c>
-      <c r="I46" s="9">
+      <c r="I46" s="3">
         <v>0.70710678100000002</v>
       </c>
       <c r="J46" s="2">
@@ -4076,36 +4067,36 @@
       <c r="K46" s="6" t="s">
         <v>340</v>
       </c>
-      <c r="L46" s="7" t="s">
+      <c r="L46" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="47" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="47" spans="1:12" ht="18">
       <c r="A47" s="1">
         <v>46</v>
       </c>
-      <c r="B47" s="8" t="s">
+      <c r="B47" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="C47" s="7" t="s">
+      <c r="C47" t="s">
         <v>152</v>
       </c>
       <c r="D47" s="2">
         <v>0.25819889000000001</v>
       </c>
-      <c r="E47" s="9">
+      <c r="E47" s="3">
         <v>0.51639777899999995</v>
       </c>
       <c r="F47" s="2">
         <v>0.25819889000000001</v>
       </c>
-      <c r="G47" s="9">
+      <c r="G47" s="3">
         <v>0.25819889000000001</v>
       </c>
       <c r="H47" s="2">
         <v>0.51639777899999995</v>
       </c>
-      <c r="I47" s="9">
+      <c r="I47" s="3">
         <v>0.51639777899999995</v>
       </c>
       <c r="J47" s="2">
@@ -4114,36 +4105,36 @@
       <c r="K47" s="6" t="s">
         <v>361</v>
       </c>
-      <c r="L47" s="7" t="s">
+      <c r="L47" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="48" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="48" spans="1:12" ht="18">
       <c r="A48" s="1">
         <v>47</v>
       </c>
-      <c r="B48" s="8" t="s">
+      <c r="B48" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="C48" s="7" t="s">
+      <c r="C48" t="s">
         <v>153</v>
       </c>
       <c r="D48" s="2">
         <v>0.25</v>
       </c>
-      <c r="E48" s="9">
+      <c r="E48" s="3">
         <v>0.25</v>
       </c>
       <c r="F48" s="2">
         <v>0</v>
       </c>
-      <c r="G48" s="9">
+      <c r="G48" s="3">
         <v>0</v>
       </c>
       <c r="H48" s="2">
         <v>0.75</v>
       </c>
-      <c r="I48" s="9">
+      <c r="I48" s="3">
         <v>0.25</v>
       </c>
       <c r="J48" s="2">
@@ -4152,36 +4143,36 @@
       <c r="K48" s="6" t="s">
         <v>362</v>
       </c>
-      <c r="L48" s="7" t="s">
+      <c r="L48" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="49" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="49" spans="1:12" ht="18">
       <c r="A49" s="1">
         <v>48</v>
       </c>
-      <c r="B49" s="8" t="s">
+      <c r="B49" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="C49" s="7" t="s">
+      <c r="C49" t="s">
         <v>154</v>
       </c>
       <c r="D49" s="2">
         <v>0</v>
       </c>
-      <c r="E49" s="9">
+      <c r="E49" s="3">
         <v>0</v>
       </c>
       <c r="F49" s="2">
         <v>0</v>
       </c>
-      <c r="G49" s="9">
+      <c r="G49" s="3">
         <v>0</v>
       </c>
       <c r="H49" s="2">
         <v>0.69631062399999999</v>
       </c>
-      <c r="I49" s="9">
+      <c r="I49" s="3">
         <v>0.69631062399999999</v>
       </c>
       <c r="J49" s="2">
@@ -4190,36 +4181,36 @@
       <c r="K49" s="6" t="s">
         <v>341</v>
       </c>
-      <c r="L49" s="7" t="s">
+      <c r="L49" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="50" spans="1:12" s="7" customFormat="1" ht="21">
+    <row r="50" spans="1:12" ht="21">
       <c r="A50" s="1">
         <v>49</v>
       </c>
-      <c r="B50" s="8" t="s">
+      <c r="B50" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="C50" s="7" t="s">
+      <c r="C50" t="s">
         <v>155</v>
       </c>
       <c r="D50" s="2">
         <v>0</v>
       </c>
-      <c r="E50" s="9">
+      <c r="E50" s="3">
         <v>0</v>
       </c>
       <c r="F50" s="2">
         <v>0</v>
       </c>
-      <c r="G50" s="9">
+      <c r="G50" s="3">
         <v>0</v>
       </c>
       <c r="H50" s="2">
         <v>0.69631062399999999</v>
       </c>
-      <c r="I50" s="9">
+      <c r="I50" s="3">
         <v>0.69631062399999999</v>
       </c>
       <c r="J50" s="2">
@@ -4228,36 +4219,36 @@
       <c r="K50" s="6" t="s">
         <v>341</v>
       </c>
-      <c r="L50" s="7" t="s">
+      <c r="L50" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="51" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="51" spans="1:12" ht="18">
       <c r="A51" s="1">
         <v>50</v>
       </c>
-      <c r="B51" s="8" t="s">
+      <c r="B51" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="C51" s="7" t="s">
+      <c r="C51" t="s">
         <v>156</v>
       </c>
       <c r="D51" s="2">
         <v>0.55470019599999998</v>
       </c>
-      <c r="E51" s="9">
+      <c r="E51" s="3">
         <v>0</v>
       </c>
       <c r="F51" s="2">
         <v>0</v>
       </c>
-      <c r="G51" s="9">
+      <c r="G51" s="3">
         <v>0.55470019599999998</v>
       </c>
       <c r="H51" s="2">
         <v>0.55470019599999998</v>
       </c>
-      <c r="I51" s="9">
+      <c r="I51" s="3">
         <v>0</v>
       </c>
       <c r="J51" s="2">
@@ -4266,36 +4257,36 @@
       <c r="K51" s="6" t="s">
         <v>342</v>
       </c>
-      <c r="L51" s="7" t="s">
+      <c r="L51" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="52" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="52" spans="1:12" ht="18">
       <c r="A52" s="1">
         <v>51</v>
       </c>
-      <c r="B52" s="8" t="s">
+      <c r="B52" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="C52" s="7" t="s">
+      <c r="C52" t="s">
         <v>157</v>
       </c>
       <c r="D52" s="2">
         <v>0</v>
       </c>
-      <c r="E52" s="9">
+      <c r="E52" s="3">
         <v>0</v>
       </c>
       <c r="F52" s="2">
         <v>0</v>
       </c>
-      <c r="G52" s="9">
+      <c r="G52" s="3">
         <v>0</v>
       </c>
       <c r="H52" s="2">
         <v>0.26726124200000001</v>
       </c>
-      <c r="I52" s="9">
+      <c r="I52" s="3">
         <v>0.53452248400000002</v>
       </c>
       <c r="J52" s="2">
@@ -4304,36 +4295,36 @@
       <c r="K52" s="6" t="s">
         <v>343</v>
       </c>
-      <c r="L52" s="7" t="s">
+      <c r="L52" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="53" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="53" spans="1:12" ht="18">
       <c r="A53" s="1">
         <v>52</v>
       </c>
-      <c r="B53" s="8" t="s">
+      <c r="B53" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="C53" s="7" t="s">
+      <c r="C53" t="s">
         <v>158</v>
       </c>
       <c r="D53" s="2">
         <v>0</v>
       </c>
-      <c r="E53" s="9">
+      <c r="E53" s="3">
         <v>0</v>
       </c>
       <c r="F53" s="2">
         <v>0</v>
       </c>
-      <c r="G53" s="9">
+      <c r="G53" s="3">
         <v>0</v>
       </c>
       <c r="H53" s="2">
         <v>0.514495755</v>
       </c>
-      <c r="I53" s="9">
+      <c r="I53" s="3">
         <v>0.68599434100000001</v>
       </c>
       <c r="J53" s="2">
@@ -4342,36 +4333,36 @@
       <c r="K53" s="6" t="s">
         <v>344</v>
       </c>
-      <c r="L53" s="7" t="s">
+      <c r="L53" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="54" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="54" spans="1:12" ht="18">
       <c r="A54" s="1">
         <v>53</v>
       </c>
-      <c r="B54" s="8" t="s">
+      <c r="B54" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="C54" s="7" t="s">
+      <c r="C54" t="s">
         <v>159</v>
       </c>
       <c r="D54" s="2">
         <v>0</v>
       </c>
-      <c r="E54" s="9">
+      <c r="E54" s="3">
         <v>0</v>
       </c>
       <c r="F54" s="2">
         <v>0</v>
       </c>
-      <c r="G54" s="9">
+      <c r="G54" s="3">
         <v>0</v>
       </c>
       <c r="H54" s="2">
         <v>0.514495755</v>
       </c>
-      <c r="I54" s="9">
+      <c r="I54" s="3">
         <v>0.68599434100000001</v>
       </c>
       <c r="J54" s="2">
@@ -4380,36 +4371,36 @@
       <c r="K54" s="6" t="s">
         <v>345</v>
       </c>
-      <c r="L54" s="7" t="s">
+      <c r="L54" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="55" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="55" spans="1:12" ht="18">
       <c r="A55" s="1">
         <v>54</v>
       </c>
-      <c r="B55" s="8" t="s">
+      <c r="B55" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="C55" s="7" t="s">
+      <c r="C55" t="s">
         <v>160</v>
       </c>
       <c r="D55" s="2">
         <v>0</v>
       </c>
-      <c r="E55" s="9">
+      <c r="E55" s="3">
         <v>0</v>
       </c>
       <c r="F55" s="2">
         <v>0</v>
       </c>
-      <c r="G55" s="9">
+      <c r="G55" s="3">
         <v>0</v>
       </c>
       <c r="H55" s="2">
         <v>0.63960214900000001</v>
       </c>
-      <c r="I55" s="9">
+      <c r="I55" s="3">
         <v>0.426401433</v>
       </c>
       <c r="J55" s="2">
@@ -4418,36 +4409,36 @@
       <c r="K55" s="6" t="s">
         <v>346</v>
       </c>
-      <c r="L55" s="7" t="s">
+      <c r="L55" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="56" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="56" spans="1:12" ht="18">
       <c r="A56" s="1">
         <v>55</v>
       </c>
-      <c r="B56" s="8" t="s">
+      <c r="B56" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="C56" s="7" t="s">
+      <c r="C56" t="s">
         <v>161</v>
       </c>
       <c r="D56" s="2">
         <v>0</v>
       </c>
-      <c r="E56" s="9">
+      <c r="E56" s="3">
         <v>0</v>
       </c>
       <c r="F56" s="2">
         <v>0</v>
       </c>
-      <c r="G56" s="9">
+      <c r="G56" s="3">
         <v>0</v>
       </c>
       <c r="H56" s="2">
         <v>0.514495755</v>
       </c>
-      <c r="I56" s="9">
+      <c r="I56" s="3">
         <v>0.514495755</v>
       </c>
       <c r="J56" s="2">
@@ -4456,36 +4447,36 @@
       <c r="K56" s="6" t="s">
         <v>373</v>
       </c>
-      <c r="L56" s="7" t="s">
+      <c r="L56" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="57" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="57" spans="1:12" ht="18">
       <c r="A57" s="1">
         <v>56</v>
       </c>
-      <c r="B57" s="8" t="s">
+      <c r="B57" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="C57" s="7" t="s">
+      <c r="C57" t="s">
         <v>162</v>
       </c>
       <c r="D57" s="2">
         <v>0</v>
       </c>
-      <c r="E57" s="9">
+      <c r="E57" s="3">
         <v>0.23570226</v>
       </c>
       <c r="F57" s="2">
         <v>0</v>
       </c>
-      <c r="G57" s="9">
+      <c r="G57" s="3">
         <v>0</v>
       </c>
       <c r="H57" s="2">
         <v>0.70710678100000002</v>
       </c>
-      <c r="I57" s="9">
+      <c r="I57" s="3">
         <v>0.47140452100000002</v>
       </c>
       <c r="J57" s="2">
@@ -4494,36 +4485,36 @@
       <c r="K57" s="6" t="s">
         <v>347</v>
       </c>
-      <c r="L57" s="7" t="s">
+      <c r="L57" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="58" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="58" spans="1:12" ht="18">
       <c r="A58" s="1">
         <v>57</v>
       </c>
-      <c r="B58" s="8" t="s">
+      <c r="B58" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="C58" s="7" t="s">
+      <c r="C58" t="s">
         <v>163</v>
       </c>
       <c r="D58" s="2">
         <v>0</v>
       </c>
-      <c r="E58" s="9">
+      <c r="E58" s="3">
         <v>0</v>
       </c>
       <c r="F58" s="2">
         <v>0</v>
       </c>
-      <c r="G58" s="9">
+      <c r="G58" s="3">
         <v>0</v>
       </c>
       <c r="H58" s="2">
         <v>0</v>
       </c>
-      <c r="I58" s="9">
+      <c r="I58" s="3">
         <v>1</v>
       </c>
       <c r="J58" s="2">
@@ -4532,36 +4523,36 @@
       <c r="K58" s="6" t="s">
         <v>348</v>
       </c>
-      <c r="L58" s="7" t="s">
+      <c r="L58" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="59" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="59" spans="1:12" ht="18">
       <c r="A59" s="1">
         <v>58</v>
       </c>
-      <c r="B59" s="8" t="s">
+      <c r="B59" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="C59" s="7" t="s">
+      <c r="C59" t="s">
         <v>164</v>
       </c>
       <c r="D59" s="2">
         <v>0</v>
       </c>
-      <c r="E59" s="9">
+      <c r="E59" s="3">
         <v>0.35921060399999999</v>
       </c>
       <c r="F59" s="2">
         <v>0</v>
       </c>
-      <c r="G59" s="9">
+      <c r="G59" s="3">
         <v>0</v>
       </c>
       <c r="H59" s="2">
         <v>0.53881590599999996</v>
       </c>
-      <c r="I59" s="9">
+      <c r="I59" s="3">
         <v>0.53881590599999996</v>
       </c>
       <c r="J59" s="2">
@@ -4570,36 +4561,36 @@
       <c r="K59" s="6" t="s">
         <v>363</v>
       </c>
-      <c r="L59" s="7" t="s">
+      <c r="L59" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="60" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="60" spans="1:12" ht="18">
       <c r="A60" s="1">
         <v>59</v>
       </c>
-      <c r="B60" s="8" t="s">
+      <c r="B60" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="C60" s="7" t="s">
+      <c r="C60" t="s">
         <v>165</v>
       </c>
       <c r="D60" s="2">
         <v>0.188982237</v>
       </c>
-      <c r="E60" s="9">
+      <c r="E60" s="3">
         <v>0.56694670999999996</v>
       </c>
       <c r="F60" s="2">
         <v>0</v>
       </c>
-      <c r="G60" s="9">
+      <c r="G60" s="3">
         <v>0</v>
       </c>
       <c r="H60" s="2">
         <v>0.56694670999999996</v>
       </c>
-      <c r="I60" s="9">
+      <c r="I60" s="3">
         <v>0.56694670999999996</v>
       </c>
       <c r="J60" s="2">
@@ -4608,36 +4599,36 @@
       <c r="K60" s="6" t="s">
         <v>349</v>
       </c>
-      <c r="L60" s="7" t="s">
+      <c r="L60" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="61" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="61" spans="1:12" ht="18">
       <c r="A61" s="1">
         <v>60</v>
       </c>
-      <c r="B61" s="8" t="s">
+      <c r="B61" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="C61" s="7" t="s">
+      <c r="C61" t="s">
         <v>166</v>
       </c>
       <c r="D61" s="2">
         <v>0.39223226999999999</v>
       </c>
-      <c r="E61" s="9">
+      <c r="E61" s="3">
         <v>0.39223226999999999</v>
       </c>
       <c r="F61" s="2">
         <v>0.39223226999999999</v>
       </c>
-      <c r="G61" s="9">
+      <c r="G61" s="3">
         <v>0.58834840499999996</v>
       </c>
       <c r="H61" s="2">
         <v>0</v>
       </c>
-      <c r="I61" s="9">
+      <c r="I61" s="3">
         <v>0.39223226999999999</v>
       </c>
       <c r="J61" s="2">
@@ -4646,36 +4637,36 @@
       <c r="K61" s="6" t="s">
         <v>350</v>
       </c>
-      <c r="L61" s="7" t="s">
+      <c r="L61" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="62" spans="1:12" s="7" customFormat="1" ht="18">
+    <row r="62" spans="1:12" ht="18">
       <c r="A62" s="1">
         <v>61</v>
       </c>
-      <c r="B62" s="8" t="s">
+      <c r="B62" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="C62" s="7" t="s">
+      <c r="C62" t="s">
         <v>167</v>
       </c>
       <c r="D62" s="2">
         <v>0.53452248400000002</v>
       </c>
-      <c r="E62" s="9">
+      <c r="E62" s="3">
         <v>0.53452248400000002</v>
       </c>
       <c r="F62" s="2">
         <v>0.26726124200000001</v>
       </c>
-      <c r="G62" s="9">
+      <c r="G62" s="3">
         <v>0.53452248400000002</v>
       </c>
       <c r="H62" s="2">
         <v>0</v>
       </c>
-      <c r="I62" s="9">
+      <c r="I62" s="3">
         <v>0.26726124200000001</v>
       </c>
       <c r="J62" s="2">
@@ -4684,7 +4675,7 @@
       <c r="K62" s="6" t="s">
         <v>351</v>
       </c>
-      <c r="L62" s="7" t="s">
+      <c r="L62" t="s">
         <v>266</v>
       </c>
     </row>
